--- a/src/data/resum_periode_meteocat.xlsx
+++ b/src/data/resum_periode_meteocat.xlsx
@@ -722,17 +722,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-09-28 22:15:33</t>
+          <t>2026-09-28 22:45:29</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -919,7 +919,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-28 22:15:35</t>
+          <t>2026-09-28 22:45:31</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-09-28 22:15:35</t>
+          <t>2026-09-28 22:45:31</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-09-28 22:15:35</t>
+          <t>2026-09-28 22:45:31</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-28 22:15:35</t>
+          <t>2026-09-28 22:45:31</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-28 22:15:38</t>
+          <t>2026-09-28 22:45:33</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -1732,7 +1732,7 @@
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>116</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>100</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1763,96 +1763,96 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
           <t>9.3</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>9.6</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>22:00 - 22:30</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>9.2</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
           <t>9.3</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>14.4</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>21:30 - 22:00</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>9.4</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>9.6</t>
-        </is>
-      </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -1867,17 +1867,17 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>116</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>116</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-28 22:15:39</t>
+          <t>2026-09-28 22:45:35</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-09-28 22:15:39</t>
+          <t>2026-09-28 22:45:35</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-09-28 22:15:39</t>
+          <t>2026-09-28 22:45:35</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-09-28 22:15:39</t>
+          <t>2026-09-28 22:45:35</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2872,17 +2872,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-09-28 22:15:42</t>
+          <t>2026-09-28 22:45:38</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>334</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2903,12 +2903,12 @@
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>95</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1019.4</t>
+          <t>1019.5</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -2928,96 +2928,96 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>18.6</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
+          <t>18.4</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
           <t>18.9</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>19.5</t>
-        </is>
-      </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>18.6</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
+          <t>18.4</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>22:00 - 22:30</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>18.6</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
           <t>18.9</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>21:30 - 22:00</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>19.2</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>19.5</t>
-        </is>
-      </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>95</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -3027,22 +3027,22 @@
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>334</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1019.4</t>
+          <t>1019.5</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1019.4</t>
+          <t>1019.5</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-09-28 22:15:44</t>
+          <t>2026-09-28 22:45:40</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-09-28 22:15:44</t>
+          <t>2026-09-28 22:45:40</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-09-28 22:15:44</t>
+          <t>2026-09-28 22:45:40</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-09-28 22:15:44</t>
+          <t>2026-09-28 22:45:40</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -4037,17 +4037,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-09-28 22:15:46</t>
+          <t>2026-09-28 22:45:43</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -4062,17 +4062,17 @@
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>338</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>82</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -4098,31 +4098,31 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>9.9</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -4132,17 +4132,17 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>9.9</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -4152,17 +4152,17 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
@@ -4172,17 +4172,17 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>9.9</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
@@ -4192,22 +4192,22 @@
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>338</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>338</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-09-28 22:15:48</t>
+          <t>2026-09-28 22:45:45</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-09-28 22:15:48</t>
+          <t>2026-09-28 22:45:45</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-09-28 22:15:48</t>
+          <t>2026-09-28 22:45:45</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-09-28 22:15:48</t>
+          <t>2026-09-28 22:45:45</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -5202,17 +5202,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-09-28 22:15:51</t>
+          <t>2026-09-28 22:45:48</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -5225,7 +5225,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>125</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -5233,7 +5233,7 @@
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>82</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -5273,21 +5273,21 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr"/>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr"/>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
@@ -5317,17 +5317,17 @@
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>125</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
@@ -5357,17 +5357,17 @@
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>125</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
@@ -5382,7 +5382,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-09-28 22:15:52</t>
+          <t>2026-09-28 22:45:50</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-09-28 22:15:52</t>
+          <t>2026-09-28 22:45:50</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-09-28 22:15:52</t>
+          <t>2026-09-28 22:45:50</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-09-28 22:15:52</t>
+          <t>2026-09-28 22:45:50</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -6352,7 +6352,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -6367,17 +6367,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-09-28 22:15:55</t>
+          <t>2026-09-28 22:45:53</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>132</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -6398,7 +6398,7 @@
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>70</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -6428,31 +6428,31 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
           <t>25.3</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>25.3</t>
-        </is>
-      </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr"/>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr"/>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
@@ -6467,52 +6467,52 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>6.8</t>
+        </is>
+      </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>22:00 - 22:30</t>
+        </is>
+      </c>
+      <c r="AN27" t="inlineStr">
+        <is>
           <t>25.3</t>
         </is>
       </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>7.9</t>
-        </is>
-      </c>
-      <c r="AL27" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>21:30 - 22:00</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
+      <c r="AO27" t="inlineStr">
         <is>
           <t>25.3</t>
         </is>
       </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>25.3</t>
-        </is>
-      </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
@@ -6522,17 +6522,17 @@
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>132</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -6600,7 +6600,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-09-28 22:15:57</t>
+          <t>2026-09-28 22:45:55</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -6833,7 +6833,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-09-28 22:15:57</t>
+          <t>2026-09-28 22:45:55</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-09-28 22:15:57</t>
+          <t>2026-09-28 22:45:55</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-09-28 22:15:57</t>
+          <t>2026-09-28 22:45:55</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -7532,17 +7532,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:00</t>
+          <t>2026-09-28 22:45:58</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -7555,7 +7555,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>141</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -7568,7 +7568,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1018.8</t>
+          <t>1018.9</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -7578,7 +7578,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -7588,12 +7588,12 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
@@ -7603,26 +7603,26 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr"/>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr"/>
       <c r="AD32" t="inlineStr"/>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
@@ -7632,54 +7632,54 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
+          <t>21.1</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>9.7</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>22:00 - 22:30</t>
+        </is>
+      </c>
+      <c r="AN32" t="inlineStr">
+        <is>
           <t>21.2</t>
         </is>
       </c>
-      <c r="AI32" t="inlineStr">
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>21.4</t>
+        </is>
+      </c>
+      <c r="AP32" t="inlineStr">
+        <is>
+          <t>21.1</t>
+        </is>
+      </c>
+      <c r="AQ32" t="inlineStr">
         <is>
           <t>84</t>
         </is>
       </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>9.4</t>
-        </is>
-      </c>
-      <c r="AL32" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>21:30 - 22:00</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>21.3</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>21.4</t>
-        </is>
-      </c>
-      <c r="AP32" t="inlineStr">
-        <is>
-          <t>21.2</t>
-        </is>
-      </c>
-      <c r="AQ32" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="AR32" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -7687,22 +7687,22 @@
       </c>
       <c r="AS32" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>141</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>1018.8</t>
+          <t>1018.9</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
@@ -7712,12 +7712,12 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>1018.8</t>
+          <t>1018.9</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
@@ -7765,7 +7765,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:01</t>
+          <t>2026-09-28 22:46:00</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:01</t>
+          <t>2026-09-28 22:46:00</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:01</t>
+          <t>2026-09-28 22:46:00</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -8464,7 +8464,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:01</t>
+          <t>2026-09-28 22:46:00</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -8697,17 +8697,17 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:04</t>
+          <t>2026-09-28 22:46:03</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -8721,14 +8721,14 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>87</t>
         </is>
       </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>90</t>
         </is>
       </c>
       <c r="R37" t="inlineStr"/>
@@ -8739,7 +8739,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -8749,96 +8749,96 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
+          <t>19.9</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
           <t>20.4</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>21.2</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr"/>
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr"/>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
+          <t>19.9</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AL37" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>22:00 - 22:30</t>
+        </is>
+      </c>
+      <c r="AN37" t="inlineStr">
+        <is>
+          <t>20.1</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
           <t>20.4</t>
         </is>
       </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>0.4</t>
-        </is>
-      </c>
-      <c r="AL37" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>21:30 - 22:00</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>21.0</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>21.2</t>
-        </is>
-      </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="AQ37" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>90</t>
         </is>
       </c>
       <c r="AR37" t="inlineStr">
@@ -8848,17 +8848,17 @@
       </c>
       <c r="AS37" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
@@ -8869,7 +8869,7 @@
       <c r="AW37" t="inlineStr"/>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -8918,7 +8918,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:05</t>
+          <t>2026-09-28 22:46:04</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:05</t>
+          <t>2026-09-28 22:46:04</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -9360,7 +9360,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:05</t>
+          <t>2026-09-28 22:46:04</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:05</t>
+          <t>2026-09-28 22:46:04</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -9787,7 +9787,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -9802,17 +9802,17 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:08</t>
+          <t>2026-09-28 22:46:07</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -9826,14 +9826,14 @@
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>74</t>
         </is>
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>92</t>
         </is>
       </c>
       <c r="R42" t="inlineStr"/>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -9854,96 +9854,96 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr"/>
       <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr"/>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
+          <t>20.3</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="AL42" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>22:00 - 22:30</t>
+        </is>
+      </c>
+      <c r="AN42" t="inlineStr">
+        <is>
           <t>20.4</t>
         </is>
       </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>0.4</t>
-        </is>
-      </c>
-      <c r="AL42" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>21:30 - 22:00</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>21.0</t>
-        </is>
-      </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="AQ42" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>92</t>
         </is>
       </c>
       <c r="AR42" t="inlineStr">
@@ -9953,17 +9953,17 @@
       </c>
       <c r="AS42" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>74</t>
         </is>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="AV42" t="inlineStr">
@@ -9974,7 +9974,7 @@
       <c r="AW42" t="inlineStr"/>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -10023,7 +10023,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:10</t>
+          <t>2026-09-28 22:46:09</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -10244,7 +10244,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:10</t>
+          <t>2026-09-28 22:46:09</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:10</t>
+          <t>2026-09-28 22:46:09</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -10686,7 +10686,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:10</t>
+          <t>2026-09-28 22:46:09</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -10892,7 +10892,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -10907,17 +10907,17 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:12</t>
+          <t>2026-09-28 22:46:12</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -10934,7 +10934,7 @@
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>85</t>
         </is>
       </c>
       <c r="R47" t="inlineStr"/>
@@ -10945,23 +10945,23 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="U47" t="inlineStr"/>
       <c r="V47" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.1</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr"/>
@@ -10972,27 +10972,27 @@
       <c r="AD47" t="inlineStr"/>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.1</t>
         </is>
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>85</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
@@ -11004,27 +11004,27 @@
       <c r="AL47" t="inlineStr"/>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.1</t>
         </is>
       </c>
       <c r="AQ47" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>85</t>
         </is>
       </c>
       <c r="AR47" t="inlineStr">
@@ -11080,7 +11080,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:14</t>
+          <t>2026-09-28 22:46:14</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -11253,7 +11253,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:14</t>
+          <t>2026-09-28 22:46:14</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -11426,7 +11426,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:14</t>
+          <t>2026-09-28 22:46:14</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -11599,7 +11599,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:14</t>
+          <t>2026-09-28 22:46:14</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -11772,17 +11772,17 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:16</t>
+          <t>2026-09-28 22:46:16</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
       <c r="K52" t="n">
@@ -11945,7 +11945,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:18</t>
+          <t>2026-09-28 22:46:18</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:18</t>
+          <t>2026-09-28 22:46:18</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -12291,7 +12291,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:18</t>
+          <t>2026-09-28 22:46:18</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -12464,7 +12464,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:18</t>
+          <t>2026-09-28 22:46:18</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -12622,7 +12622,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -12637,17 +12637,17 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:20</t>
+          <t>2026-09-28 22:46:21</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
       <c r="K57" t="n">
@@ -12660,7 +12660,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>213</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -12672,12 +12672,12 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>75</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1019.2</t>
+          <t>1019.3</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -12687,7 +12687,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -12697,56 +12697,56 @@
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>15.3</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>14.9</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr"/>
       <c r="AA57" t="inlineStr"/>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr"/>
       <c r="AD57" t="inlineStr"/>
       <c r="AE57" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>15.3</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>14.9</t>
         </is>
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AJ57" t="inlineStr">
@@ -12761,32 +12761,32 @@
       </c>
       <c r="AL57" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="AN57" t="inlineStr">
         <is>
-          <t>15.3</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>14.9</t>
         </is>
       </c>
       <c r="AQ57" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AR57" t="inlineStr">
@@ -12801,37 +12801,37 @@
       </c>
       <c r="AT57" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>213</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>1019.2</t>
+          <t>1019.3</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>213</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>1019.2</t>
+          <t>1019.3</t>
         </is>
       </c>
       <c r="BA57" t="inlineStr">
@@ -12878,7 +12878,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:22</t>
+          <t>2026-09-28 22:46:23</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -13119,7 +13119,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:22</t>
+          <t>2026-09-28 22:46:23</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:22</t>
+          <t>2026-09-28 22:46:23</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -13601,7 +13601,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:22</t>
+          <t>2026-09-28 22:46:23</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -13827,7 +13827,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -13842,17 +13842,17 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:25</t>
+          <t>2026-09-28 22:46:26</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
       <c r="K62" t="n">
@@ -13865,7 +13865,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>136</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -13873,7 +13873,7 @@
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="R62" t="inlineStr"/>
@@ -13884,7 +13884,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -13894,96 +13894,96 @@
       </c>
       <c r="V62" t="inlineStr">
         <is>
+          <t>23.9</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>23.6</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
           <t>24.2</t>
         </is>
       </c>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>23.9</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>24.5</t>
-        </is>
-      </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="inlineStr"/>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr"/>
       <c r="AD62" t="inlineStr"/>
       <c r="AE62" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="AF62" t="inlineStr">
         <is>
+          <t>23.9</t>
+        </is>
+      </c>
+      <c r="AG62" t="inlineStr">
+        <is>
           <t>24.2</t>
         </is>
       </c>
-      <c r="AG62" t="inlineStr">
-        <is>
-          <t>24.5</t>
-        </is>
-      </c>
       <c r="AH62" t="inlineStr">
         <is>
+          <t>23.6</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AL62" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>22:00 - 22:30</t>
+        </is>
+      </c>
+      <c r="AN62" t="inlineStr">
+        <is>
           <t>23.9</t>
         </is>
       </c>
-      <c r="AI62" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>6.8</t>
-        </is>
-      </c>
-      <c r="AL62" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>21:30 - 22:00</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
+      <c r="AO62" t="inlineStr">
         <is>
           <t>24.2</t>
         </is>
       </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>24.5</t>
-        </is>
-      </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>23.9</t>
+          <t>23.6</t>
         </is>
       </c>
       <c r="AQ62" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AR62" t="inlineStr">
@@ -13993,17 +13993,17 @@
       </c>
       <c r="AS62" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>136</t>
         </is>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
@@ -14014,7 +14014,7 @@
       <c r="AW62" t="inlineStr"/>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -14063,7 +14063,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:26</t>
+          <t>2026-09-28 22:46:28</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -14284,7 +14284,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:26</t>
+          <t>2026-09-28 22:46:28</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -14505,7 +14505,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:26</t>
+          <t>2026-09-28 22:46:28</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -14726,7 +14726,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:26</t>
+          <t>2026-09-28 22:46:28</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -14947,17 +14947,17 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:29</t>
+          <t>2026-09-28 22:46:31</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
       <c r="K67" t="n">
@@ -15120,7 +15120,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:30</t>
+          <t>2026-09-28 22:46:33</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -15293,7 +15293,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:30</t>
+          <t>2026-09-28 22:46:33</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -15466,7 +15466,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:30</t>
+          <t>2026-09-28 22:46:33</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -15639,7 +15639,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:30</t>
+          <t>2026-09-28 22:46:33</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -15797,7 +15797,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -15812,17 +15812,17 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:33</t>
+          <t>2026-09-28 22:46:36</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
       <c r="K72" t="n">
@@ -15835,7 +15835,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>250</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
@@ -15843,7 +15843,7 @@
       <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>91</t>
         </is>
       </c>
       <c r="R72" t="inlineStr"/>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -15864,56 +15864,56 @@
       </c>
       <c r="V72" t="inlineStr">
         <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="W72" t="inlineStr">
-        <is>
-          <t>7.8</t>
-        </is>
-      </c>
-      <c r="X72" t="inlineStr">
-        <is>
-          <t>8.1</t>
-        </is>
-      </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr"/>
       <c r="AA72" t="inlineStr"/>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr"/>
       <c r="AD72" t="inlineStr"/>
       <c r="AE72" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="AF72" t="inlineStr">
         <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="AG72" t="inlineStr">
+        <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="AG72" t="inlineStr">
-        <is>
-          <t>8.1</t>
-        </is>
-      </c>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>91</t>
         </is>
       </c>
       <c r="AJ72" t="inlineStr">
@@ -15924,32 +15924,32 @@
       <c r="AK72" t="inlineStr"/>
       <c r="AL72" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="AN72" t="inlineStr">
         <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>8.1</t>
-        </is>
-      </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="AQ72" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>91</t>
         </is>
       </c>
       <c r="AR72" t="inlineStr">
@@ -15960,17 +15960,17 @@
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>250</t>
         </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="AW72" t="inlineStr">
@@ -15980,12 +15980,12 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>250</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="AZ72" t="inlineStr">
@@ -16033,7 +16033,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:35</t>
+          <t>2026-09-28 22:46:38</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -16266,7 +16266,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:35</t>
+          <t>2026-09-28 22:46:38</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -16499,7 +16499,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:35</t>
+          <t>2026-09-28 22:46:38</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -16732,7 +16732,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:35</t>
+          <t>2026-09-28 22:46:38</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -16950,7 +16950,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -16965,17 +16965,17 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:38</t>
+          <t>2026-09-28 22:46:41</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
       <c r="K77" t="n">
@@ -16988,15 +16988,19 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>189</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>100</t>
         </is>
       </c>
       <c r="R77" t="inlineStr"/>
@@ -17007,7 +17011,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -17017,56 +17021,56 @@
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="W77" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr"/>
       <c r="AA77" t="inlineStr"/>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr"/>
       <c r="AD77" t="inlineStr"/>
       <c r="AE77" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="AF77" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="AG77" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AJ77" t="inlineStr">
@@ -17074,35 +17078,39 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="AK77" t="inlineStr"/>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="AL77" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="AN77" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="AQ77" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AR77" t="inlineStr">
@@ -17110,20 +17118,24 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="AS77" t="inlineStr"/>
+      <c r="AS77" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="AT77" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>189</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="AW77" t="inlineStr">
@@ -17133,12 +17145,12 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>189</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="AZ77" t="inlineStr">
@@ -17186,7 +17198,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:39</t>
+          <t>2026-09-28 22:46:43</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -17419,7 +17431,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:39</t>
+          <t>2026-09-28 22:46:43</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -17652,7 +17664,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:39</t>
+          <t>2026-09-28 22:46:43</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -17885,7 +17897,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:39</t>
+          <t>2026-09-28 22:46:43</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -18118,17 +18130,17 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:42</t>
+          <t>2026-09-28 22:46:46</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
       <c r="K82" t="n">
@@ -18351,7 +18363,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:44</t>
+          <t>2026-09-28 22:46:48</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -18584,7 +18596,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:44</t>
+          <t>2026-09-28 22:46:48</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -18817,7 +18829,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:44</t>
+          <t>2026-09-28 22:46:48</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -19050,7 +19062,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:44</t>
+          <t>2026-09-28 22:46:48</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -19268,7 +19280,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -19283,17 +19295,17 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:47</t>
+          <t>2026-09-28 22:46:51</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
       <c r="K87" t="n">
@@ -19306,7 +19318,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>21</t>
         </is>
       </c>
       <c r="N87" t="inlineStr"/>
@@ -19314,7 +19326,7 @@
       <c r="P87" t="inlineStr"/>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>96</t>
         </is>
       </c>
       <c r="R87" t="inlineStr"/>
@@ -19325,7 +19337,7 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
@@ -19335,56 +19347,56 @@
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>15.3</t>
         </is>
       </c>
       <c r="W87" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>15.4</t>
         </is>
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Z87" t="inlineStr"/>
       <c r="AA87" t="inlineStr"/>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr"/>
       <c r="AD87" t="inlineStr"/>
       <c r="AE87" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="AF87" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>15.3</t>
         </is>
       </c>
       <c r="AG87" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>15.4</t>
         </is>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>96</t>
         </is>
       </c>
       <c r="AJ87" t="inlineStr">
@@ -19394,37 +19406,37 @@
       </c>
       <c r="AK87" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AL87" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="AN87" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>15.3</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>15.4</t>
         </is>
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AQ87" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>96</t>
         </is>
       </c>
       <c r="AR87" t="inlineStr">
@@ -19434,17 +19446,17 @@
       </c>
       <c r="AS87" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
@@ -19455,7 +19467,7 @@
       <c r="AW87" t="inlineStr"/>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -19504,7 +19516,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:48</t>
+          <t>2026-09-28 22:46:53</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -19725,7 +19737,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:48</t>
+          <t>2026-09-28 22:46:53</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -19946,7 +19958,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:48</t>
+          <t>2026-09-28 22:46:53</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -20167,7 +20179,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:48</t>
+          <t>2026-09-28 22:46:53</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -20373,7 +20385,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -20388,17 +20400,17 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:51</t>
+          <t>2026-09-28 22:46:56</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
       <c r="K92" t="n">
@@ -20411,7 +20423,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>166</t>
         </is>
       </c>
       <c r="N92" t="inlineStr"/>
@@ -20430,7 +20442,7 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
@@ -20440,51 +20452,51 @@
       </c>
       <c r="V92" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="W92" t="inlineStr">
         <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
           <t>7.3</t>
         </is>
       </c>
-      <c r="X92" t="inlineStr">
-        <is>
-          <t>7.4</t>
-        </is>
-      </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="Z92" t="inlineStr"/>
       <c r="AA92" t="inlineStr"/>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr"/>
       <c r="AD92" t="inlineStr"/>
       <c r="AE92" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="AF92" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="AG92" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AI92" t="inlineStr">
@@ -20500,27 +20512,27 @@
       <c r="AK92" t="inlineStr"/>
       <c r="AL92" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="AM92" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="AN92" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AQ92" t="inlineStr">
@@ -20536,17 +20548,17 @@
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>166</t>
         </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="AW92" t="inlineStr">
@@ -20556,12 +20568,12 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>166</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="AZ92" t="inlineStr">
@@ -20609,7 +20621,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:53</t>
+          <t>2026-09-28 22:46:58</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -20842,7 +20854,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:53</t>
+          <t>2026-09-28 22:46:58</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -21075,7 +21087,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:53</t>
+          <t>2026-09-28 22:46:58</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -21308,7 +21320,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:53</t>
+          <t>2026-09-28 22:46:58</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -21526,7 +21538,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -21541,17 +21553,17 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:55</t>
+          <t>2026-09-28 22:47:01</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
       <c r="K97" t="n">
@@ -21564,7 +21576,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>295</t>
         </is>
       </c>
       <c r="N97" t="inlineStr"/>
@@ -21572,12 +21584,12 @@
       <c r="P97" t="inlineStr"/>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>75</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>1018.6</t>
+          <t>1018.7</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
@@ -21587,7 +21599,7 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
@@ -21597,96 +21609,96 @@
       </c>
       <c r="V97" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="W97" t="inlineStr">
         <is>
+          <t>18.2</t>
+        </is>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
           <t>18.3</t>
         </is>
       </c>
-      <c r="X97" t="inlineStr">
-        <is>
-          <t>18.7</t>
-        </is>
-      </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="Z97" t="inlineStr"/>
       <c r="AA97" t="inlineStr"/>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr"/>
       <c r="AD97" t="inlineStr"/>
       <c r="AE97" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="AF97" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="AG97" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.3</t>
         </is>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
+          <t>18.2</t>
+        </is>
+      </c>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AL97" t="inlineStr">
+        <is>
+          <t>295</t>
+        </is>
+      </c>
+      <c r="AM97" t="inlineStr">
+        <is>
+          <t>22:00 - 22:30</t>
+        </is>
+      </c>
+      <c r="AN97" t="inlineStr">
+        <is>
+          <t>18.2</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
           <t>18.3</t>
         </is>
       </c>
-      <c r="AI97" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="AJ97" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK97" t="inlineStr">
-        <is>
-          <t>6.1</t>
-        </is>
-      </c>
-      <c r="AL97" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>21:30 - 22:00</t>
-        </is>
-      </c>
-      <c r="AN97" t="inlineStr">
-        <is>
-          <t>18.5</t>
-        </is>
-      </c>
-      <c r="AO97" t="inlineStr">
-        <is>
-          <t>18.7</t>
-        </is>
-      </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>18.3</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="AQ97" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AR97" t="inlineStr">
@@ -21696,22 +21708,22 @@
       </c>
       <c r="AS97" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>295</t>
         </is>
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
-          <t>1018.6</t>
+          <t>1018.7</t>
         </is>
       </c>
       <c r="AW97" t="inlineStr">
@@ -21721,12 +21733,12 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
-          <t>1018.6</t>
+          <t>1018.7</t>
         </is>
       </c>
       <c r="AZ97" t="inlineStr">
@@ -21774,7 +21786,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:57</t>
+          <t>2026-09-28 22:47:02</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -22007,7 +22019,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:57</t>
+          <t>2026-09-28 22:47:02</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -22240,7 +22252,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:57</t>
+          <t>2026-09-28 22:47:02</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -22473,7 +22485,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-09-28 22:16:57</t>
+          <t>2026-09-28 22:47:02</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -22691,7 +22703,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -22706,17 +22718,17 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:00</t>
+          <t>2026-09-28 22:47:05</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
       <c r="K102" t="n">
@@ -22731,12 +22743,12 @@
       <c r="N102" t="inlineStr"/>
       <c r="O102" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>277</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
@@ -22752,7 +22764,7 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
@@ -22762,48 +22774,48 @@
       </c>
       <c r="V102" t="inlineStr">
         <is>
+          <t>6.8</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
+      <c r="X102" t="inlineStr">
+        <is>
           <t>6.9</t>
-        </is>
-      </c>
-      <c r="W102" t="inlineStr">
-        <is>
-          <t>6.4</t>
-        </is>
-      </c>
-      <c r="X102" t="inlineStr">
-        <is>
-          <t>7.1</t>
         </is>
       </c>
       <c r="Y102" t="inlineStr"/>
       <c r="Z102" t="inlineStr"/>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr"/>
       <c r="AC102" t="inlineStr"/>
       <c r="AD102" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="AE102" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="AF102" t="inlineStr">
         <is>
+          <t>6.8</t>
+        </is>
+      </c>
+      <c r="AG102" t="inlineStr">
+        <is>
           <t>6.9</t>
         </is>
       </c>
-      <c r="AG102" t="inlineStr">
-        <is>
-          <t>7.1</t>
-        </is>
-      </c>
       <c r="AH102" t="inlineStr">
         <is>
           <t>6.4</t>
@@ -22821,29 +22833,29 @@
       </c>
       <c r="AK102" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AL102" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="AN102" t="inlineStr">
         <is>
+          <t>6.8</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
           <t>6.9</t>
         </is>
       </c>
-      <c r="AO102" t="inlineStr">
-        <is>
-          <t>7.1</t>
-        </is>
-      </c>
       <c r="AP102" t="inlineStr">
         <is>
           <t>6.4</t>
@@ -22861,22 +22873,22 @@
       </c>
       <c r="AS102" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>277</t>
         </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="AW102" t="inlineStr">
@@ -22886,12 +22898,12 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>277</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="AZ102" t="inlineStr">
@@ -22939,7 +22951,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:01</t>
+          <t>2026-09-28 22:47:07</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -23172,7 +23184,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:01</t>
+          <t>2026-09-28 22:47:07</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -23405,7 +23417,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:01</t>
+          <t>2026-09-28 22:47:07</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -23638,7 +23650,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:01</t>
+          <t>2026-09-28 22:47:07</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -23856,7 +23868,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -23871,17 +23883,17 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:04</t>
+          <t>2026-09-28 22:47:10</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
       <c r="K107" t="n">
@@ -23896,13 +23908,13 @@
       <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>223</t>
         </is>
       </c>
       <c r="P107" t="inlineStr"/>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>98</t>
         </is>
       </c>
       <c r="R107" t="inlineStr"/>
@@ -23913,7 +23925,7 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
@@ -23923,7 +23935,7 @@
       </c>
       <c r="V107" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="W107" t="inlineStr">
@@ -23933,7 +23945,7 @@
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="Y107" t="inlineStr"/>
@@ -23952,17 +23964,17 @@
       </c>
       <c r="AE107" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="AF107" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="AG107" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="AH107" t="inlineStr">
@@ -23972,7 +23984,7 @@
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>98</t>
         </is>
       </c>
       <c r="AJ107" t="inlineStr">
@@ -23988,17 +24000,17 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="AN107" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="AP107" t="inlineStr">
@@ -24008,7 +24020,7 @@
       </c>
       <c r="AQ107" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>98</t>
         </is>
       </c>
       <c r="AR107" t="inlineStr">
@@ -24024,7 +24036,7 @@
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>223</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
@@ -24039,7 +24051,7 @@
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>223</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
@@ -24092,7 +24104,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:06</t>
+          <t>2026-09-28 22:47:12</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -24325,7 +24337,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:06</t>
+          <t>2026-09-28 22:47:12</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -24558,7 +24570,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:06</t>
+          <t>2026-09-28 22:47:12</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -24791,7 +24803,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:06</t>
+          <t>2026-09-28 22:47:12</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -25009,7 +25021,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -25024,17 +25036,17 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:08</t>
+          <t>2026-09-28 22:47:15</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
       <c r="K112" t="n">
@@ -25047,7 +25059,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>103</t>
         </is>
       </c>
       <c r="N112" t="inlineStr"/>
@@ -25055,12 +25067,12 @@
       <c r="P112" t="inlineStr"/>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>1018.3</t>
+          <t>1018.1</t>
         </is>
       </c>
       <c r="S112" t="inlineStr">
@@ -25070,7 +25082,7 @@
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
@@ -25080,56 +25092,56 @@
       </c>
       <c r="V112" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="W112" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="Z112" t="inlineStr"/>
       <c r="AA112" t="inlineStr"/>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="AC112" t="inlineStr"/>
       <c r="AD112" t="inlineStr"/>
       <c r="AE112" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="AF112" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="AG112" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="AJ112" t="inlineStr">
@@ -25139,37 +25151,37 @@
       </c>
       <c r="AK112" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="AL112" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>103</t>
         </is>
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="AN112" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="AQ112" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="AR112" t="inlineStr">
@@ -25179,22 +25191,22 @@
       </c>
       <c r="AS112" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>103</t>
         </is>
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>1018.3</t>
+          <t>1018.1</t>
         </is>
       </c>
       <c r="AW112" t="inlineStr">
@@ -25204,12 +25216,12 @@
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
-          <t>1018.3</t>
+          <t>1018.1</t>
         </is>
       </c>
       <c r="AZ112" t="inlineStr">
@@ -25257,7 +25269,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:10</t>
+          <t>2026-09-28 22:47:17</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -25490,7 +25502,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:10</t>
+          <t>2026-09-28 22:47:17</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -25723,7 +25735,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:10</t>
+          <t>2026-09-28 22:47:17</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -25956,7 +25968,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:10</t>
+          <t>2026-09-28 22:47:17</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -26174,7 +26186,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -26189,17 +26201,17 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:13</t>
+          <t>2026-09-28 22:47:20</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
       <c r="K117" t="n">
@@ -26214,7 +26226,7 @@
       <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>232</t>
         </is>
       </c>
       <c r="P117" t="inlineStr"/>
@@ -26231,7 +26243,7 @@
       </c>
       <c r="T117" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="U117" t="inlineStr">
@@ -26241,7 +26253,7 @@
       </c>
       <c r="V117" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="W117" t="inlineStr">
@@ -26251,36 +26263,36 @@
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>8.9</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="Y117" t="inlineStr"/>
       <c r="Z117" t="inlineStr"/>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr"/>
       <c r="AC117" t="inlineStr"/>
       <c r="AD117" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="AE117" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="AF117" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="AG117" t="inlineStr">
         <is>
-          <t>8.9</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AH117" t="inlineStr">
@@ -26301,22 +26313,22 @@
       <c r="AK117" t="inlineStr"/>
       <c r="AL117" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="AN117" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>8.9</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AP117" t="inlineStr">
@@ -26337,17 +26349,17 @@
       <c r="AS117" t="inlineStr"/>
       <c r="AT117" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>232</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
@@ -26357,12 +26369,12 @@
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>232</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
@@ -26410,7 +26422,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:15</t>
+          <t>2026-09-28 22:47:22</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -26643,7 +26655,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:15</t>
+          <t>2026-09-28 22:47:22</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -26876,7 +26888,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:15</t>
+          <t>2026-09-28 22:47:22</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -27109,7 +27121,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:15</t>
+          <t>2026-09-28 22:47:22</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -27342,17 +27354,17 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:17</t>
+          <t>2026-09-28 22:47:25</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
       <c r="K122" t="n">
@@ -27583,7 +27595,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:19</t>
+          <t>2026-09-28 22:47:27</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -27824,7 +27836,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:19</t>
+          <t>2026-09-28 22:47:27</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -28065,7 +28077,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:19</t>
+          <t>2026-09-28 22:47:27</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -28306,7 +28318,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:19</t>
+          <t>2026-09-28 22:47:27</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -28532,7 +28544,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -28547,17 +28559,17 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:22</t>
+          <t>2026-09-28 22:47:30</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
       <c r="K127" t="n">
@@ -28570,7 +28582,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>356</t>
         </is>
       </c>
       <c r="N127" t="inlineStr"/>
@@ -28582,7 +28594,7 @@
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>87</t>
         </is>
       </c>
       <c r="R127" t="inlineStr"/>
@@ -28593,7 +28605,7 @@
       </c>
       <c r="T127" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="U127" t="inlineStr">
@@ -28603,121 +28615,121 @@
       </c>
       <c r="V127" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="W127" t="inlineStr">
         <is>
+          <t>8.9</t>
+        </is>
+      </c>
+      <c r="X127" t="inlineStr">
+        <is>
           <t>9.2</t>
         </is>
       </c>
-      <c r="X127" t="inlineStr">
-        <is>
-          <t>9.4</t>
-        </is>
-      </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="Z127" t="inlineStr"/>
       <c r="AA127" t="inlineStr"/>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="AC127" t="inlineStr"/>
       <c r="AD127" t="inlineStr"/>
       <c r="AE127" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="AF127" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="AG127" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
+          <t>8.9</t>
+        </is>
+      </c>
+      <c r="AI127" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="AJ127" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK127" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL127" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="AM127" t="inlineStr">
+        <is>
+          <t>22:00 - 22:30</t>
+        </is>
+      </c>
+      <c r="AN127" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="AO127" t="inlineStr">
+        <is>
           <t>9.2</t>
         </is>
       </c>
-      <c r="AI127" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="AJ127" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK127" t="inlineStr">
+      <c r="AP127" t="inlineStr">
+        <is>
+          <t>8.9</t>
+        </is>
+      </c>
+      <c r="AQ127" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="AR127" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AL127" t="inlineStr">
-        <is>
-          <t>4.3</t>
-        </is>
-      </c>
-      <c r="AM127" t="inlineStr">
-        <is>
-          <t>21:30 - 22:00</t>
-        </is>
-      </c>
-      <c r="AN127" t="inlineStr">
-        <is>
-          <t>9.4</t>
-        </is>
-      </c>
-      <c r="AO127" t="inlineStr">
-        <is>
-          <t>9.4</t>
-        </is>
-      </c>
-      <c r="AP127" t="inlineStr">
-        <is>
-          <t>9.2</t>
-        </is>
-      </c>
-      <c r="AQ127" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="AR127" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS127" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AT127" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>356</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="AW127" t="inlineStr">
@@ -28727,12 +28739,12 @@
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>356</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
@@ -28780,7 +28792,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:23</t>
+          <t>2026-09-28 22:47:32</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -29013,7 +29025,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:23</t>
+          <t>2026-09-28 22:47:32</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -29246,7 +29258,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:23</t>
+          <t>2026-09-28 22:47:32</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -29479,7 +29491,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:23</t>
+          <t>2026-09-28 22:47:32</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -29697,7 +29709,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -29712,17 +29724,17 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:26</t>
+          <t>2026-09-28 22:47:35</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
       <c r="K132" t="n">
@@ -29735,7 +29747,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>256</t>
         </is>
       </c>
       <c r="N132" t="inlineStr"/>
@@ -29748,7 +29760,7 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>1019.4</t>
+          <t>1019.5</t>
         </is>
       </c>
       <c r="S132" t="inlineStr">
@@ -29758,7 +29770,7 @@
       </c>
       <c r="T132" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="U132" t="inlineStr">
@@ -29768,98 +29780,98 @@
       </c>
       <c r="V132" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="W132" t="inlineStr">
         <is>
+          <t>18.7</t>
+        </is>
+      </c>
+      <c r="X132" t="inlineStr">
+        <is>
           <t>19.8</t>
         </is>
       </c>
-      <c r="X132" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="Z132" t="inlineStr"/>
       <c r="AA132" t="inlineStr"/>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AC132" t="inlineStr"/>
       <c r="AD132" t="inlineStr"/>
       <c r="AE132" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="AF132" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="AG132" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
+          <t>18.7</t>
+        </is>
+      </c>
+      <c r="AI132" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="AJ132" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK132" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
+      <c r="AL132" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="AM132" t="inlineStr">
+        <is>
+          <t>22:00 - 22:30</t>
+        </is>
+      </c>
+      <c r="AN132" t="inlineStr">
+        <is>
+          <t>19.3</t>
+        </is>
+      </c>
+      <c r="AO132" t="inlineStr">
+        <is>
           <t>19.8</t>
         </is>
       </c>
-      <c r="AI132" t="inlineStr">
+      <c r="AP132" t="inlineStr">
+        <is>
+          <t>18.7</t>
+        </is>
+      </c>
+      <c r="AQ132" t="inlineStr">
         <is>
           <t>83</t>
         </is>
       </c>
-      <c r="AJ132" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK132" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="AL132" t="inlineStr">
-        <is>
-          <t>252</t>
-        </is>
-      </c>
-      <c r="AM132" t="inlineStr">
-        <is>
-          <t>21:30 - 22:00</t>
-        </is>
-      </c>
-      <c r="AN132" t="inlineStr">
-        <is>
-          <t>19.9</t>
-        </is>
-      </c>
-      <c r="AO132" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
-      <c r="AP132" t="inlineStr">
-        <is>
-          <t>19.8</t>
-        </is>
-      </c>
-      <c r="AQ132" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="AR132" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -29867,22 +29879,22 @@
       </c>
       <c r="AS132" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="AT132" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>256</t>
         </is>
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AV132" t="inlineStr">
         <is>
-          <t>1019.4</t>
+          <t>1019.5</t>
         </is>
       </c>
       <c r="AW132" t="inlineStr">
@@ -29892,12 +29904,12 @@
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
-          <t>1019.4</t>
+          <t>1019.5</t>
         </is>
       </c>
       <c r="AZ132" t="inlineStr">
@@ -29945,7 +29957,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:28</t>
+          <t>2026-09-28 22:47:37</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -30178,7 +30190,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:28</t>
+          <t>2026-09-28 22:47:37</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -30411,7 +30423,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:28</t>
+          <t>2026-09-28 22:47:37</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -30644,7 +30656,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:28</t>
+          <t>2026-09-28 22:47:37</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -30877,17 +30889,17 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:30</t>
+          <t>2026-09-28 22:47:40</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
       <c r="K137" t="n">
@@ -31098,7 +31110,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:32</t>
+          <t>2026-09-28 22:47:42</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -31319,7 +31331,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:32</t>
+          <t>2026-09-28 22:47:42</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -31540,7 +31552,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:32</t>
+          <t>2026-09-28 22:47:42</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -31761,7 +31773,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:32</t>
+          <t>2026-09-28 22:47:42</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -31967,7 +31979,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -31982,17 +31994,17 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:35</t>
+          <t>2026-09-28 22:47:45</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
       <c r="K142" t="n">
@@ -32005,7 +32017,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>186</t>
         </is>
       </c>
       <c r="N142" t="inlineStr"/>
@@ -32023,12 +32035,12 @@
       </c>
       <c r="S142" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="T142" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="U142" t="inlineStr">
@@ -32038,17 +32050,17 @@
       </c>
       <c r="V142" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="W142" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="X142" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="Y142" t="inlineStr">
@@ -32060,94 +32072,94 @@
       <c r="AA142" t="inlineStr"/>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="AC142" t="inlineStr"/>
       <c r="AD142" t="inlineStr"/>
       <c r="AE142" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="AF142" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="AG142" t="inlineStr">
         <is>
+          <t>22.0</t>
+        </is>
+      </c>
+      <c r="AH142" t="inlineStr">
+        <is>
+          <t>21.2</t>
+        </is>
+      </c>
+      <c r="AI142" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="AJ142" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="AK142" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="AL142" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="AM142" t="inlineStr">
+        <is>
+          <t>22:00 - 22:30</t>
+        </is>
+      </c>
+      <c r="AN142" t="inlineStr">
+        <is>
           <t>21.9</t>
         </is>
       </c>
-      <c r="AH142" t="inlineStr">
-        <is>
-          <t>21.7</t>
-        </is>
-      </c>
-      <c r="AI142" t="inlineStr">
+      <c r="AO142" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
+      <c r="AP142" t="inlineStr">
+        <is>
+          <t>21.2</t>
+        </is>
+      </c>
+      <c r="AQ142" t="inlineStr">
         <is>
           <t>81</t>
         </is>
       </c>
-      <c r="AJ142" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK142" t="inlineStr">
+      <c r="AR142" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="AS142" t="inlineStr">
         <is>
           <t>7.9</t>
         </is>
       </c>
-      <c r="AL142" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="AM142" t="inlineStr">
-        <is>
-          <t>21:30 - 22:00</t>
-        </is>
-      </c>
-      <c r="AN142" t="inlineStr">
-        <is>
-          <t>21.8</t>
-        </is>
-      </c>
-      <c r="AO142" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
-      <c r="AP142" t="inlineStr">
-        <is>
-          <t>21.7</t>
-        </is>
-      </c>
-      <c r="AQ142" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="AR142" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS142" t="inlineStr">
-        <is>
-          <t>7.9</t>
-        </is>
-      </c>
       <c r="AT142" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>186</t>
         </is>
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="AV142" t="inlineStr">
@@ -32162,7 +32174,7 @@
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
@@ -32215,7 +32227,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:36</t>
+          <t>2026-09-28 22:47:46</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -32448,7 +32460,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:36</t>
+          <t>2026-09-28 22:47:46</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -32681,7 +32693,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:36</t>
+          <t>2026-09-28 22:47:46</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -32914,7 +32926,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:36</t>
+          <t>2026-09-28 22:47:46</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -33132,7 +33144,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -33147,17 +33159,17 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:39</t>
+          <t>2026-09-28 22:47:49</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
       <c r="K147" t="n">
@@ -33193,7 +33205,7 @@
       </c>
       <c r="T147" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="U147" t="inlineStr">
@@ -33203,116 +33215,116 @@
       </c>
       <c r="V147" t="inlineStr">
         <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>21.7</t>
+        </is>
+      </c>
+      <c r="X147" t="inlineStr">
+        <is>
           <t>22.0</t>
         </is>
       </c>
-      <c r="W147" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
-      <c r="X147" t="inlineStr">
-        <is>
-          <t>22.0</t>
-        </is>
-      </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="Z147" t="inlineStr"/>
       <c r="AA147" t="inlineStr"/>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>37.4</t>
+          <t>33.1</t>
         </is>
       </c>
       <c r="AC147" t="inlineStr"/>
       <c r="AD147" t="inlineStr"/>
       <c r="AE147" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="AF147" t="inlineStr">
         <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="AG147" t="inlineStr">
+        <is>
           <t>22.0</t>
         </is>
       </c>
-      <c r="AG147" t="inlineStr">
+      <c r="AH147" t="inlineStr">
+        <is>
+          <t>21.7</t>
+        </is>
+      </c>
+      <c r="AI147" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="AJ147" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK147" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="AL147" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="AM147" t="inlineStr">
+        <is>
+          <t>22:00 - 22:30</t>
+        </is>
+      </c>
+      <c r="AN147" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="AO147" t="inlineStr">
         <is>
           <t>22.0</t>
         </is>
       </c>
-      <c r="AH147" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
-      <c r="AI147" t="inlineStr">
+      <c r="AP147" t="inlineStr">
+        <is>
+          <t>21.7</t>
+        </is>
+      </c>
+      <c r="AQ147" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="AJ147" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK147" t="inlineStr">
-        <is>
-          <t>25.9</t>
-        </is>
-      </c>
-      <c r="AL147" t="inlineStr">
+      <c r="AR147" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS147" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="AT147" t="inlineStr">
         <is>
           <t>175</t>
         </is>
       </c>
-      <c r="AM147" t="inlineStr">
-        <is>
-          <t>21:30 - 22:00</t>
-        </is>
-      </c>
-      <c r="AN147" t="inlineStr">
-        <is>
-          <t>22.0</t>
-        </is>
-      </c>
-      <c r="AO147" t="inlineStr">
-        <is>
-          <t>22.0</t>
-        </is>
-      </c>
-      <c r="AP147" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
-      <c r="AQ147" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="AR147" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS147" t="inlineStr">
-        <is>
-          <t>25.9</t>
-        </is>
-      </c>
-      <c r="AT147" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
       <c r="AU147" t="inlineStr">
         <is>
-          <t>37.4</t>
+          <t>33.1</t>
         </is>
       </c>
       <c r="AV147" t="inlineStr">
@@ -33327,7 +33339,7 @@
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>37.4</t>
+          <t>33.1</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
@@ -33380,7 +33392,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:40</t>
+          <t>2026-09-28 22:47:51</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -33613,7 +33625,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:40</t>
+          <t>2026-09-28 22:47:51</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -33846,7 +33858,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:40</t>
+          <t>2026-09-28 22:47:51</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -34079,7 +34091,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:40</t>
+          <t>2026-09-28 22:47:51</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -34297,7 +34309,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -34312,17 +34324,17 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:43</t>
+          <t>2026-09-28 22:47:54</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
       <c r="K152" t="n">
@@ -34336,7 +34348,7 @@
       <c r="M152" t="inlineStr"/>
       <c r="N152" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>121</t>
         </is>
       </c>
       <c r="O152" t="inlineStr"/>
@@ -34358,7 +34370,7 @@
       </c>
       <c r="T152" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="U152" t="inlineStr">
@@ -34368,12 +34380,12 @@
       </c>
       <c r="V152" t="inlineStr">
         <is>
+          <t>16.2</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
           <t>16.1</t>
-        </is>
-      </c>
-      <c r="W152" t="inlineStr">
-        <is>
-          <t>15.9</t>
         </is>
       </c>
       <c r="X152" t="inlineStr">
@@ -34384,105 +34396,105 @@
       <c r="Y152" t="inlineStr"/>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr"/>
       <c r="AB152" t="inlineStr"/>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AD152" t="inlineStr"/>
       <c r="AE152" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="AF152" t="inlineStr">
         <is>
+          <t>16.2</t>
+        </is>
+      </c>
+      <c r="AG152" t="inlineStr">
+        <is>
+          <t>16.2</t>
+        </is>
+      </c>
+      <c r="AH152" t="inlineStr">
+        <is>
           <t>16.1</t>
         </is>
       </c>
-      <c r="AG152" t="inlineStr">
+      <c r="AI152" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AJ152" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK152" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AL152" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
+      <c r="AM152" t="inlineStr">
+        <is>
+          <t>22:00 - 22:30</t>
+        </is>
+      </c>
+      <c r="AN152" t="inlineStr">
         <is>
           <t>16.2</t>
         </is>
       </c>
-      <c r="AH152" t="inlineStr">
-        <is>
-          <t>15.9</t>
-        </is>
-      </c>
-      <c r="AI152" t="inlineStr">
+      <c r="AO152" t="inlineStr">
+        <is>
+          <t>16.2</t>
+        </is>
+      </c>
+      <c r="AP152" t="inlineStr">
+        <is>
+          <t>16.1</t>
+        </is>
+      </c>
+      <c r="AQ152" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AJ152" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK152" t="inlineStr">
+      <c r="AR152" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS152" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AL152" t="inlineStr">
-        <is>
-          <t>4.7</t>
-        </is>
-      </c>
-      <c r="AM152" t="inlineStr">
-        <is>
-          <t>21:30 - 22:00</t>
-        </is>
-      </c>
-      <c r="AN152" t="inlineStr">
-        <is>
-          <t>16.1</t>
-        </is>
-      </c>
-      <c r="AO152" t="inlineStr">
-        <is>
-          <t>16.2</t>
-        </is>
-      </c>
-      <c r="AP152" t="inlineStr">
-        <is>
-          <t>15.9</t>
-        </is>
-      </c>
-      <c r="AQ152" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="AR152" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS152" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AT152" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>121</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
@@ -34492,12 +34504,12 @@
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>121</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
@@ -34545,7 +34557,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:45</t>
+          <t>2026-09-28 22:47:56</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -34778,7 +34790,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:45</t>
+          <t>2026-09-28 22:47:56</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -35011,7 +35023,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:45</t>
+          <t>2026-09-28 22:47:56</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -35244,7 +35256,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:45</t>
+          <t>2026-09-28 22:47:56</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -35477,17 +35489,17 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:48</t>
+          <t>2026-09-28 22:47:59</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
       <c r="K157" t="n">
@@ -35710,7 +35722,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:49</t>
+          <t>2026-09-28 22:48:01</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -35943,7 +35955,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:49</t>
+          <t>2026-09-28 22:48:01</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -36176,7 +36188,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:49</t>
+          <t>2026-09-28 22:48:01</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -36409,7 +36421,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:49</t>
+          <t>2026-09-28 22:48:01</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -36642,17 +36654,17 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:52</t>
+          <t>2026-09-28 22:48:04</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
       <c r="K162" t="n">
@@ -36883,7 +36895,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:54</t>
+          <t>2026-09-28 22:48:06</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -37124,7 +37136,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:54</t>
+          <t>2026-09-28 22:48:06</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -37365,7 +37377,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:54</t>
+          <t>2026-09-28 22:48:06</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -37606,7 +37618,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:54</t>
+          <t>2026-09-28 22:48:06</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -37832,7 +37844,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -37847,17 +37859,17 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:57</t>
+          <t>2026-09-28 22:48:09</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
       <c r="K167" t="n">
@@ -37870,7 +37882,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>37</t>
         </is>
       </c>
       <c r="N167" t="inlineStr"/>
@@ -37878,12 +37890,12 @@
       <c r="P167" t="inlineStr"/>
       <c r="Q167" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>91</t>
         </is>
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>1018.4</t>
+          <t>1018.5</t>
         </is>
       </c>
       <c r="S167" t="inlineStr">
@@ -37893,7 +37905,7 @@
       </c>
       <c r="T167" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="U167" t="inlineStr">
@@ -37903,56 +37915,56 @@
       </c>
       <c r="V167" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>15.7</t>
         </is>
       </c>
       <c r="W167" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>15.6</t>
         </is>
       </c>
       <c r="X167" t="inlineStr">
         <is>
-          <t>15.7</t>
+          <t>15.9</t>
         </is>
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="Z167" t="inlineStr"/>
       <c r="AA167" t="inlineStr"/>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="AC167" t="inlineStr"/>
       <c r="AD167" t="inlineStr"/>
       <c r="AE167" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="AF167" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>15.7</t>
         </is>
       </c>
       <c r="AG167" t="inlineStr">
         <is>
-          <t>15.7</t>
+          <t>15.9</t>
         </is>
       </c>
       <c r="AH167" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>15.6</t>
         </is>
       </c>
       <c r="AI167" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>91</t>
         </is>
       </c>
       <c r="AJ167" t="inlineStr">
@@ -37963,32 +37975,32 @@
       <c r="AK167" t="inlineStr"/>
       <c r="AL167" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="AN167" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>15.7</t>
         </is>
       </c>
       <c r="AO167" t="inlineStr">
         <is>
-          <t>15.7</t>
+          <t>15.9</t>
         </is>
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>15.6</t>
         </is>
       </c>
       <c r="AQ167" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>91</t>
         </is>
       </c>
       <c r="AR167" t="inlineStr">
@@ -37999,37 +38011,37 @@
       <c r="AS167" t="inlineStr"/>
       <c r="AT167" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AU167" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>1018.4</t>
+          <t>1018.5</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>1018.4</t>
+          <t>1018.5</t>
         </is>
       </c>
       <c r="BA167" t="inlineStr">
@@ -38076,7 +38088,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:58</t>
+          <t>2026-09-28 22:48:11</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -38317,7 +38329,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:58</t>
+          <t>2026-09-28 22:48:11</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -38558,7 +38570,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:58</t>
+          <t>2026-09-28 22:48:11</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -38799,7 +38811,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026-09-28 22:17:58</t>
+          <t>2026-09-28 22:48:11</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -39040,17 +39052,17 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-09-28 22:18:01</t>
+          <t>2026-09-28 22:48:14</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
       <c r="K172" t="n">
@@ -39273,7 +39285,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-09-28 22:18:03</t>
+          <t>2026-09-28 22:48:16</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -39506,7 +39518,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026-09-28 22:18:03</t>
+          <t>2026-09-28 22:48:16</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -39739,7 +39751,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026-09-28 22:18:03</t>
+          <t>2026-09-28 22:48:16</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -39972,7 +39984,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026-09-28 22:18:03</t>
+          <t>2026-09-28 22:48:16</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -40205,17 +40217,17 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026-09-28 22:18:05</t>
+          <t>2026-09-28 22:48:19</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
       <c r="K177" t="n">
@@ -40426,7 +40438,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026-09-28 22:18:07</t>
+          <t>2026-09-28 22:48:21</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -40647,7 +40659,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-09-28 22:18:07</t>
+          <t>2026-09-28 22:48:21</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -40868,7 +40880,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-09-28 22:18:07</t>
+          <t>2026-09-28 22:48:21</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -41089,7 +41101,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026-09-28 22:18:07</t>
+          <t>2026-09-28 22:48:21</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -41295,7 +41307,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -41310,17 +41322,17 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026-09-28 22:18:10</t>
+          <t>2026-09-28 22:48:24</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
       <c r="K182" t="n">
@@ -41333,7 +41345,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>294</t>
         </is>
       </c>
       <c r="N182" t="inlineStr"/>
@@ -41352,7 +41364,7 @@
       </c>
       <c r="T182" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="U182" t="inlineStr">
@@ -41362,17 +41374,17 @@
       </c>
       <c r="V182" t="inlineStr">
         <is>
+          <t>20.7</t>
+        </is>
+      </c>
+      <c r="W182" t="inlineStr">
+        <is>
+          <t>20.6</t>
+        </is>
+      </c>
+      <c r="X182" t="inlineStr">
+        <is>
           <t>21.0</t>
-        </is>
-      </c>
-      <c r="W182" t="inlineStr">
-        <is>
-          <t>20.9</t>
-        </is>
-      </c>
-      <c r="X182" t="inlineStr">
-        <is>
-          <t>21.1</t>
         </is>
       </c>
       <c r="Y182" t="inlineStr">
@@ -41384,29 +41396,29 @@
       <c r="AA182" t="inlineStr"/>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="AC182" t="inlineStr"/>
       <c r="AD182" t="inlineStr"/>
       <c r="AE182" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="AF182" t="inlineStr">
         <is>
+          <t>20.7</t>
+        </is>
+      </c>
+      <c r="AG182" t="inlineStr">
+        <is>
           <t>21.0</t>
         </is>
       </c>
-      <c r="AG182" t="inlineStr">
-        <is>
-          <t>21.1</t>
-        </is>
-      </c>
       <c r="AH182" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="AI182" t="inlineStr">
@@ -41426,27 +41438,27 @@
       </c>
       <c r="AL182" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>294</t>
         </is>
       </c>
       <c r="AM182" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="AN182" t="inlineStr">
         <is>
+          <t>20.7</t>
+        </is>
+      </c>
+      <c r="AO182" t="inlineStr">
+        <is>
           <t>21.0</t>
         </is>
       </c>
-      <c r="AO182" t="inlineStr">
-        <is>
-          <t>21.1</t>
-        </is>
-      </c>
       <c r="AP182" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="AQ182" t="inlineStr">
@@ -41466,12 +41478,12 @@
       </c>
       <c r="AT182" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>294</t>
         </is>
       </c>
       <c r="AU182" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="AV182" t="inlineStr">
@@ -41482,7 +41494,7 @@
       <c r="AW182" t="inlineStr"/>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr">
@@ -41531,7 +41543,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026-09-28 22:18:11</t>
+          <t>2026-09-28 22:48:25</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -41752,7 +41764,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026-09-28 22:18:11</t>
+          <t>2026-09-28 22:48:25</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -41973,7 +41985,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-09-28 22:18:11</t>
+          <t>2026-09-28 22:48:25</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -42194,7 +42206,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-09-28 22:18:11</t>
+          <t>2026-09-28 22:48:25</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -42415,17 +42427,17 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2026-09-28 22:18:14</t>
+          <t>2026-09-28 22:48:28</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
       <c r="K187" t="n">
@@ -42636,7 +42648,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2026-09-28 22:18:16</t>
+          <t>2026-09-28 22:48:30</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -42869,7 +42881,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2026-09-28 22:18:16</t>
+          <t>2026-09-28 22:48:30</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -43102,7 +43114,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-09-28 22:18:16</t>
+          <t>2026-09-28 22:48:30</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -43335,7 +43347,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-09-28 22:18:16</t>
+          <t>2026-09-28 22:48:30</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -43553,7 +43565,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -43568,17 +43580,17 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2026-09-28 22:18:18</t>
+          <t>2026-09-28 22:48:33</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
       <c r="K192" t="n">
@@ -43599,12 +43611,12 @@
       </c>
       <c r="Q192" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>70</t>
         </is>
       </c>
       <c r="R192" t="inlineStr">
         <is>
-          <t>1017.8</t>
+          <t>1018.0</t>
         </is>
       </c>
       <c r="S192" t="inlineStr">
@@ -43614,23 +43626,23 @@
       </c>
       <c r="T192" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="U192" t="inlineStr"/>
       <c r="V192" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="W192" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="X192" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="Y192" t="inlineStr"/>
@@ -43641,82 +43653,82 @@
       <c r="AD192" t="inlineStr"/>
       <c r="AE192" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="AF192" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="AG192" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="AH192" t="inlineStr">
         <is>
+          <t>19.1</t>
+        </is>
+      </c>
+      <c r="AI192" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="AJ192" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK192" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL192" t="inlineStr">
+        <is>
+          <t>1018.0</t>
+        </is>
+      </c>
+      <c r="AM192" t="inlineStr">
+        <is>
+          <t>22:00 - 22:30</t>
+        </is>
+      </c>
+      <c r="AN192" t="inlineStr">
+        <is>
           <t>19.7</t>
         </is>
       </c>
-      <c r="AI192" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="AJ192" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK192" t="inlineStr">
+      <c r="AO192" t="inlineStr">
+        <is>
+          <t>19.9</t>
+        </is>
+      </c>
+      <c r="AP192" t="inlineStr">
+        <is>
+          <t>19.1</t>
+        </is>
+      </c>
+      <c r="AQ192" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="AR192" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS192" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AL192" t="inlineStr">
-        <is>
-          <t>1017.8</t>
-        </is>
-      </c>
-      <c r="AM192" t="inlineStr">
-        <is>
-          <t>21:30 - 22:00</t>
-        </is>
-      </c>
-      <c r="AN192" t="inlineStr">
-        <is>
-          <t>20.2</t>
-        </is>
-      </c>
-      <c r="AO192" t="inlineStr">
-        <is>
-          <t>20.6</t>
-        </is>
-      </c>
-      <c r="AP192" t="inlineStr">
-        <is>
-          <t>19.7</t>
-        </is>
-      </c>
-      <c r="AQ192" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="AR192" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS192" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AT192" t="inlineStr">
         <is>
-          <t>1017.8</t>
+          <t>1018.0</t>
         </is>
       </c>
       <c r="AU192" t="inlineStr"/>
@@ -43765,7 +43777,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2026-09-28 22:18:20</t>
+          <t>2026-09-28 22:48:35</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -43962,7 +43974,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2026-09-28 22:18:20</t>
+          <t>2026-09-28 22:48:35</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -44159,7 +44171,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026-09-28 22:18:20</t>
+          <t>2026-09-28 22:48:35</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -44356,7 +44368,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2026-09-28 22:18:20</t>
+          <t>2026-09-28 22:48:35</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -44538,7 +44550,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -44553,17 +44565,17 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2026-09-28 22:18:23</t>
+          <t>2026-09-28 22:48:38</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
       <c r="K197" t="n">
@@ -44576,7 +44588,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="N197" t="inlineStr"/>
@@ -44589,7 +44601,7 @@
       </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>1018.3</t>
+          <t>1018.1</t>
         </is>
       </c>
       <c r="S197" t="inlineStr">
@@ -44599,7 +44611,7 @@
       </c>
       <c r="T197" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="U197" t="inlineStr">
@@ -44609,98 +44621,98 @@
       </c>
       <c r="V197" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>23.1</t>
         </is>
       </c>
       <c r="W197" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="X197" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.3</t>
         </is>
       </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="Z197" t="inlineStr"/>
       <c r="AA197" t="inlineStr"/>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AC197" t="inlineStr"/>
       <c r="AD197" t="inlineStr"/>
       <c r="AE197" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="AF197" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>23.1</t>
         </is>
       </c>
       <c r="AG197" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.3</t>
         </is>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
+          <t>22.9</t>
+        </is>
+      </c>
+      <c r="AI197" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="AJ197" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK197" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
+      </c>
+      <c r="AL197" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AM197" t="inlineStr">
+        <is>
+          <t>22:00 - 22:30</t>
+        </is>
+      </c>
+      <c r="AN197" t="inlineStr">
+        <is>
           <t>23.1</t>
         </is>
       </c>
-      <c r="AI197" t="inlineStr">
+      <c r="AO197" t="inlineStr">
+        <is>
+          <t>23.3</t>
+        </is>
+      </c>
+      <c r="AP197" t="inlineStr">
+        <is>
+          <t>22.9</t>
+        </is>
+      </c>
+      <c r="AQ197" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="AJ197" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK197" t="inlineStr">
-        <is>
-          <t>4.7</t>
-        </is>
-      </c>
-      <c r="AL197" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AM197" t="inlineStr">
-        <is>
-          <t>21:30 - 22:00</t>
-        </is>
-      </c>
-      <c r="AN197" t="inlineStr">
-        <is>
-          <t>23.2</t>
-        </is>
-      </c>
-      <c r="AO197" t="inlineStr">
-        <is>
-          <t>23.5</t>
-        </is>
-      </c>
-      <c r="AP197" t="inlineStr">
-        <is>
-          <t>23.1</t>
-        </is>
-      </c>
-      <c r="AQ197" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
       <c r="AR197" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -44708,22 +44720,22 @@
       </c>
       <c r="AS197" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AT197" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AU197" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AV197" t="inlineStr">
         <is>
-          <t>1018.3</t>
+          <t>1018.1</t>
         </is>
       </c>
       <c r="AW197" t="inlineStr">
@@ -44733,12 +44745,12 @@
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr">
         <is>
-          <t>1018.3</t>
+          <t>1018.1</t>
         </is>
       </c>
       <c r="AZ197" t="inlineStr">
@@ -44786,7 +44798,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2026-09-28 22:18:24</t>
+          <t>2026-09-28 22:48:39</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -45019,7 +45031,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2026-09-28 22:18:24</t>
+          <t>2026-09-28 22:48:39</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -45252,7 +45264,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2026-09-28 22:18:24</t>
+          <t>2026-09-28 22:48:39</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -45485,7 +45497,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-09-28 22:18:24</t>
+          <t>2026-09-28 22:48:39</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -45718,17 +45730,17 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>2026-09-28 22:18:27</t>
+          <t>2026-09-28 22:48:42</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
       <c r="K202" t="n">
@@ -45891,7 +45903,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>2026-09-28 22:18:28</t>
+          <t>2026-09-28 22:48:44</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -46064,7 +46076,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>2026-09-28 22:18:28</t>
+          <t>2026-09-28 22:48:44</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -46237,7 +46249,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>2026-09-28 22:18:28</t>
+          <t>2026-09-28 22:48:44</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -46410,7 +46422,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>2026-09-28 22:18:28</t>
+          <t>2026-09-28 22:48:44</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -46568,7 +46580,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -46583,17 +46595,17 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>2026-09-28 22:18:31</t>
+          <t>2026-09-28 22:48:47</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
       <c r="K207" t="n">
@@ -46606,7 +46618,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>174</t>
         </is>
       </c>
       <c r="N207" t="inlineStr"/>
@@ -46614,7 +46626,7 @@
       <c r="P207" t="inlineStr"/>
       <c r="Q207" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>86</t>
         </is>
       </c>
       <c r="R207" t="inlineStr"/>
@@ -46625,7 +46637,7 @@
       </c>
       <c r="T207" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="U207" t="inlineStr">
@@ -46635,56 +46647,56 @@
       </c>
       <c r="V207" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="W207" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="X207" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="Z207" t="inlineStr"/>
       <c r="AA207" t="inlineStr"/>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AC207" t="inlineStr"/>
       <c r="AD207" t="inlineStr"/>
       <c r="AE207" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="AF207" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AG207" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="AH207" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="AI207" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>86</t>
         </is>
       </c>
       <c r="AJ207" t="inlineStr">
@@ -46694,37 +46706,37 @@
       </c>
       <c r="AK207" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="AL207" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>174</t>
         </is>
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="AN207" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AO207" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="AQ207" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>86</t>
         </is>
       </c>
       <c r="AR207" t="inlineStr">
@@ -46734,17 +46746,17 @@
       </c>
       <c r="AS207" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="AT207" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>174</t>
         </is>
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AV207" t="inlineStr">
@@ -46755,7 +46767,7 @@
       <c r="AW207" t="inlineStr"/>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
@@ -46804,7 +46816,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>2026-09-28 22:18:33</t>
+          <t>2026-09-28 22:48:49</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -47025,7 +47037,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>2026-09-28 22:18:33</t>
+          <t>2026-09-28 22:48:49</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -47246,7 +47258,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>2026-09-28 22:18:33</t>
+          <t>2026-09-28 22:48:49</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -47467,7 +47479,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>2026-09-28 22:18:33</t>
+          <t>2026-09-28 22:48:49</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -47673,7 +47685,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -47688,17 +47700,17 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>2026-09-28 22:18:36</t>
+          <t>2026-09-28 22:48:52</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
       <c r="K212" t="n">
@@ -47711,7 +47723,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>196</t>
         </is>
       </c>
       <c r="N212" t="inlineStr"/>
@@ -47719,7 +47731,7 @@
       <c r="P212" t="inlineStr"/>
       <c r="Q212" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>99</t>
         </is>
       </c>
       <c r="R212" t="inlineStr">
@@ -47734,7 +47746,7 @@
       </c>
       <c r="T212" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="U212" t="inlineStr">
@@ -47744,56 +47756,56 @@
       </c>
       <c r="V212" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="W212" t="inlineStr">
         <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="X212" t="inlineStr">
+        <is>
           <t>9.3</t>
         </is>
       </c>
-      <c r="X212" t="inlineStr">
-        <is>
-          <t>9.8</t>
-        </is>
-      </c>
       <c r="Y212" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="Z212" t="inlineStr"/>
       <c r="AA212" t="inlineStr"/>
       <c r="AB212" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>37.4</t>
         </is>
       </c>
       <c r="AC212" t="inlineStr"/>
       <c r="AD212" t="inlineStr"/>
       <c r="AE212" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="AF212" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="AG212" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="AH212" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="AI212" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AJ212" t="inlineStr">
@@ -47804,32 +47816,32 @@
       <c r="AK212" t="inlineStr"/>
       <c r="AL212" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="AM212" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="AN212" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="AO212" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="AP212" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="AQ212" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AR212" t="inlineStr">
@@ -47840,17 +47852,17 @@
       <c r="AS212" t="inlineStr"/>
       <c r="AT212" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="AU212" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>196</t>
         </is>
       </c>
       <c r="AV212" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>37.4</t>
         </is>
       </c>
       <c r="AW212" t="inlineStr">
@@ -47860,12 +47872,12 @@
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>196</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>37.4</t>
         </is>
       </c>
       <c r="AZ212" t="inlineStr">
@@ -47917,7 +47929,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>2026-09-28 22:18:37</t>
+          <t>2026-09-28 22:48:54</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -48158,7 +48170,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>2026-09-28 22:18:37</t>
+          <t>2026-09-28 22:48:54</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -48399,7 +48411,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>2026-09-28 22:18:37</t>
+          <t>2026-09-28 22:48:54</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -48640,7 +48652,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>2026-09-28 22:18:37</t>
+          <t>2026-09-28 22:48:54</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -48866,7 +48878,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -48881,17 +48893,17 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>2026-09-28 22:18:40</t>
+          <t>2026-09-28 22:48:57</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
       <c r="K217" t="n">
@@ -48906,17 +48918,17 @@
       <c r="N217" t="inlineStr"/>
       <c r="O217" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>151</t>
         </is>
       </c>
       <c r="P217" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q217" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>59</t>
         </is>
       </c>
       <c r="R217" t="inlineStr">
@@ -48931,7 +48943,7 @@
       </c>
       <c r="T217" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="U217" t="inlineStr">
@@ -48941,56 +48953,56 @@
       </c>
       <c r="V217" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="W217" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="X217" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="Y217" t="inlineStr"/>
       <c r="Z217" t="inlineStr"/>
       <c r="AA217" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AB217" t="inlineStr"/>
       <c r="AC217" t="inlineStr"/>
       <c r="AD217" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AE217" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="AF217" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="AG217" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="AH217" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="AI217" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>59</t>
         </is>
       </c>
       <c r="AJ217" t="inlineStr">
@@ -49000,37 +49012,37 @@
       </c>
       <c r="AK217" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AL217" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AM217" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="AN217" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="AO217" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="AP217" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="AQ217" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>59</t>
         </is>
       </c>
       <c r="AR217" t="inlineStr">
@@ -49040,22 +49052,22 @@
       </c>
       <c r="AS217" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AT217" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AU217" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>151</t>
         </is>
       </c>
       <c r="AV217" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AW217" t="inlineStr">
@@ -49065,12 +49077,12 @@
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>151</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AZ217" t="inlineStr">
@@ -49122,7 +49134,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>2026-09-28 22:18:42</t>
+          <t>2026-09-28 22:48:59</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -49363,7 +49375,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>2026-09-28 22:18:42</t>
+          <t>2026-09-28 22:48:59</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -49604,7 +49616,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>2026-09-28 22:18:42</t>
+          <t>2026-09-28 22:48:59</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -49845,7 +49857,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>2026-09-28 22:18:42</t>
+          <t>2026-09-28 22:48:59</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -50071,7 +50083,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -50086,17 +50098,17 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>2026-09-28 22:18:44</t>
+          <t>2026-09-28 22:49:02</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
       <c r="K222" t="n">
@@ -50109,7 +50121,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>100</t>
         </is>
       </c>
       <c r="N222" t="inlineStr"/>
@@ -50117,12 +50129,12 @@
       <c r="P222" t="inlineStr"/>
       <c r="Q222" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>68</t>
         </is>
       </c>
       <c r="R222" t="inlineStr">
         <is>
-          <t>1017.9</t>
+          <t>1017.6</t>
         </is>
       </c>
       <c r="S222" t="inlineStr">
@@ -50132,7 +50144,7 @@
       </c>
       <c r="T222" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="U222" t="inlineStr">
@@ -50142,96 +50154,96 @@
       </c>
       <c r="V222" t="inlineStr">
         <is>
+          <t>23.6</t>
+        </is>
+      </c>
+      <c r="W222" t="inlineStr">
+        <is>
+          <t>23.4</t>
+        </is>
+      </c>
+      <c r="X222" t="inlineStr">
+        <is>
           <t>23.7</t>
         </is>
       </c>
-      <c r="W222" t="inlineStr">
-        <is>
-          <t>23.6</t>
-        </is>
-      </c>
-      <c r="X222" t="inlineStr">
-        <is>
-          <t>23.7</t>
-        </is>
-      </c>
       <c r="Y222" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="Z222" t="inlineStr"/>
       <c r="AA222" t="inlineStr"/>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AC222" t="inlineStr"/>
       <c r="AD222" t="inlineStr"/>
       <c r="AE222" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:00 - 22:30</t>
         </is>
       </c>
       <c r="AF222" t="inlineStr">
         <is>
+          <t>23.6</t>
+        </is>
+      </c>
+      <c r="AG222" t="inlineStr">
+        <is>
           <t>23.7</t>
         </is>
       </c>
-      <c r="AG222" t="inlineStr">
+      <c r="AH222" t="inlineStr">
+        <is>
+          <t>23.4</t>
+        </is>
+      </c>
+      <c r="AI222" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="AJ222" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK222" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
+      <c r="AL222" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AM222" t="inlineStr">
+        <is>
+          <t>22:00 - 22:30</t>
+        </is>
+      </c>
+      <c r="AN222" t="inlineStr">
+        <is>
+          <t>23.6</t>
+        </is>
+      </c>
+      <c r="AO222" t="inlineStr">
         <is>
           <t>23.7</t>
         </is>
       </c>
-      <c r="AH222" t="inlineStr">
-        <is>
-          <t>23.6</t>
-        </is>
-      </c>
-      <c r="AI222" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="AJ222" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK222" t="inlineStr">
-        <is>
-          <t>6.8</t>
-        </is>
-      </c>
-      <c r="AL222" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="AM222" t="inlineStr">
-        <is>
-          <t>21:30 - 22:00</t>
-        </is>
-      </c>
-      <c r="AN222" t="inlineStr">
-        <is>
-          <t>23.7</t>
-        </is>
-      </c>
-      <c r="AO222" t="inlineStr">
-        <is>
-          <t>23.7</t>
-        </is>
-      </c>
       <c r="AP222" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="AQ222" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>68</t>
         </is>
       </c>
       <c r="AR222" t="inlineStr">
@@ -50241,22 +50253,22 @@
       </c>
       <c r="AS222" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="AT222" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AU222" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AV222" t="inlineStr">
         <is>
-          <t>1017.9</t>
+          <t>1017.6</t>
         </is>
       </c>
       <c r="AW222" t="inlineStr">
@@ -50266,12 +50278,12 @@
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr">
         <is>
-          <t>1017.9</t>
+          <t>1017.6</t>
         </is>
       </c>
       <c r="AZ222" t="inlineStr">
@@ -50319,7 +50331,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>2026-09-28 22:18:46</t>
+          <t>2026-09-28 22:49:03</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -50552,7 +50564,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>2026-09-28 22:18:46</t>
+          <t>2026-09-28 22:49:03</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -50785,7 +50797,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>2026-09-28 22:18:46</t>
+          <t>2026-09-28 22:49:03</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -51018,7 +51030,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>2026-09-28 22:18:46</t>
+          <t>2026-09-28 22:49:03</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -51285,7 +51297,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
     </row>
@@ -51315,7 +51327,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
     </row>
@@ -51345,7 +51357,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
     </row>
@@ -51375,7 +51387,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
     </row>
@@ -51405,7 +51417,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
     </row>
@@ -51435,7 +51447,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
     </row>
@@ -51465,7 +51477,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
     </row>
@@ -51495,7 +51507,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
     </row>
@@ -51525,7 +51537,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
     </row>
@@ -51555,7 +51567,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
     </row>
@@ -51585,7 +51597,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
     </row>
@@ -51615,7 +51627,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
     </row>
@@ -51645,7 +51657,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
     </row>
@@ -51675,7 +51687,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
     </row>
@@ -51705,7 +51717,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
     </row>
@@ -51735,7 +51747,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
     </row>
@@ -51765,7 +51777,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
     </row>
@@ -51795,7 +51807,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
     </row>
@@ -51825,7 +51837,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
     </row>
@@ -51855,7 +51867,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
     </row>
@@ -51885,7 +51897,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
     </row>
@@ -51915,7 +51927,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
     </row>
@@ -51945,7 +51957,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
     </row>
@@ -51975,7 +51987,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
     </row>
@@ -52005,7 +52017,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
     </row>
@@ -52035,7 +52047,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
     </row>
@@ -52065,7 +52077,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
     </row>
@@ -52095,7 +52107,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
     </row>
@@ -52125,7 +52137,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
     </row>
@@ -52155,7 +52167,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
     </row>
@@ -52185,7 +52197,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
     </row>
@@ -52215,7 +52227,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
     </row>
@@ -52245,7 +52257,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
     </row>
@@ -52275,7 +52287,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
     </row>
@@ -52305,7 +52317,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
     </row>
@@ -52335,7 +52347,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
     </row>
@@ -52365,7 +52377,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
     </row>
@@ -52395,7 +52407,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
     </row>
@@ -52425,7 +52437,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
     </row>
@@ -52455,7 +52467,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
     </row>
@@ -52485,7 +52497,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
     </row>
@@ -52515,7 +52527,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
     </row>
@@ -52545,7 +52557,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
     </row>
@@ -52575,7 +52587,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
     </row>
@@ -52605,7 +52617,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-09-28T21:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-09-28T22:00Z</t>
         </is>
       </c>
     </row>

--- a/src/data/resum_periode_meteocat.xlsx
+++ b/src/data/resum_periode_meteocat.xlsx
@@ -722,17 +722,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-09-28 22:45:29</t>
+          <t>2026-09-28 23:15:34</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -919,7 +919,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-28 22:45:31</t>
+          <t>2026-09-28 23:15:36</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-09-28 22:45:31</t>
+          <t>2026-09-28 23:15:36</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-09-28 22:45:31</t>
+          <t>2026-09-28 23:15:36</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-28 22:45:31</t>
+          <t>2026-09-28 23:15:36</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-28 22:45:33</t>
+          <t>2026-09-28 23:15:38</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -1732,7 +1732,7 @@
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>126</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1763,98 +1763,98 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
+          <t>8.9</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
           <t>9.1</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>9.3</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
+          <t>8.9</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>22:30 - 23:00</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
           <t>9.1</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>8.9</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>7.9</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>22:00 - 22:30</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>9.2</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>9.3</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>9.1</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
       <c r="AR7" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -1867,17 +1867,17 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>126</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>126</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-28 22:45:35</t>
+          <t>2026-09-28 23:15:40</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-09-28 22:45:35</t>
+          <t>2026-09-28 23:15:40</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-09-28 22:45:35</t>
+          <t>2026-09-28 23:15:40</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-09-28 22:45:35</t>
+          <t>2026-09-28 23:15:40</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2872,17 +2872,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-09-28 22:45:38</t>
+          <t>2026-09-28 23:15:43</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>293</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2903,7 +2903,7 @@
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>94</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -2943,26 +2943,26 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>94</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2987,22 +2987,22 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>293</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>94</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -3027,17 +3027,17 @@
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>293</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-09-28 22:45:40</t>
+          <t>2026-09-28 23:15:45</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-09-28 22:45:40</t>
+          <t>2026-09-28 23:15:45</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-09-28 22:45:40</t>
+          <t>2026-09-28 23:15:45</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-09-28 22:45:40</t>
+          <t>2026-09-28 23:15:45</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -4037,17 +4037,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-09-28 22:45:43</t>
+          <t>2026-09-28 23:15:48</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-09-28 22:45:45</t>
+          <t>2026-09-28 23:15:49</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-09-28 22:45:45</t>
+          <t>2026-09-28 23:15:49</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-09-28 22:45:45</t>
+          <t>2026-09-28 23:15:49</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-09-28 22:45:45</t>
+          <t>2026-09-28 23:15:49</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -5202,17 +5202,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-09-28 22:45:48</t>
+          <t>2026-09-28 23:15:52</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -5225,7 +5225,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>159</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -5233,12 +5233,12 @@
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>86</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1019.4</t>
+          <t>1019.5</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -5258,17 +5258,17 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -5280,34 +5280,34 @@
       <c r="AA22" t="inlineStr"/>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr"/>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>86</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
@@ -5322,32 +5322,32 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>159</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>86</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
@@ -5362,17 +5362,17 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>159</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1019.4</t>
+          <t>1019.5</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>1019.4</t>
+          <t>1019.5</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-09-28 22:45:50</t>
+          <t>2026-09-28 23:15:54</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-09-28 22:45:50</t>
+          <t>2026-09-28 23:15:54</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-09-28 22:45:50</t>
+          <t>2026-09-28 23:15:54</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-09-28 22:45:50</t>
+          <t>2026-09-28 23:15:54</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -6352,7 +6352,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -6367,17 +6367,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-09-28 22:45:53</t>
+          <t>2026-09-28 23:15:57</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>129</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -6398,12 +6398,12 @@
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>71</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1018.8</t>
+          <t>1018.7</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -6423,96 +6423,96 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>25.1</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
           <t>25.3</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>25.3</t>
-        </is>
-      </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr"/>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr"/>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
           <t>25.3</t>
         </is>
       </c>
-      <c r="AG27" t="inlineStr">
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>25.1</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>22:30 - 23:00</t>
+        </is>
+      </c>
+      <c r="AN27" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
         <is>
           <t>25.3</t>
         </is>
       </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>6.8</t>
-        </is>
-      </c>
-      <c r="AL27" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>22:00 - 22:30</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>25.3</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>25.3</t>
-        </is>
-      </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
@@ -6522,22 +6522,22 @@
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>129</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>1018.8</t>
+          <t>1018.7</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
@@ -6547,12 +6547,12 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>1018.8</t>
+          <t>1018.7</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
@@ -6600,7 +6600,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-09-28 22:45:55</t>
+          <t>2026-09-28 23:15:59</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -6833,7 +6833,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-09-28 22:45:55</t>
+          <t>2026-09-28 23:15:59</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-09-28 22:45:55</t>
+          <t>2026-09-28 23:15:59</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-09-28 22:45:55</t>
+          <t>2026-09-28 23:15:59</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -7532,17 +7532,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-09-28 22:45:58</t>
+          <t>2026-09-28 23:16:02</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -7555,7 +7555,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>152</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -7563,12 +7563,12 @@
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>85</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1018.9</t>
+          <t>1018.8</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -7578,7 +7578,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -7588,7 +7588,7 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
@@ -7598,126 +7598,126 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr"/>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr"/>
       <c r="AD32" t="inlineStr"/>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
+          <t>21.1</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>21.1</t>
+        </is>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>21.1</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>22:30 - 23:00</t>
+        </is>
+      </c>
+      <c r="AN32" t="inlineStr">
+        <is>
+          <t>21.1</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>21.1</t>
+        </is>
+      </c>
+      <c r="AP32" t="inlineStr">
+        <is>
+          <t>21.1</t>
+        </is>
+      </c>
+      <c r="AQ32" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
           <t>21.2</t>
         </is>
       </c>
-      <c r="AG32" t="inlineStr">
-        <is>
-          <t>21.4</t>
-        </is>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>21.1</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>9.7</t>
-        </is>
-      </c>
-      <c r="AL32" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>22:00 - 22:30</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
+      <c r="AV32" t="inlineStr">
+        <is>
+          <t>1018.8</t>
+        </is>
+      </c>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
         <is>
           <t>21.2</t>
         </is>
       </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>21.4</t>
-        </is>
-      </c>
-      <c r="AP32" t="inlineStr">
-        <is>
-          <t>21.1</t>
-        </is>
-      </c>
-      <c r="AQ32" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS32" t="inlineStr">
-        <is>
-          <t>9.7</t>
-        </is>
-      </c>
-      <c r="AT32" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>20.2</t>
-        </is>
-      </c>
-      <c r="AV32" t="inlineStr">
-        <is>
-          <t>1018.9</t>
-        </is>
-      </c>
-      <c r="AW32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>20.2</t>
-        </is>
-      </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>1018.9</t>
+          <t>1018.8</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
@@ -7765,7 +7765,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:00</t>
+          <t>2026-09-28 23:16:04</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:00</t>
+          <t>2026-09-28 23:16:04</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:00</t>
+          <t>2026-09-28 23:16:04</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -8464,7 +8464,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:00</t>
+          <t>2026-09-28 23:16:04</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -8697,17 +8697,17 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:03</t>
+          <t>2026-09-28 23:16:06</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -8721,7 +8721,7 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>281</t>
         </is>
       </c>
       <c r="O37" t="inlineStr"/>
@@ -8739,7 +8739,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -8749,7 +8749,7 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
@@ -8765,25 +8765,25 @@
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr"/>
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr"/>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AG37" t="inlineStr">
@@ -8808,22 +8808,22 @@
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>281</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
@@ -8848,17 +8848,17 @@
       </c>
       <c r="AS37" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>281</t>
         </is>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
@@ -8869,7 +8869,7 @@
       <c r="AW37" t="inlineStr"/>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -8918,7 +8918,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:04</t>
+          <t>2026-09-28 23:16:08</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:04</t>
+          <t>2026-09-28 23:16:08</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -9360,7 +9360,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:04</t>
+          <t>2026-09-28 23:16:08</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:04</t>
+          <t>2026-09-28 23:16:08</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -9787,7 +9787,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -9802,17 +9802,17 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:07</t>
+          <t>2026-09-28 23:16:11</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -9826,14 +9826,14 @@
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>82</t>
         </is>
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>93</t>
         </is>
       </c>
       <c r="R42" t="inlineStr"/>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -9854,56 +9854,56 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
+          <t>19.8</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>19.3</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
           <t>20.4</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>20.3</t>
-        </is>
-      </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>20.6</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr"/>
       <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr"/>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
+          <t>19.8</t>
+        </is>
+      </c>
+      <c r="AG42" t="inlineStr">
+        <is>
           <t>20.4</t>
         </is>
       </c>
-      <c r="AG42" t="inlineStr">
-        <is>
-          <t>20.6</t>
-        </is>
-      </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>93</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
@@ -9913,37 +9913,37 @@
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="AL42" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
+          <t>19.8</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
           <t>20.4</t>
         </is>
       </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>20.6</t>
-        </is>
-      </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="AQ42" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>93</t>
         </is>
       </c>
       <c r="AR42" t="inlineStr">
@@ -9953,17 +9953,17 @@
       </c>
       <c r="AS42" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="AV42" t="inlineStr">
@@ -9974,7 +9974,7 @@
       <c r="AW42" t="inlineStr"/>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -10023,7 +10023,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:09</t>
+          <t>2026-09-28 23:16:12</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -10244,7 +10244,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:09</t>
+          <t>2026-09-28 23:16:12</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:09</t>
+          <t>2026-09-28 23:16:12</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -10686,7 +10686,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:09</t>
+          <t>2026-09-28 23:16:12</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -10892,7 +10892,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -10907,17 +10907,17 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:12</t>
+          <t>2026-09-28 23:16:15</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -10934,7 +10934,7 @@
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>88</t>
         </is>
       </c>
       <c r="R47" t="inlineStr"/>
@@ -10945,23 +10945,23 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="U47" t="inlineStr"/>
       <c r="V47" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>15.6</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>16.1</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr"/>
@@ -10972,27 +10972,27 @@
       <c r="AD47" t="inlineStr"/>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>15.6</t>
         </is>
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>16.1</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
@@ -11004,27 +11004,27 @@
       <c r="AL47" t="inlineStr"/>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>15.6</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>16.1</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="AQ47" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AR47" t="inlineStr">
@@ -11080,7 +11080,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:14</t>
+          <t>2026-09-28 23:16:17</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -11253,7 +11253,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:14</t>
+          <t>2026-09-28 23:16:17</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -11426,7 +11426,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:14</t>
+          <t>2026-09-28 23:16:17</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -11599,7 +11599,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:14</t>
+          <t>2026-09-28 23:16:17</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -11772,17 +11772,17 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:16</t>
+          <t>2026-09-28 23:16:19</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
       <c r="K52" t="n">
@@ -11810,23 +11810,23 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr"/>
@@ -11837,22 +11837,22 @@
       <c r="AD52" t="inlineStr"/>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="AI52" t="inlineStr">
@@ -11869,22 +11869,22 @@
       <c r="AL52" t="inlineStr"/>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AN52" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="AQ52" t="inlineStr">
@@ -11945,7 +11945,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:18</t>
+          <t>2026-09-28 23:16:21</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:18</t>
+          <t>2026-09-28 23:16:21</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -12291,7 +12291,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:18</t>
+          <t>2026-09-28 23:16:21</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -12464,7 +12464,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:18</t>
+          <t>2026-09-28 23:16:21</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -12622,7 +12622,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -12637,17 +12637,17 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:21</t>
+          <t>2026-09-28 23:16:23</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
       <c r="K57" t="n">
@@ -12660,7 +12660,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>237</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -12677,7 +12677,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1019.3</t>
+          <t>1019.4</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -12687,7 +12687,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -12697,51 +12697,51 @@
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>14.9</t>
+          <t>14.6</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr"/>
       <c r="AA57" t="inlineStr"/>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr"/>
       <c r="AD57" t="inlineStr"/>
       <c r="AE57" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>14.9</t>
+          <t>14.6</t>
         </is>
       </c>
       <c r="AI57" t="inlineStr">
@@ -12761,27 +12761,27 @@
       </c>
       <c r="AL57" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AN57" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>14.9</t>
+          <t>14.6</t>
         </is>
       </c>
       <c r="AQ57" t="inlineStr">
@@ -12801,37 +12801,37 @@
       </c>
       <c r="AT57" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>237</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>1019.3</t>
+          <t>1019.4</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>237</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>1019.3</t>
+          <t>1019.4</t>
         </is>
       </c>
       <c r="BA57" t="inlineStr">
@@ -12878,7 +12878,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:23</t>
+          <t>2026-09-28 23:16:25</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -13119,7 +13119,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:23</t>
+          <t>2026-09-28 23:16:25</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:23</t>
+          <t>2026-09-28 23:16:25</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -13601,7 +13601,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:23</t>
+          <t>2026-09-28 23:16:25</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -13827,7 +13827,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -13842,17 +13842,17 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:26</t>
+          <t>2026-09-28 23:16:27</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
       <c r="K62" t="n">
@@ -13865,7 +13865,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>131</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -13873,7 +13873,7 @@
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>79</t>
         </is>
       </c>
       <c r="R62" t="inlineStr"/>
@@ -13884,7 +13884,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -13909,21 +13909,21 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="inlineStr"/>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr"/>
       <c r="AD62" t="inlineStr"/>
       <c r="AE62" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AF62" t="inlineStr">
@@ -13943,7 +13943,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AJ62" t="inlineStr">
@@ -13953,17 +13953,17 @@
       </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AL62" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>131</t>
         </is>
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AN62" t="inlineStr">
@@ -13983,7 +13983,7 @@
       </c>
       <c r="AQ62" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AR62" t="inlineStr">
@@ -13993,17 +13993,17 @@
       </c>
       <c r="AS62" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>131</t>
         </is>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
@@ -14014,7 +14014,7 @@
       <c r="AW62" t="inlineStr"/>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -14063,7 +14063,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:28</t>
+          <t>2026-09-28 23:16:29</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -14284,7 +14284,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:28</t>
+          <t>2026-09-28 23:16:29</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -14505,7 +14505,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:28</t>
+          <t>2026-09-28 23:16:29</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -14726,7 +14726,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:28</t>
+          <t>2026-09-28 23:16:29</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -14932,7 +14932,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -14947,17 +14947,17 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:31</t>
+          <t>2026-09-28 23:16:31</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
       <c r="K67" t="n">
@@ -14974,7 +14974,7 @@
       <c r="P67" t="inlineStr"/>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>95</t>
         </is>
       </c>
       <c r="R67" t="inlineStr"/>
@@ -14985,23 +14985,23 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="U67" t="inlineStr"/>
       <c r="V67" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr"/>
@@ -15012,27 +15012,27 @@
       <c r="AD67" t="inlineStr"/>
       <c r="AE67" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AF67" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="AG67" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>95</t>
         </is>
       </c>
       <c r="AJ67" t="inlineStr">
@@ -15044,27 +15044,27 @@
       <c r="AL67" t="inlineStr"/>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AN67" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="AQ67" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>95</t>
         </is>
       </c>
       <c r="AR67" t="inlineStr">
@@ -15120,7 +15120,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:33</t>
+          <t>2026-09-28 23:16:33</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -15293,7 +15293,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:33</t>
+          <t>2026-09-28 23:16:33</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -15466,7 +15466,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:33</t>
+          <t>2026-09-28 23:16:33</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -15639,7 +15639,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:33</t>
+          <t>2026-09-28 23:16:33</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -15797,7 +15797,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -15812,17 +15812,17 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:36</t>
+          <t>2026-09-28 23:16:36</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
       <c r="K72" t="n">
@@ -15835,7 +15835,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>297</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
@@ -15843,7 +15843,7 @@
       <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>93</t>
         </is>
       </c>
       <c r="R72" t="inlineStr"/>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -15864,56 +15864,56 @@
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="W72" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr"/>
       <c r="AA72" t="inlineStr"/>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr"/>
       <c r="AD72" t="inlineStr"/>
       <c r="AE72" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AF72" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="AG72" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>93</t>
         </is>
       </c>
       <c r="AJ72" t="inlineStr">
@@ -15924,32 +15924,32 @@
       <c r="AK72" t="inlineStr"/>
       <c r="AL72" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AN72" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="AQ72" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>93</t>
         </is>
       </c>
       <c r="AR72" t="inlineStr">
@@ -15960,17 +15960,17 @@
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>297</t>
         </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="AW72" t="inlineStr">
@@ -15980,12 +15980,12 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>297</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="AZ72" t="inlineStr">
@@ -16033,7 +16033,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:38</t>
+          <t>2026-09-28 23:16:38</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -16266,7 +16266,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:38</t>
+          <t>2026-09-28 23:16:38</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -16499,7 +16499,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:38</t>
+          <t>2026-09-28 23:16:38</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -16732,7 +16732,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:38</t>
+          <t>2026-09-28 23:16:38</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -16950,7 +16950,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -16965,17 +16965,17 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:41</t>
+          <t>2026-09-28 23:16:40</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
       <c r="K77" t="n">
@@ -16988,7 +16988,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>195</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -17011,7 +17011,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -17021,53 +17021,53 @@
       </c>
       <c r="V77" t="inlineStr">
         <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
           <t>11.7</t>
         </is>
       </c>
-      <c r="W77" t="inlineStr">
-        <is>
-          <t>11.3</t>
-        </is>
-      </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr"/>
       <c r="AA77" t="inlineStr"/>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>32.8</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr"/>
       <c r="AD77" t="inlineStr"/>
       <c r="AE77" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AF77" t="inlineStr">
         <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="AG77" t="inlineStr">
+        <is>
+          <t>12.4</t>
+        </is>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
           <t>11.7</t>
         </is>
       </c>
-      <c r="AG77" t="inlineStr">
-        <is>
-          <t>12.1</t>
-        </is>
-      </c>
-      <c r="AH77" t="inlineStr">
-        <is>
-          <t>11.3</t>
-        </is>
-      </c>
       <c r="AI77" t="inlineStr">
         <is>
           <t>100</t>
@@ -17085,29 +17085,29 @@
       </c>
       <c r="AL77" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AN77" t="inlineStr">
         <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>12.4</t>
+        </is>
+      </c>
+      <c r="AP77" t="inlineStr">
+        <is>
           <t>11.7</t>
         </is>
       </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>12.1</t>
-        </is>
-      </c>
-      <c r="AP77" t="inlineStr">
-        <is>
-          <t>11.3</t>
-        </is>
-      </c>
       <c r="AQ77" t="inlineStr">
         <is>
           <t>100</t>
@@ -17125,17 +17125,17 @@
       </c>
       <c r="AT77" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>195</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>32.8</t>
         </is>
       </c>
       <c r="AW77" t="inlineStr">
@@ -17145,12 +17145,12 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>195</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>32.8</t>
         </is>
       </c>
       <c r="AZ77" t="inlineStr">
@@ -17198,7 +17198,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:43</t>
+          <t>2026-09-28 23:16:42</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -17431,7 +17431,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:43</t>
+          <t>2026-09-28 23:16:42</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -17664,7 +17664,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:43</t>
+          <t>2026-09-28 23:16:42</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -17897,7 +17897,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:43</t>
+          <t>2026-09-28 23:16:42</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -18115,7 +18115,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -18130,17 +18130,17 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:46</t>
+          <t>2026-09-28 23:16:45</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
       <c r="K82" t="n">
@@ -18153,7 +18153,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>295</t>
         </is>
       </c>
       <c r="N82" t="inlineStr"/>
@@ -18161,7 +18161,7 @@
       <c r="P82" t="inlineStr"/>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>99</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
@@ -18171,12 +18171,12 @@
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -18186,17 +18186,17 @@
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="W82" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="Y82" t="inlineStr">
@@ -18208,39 +18208,39 @@
       <c r="AA82" t="inlineStr"/>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr"/>
       <c r="AD82" t="inlineStr"/>
       <c r="AE82" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AF82" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="AG82" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -18250,37 +18250,37 @@
       </c>
       <c r="AL82" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>295</t>
         </is>
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AN82" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="AQ82" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AR82" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr">
@@ -18290,12 +18290,12 @@
       </c>
       <c r="AT82" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>295</t>
         </is>
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AV82" t="inlineStr">
@@ -18310,7 +18310,7 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -18363,7 +18363,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:48</t>
+          <t>2026-09-28 23:16:47</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -18596,7 +18596,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:48</t>
+          <t>2026-09-28 23:16:47</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -18829,7 +18829,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:48</t>
+          <t>2026-09-28 23:16:47</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -19062,7 +19062,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:48</t>
+          <t>2026-09-28 23:16:47</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -19280,7 +19280,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -19295,17 +19295,17 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:51</t>
+          <t>2026-09-28 23:16:49</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
       <c r="K87" t="n">
@@ -19318,7 +19318,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>82</t>
         </is>
       </c>
       <c r="N87" t="inlineStr"/>
@@ -19326,7 +19326,7 @@
       <c r="P87" t="inlineStr"/>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>94</t>
         </is>
       </c>
       <c r="R87" t="inlineStr"/>
@@ -19337,7 +19337,7 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
@@ -19347,56 +19347,56 @@
       </c>
       <c r="V87" t="inlineStr">
         <is>
+          <t>15.2</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>15.1</t>
+        </is>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
           <t>15.3</t>
         </is>
       </c>
-      <c r="W87" t="inlineStr">
-        <is>
-          <t>15.0</t>
-        </is>
-      </c>
-      <c r="X87" t="inlineStr">
-        <is>
-          <t>15.4</t>
-        </is>
-      </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="Z87" t="inlineStr"/>
       <c r="AA87" t="inlineStr"/>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr"/>
       <c r="AD87" t="inlineStr"/>
       <c r="AE87" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AF87" t="inlineStr">
         <is>
+          <t>15.2</t>
+        </is>
+      </c>
+      <c r="AG87" t="inlineStr">
+        <is>
           <t>15.3</t>
         </is>
       </c>
-      <c r="AG87" t="inlineStr">
-        <is>
-          <t>15.4</t>
-        </is>
-      </c>
       <c r="AH87" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>94</t>
         </is>
       </c>
       <c r="AJ87" t="inlineStr">
@@ -19406,37 +19406,37 @@
       </c>
       <c r="AK87" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AL87" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AN87" t="inlineStr">
         <is>
+          <t>15.2</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
           <t>15.3</t>
         </is>
       </c>
-      <c r="AO87" t="inlineStr">
-        <is>
-          <t>15.4</t>
-        </is>
-      </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="AQ87" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>94</t>
         </is>
       </c>
       <c r="AR87" t="inlineStr">
@@ -19446,17 +19446,17 @@
       </c>
       <c r="AS87" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
@@ -19467,7 +19467,7 @@
       <c r="AW87" t="inlineStr"/>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -19516,7 +19516,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:53</t>
+          <t>2026-09-28 23:16:50</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -19737,7 +19737,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:53</t>
+          <t>2026-09-28 23:16:50</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -19958,7 +19958,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:53</t>
+          <t>2026-09-28 23:16:50</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -20179,7 +20179,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:53</t>
+          <t>2026-09-28 23:16:50</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -20385,7 +20385,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -20400,17 +20400,17 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:56</t>
+          <t>2026-09-28 23:16:53</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
       <c r="K92" t="n">
@@ -20423,7 +20423,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>161</t>
         </is>
       </c>
       <c r="N92" t="inlineStr"/>
@@ -20442,7 +20442,7 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
@@ -20452,51 +20452,51 @@
       </c>
       <c r="V92" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="W92" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="Z92" t="inlineStr"/>
       <c r="AA92" t="inlineStr"/>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>22.7</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr"/>
       <c r="AD92" t="inlineStr"/>
       <c r="AE92" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AF92" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AG92" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="AI92" t="inlineStr">
@@ -20512,27 +20512,27 @@
       <c r="AK92" t="inlineStr"/>
       <c r="AL92" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="AM92" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AN92" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="AQ92" t="inlineStr">
@@ -20548,17 +20548,17 @@
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>161</t>
         </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>22.7</t>
         </is>
       </c>
       <c r="AW92" t="inlineStr">
@@ -20568,12 +20568,12 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>161</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>22.7</t>
         </is>
       </c>
       <c r="AZ92" t="inlineStr">
@@ -20621,7 +20621,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:58</t>
+          <t>2026-09-28 23:16:55</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -20854,7 +20854,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:58</t>
+          <t>2026-09-28 23:16:55</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -21087,7 +21087,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:58</t>
+          <t>2026-09-28 23:16:55</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -21320,7 +21320,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-09-28 22:46:58</t>
+          <t>2026-09-28 23:16:55</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -21553,17 +21553,17 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:01</t>
+          <t>2026-09-28 23:16:58</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
       <c r="K97" t="n">
@@ -21786,7 +21786,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:02</t>
+          <t>2026-09-28 23:17:00</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -22019,7 +22019,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:02</t>
+          <t>2026-09-28 23:17:00</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -22252,7 +22252,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:02</t>
+          <t>2026-09-28 23:17:00</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -22485,7 +22485,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:02</t>
+          <t>2026-09-28 23:17:00</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -22703,7 +22703,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -22718,17 +22718,17 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:05</t>
+          <t>2026-09-28 23:17:02</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
       <c r="K102" t="n">
@@ -22743,7 +22743,7 @@
       <c r="N102" t="inlineStr"/>
       <c r="O102" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>264</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
@@ -22779,31 +22779,31 @@
       </c>
       <c r="W102" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="Y102" t="inlineStr"/>
       <c r="Z102" t="inlineStr"/>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr"/>
       <c r="AC102" t="inlineStr"/>
       <c r="AD102" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="AE102" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AF102" t="inlineStr">
@@ -22813,12 +22813,12 @@
       </c>
       <c r="AG102" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="AI102" t="inlineStr">
@@ -22838,12 +22838,12 @@
       </c>
       <c r="AL102" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AN102" t="inlineStr">
@@ -22853,12 +22853,12 @@
       </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="AQ102" t="inlineStr">
@@ -22878,17 +22878,17 @@
       </c>
       <c r="AT102" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>264</t>
         </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="AW102" t="inlineStr">
@@ -22898,12 +22898,12 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>264</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="AZ102" t="inlineStr">
@@ -22951,7 +22951,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:07</t>
+          <t>2026-09-28 23:17:04</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:07</t>
+          <t>2026-09-28 23:17:04</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -23417,7 +23417,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:07</t>
+          <t>2026-09-28 23:17:04</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -23650,7 +23650,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:07</t>
+          <t>2026-09-28 23:17:04</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -23868,7 +23868,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -23883,17 +23883,17 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:10</t>
+          <t>2026-09-28 23:17:07</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
       <c r="K107" t="n">
@@ -23908,7 +23908,7 @@
       <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>255</t>
         </is>
       </c>
       <c r="P107" t="inlineStr"/>
@@ -23925,7 +23925,7 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
@@ -23935,7 +23935,7 @@
       </c>
       <c r="V107" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="W107" t="inlineStr">
@@ -23945,36 +23945,36 @@
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="Y107" t="inlineStr"/>
       <c r="Z107" t="inlineStr"/>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr"/>
       <c r="AC107" t="inlineStr"/>
       <c r="AD107" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="AE107" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AF107" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="AG107" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="AH107" t="inlineStr">
@@ -23995,22 +23995,22 @@
       <c r="AK107" t="inlineStr"/>
       <c r="AL107" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AN107" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="AP107" t="inlineStr">
@@ -24031,17 +24031,17 @@
       <c r="AS107" t="inlineStr"/>
       <c r="AT107" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>255</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="AW107" t="inlineStr">
@@ -24051,12 +24051,12 @@
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>255</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="AZ107" t="inlineStr">
@@ -24104,7 +24104,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:12</t>
+          <t>2026-09-28 23:17:08</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -24337,7 +24337,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:12</t>
+          <t>2026-09-28 23:17:08</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -24570,7 +24570,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:12</t>
+          <t>2026-09-28 23:17:08</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -24803,7 +24803,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:12</t>
+          <t>2026-09-28 23:17:08</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -25036,17 +25036,17 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:15</t>
+          <t>2026-09-28 23:17:11</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
       <c r="K112" t="n">
@@ -25269,7 +25269,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:17</t>
+          <t>2026-09-28 23:17:13</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -25502,7 +25502,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:17</t>
+          <t>2026-09-28 23:17:13</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -25735,7 +25735,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:17</t>
+          <t>2026-09-28 23:17:13</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -25968,7 +25968,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:17</t>
+          <t>2026-09-28 23:17:13</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -26186,7 +26186,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -26201,17 +26201,17 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:20</t>
+          <t>2026-09-28 23:17:16</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
       <c r="K117" t="n">
@@ -26226,7 +26226,7 @@
       <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>238</t>
         </is>
       </c>
       <c r="P117" t="inlineStr"/>
@@ -26243,7 +26243,7 @@
       </c>
       <c r="T117" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="U117" t="inlineStr">
@@ -26253,12 +26253,12 @@
       </c>
       <c r="V117" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="W117" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="X117" t="inlineStr">
@@ -26277,17 +26277,17 @@
       <c r="AC117" t="inlineStr"/>
       <c r="AD117" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="AE117" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AF117" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="AG117" t="inlineStr">
@@ -26297,7 +26297,7 @@
       </c>
       <c r="AH117" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="AI117" t="inlineStr">
@@ -26318,12 +26318,12 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AN117" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="AO117" t="inlineStr">
@@ -26333,7 +26333,7 @@
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="AQ117" t="inlineStr">
@@ -26354,12 +26354,12 @@
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>238</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
@@ -26369,12 +26369,12 @@
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>238</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
@@ -26422,7 +26422,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:22</t>
+          <t>2026-09-28 23:17:17</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -26655,7 +26655,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:22</t>
+          <t>2026-09-28 23:17:17</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -26888,7 +26888,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:22</t>
+          <t>2026-09-28 23:17:17</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -27121,7 +27121,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:22</t>
+          <t>2026-09-28 23:17:17</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -27339,7 +27339,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -27354,17 +27354,17 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:25</t>
+          <t>2026-09-28 23:17:20</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
       <c r="K122" t="n">
@@ -27377,7 +27377,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>224</t>
         </is>
       </c>
       <c r="N122" t="inlineStr"/>
@@ -27394,7 +27394,7 @@
       </c>
       <c r="R122" t="inlineStr">
         <is>
-          <t>1019.6</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="S122" t="inlineStr">
@@ -27404,7 +27404,7 @@
       </c>
       <c r="T122" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="U122" t="inlineStr">
@@ -27414,51 +27414,51 @@
       </c>
       <c r="V122" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="W122" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>12.7</t>
         </is>
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="Z122" t="inlineStr"/>
       <c r="AA122" t="inlineStr"/>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AC122" t="inlineStr"/>
       <c r="AD122" t="inlineStr"/>
       <c r="AE122" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AF122" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AG122" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>12.7</t>
         </is>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="AI122" t="inlineStr">
@@ -27478,27 +27478,27 @@
       </c>
       <c r="AL122" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AM122" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AN122" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>12.7</t>
         </is>
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="AQ122" t="inlineStr">
@@ -27518,37 +27518,37 @@
       </c>
       <c r="AT122" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>224</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>1019.6</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>224</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>1019.6</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="BA122" t="inlineStr">
@@ -27595,7 +27595,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:27</t>
+          <t>2026-09-28 23:17:22</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -27836,7 +27836,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:27</t>
+          <t>2026-09-28 23:17:22</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -28077,7 +28077,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:27</t>
+          <t>2026-09-28 23:17:22</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -28318,7 +28318,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:27</t>
+          <t>2026-09-28 23:17:22</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -28544,7 +28544,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -28559,17 +28559,17 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:30</t>
+          <t>2026-09-28 23:17:25</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
       <c r="K127" t="n">
@@ -28582,7 +28582,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>288</t>
         </is>
       </c>
       <c r="N127" t="inlineStr"/>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>85</t>
         </is>
       </c>
       <c r="R127" t="inlineStr"/>
@@ -28605,7 +28605,7 @@
       </c>
       <c r="T127" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="U127" t="inlineStr">
@@ -28615,121 +28615,121 @@
       </c>
       <c r="V127" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>8.9</t>
         </is>
       </c>
       <c r="W127" t="inlineStr">
         <is>
-          <t>8.9</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="Z127" t="inlineStr"/>
       <c r="AA127" t="inlineStr"/>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AC127" t="inlineStr"/>
       <c r="AD127" t="inlineStr"/>
       <c r="AE127" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AF127" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>8.9</t>
         </is>
       </c>
       <c r="AG127" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
+          <t>8.8</t>
+        </is>
+      </c>
+      <c r="AI127" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="AJ127" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK127" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL127" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="AM127" t="inlineStr">
+        <is>
+          <t>22:30 - 23:00</t>
+        </is>
+      </c>
+      <c r="AN127" t="inlineStr">
+        <is>
           <t>8.9</t>
         </is>
       </c>
-      <c r="AI127" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="AJ127" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK127" t="inlineStr">
+      <c r="AO127" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="AP127" t="inlineStr">
+        <is>
+          <t>8.8</t>
+        </is>
+      </c>
+      <c r="AQ127" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="AR127" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AL127" t="inlineStr">
-        <is>
-          <t>3.2</t>
-        </is>
-      </c>
-      <c r="AM127" t="inlineStr">
-        <is>
-          <t>22:00 - 22:30</t>
-        </is>
-      </c>
-      <c r="AN127" t="inlineStr">
-        <is>
-          <t>9.1</t>
-        </is>
-      </c>
-      <c r="AO127" t="inlineStr">
-        <is>
-          <t>9.2</t>
-        </is>
-      </c>
-      <c r="AP127" t="inlineStr">
-        <is>
-          <t>8.9</t>
-        </is>
-      </c>
-      <c r="AQ127" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="AR127" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS127" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AT127" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>288</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AW127" t="inlineStr">
@@ -28739,12 +28739,12 @@
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>288</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
@@ -28792,7 +28792,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:32</t>
+          <t>2026-09-28 23:17:27</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -29025,7 +29025,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:32</t>
+          <t>2026-09-28 23:17:27</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -29258,7 +29258,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:32</t>
+          <t>2026-09-28 23:17:27</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -29491,7 +29491,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:32</t>
+          <t>2026-09-28 23:17:27</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -29709,7 +29709,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -29724,17 +29724,17 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:35</t>
+          <t>2026-09-28 23:17:29</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
       <c r="K132" t="n">
@@ -29747,7 +29747,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>254</t>
         </is>
       </c>
       <c r="N132" t="inlineStr"/>
@@ -29755,12 +29755,12 @@
       <c r="P132" t="inlineStr"/>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>86</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>1019.5</t>
+          <t>1019.7</t>
         </is>
       </c>
       <c r="S132" t="inlineStr">
@@ -29770,7 +29770,7 @@
       </c>
       <c r="T132" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="U132" t="inlineStr">
@@ -29780,17 +29780,17 @@
       </c>
       <c r="V132" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="W132" t="inlineStr">
         <is>
+          <t>18.1</t>
+        </is>
+      </c>
+      <c r="X132" t="inlineStr">
+        <is>
           <t>18.7</t>
-        </is>
-      </c>
-      <c r="X132" t="inlineStr">
-        <is>
-          <t>19.8</t>
         </is>
       </c>
       <c r="Y132" t="inlineStr">
@@ -29802,99 +29802,99 @@
       <c r="AA132" t="inlineStr"/>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AC132" t="inlineStr"/>
       <c r="AD132" t="inlineStr"/>
       <c r="AE132" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AF132" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="AG132" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
+          <t>18.1</t>
+        </is>
+      </c>
+      <c r="AI132" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="AJ132" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK132" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
+      <c r="AL132" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="AM132" t="inlineStr">
+        <is>
+          <t>22:30 - 23:00</t>
+        </is>
+      </c>
+      <c r="AN132" t="inlineStr">
+        <is>
+          <t>18.5</t>
+        </is>
+      </c>
+      <c r="AO132" t="inlineStr">
+        <is>
           <t>18.7</t>
         </is>
       </c>
-      <c r="AI132" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="AJ132" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK132" t="inlineStr">
+      <c r="AP132" t="inlineStr">
+        <is>
+          <t>18.1</t>
+        </is>
+      </c>
+      <c r="AQ132" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="AR132" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS132" t="inlineStr">
         <is>
           <t>3.6</t>
         </is>
       </c>
-      <c r="AL132" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
-      </c>
-      <c r="AM132" t="inlineStr">
-        <is>
-          <t>22:00 - 22:30</t>
-        </is>
-      </c>
-      <c r="AN132" t="inlineStr">
-        <is>
-          <t>19.3</t>
-        </is>
-      </c>
-      <c r="AO132" t="inlineStr">
-        <is>
-          <t>19.8</t>
-        </is>
-      </c>
-      <c r="AP132" t="inlineStr">
-        <is>
-          <t>18.7</t>
-        </is>
-      </c>
-      <c r="AQ132" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="AR132" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS132" t="inlineStr">
-        <is>
-          <t>3.6</t>
-        </is>
-      </c>
       <c r="AT132" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>254</t>
         </is>
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AV132" t="inlineStr">
         <is>
-          <t>1019.5</t>
+          <t>1019.7</t>
         </is>
       </c>
       <c r="AW132" t="inlineStr">
@@ -29904,12 +29904,12 @@
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
-          <t>1019.5</t>
+          <t>1019.7</t>
         </is>
       </c>
       <c r="AZ132" t="inlineStr">
@@ -29957,7 +29957,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:37</t>
+          <t>2026-09-28 23:17:31</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -30190,7 +30190,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:37</t>
+          <t>2026-09-28 23:17:31</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -30423,7 +30423,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:37</t>
+          <t>2026-09-28 23:17:31</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -30656,7 +30656,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:37</t>
+          <t>2026-09-28 23:17:31</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -30874,7 +30874,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -30889,17 +30889,17 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:40</t>
+          <t>2026-09-28 23:17:34</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
       <c r="K137" t="n">
@@ -30912,7 +30912,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>169</t>
         </is>
       </c>
       <c r="N137" t="inlineStr"/>
@@ -30920,7 +30920,7 @@
       <c r="P137" t="inlineStr"/>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>77</t>
         </is>
       </c>
       <c r="R137" t="inlineStr"/>
@@ -30931,7 +30931,7 @@
       </c>
       <c r="T137" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="U137" t="inlineStr">
@@ -30941,56 +30941,56 @@
       </c>
       <c r="V137" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="W137" t="inlineStr">
         <is>
-          <t>23.4</t>
+          <t>23.1</t>
         </is>
       </c>
       <c r="X137" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>23.3</t>
         </is>
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="Z137" t="inlineStr"/>
       <c r="AA137" t="inlineStr"/>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>16.2</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="AC137" t="inlineStr"/>
       <c r="AD137" t="inlineStr"/>
       <c r="AE137" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AF137" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="AG137" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>23.3</t>
         </is>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
-          <t>23.4</t>
+          <t>23.1</t>
         </is>
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>77</t>
         </is>
       </c>
       <c r="AJ137" t="inlineStr">
@@ -31000,37 +31000,37 @@
       </c>
       <c r="AK137" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AL137" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>169</t>
         </is>
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AN137" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="AO137" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>23.3</t>
         </is>
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>23.4</t>
+          <t>23.1</t>
         </is>
       </c>
       <c r="AQ137" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>77</t>
         </is>
       </c>
       <c r="AR137" t="inlineStr">
@@ -31040,17 +31040,17 @@
       </c>
       <c r="AS137" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AT137" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>169</t>
         </is>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>16.2</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
@@ -31061,7 +31061,7 @@
       <c r="AW137" t="inlineStr"/>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>16.2</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
@@ -31110,7 +31110,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:42</t>
+          <t>2026-09-28 23:17:35</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -31331,7 +31331,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:42</t>
+          <t>2026-09-28 23:17:35</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -31552,7 +31552,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:42</t>
+          <t>2026-09-28 23:17:35</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -31773,7 +31773,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:42</t>
+          <t>2026-09-28 23:17:35</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -31979,7 +31979,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -31994,17 +31994,17 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:45</t>
+          <t>2026-09-28 23:17:38</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
       <c r="K142" t="n">
@@ -32017,7 +32017,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>185</t>
         </is>
       </c>
       <c r="N142" t="inlineStr"/>
@@ -32025,7 +32025,7 @@
       <c r="P142" t="inlineStr"/>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>92</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
@@ -32035,12 +32035,12 @@
       </c>
       <c r="S142" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="T142" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="U142" t="inlineStr">
@@ -32050,116 +32050,116 @@
       </c>
       <c r="V142" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="W142" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="X142" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="Z142" t="inlineStr"/>
       <c r="AA142" t="inlineStr"/>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>16.2</t>
         </is>
       </c>
       <c r="AC142" t="inlineStr"/>
       <c r="AD142" t="inlineStr"/>
       <c r="AE142" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AF142" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="AG142" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="AH142" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>92</t>
         </is>
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AL142" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>185</t>
         </is>
       </c>
       <c r="AM142" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AN142" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="AO142" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="AQ142" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>92</t>
         </is>
       </c>
       <c r="AR142" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="AS142" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AT142" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>185</t>
         </is>
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>16.2</t>
         </is>
       </c>
       <c r="AV142" t="inlineStr">
@@ -32174,7 +32174,7 @@
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>16.2</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
@@ -32227,7 +32227,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:46</t>
+          <t>2026-09-28 23:17:40</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -32460,7 +32460,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:46</t>
+          <t>2026-09-28 23:17:40</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -32693,7 +32693,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:46</t>
+          <t>2026-09-28 23:17:40</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -32926,7 +32926,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:46</t>
+          <t>2026-09-28 23:17:40</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -33144,7 +33144,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -33159,17 +33159,17 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:49</t>
+          <t>2026-09-28 23:17:42</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
       <c r="K147" t="n">
@@ -33190,12 +33190,12 @@
       <c r="P147" t="inlineStr"/>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>90</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>1018.7</t>
+          <t>1018.8</t>
         </is>
       </c>
       <c r="S147" t="inlineStr">
@@ -33205,7 +33205,7 @@
       </c>
       <c r="T147" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="U147" t="inlineStr">
@@ -33215,17 +33215,17 @@
       </c>
       <c r="V147" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="W147" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="X147" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="Y147" t="inlineStr">
@@ -33237,34 +33237,34 @@
       <c r="AA147" t="inlineStr"/>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>33.1</t>
+          <t>34.2</t>
         </is>
       </c>
       <c r="AC147" t="inlineStr"/>
       <c r="AD147" t="inlineStr"/>
       <c r="AE147" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AF147" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="AG147" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="AI147" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>90</t>
         </is>
       </c>
       <c r="AJ147" t="inlineStr">
@@ -33284,27 +33284,27 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AN147" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="AO147" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="AQ147" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>90</t>
         </is>
       </c>
       <c r="AR147" t="inlineStr">
@@ -33324,12 +33324,12 @@
       </c>
       <c r="AU147" t="inlineStr">
         <is>
-          <t>33.1</t>
+          <t>34.2</t>
         </is>
       </c>
       <c r="AV147" t="inlineStr">
         <is>
-          <t>1018.7</t>
+          <t>1018.8</t>
         </is>
       </c>
       <c r="AW147" t="inlineStr">
@@ -33339,12 +33339,12 @@
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>33.1</t>
+          <t>34.2</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
         <is>
-          <t>1018.7</t>
+          <t>1018.8</t>
         </is>
       </c>
       <c r="AZ147" t="inlineStr">
@@ -33392,7 +33392,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:51</t>
+          <t>2026-09-28 23:17:44</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -33625,7 +33625,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:51</t>
+          <t>2026-09-28 23:17:44</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -33858,7 +33858,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:51</t>
+          <t>2026-09-28 23:17:44</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -34091,7 +34091,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:51</t>
+          <t>2026-09-28 23:17:44</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -34309,7 +34309,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -34324,17 +34324,17 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:54</t>
+          <t>2026-09-28 23:17:46</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
       <c r="K152" t="n">
@@ -34348,13 +34348,13 @@
       <c r="M152" t="inlineStr"/>
       <c r="N152" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>120</t>
         </is>
       </c>
       <c r="O152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Q152" t="inlineStr">
@@ -34370,7 +34370,7 @@
       </c>
       <c r="T152" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="U152" t="inlineStr">
@@ -34380,7 +34380,7 @@
       </c>
       <c r="V152" t="inlineStr">
         <is>
-          <t>16.2</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="W152" t="inlineStr">
@@ -34390,36 +34390,36 @@
       </c>
       <c r="X152" t="inlineStr">
         <is>
-          <t>16.2</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="Y152" t="inlineStr"/>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr"/>
       <c r="AB152" t="inlineStr"/>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AD152" t="inlineStr"/>
       <c r="AE152" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AF152" t="inlineStr">
         <is>
-          <t>16.2</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="AG152" t="inlineStr">
         <is>
-          <t>16.2</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="AH152" t="inlineStr">
@@ -34439,27 +34439,27 @@
       </c>
       <c r="AK152" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AL152" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AM152" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AN152" t="inlineStr">
         <is>
-          <t>16.2</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="AO152" t="inlineStr">
         <is>
-          <t>16.2</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="AP152" t="inlineStr">
@@ -34479,22 +34479,22 @@
       </c>
       <c r="AS152" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AT152" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>120</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
@@ -34504,12 +34504,12 @@
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>120</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
@@ -34557,7 +34557,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:56</t>
+          <t>2026-09-28 23:17:48</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -34790,7 +34790,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:56</t>
+          <t>2026-09-28 23:17:48</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -35023,7 +35023,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:56</t>
+          <t>2026-09-28 23:17:48</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -35256,7 +35256,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:56</t>
+          <t>2026-09-28 23:17:48</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -35474,7 +35474,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -35489,17 +35489,17 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-09-28 22:47:59</t>
+          <t>2026-09-28 23:17:51</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
       <c r="K157" t="n">
@@ -35512,7 +35512,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>231</t>
         </is>
       </c>
       <c r="N157" t="inlineStr"/>
@@ -35520,12 +35520,12 @@
       <c r="P157" t="inlineStr"/>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>72</t>
         </is>
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>1018.4</t>
+          <t>1018.6</t>
         </is>
       </c>
       <c r="S157" t="inlineStr">
@@ -35535,7 +35535,7 @@
       </c>
       <c r="T157" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="U157" t="inlineStr">
@@ -35545,56 +35545,56 @@
       </c>
       <c r="V157" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="W157" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="X157" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>16.2</t>
         </is>
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="Z157" t="inlineStr"/>
       <c r="AA157" t="inlineStr"/>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="AC157" t="inlineStr"/>
       <c r="AD157" t="inlineStr"/>
       <c r="AE157" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AF157" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="AG157" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>16.2</t>
         </is>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="AI157" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>72</t>
         </is>
       </c>
       <c r="AJ157" t="inlineStr">
@@ -35604,37 +35604,37 @@
       </c>
       <c r="AK157" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="AL157" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>231</t>
         </is>
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AN157" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="AO157" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>16.2</t>
         </is>
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="AQ157" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>72</t>
         </is>
       </c>
       <c r="AR157" t="inlineStr">
@@ -35644,22 +35644,22 @@
       </c>
       <c r="AS157" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="AT157" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>231</t>
         </is>
       </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
-          <t>1018.4</t>
+          <t>1018.6</t>
         </is>
       </c>
       <c r="AW157" t="inlineStr">
@@ -35669,12 +35669,12 @@
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
         <is>
-          <t>1018.4</t>
+          <t>1018.6</t>
         </is>
       </c>
       <c r="AZ157" t="inlineStr">
@@ -35722,7 +35722,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:01</t>
+          <t>2026-09-28 23:17:53</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -35955,7 +35955,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:01</t>
+          <t>2026-09-28 23:17:53</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -36188,7 +36188,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:01</t>
+          <t>2026-09-28 23:17:53</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -36421,7 +36421,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:01</t>
+          <t>2026-09-28 23:17:53</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -36639,7 +36639,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -36654,17 +36654,17 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:04</t>
+          <t>2026-09-28 23:17:56</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
       <c r="K162" t="n">
@@ -36677,24 +36677,24 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>48</t>
         </is>
       </c>
       <c r="N162" t="inlineStr"/>
       <c r="O162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q162" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>97</t>
         </is>
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>856.2</t>
+          <t>856.3</t>
         </is>
       </c>
       <c r="S162" t="inlineStr">
@@ -36704,7 +36704,7 @@
       </c>
       <c r="T162" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="U162" t="inlineStr">
@@ -36714,56 +36714,56 @@
       </c>
       <c r="V162" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="W162" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="X162" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="Z162" t="inlineStr"/>
       <c r="AA162" t="inlineStr"/>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="AC162" t="inlineStr"/>
       <c r="AD162" t="inlineStr"/>
       <c r="AE162" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AF162" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AG162" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="AH162" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="AI162" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AJ162" t="inlineStr">
@@ -36773,37 +36773,37 @@
       </c>
       <c r="AK162" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AL162" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="AM162" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AN162" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AO162" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="AQ162" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AR162" t="inlineStr">
@@ -36813,42 +36813,42 @@
       </c>
       <c r="AS162" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AT162" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="AU162" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>856.2</t>
+          <t>856.3</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>856.2</t>
+          <t>856.3</t>
         </is>
       </c>
       <c r="BA162" t="inlineStr">
@@ -36895,7 +36895,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:06</t>
+          <t>2026-09-28 23:17:57</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -37136,7 +37136,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:06</t>
+          <t>2026-09-28 23:17:57</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -37377,7 +37377,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:06</t>
+          <t>2026-09-28 23:17:57</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -37618,7 +37618,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:06</t>
+          <t>2026-09-28 23:17:57</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -37844,7 +37844,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -37859,17 +37859,17 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:09</t>
+          <t>2026-09-28 23:18:00</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
       <c r="K167" t="n">
@@ -37882,7 +37882,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>330</t>
         </is>
       </c>
       <c r="N167" t="inlineStr"/>
@@ -37890,7 +37890,7 @@
       <c r="P167" t="inlineStr"/>
       <c r="Q167" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>92</t>
         </is>
       </c>
       <c r="R167" t="inlineStr">
@@ -37905,7 +37905,7 @@
       </c>
       <c r="T167" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="U167" t="inlineStr">
@@ -37915,56 +37915,56 @@
       </c>
       <c r="V167" t="inlineStr">
         <is>
+          <t>15.8</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
           <t>15.7</t>
         </is>
       </c>
-      <c r="W167" t="inlineStr">
-        <is>
-          <t>15.6</t>
-        </is>
-      </c>
       <c r="X167" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="Z167" t="inlineStr"/>
       <c r="AA167" t="inlineStr"/>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="AC167" t="inlineStr"/>
       <c r="AD167" t="inlineStr"/>
       <c r="AE167" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AF167" t="inlineStr">
         <is>
+          <t>15.8</t>
+        </is>
+      </c>
+      <c r="AG167" t="inlineStr">
+        <is>
+          <t>15.8</t>
+        </is>
+      </c>
+      <c r="AH167" t="inlineStr">
+        <is>
           <t>15.7</t>
         </is>
       </c>
-      <c r="AG167" t="inlineStr">
-        <is>
-          <t>15.9</t>
-        </is>
-      </c>
-      <c r="AH167" t="inlineStr">
-        <is>
-          <t>15.6</t>
-        </is>
-      </c>
       <c r="AI167" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>92</t>
         </is>
       </c>
       <c r="AJ167" t="inlineStr">
@@ -37975,32 +37975,32 @@
       <c r="AK167" t="inlineStr"/>
       <c r="AL167" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AN167" t="inlineStr">
         <is>
+          <t>15.8</t>
+        </is>
+      </c>
+      <c r="AO167" t="inlineStr">
+        <is>
+          <t>15.8</t>
+        </is>
+      </c>
+      <c r="AP167" t="inlineStr">
+        <is>
           <t>15.7</t>
         </is>
       </c>
-      <c r="AO167" t="inlineStr">
-        <is>
-          <t>15.9</t>
-        </is>
-      </c>
-      <c r="AP167" t="inlineStr">
-        <is>
-          <t>15.6</t>
-        </is>
-      </c>
       <c r="AQ167" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>92</t>
         </is>
       </c>
       <c r="AR167" t="inlineStr">
@@ -38011,17 +38011,17 @@
       <c r="AS167" t="inlineStr"/>
       <c r="AT167" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AU167" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>330</t>
         </is>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="AW167" t="inlineStr">
@@ -38031,12 +38031,12 @@
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>330</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="AZ167" t="inlineStr">
@@ -38088,7 +38088,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:11</t>
+          <t>2026-09-28 23:18:03</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -38329,7 +38329,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:11</t>
+          <t>2026-09-28 23:18:03</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -38570,7 +38570,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:11</t>
+          <t>2026-09-28 23:18:03</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -38811,7 +38811,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:11</t>
+          <t>2026-09-28 23:18:03</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -39037,7 +39037,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -39052,17 +39052,17 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:14</t>
+          <t>2026-09-28 23:18:06</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
       <c r="K172" t="n">
@@ -39075,7 +39075,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>108</t>
         </is>
       </c>
       <c r="N172" t="inlineStr"/>
@@ -39098,7 +39098,7 @@
       </c>
       <c r="T172" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="U172" t="inlineStr">
@@ -39108,12 +39108,12 @@
       </c>
       <c r="V172" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="W172" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="X172" t="inlineStr">
@@ -39123,26 +39123,26 @@
       </c>
       <c r="Y172" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="Z172" t="inlineStr"/>
       <c r="AA172" t="inlineStr"/>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="AC172" t="inlineStr"/>
       <c r="AD172" t="inlineStr"/>
       <c r="AE172" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AF172" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="AG172" t="inlineStr">
@@ -39152,7 +39152,7 @@
       </c>
       <c r="AH172" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="AI172" t="inlineStr">
@@ -39167,22 +39167,22 @@
       </c>
       <c r="AK172" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="AL172" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AM172" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AN172" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="AO172" t="inlineStr">
@@ -39192,7 +39192,7 @@
       </c>
       <c r="AP172" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="AQ172" t="inlineStr">
@@ -39207,17 +39207,17 @@
       </c>
       <c r="AS172" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="AT172" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AU172" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="AV172" t="inlineStr">
@@ -39232,7 +39232,7 @@
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr">
@@ -39285,7 +39285,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:16</t>
+          <t>2026-09-28 23:18:07</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -39518,7 +39518,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:16</t>
+          <t>2026-09-28 23:18:07</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -39751,7 +39751,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:16</t>
+          <t>2026-09-28 23:18:07</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -39984,7 +39984,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:16</t>
+          <t>2026-09-28 23:18:07</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -40202,7 +40202,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -40217,17 +40217,17 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:19</t>
+          <t>2026-09-28 23:18:10</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
       <c r="K177" t="n">
@@ -40240,7 +40240,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>203</t>
         </is>
       </c>
       <c r="N177" t="inlineStr"/>
@@ -40248,12 +40248,12 @@
       <c r="P177" t="inlineStr"/>
       <c r="Q177" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>89</t>
         </is>
       </c>
       <c r="R177" t="inlineStr">
         <is>
-          <t>1020.4</t>
+          <t>1020.9</t>
         </is>
       </c>
       <c r="S177" t="inlineStr">
@@ -40263,62 +40263,62 @@
       </c>
       <c r="T177" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="U177" t="inlineStr"/>
       <c r="V177" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="W177" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>15.9</t>
         </is>
       </c>
       <c r="X177" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>16.2</t>
         </is>
       </c>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="Z177" t="inlineStr"/>
       <c r="AA177" t="inlineStr"/>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AC177" t="inlineStr"/>
       <c r="AD177" t="inlineStr"/>
       <c r="AE177" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AF177" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="AG177" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>16.2</t>
         </is>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>15.9</t>
         </is>
       </c>
       <c r="AI177" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>89</t>
         </is>
       </c>
       <c r="AJ177" t="inlineStr">
@@ -40328,37 +40328,37 @@
       </c>
       <c r="AK177" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AL177" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>203</t>
         </is>
       </c>
       <c r="AM177" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AN177" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="AO177" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>16.2</t>
         </is>
       </c>
       <c r="AP177" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>15.9</t>
         </is>
       </c>
       <c r="AQ177" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>89</t>
         </is>
       </c>
       <c r="AR177" t="inlineStr">
@@ -40368,33 +40368,33 @@
       </c>
       <c r="AS177" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AT177" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>203</t>
         </is>
       </c>
       <c r="AU177" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AV177" t="inlineStr">
         <is>
-          <t>1020.4</t>
+          <t>1020.9</t>
         </is>
       </c>
       <c r="AW177" t="inlineStr"/>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
         <is>
-          <t>1020.4</t>
+          <t>1020.9</t>
         </is>
       </c>
       <c r="AZ177" t="inlineStr"/>
@@ -40438,7 +40438,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:21</t>
+          <t>2026-09-28 23:18:12</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -40659,7 +40659,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:21</t>
+          <t>2026-09-28 23:18:12</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -40880,7 +40880,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:21</t>
+          <t>2026-09-28 23:18:12</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -41101,7 +41101,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:21</t>
+          <t>2026-09-28 23:18:12</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -41307,7 +41307,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -41322,17 +41322,17 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:24</t>
+          <t>2026-09-28 23:18:15</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
       <c r="K182" t="n">
@@ -41345,7 +41345,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>286</t>
         </is>
       </c>
       <c r="N182" t="inlineStr"/>
@@ -41364,7 +41364,7 @@
       </c>
       <c r="T182" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="U182" t="inlineStr">
@@ -41374,98 +41374,98 @@
       </c>
       <c r="V182" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="W182" t="inlineStr">
         <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="X182" t="inlineStr">
+        <is>
           <t>20.6</t>
         </is>
       </c>
-      <c r="X182" t="inlineStr">
-        <is>
-          <t>21.0</t>
-        </is>
-      </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="Z182" t="inlineStr"/>
       <c r="AA182" t="inlineStr"/>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="AC182" t="inlineStr"/>
       <c r="AD182" t="inlineStr"/>
       <c r="AE182" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AF182" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="AG182" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="AH182" t="inlineStr">
         <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="AI182" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="AJ182" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK182" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AL182" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="AM182" t="inlineStr">
+        <is>
+          <t>22:30 - 23:00</t>
+        </is>
+      </c>
+      <c r="AN182" t="inlineStr">
+        <is>
           <t>20.6</t>
         </is>
       </c>
-      <c r="AI182" t="inlineStr">
+      <c r="AO182" t="inlineStr">
+        <is>
+          <t>20.6</t>
+        </is>
+      </c>
+      <c r="AP182" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="AQ182" t="inlineStr">
         <is>
           <t>82</t>
         </is>
       </c>
-      <c r="AJ182" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK182" t="inlineStr">
-        <is>
-          <t>4.3</t>
-        </is>
-      </c>
-      <c r="AL182" t="inlineStr">
-        <is>
-          <t>294</t>
-        </is>
-      </c>
-      <c r="AM182" t="inlineStr">
-        <is>
-          <t>22:00 - 22:30</t>
-        </is>
-      </c>
-      <c r="AN182" t="inlineStr">
-        <is>
-          <t>20.7</t>
-        </is>
-      </c>
-      <c r="AO182" t="inlineStr">
-        <is>
-          <t>21.0</t>
-        </is>
-      </c>
-      <c r="AP182" t="inlineStr">
-        <is>
-          <t>20.6</t>
-        </is>
-      </c>
-      <c r="AQ182" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
       <c r="AR182" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -41473,17 +41473,17 @@
       </c>
       <c r="AS182" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AT182" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>286</t>
         </is>
       </c>
       <c r="AU182" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="AV182" t="inlineStr">
@@ -41494,7 +41494,7 @@
       <c r="AW182" t="inlineStr"/>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr">
@@ -41543,7 +41543,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:25</t>
+          <t>2026-09-28 23:18:16</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -41764,7 +41764,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:25</t>
+          <t>2026-09-28 23:18:16</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -41985,7 +41985,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:25</t>
+          <t>2026-09-28 23:18:16</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -42206,7 +42206,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:25</t>
+          <t>2026-09-28 23:18:16</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -42412,7 +42412,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -42427,17 +42427,17 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:28</t>
+          <t>2026-09-28 23:18:19</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
       <c r="K187" t="n">
@@ -42450,7 +42450,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>228</t>
         </is>
       </c>
       <c r="N187" t="inlineStr"/>
@@ -42458,7 +42458,7 @@
       <c r="P187" t="inlineStr"/>
       <c r="Q187" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>94</t>
         </is>
       </c>
       <c r="R187" t="inlineStr"/>
@@ -42469,7 +42469,7 @@
       </c>
       <c r="T187" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="U187" t="inlineStr">
@@ -42479,56 +42479,56 @@
       </c>
       <c r="V187" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="W187" t="inlineStr">
         <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="X187" t="inlineStr">
+        <is>
           <t>6.9</t>
         </is>
       </c>
-      <c r="X187" t="inlineStr">
-        <is>
-          <t>7.3</t>
-        </is>
-      </c>
       <c r="Y187" t="inlineStr">
         <is>
-          <t>22.7</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="Z187" t="inlineStr"/>
       <c r="AA187" t="inlineStr"/>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>37.4</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="AC187" t="inlineStr"/>
       <c r="AD187" t="inlineStr"/>
       <c r="AE187" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AF187" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="AG187" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="AH187" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AI187" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>94</t>
         </is>
       </c>
       <c r="AJ187" t="inlineStr">
@@ -42539,32 +42539,32 @@
       <c r="AK187" t="inlineStr"/>
       <c r="AL187" t="inlineStr">
         <is>
-          <t>22.7</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AN187" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="AO187" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="AP187" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ187" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>94</t>
         </is>
       </c>
       <c r="AR187" t="inlineStr">
@@ -42575,17 +42575,17 @@
       <c r="AS187" t="inlineStr"/>
       <c r="AT187" t="inlineStr">
         <is>
-          <t>22.7</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="AU187" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>228</t>
         </is>
       </c>
       <c r="AV187" t="inlineStr">
         <is>
-          <t>37.4</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="AW187" t="inlineStr">
@@ -42595,12 +42595,12 @@
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>228</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr">
         <is>
-          <t>37.4</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="AZ187" t="inlineStr">
@@ -42648,7 +42648,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:30</t>
+          <t>2026-09-28 23:18:21</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -42881,7 +42881,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:30</t>
+          <t>2026-09-28 23:18:21</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -43114,7 +43114,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:30</t>
+          <t>2026-09-28 23:18:21</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -43347,7 +43347,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:30</t>
+          <t>2026-09-28 23:18:21</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -43580,17 +43580,17 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:33</t>
+          <t>2026-09-28 23:18:23</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
       <c r="K192" t="n">
@@ -43777,7 +43777,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:35</t>
+          <t>2026-09-28 23:18:24</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -43974,7 +43974,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:35</t>
+          <t>2026-09-28 23:18:24</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -44171,7 +44171,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:35</t>
+          <t>2026-09-28 23:18:24</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -44368,7 +44368,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:35</t>
+          <t>2026-09-28 23:18:24</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -44550,7 +44550,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -44565,17 +44565,17 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:38</t>
+          <t>2026-09-28 23:18:27</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
       <c r="K197" t="n">
@@ -44588,7 +44588,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N197" t="inlineStr"/>
@@ -44596,12 +44596,12 @@
       <c r="P197" t="inlineStr"/>
       <c r="Q197" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>81</t>
         </is>
       </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>1018.1</t>
+          <t>1017.9</t>
         </is>
       </c>
       <c r="S197" t="inlineStr">
@@ -44611,7 +44611,7 @@
       </c>
       <c r="T197" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="U197" t="inlineStr">
@@ -44621,48 +44621,48 @@
       </c>
       <c r="V197" t="inlineStr">
         <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="W197" t="inlineStr">
+        <is>
+          <t>22.9</t>
+        </is>
+      </c>
+      <c r="X197" t="inlineStr">
+        <is>
           <t>23.1</t>
         </is>
       </c>
-      <c r="W197" t="inlineStr">
-        <is>
-          <t>22.9</t>
-        </is>
-      </c>
-      <c r="X197" t="inlineStr">
-        <is>
-          <t>23.3</t>
-        </is>
-      </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="Z197" t="inlineStr"/>
       <c r="AA197" t="inlineStr"/>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="AC197" t="inlineStr"/>
       <c r="AD197" t="inlineStr"/>
       <c r="AE197" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AF197" t="inlineStr">
         <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="AG197" t="inlineStr">
+        <is>
           <t>23.1</t>
         </is>
       </c>
-      <c r="AG197" t="inlineStr">
-        <is>
-          <t>23.3</t>
-        </is>
-      </c>
       <c r="AH197" t="inlineStr">
         <is>
           <t>22.9</t>
@@ -44670,7 +44670,7 @@
       </c>
       <c r="AI197" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AJ197" t="inlineStr">
@@ -44680,29 +44680,29 @@
       </c>
       <c r="AK197" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AL197" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AM197" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AN197" t="inlineStr">
         <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="AO197" t="inlineStr">
+        <is>
           <t>23.1</t>
         </is>
       </c>
-      <c r="AO197" t="inlineStr">
-        <is>
-          <t>23.3</t>
-        </is>
-      </c>
       <c r="AP197" t="inlineStr">
         <is>
           <t>22.9</t>
@@ -44710,7 +44710,7 @@
       </c>
       <c r="AQ197" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AR197" t="inlineStr">
@@ -44720,22 +44720,22 @@
       </c>
       <c r="AS197" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AT197" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AU197" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="AV197" t="inlineStr">
         <is>
-          <t>1018.1</t>
+          <t>1017.9</t>
         </is>
       </c>
       <c r="AW197" t="inlineStr">
@@ -44745,12 +44745,12 @@
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr">
         <is>
-          <t>1018.1</t>
+          <t>1017.9</t>
         </is>
       </c>
       <c r="AZ197" t="inlineStr">
@@ -44798,7 +44798,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:39</t>
+          <t>2026-09-28 23:18:29</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -45031,7 +45031,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:39</t>
+          <t>2026-09-28 23:18:29</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -45264,7 +45264,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:39</t>
+          <t>2026-09-28 23:18:29</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -45497,7 +45497,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:39</t>
+          <t>2026-09-28 23:18:29</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -45715,7 +45715,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -45730,17 +45730,17 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:42</t>
+          <t>2026-09-28 23:18:31</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
       <c r="K202" t="n">
@@ -45757,7 +45757,7 @@
       <c r="P202" t="inlineStr"/>
       <c r="Q202" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>96</t>
         </is>
       </c>
       <c r="R202" t="inlineStr"/>
@@ -45768,23 +45768,23 @@
       </c>
       <c r="T202" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="U202" t="inlineStr"/>
       <c r="V202" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="W202" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="X202" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="Y202" t="inlineStr"/>
@@ -45795,27 +45795,27 @@
       <c r="AD202" t="inlineStr"/>
       <c r="AE202" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AF202" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="AG202" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AH202" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="AI202" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>96</t>
         </is>
       </c>
       <c r="AJ202" t="inlineStr">
@@ -45827,27 +45827,27 @@
       <c r="AL202" t="inlineStr"/>
       <c r="AM202" t="inlineStr">
         <is>
-          <t>21:30 - 22:00</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AN202" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="AO202" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AP202" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="AQ202" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>96</t>
         </is>
       </c>
       <c r="AR202" t="inlineStr">
@@ -45903,7 +45903,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:44</t>
+          <t>2026-09-28 23:18:33</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -46076,7 +46076,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:44</t>
+          <t>2026-09-28 23:18:33</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -46249,7 +46249,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:44</t>
+          <t>2026-09-28 23:18:33</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -46422,7 +46422,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:44</t>
+          <t>2026-09-28 23:18:33</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -46580,7 +46580,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -46595,17 +46595,17 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:47</t>
+          <t>2026-09-28 23:18:35</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
       <c r="K207" t="n">
@@ -46618,7 +46618,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>203</t>
         </is>
       </c>
       <c r="N207" t="inlineStr"/>
@@ -46626,7 +46626,7 @@
       <c r="P207" t="inlineStr"/>
       <c r="Q207" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>88</t>
         </is>
       </c>
       <c r="R207" t="inlineStr"/>
@@ -46637,7 +46637,7 @@
       </c>
       <c r="T207" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="U207" t="inlineStr">
@@ -46647,17 +46647,17 @@
       </c>
       <c r="V207" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="W207" t="inlineStr">
         <is>
+          <t>16.6</t>
+        </is>
+      </c>
+      <c r="X207" t="inlineStr">
+        <is>
           <t>17.1</t>
-        </is>
-      </c>
-      <c r="X207" t="inlineStr">
-        <is>
-          <t>18.0</t>
         </is>
       </c>
       <c r="Y207" t="inlineStr">
@@ -46669,94 +46669,94 @@
       <c r="AA207" t="inlineStr"/>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="AC207" t="inlineStr"/>
       <c r="AD207" t="inlineStr"/>
       <c r="AE207" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AF207" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="AG207" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="AH207" t="inlineStr">
         <is>
+          <t>16.6</t>
+        </is>
+      </c>
+      <c r="AI207" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="AJ207" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK207" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="AL207" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="AM207" t="inlineStr">
+        <is>
+          <t>22:30 - 23:00</t>
+        </is>
+      </c>
+      <c r="AN207" t="inlineStr">
+        <is>
+          <t>16.9</t>
+        </is>
+      </c>
+      <c r="AO207" t="inlineStr">
+        <is>
           <t>17.1</t>
         </is>
       </c>
-      <c r="AI207" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="AJ207" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK207" t="inlineStr">
+      <c r="AP207" t="inlineStr">
+        <is>
+          <t>16.6</t>
+        </is>
+      </c>
+      <c r="AQ207" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="AR207" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS207" t="inlineStr">
         <is>
           <t>1.8</t>
         </is>
       </c>
-      <c r="AL207" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="AM207" t="inlineStr">
-        <is>
-          <t>22:00 - 22:30</t>
-        </is>
-      </c>
-      <c r="AN207" t="inlineStr">
-        <is>
-          <t>17.4</t>
-        </is>
-      </c>
-      <c r="AO207" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="AP207" t="inlineStr">
-        <is>
-          <t>17.1</t>
-        </is>
-      </c>
-      <c r="AQ207" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="AR207" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS207" t="inlineStr">
-        <is>
-          <t>1.8</t>
-        </is>
-      </c>
       <c r="AT207" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>203</t>
         </is>
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="AV207" t="inlineStr">
@@ -46767,7 +46767,7 @@
       <c r="AW207" t="inlineStr"/>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
@@ -46816,7 +46816,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:49</t>
+          <t>2026-09-28 23:18:37</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -47037,7 +47037,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:49</t>
+          <t>2026-09-28 23:18:37</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -47258,7 +47258,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:49</t>
+          <t>2026-09-28 23:18:37</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -47479,7 +47479,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:49</t>
+          <t>2026-09-28 23:18:37</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -47685,7 +47685,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -47700,17 +47700,17 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:52</t>
+          <t>2026-09-28 23:18:39</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
       <c r="K212" t="n">
@@ -47723,7 +47723,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>193</t>
         </is>
       </c>
       <c r="N212" t="inlineStr"/>
@@ -47736,7 +47736,7 @@
       </c>
       <c r="R212" t="inlineStr">
         <is>
-          <t>855.0</t>
+          <t>854.8</t>
         </is>
       </c>
       <c r="S212" t="inlineStr">
@@ -47746,7 +47746,7 @@
       </c>
       <c r="T212" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="U212" t="inlineStr">
@@ -47756,51 +47756,51 @@
       </c>
       <c r="V212" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="W212" t="inlineStr">
         <is>
+          <t>8.9</t>
+        </is>
+      </c>
+      <c r="X212" t="inlineStr">
+        <is>
           <t>9.1</t>
         </is>
       </c>
-      <c r="X212" t="inlineStr">
-        <is>
-          <t>9.3</t>
-        </is>
-      </c>
       <c r="Y212" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="Z212" t="inlineStr"/>
       <c r="AA212" t="inlineStr"/>
       <c r="AB212" t="inlineStr">
         <is>
-          <t>37.4</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="AC212" t="inlineStr"/>
       <c r="AD212" t="inlineStr"/>
       <c r="AE212" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AF212" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="AG212" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="AH212" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>8.9</t>
         </is>
       </c>
       <c r="AI212" t="inlineStr">
@@ -47816,27 +47816,27 @@
       <c r="AK212" t="inlineStr"/>
       <c r="AL212" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="AM212" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AN212" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="AO212" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="AP212" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>8.9</t>
         </is>
       </c>
       <c r="AQ212" t="inlineStr">
@@ -47852,37 +47852,37 @@
       <c r="AS212" t="inlineStr"/>
       <c r="AT212" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="AU212" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>193</t>
         </is>
       </c>
       <c r="AV212" t="inlineStr">
         <is>
-          <t>37.4</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>855.0</t>
+          <t>854.8</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>193</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr">
         <is>
-          <t>37.4</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>855.0</t>
+          <t>854.8</t>
         </is>
       </c>
       <c r="BA212" t="inlineStr">
@@ -47929,7 +47929,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:54</t>
+          <t>2026-09-28 23:18:41</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -48170,7 +48170,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:54</t>
+          <t>2026-09-28 23:18:41</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -48411,7 +48411,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:54</t>
+          <t>2026-09-28 23:18:41</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -48652,7 +48652,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:54</t>
+          <t>2026-09-28 23:18:41</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -48893,17 +48893,17 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:57</t>
+          <t>2026-09-28 23:18:44</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
       <c r="K217" t="n">
@@ -49134,7 +49134,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:59</t>
+          <t>2026-09-28 23:18:46</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -49375,7 +49375,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:59</t>
+          <t>2026-09-28 23:18:46</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -49616,7 +49616,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:59</t>
+          <t>2026-09-28 23:18:46</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -49857,7 +49857,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>2026-09-28 22:48:59</t>
+          <t>2026-09-28 23:18:46</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -50083,7 +50083,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -50098,17 +50098,17 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>2026-09-28 22:49:02</t>
+          <t>2026-09-28 23:18:48</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
       <c r="K222" t="n">
@@ -50121,7 +50121,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>188</t>
         </is>
       </c>
       <c r="N222" t="inlineStr"/>
@@ -50129,7 +50129,7 @@
       <c r="P222" t="inlineStr"/>
       <c r="Q222" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>70</t>
         </is>
       </c>
       <c r="R222" t="inlineStr">
@@ -50144,7 +50144,7 @@
       </c>
       <c r="T222" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="U222" t="inlineStr">
@@ -50154,96 +50154,96 @@
       </c>
       <c r="V222" t="inlineStr">
         <is>
+          <t>23.4</t>
+        </is>
+      </c>
+      <c r="W222" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="X222" t="inlineStr">
+        <is>
           <t>23.6</t>
         </is>
       </c>
-      <c r="W222" t="inlineStr">
-        <is>
-          <t>23.4</t>
-        </is>
-      </c>
-      <c r="X222" t="inlineStr">
-        <is>
-          <t>23.7</t>
-        </is>
-      </c>
       <c r="Y222" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="Z222" t="inlineStr"/>
       <c r="AA222" t="inlineStr"/>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="AC222" t="inlineStr"/>
       <c r="AD222" t="inlineStr"/>
       <c r="AE222" t="inlineStr">
         <is>
-          <t>22:00 - 22:30</t>
+          <t>22:30 - 23:00</t>
         </is>
       </c>
       <c r="AF222" t="inlineStr">
         <is>
+          <t>23.4</t>
+        </is>
+      </c>
+      <c r="AG222" t="inlineStr">
+        <is>
           <t>23.6</t>
         </is>
       </c>
-      <c r="AG222" t="inlineStr">
-        <is>
-          <t>23.7</t>
-        </is>
-      </c>
       <c r="AH222" t="inlineStr">
         <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="AI222" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="AJ222" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK222" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="AL222" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="AM222" t="inlineStr">
+        <is>
+          <t>22:30 - 23:00</t>
+        </is>
+      </c>
+      <c r="AN222" t="inlineStr">
+        <is>
           <t>23.4</t>
         </is>
       </c>
-      <c r="AI222" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="AJ222" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK222" t="inlineStr">
-        <is>
-          <t>3.6</t>
-        </is>
-      </c>
-      <c r="AL222" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="AM222" t="inlineStr">
-        <is>
-          <t>22:00 - 22:30</t>
-        </is>
-      </c>
-      <c r="AN222" t="inlineStr">
+      <c r="AO222" t="inlineStr">
         <is>
           <t>23.6</t>
         </is>
       </c>
-      <c r="AO222" t="inlineStr">
-        <is>
-          <t>23.7</t>
-        </is>
-      </c>
       <c r="AP222" t="inlineStr">
         <is>
-          <t>23.4</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="AQ222" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AR222" t="inlineStr">
@@ -50253,17 +50253,17 @@
       </c>
       <c r="AS222" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AT222" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>188</t>
         </is>
       </c>
       <c r="AU222" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="AV222" t="inlineStr">
@@ -50278,7 +50278,7 @@
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr">
@@ -50331,7 +50331,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>2026-09-28 22:49:03</t>
+          <t>2026-09-28 23:18:50</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -50564,7 +50564,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>2026-09-28 22:49:03</t>
+          <t>2026-09-28 23:18:50</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -50797,7 +50797,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>2026-09-28 22:49:03</t>
+          <t>2026-09-28 23:18:50</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -51030,7 +51030,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>2026-09-28 22:49:03</t>
+          <t>2026-09-28 23:18:50</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -51297,7 +51297,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
     </row>
@@ -51327,7 +51327,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
     </row>
@@ -51357,7 +51357,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
     </row>
@@ -51387,7 +51387,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
     </row>
@@ -51417,7 +51417,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
     </row>
@@ -51447,7 +51447,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
     </row>
@@ -51477,7 +51477,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
     </row>
@@ -51507,7 +51507,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
     </row>
@@ -51537,7 +51537,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
     </row>
@@ -51567,7 +51567,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
     </row>
@@ -51597,7 +51597,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
     </row>
@@ -51627,7 +51627,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
     </row>
@@ -51657,7 +51657,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
     </row>
@@ -51687,7 +51687,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
     </row>
@@ -51717,7 +51717,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
     </row>
@@ -51747,7 +51747,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
     </row>
@@ -51777,7 +51777,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
     </row>
@@ -51807,7 +51807,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
     </row>
@@ -51837,7 +51837,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
     </row>
@@ -51867,7 +51867,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
     </row>
@@ -51897,7 +51897,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
     </row>
@@ -51927,7 +51927,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
     </row>
@@ -51957,7 +51957,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
     </row>
@@ -51987,7 +51987,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
     </row>
@@ -52017,7 +52017,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
     </row>
@@ -52047,7 +52047,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
     </row>
@@ -52077,7 +52077,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
     </row>
@@ -52107,7 +52107,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
     </row>
@@ -52137,7 +52137,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
     </row>
@@ -52167,7 +52167,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
     </row>
@@ -52197,7 +52197,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
     </row>
@@ -52227,7 +52227,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
     </row>
@@ -52257,7 +52257,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
     </row>
@@ -52287,7 +52287,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
     </row>
@@ -52317,7 +52317,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
     </row>
@@ -52347,7 +52347,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
     </row>
@@ -52377,7 +52377,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
     </row>
@@ -52407,7 +52407,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
     </row>
@@ -52437,7 +52437,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
     </row>
@@ -52467,7 +52467,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
     </row>
@@ -52497,7 +52497,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
     </row>
@@ -52527,7 +52527,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
     </row>
@@ -52557,7 +52557,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
     </row>
@@ -52587,7 +52587,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
     </row>
@@ -52617,7 +52617,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-09-28T22:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-09-28T22:30Z</t>
         </is>
       </c>
     </row>

--- a/src/data/resum_periode_meteocat.xlsx
+++ b/src/data/resum_periode_meteocat.xlsx
@@ -722,17 +722,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-06 09:45:52</t>
+          <t>2026-10-06 10:15:53</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -955,7 +955,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-10-06 09:45:55</t>
+          <t>2026-10-06 10:15:55</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-10-06 09:45:55</t>
+          <t>2026-10-06 10:15:55</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-10-06 09:45:55</t>
+          <t>2026-10-06 10:15:55</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-10-06 09:45:55</t>
+          <t>2026-10-06 10:15:55</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1887,17 +1887,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-06 09:45:58</t>
+          <t>2026-10-06 10:15:58</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-06 09:46:00</t>
+          <t>2026-10-06 10:16:00</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-06 09:46:00</t>
+          <t>2026-10-06 10:16:00</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-06 09:46:00</t>
+          <t>2026-10-06 10:16:00</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-10-06 09:46:00</t>
+          <t>2026-10-06 10:16:00</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -3052,17 +3052,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-10-06 09:46:03</t>
+          <t>2026-10-06 10:16:04</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-10-06 09:46:05</t>
+          <t>2026-10-06 10:16:06</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-10-06 09:46:05</t>
+          <t>2026-10-06 10:16:06</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-10-06 09:46:05</t>
+          <t>2026-10-06 10:16:06</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-10-06 09:46:05</t>
+          <t>2026-10-06 10:16:06</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -4217,17 +4217,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-10-06 09:46:09</t>
+          <t>2026-10-06 10:16:09</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-10-06 09:46:11</t>
+          <t>2026-10-06 10:16:12</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-10-06 09:46:11</t>
+          <t>2026-10-06 10:16:12</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-10-06 09:46:11</t>
+          <t>2026-10-06 10:16:12</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -5149,7 +5149,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-10-06 09:46:11</t>
+          <t>2026-10-06 10:16:12</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -5382,17 +5382,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-10-06 09:46:14</t>
+          <t>2026-10-06 10:16:15</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-10-06 09:46:16</t>
+          <t>2026-10-06 10:16:17</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -5848,7 +5848,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-10-06 09:46:16</t>
+          <t>2026-10-06 10:16:17</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-10-06 09:46:16</t>
+          <t>2026-10-06 10:16:17</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-10-06 09:46:16</t>
+          <t>2026-10-06 10:16:17</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -6547,17 +6547,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-10-06 09:46:18</t>
+          <t>2026-10-06 10:16:21</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-10-06 09:46:20</t>
+          <t>2026-10-06 10:16:23</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -7013,7 +7013,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-10-06 09:46:20</t>
+          <t>2026-10-06 10:16:23</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-10-06 09:46:20</t>
+          <t>2026-10-06 10:16:23</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -7479,7 +7479,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-10-06 09:46:20</t>
+          <t>2026-10-06 10:16:23</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -7712,17 +7712,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-10-06 09:46:23</t>
+          <t>2026-10-06 10:16:26</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -7933,7 +7933,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-10-06 09:46:26</t>
+          <t>2026-10-06 10:16:29</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-10-06 09:46:26</t>
+          <t>2026-10-06 10:16:29</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -8375,7 +8375,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-10-06 09:46:26</t>
+          <t>2026-10-06 10:16:29</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-10-06 09:46:26</t>
+          <t>2026-10-06 10:16:29</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -8817,17 +8817,17 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-10-06 09:46:29</t>
+          <t>2026-10-06 10:16:32</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -9038,7 +9038,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-10-06 09:46:31</t>
+          <t>2026-10-06 10:16:34</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -9259,7 +9259,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-10-06 09:46:31</t>
+          <t>2026-10-06 10:16:34</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -9480,7 +9480,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-10-06 09:46:31</t>
+          <t>2026-10-06 10:16:34</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-10-06 09:46:31</t>
+          <t>2026-10-06 10:16:34</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -9922,17 +9922,17 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-10-06 09:46:33</t>
+          <t>2026-10-06 10:16:38</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -10095,7 +10095,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-10-06 09:46:35</t>
+          <t>2026-10-06 10:16:40</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-10-06 09:46:35</t>
+          <t>2026-10-06 10:16:40</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -10441,7 +10441,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-10-06 09:46:35</t>
+          <t>2026-10-06 10:16:40</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-10-06 09:46:35</t>
+          <t>2026-10-06 10:16:40</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -10787,17 +10787,17 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-10-06 09:46:38</t>
+          <t>2026-10-06 10:16:43</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -10960,7 +10960,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-10-06 09:46:40</t>
+          <t>2026-10-06 10:16:44</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -11133,7 +11133,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-10-06 09:46:40</t>
+          <t>2026-10-06 10:16:44</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -11306,7 +11306,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-10-06 09:46:40</t>
+          <t>2026-10-06 10:16:44</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -11479,7 +11479,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-10-06 09:46:40</t>
+          <t>2026-10-06 10:16:44</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -11652,17 +11652,17 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-10-06 09:46:43</t>
+          <t>2026-10-06 10:16:47</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="K52" t="n">
@@ -11893,7 +11893,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-10-06 09:46:45</t>
+          <t>2026-10-06 10:16:50</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -12134,7 +12134,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-10-06 09:46:45</t>
+          <t>2026-10-06 10:16:50</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -12375,7 +12375,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-10-06 09:46:45</t>
+          <t>2026-10-06 10:16:50</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -12616,7 +12616,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-10-06 09:46:45</t>
+          <t>2026-10-06 10:16:50</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -12857,17 +12857,17 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-10-06 09:46:48</t>
+          <t>2026-10-06 10:16:53</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="K57" t="n">
@@ -13078,7 +13078,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-10-06 09:46:51</t>
+          <t>2026-10-06 10:16:55</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -13299,7 +13299,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-10-06 09:46:51</t>
+          <t>2026-10-06 10:16:55</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -13520,7 +13520,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-10-06 09:46:51</t>
+          <t>2026-10-06 10:16:55</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -13741,7 +13741,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-10-06 09:46:51</t>
+          <t>2026-10-06 10:16:55</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -13962,17 +13962,17 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-10-06 09:46:54</t>
+          <t>2026-10-06 10:16:58</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="K62" t="n">
@@ -14135,7 +14135,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-10-06 09:46:55</t>
+          <t>2026-10-06 10:17:00</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-10-06 09:46:55</t>
+          <t>2026-10-06 10:17:00</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -14481,7 +14481,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-10-06 09:46:55</t>
+          <t>2026-10-06 10:17:00</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -14654,7 +14654,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-10-06 09:46:55</t>
+          <t>2026-10-06 10:17:00</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -14827,17 +14827,17 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-10-06 09:46:59</t>
+          <t>2026-10-06 10:17:04</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="K67" t="n">
@@ -15048,7 +15048,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-10-06 09:47:01</t>
+          <t>2026-10-06 10:17:06</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -15281,7 +15281,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-10-06 09:47:01</t>
+          <t>2026-10-06 10:17:06</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -15514,7 +15514,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-10-06 09:47:01</t>
+          <t>2026-10-06 10:17:06</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -15747,7 +15747,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-10-06 09:47:01</t>
+          <t>2026-10-06 10:17:06</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -15980,17 +15980,17 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-10-06 09:47:04</t>
+          <t>2026-10-06 10:17:09</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="K72" t="n">
@@ -16213,7 +16213,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-10-06 09:47:06</t>
+          <t>2026-10-06 10:17:11</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -16446,7 +16446,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-10-06 09:47:06</t>
+          <t>2026-10-06 10:17:11</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -16679,7 +16679,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-10-06 09:47:06</t>
+          <t>2026-10-06 10:17:11</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -16912,7 +16912,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-10-06 09:47:06</t>
+          <t>2026-10-06 10:17:11</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -17145,17 +17145,17 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-10-06 09:47:09</t>
+          <t>2026-10-06 10:17:13</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="K77" t="n">
@@ -17378,7 +17378,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-10-06 09:47:11</t>
+          <t>2026-10-06 10:17:16</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -17611,7 +17611,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-10-06 09:47:11</t>
+          <t>2026-10-06 10:17:16</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -17844,7 +17844,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-10-06 09:47:11</t>
+          <t>2026-10-06 10:17:16</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -18077,7 +18077,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-10-06 09:47:11</t>
+          <t>2026-10-06 10:17:16</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -18310,17 +18310,17 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-10-06 09:47:14</t>
+          <t>2026-10-06 10:17:18</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="K82" t="n">
@@ -18531,7 +18531,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-10-06 09:47:16</t>
+          <t>2026-10-06 10:17:20</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -18752,7 +18752,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-10-06 09:47:16</t>
+          <t>2026-10-06 10:17:20</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -18973,7 +18973,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-10-06 09:47:16</t>
+          <t>2026-10-06 10:17:20</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -19194,7 +19194,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-10-06 09:47:16</t>
+          <t>2026-10-06 10:17:20</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -19415,17 +19415,17 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-10-06 09:47:19</t>
+          <t>2026-10-06 10:17:22</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="K87" t="n">
@@ -19636,7 +19636,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-10-06 09:47:22</t>
+          <t>2026-10-06 10:17:25</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -19869,7 +19869,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-10-06 09:47:22</t>
+          <t>2026-10-06 10:17:25</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -20102,7 +20102,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-10-06 09:47:22</t>
+          <t>2026-10-06 10:17:25</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -20335,7 +20335,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-10-06 09:47:22</t>
+          <t>2026-10-06 10:17:25</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -20568,17 +20568,17 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-10-06 09:47:25</t>
+          <t>2026-10-06 10:17:28</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="K92" t="n">
@@ -20801,7 +20801,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-10-06 09:47:27</t>
+          <t>2026-10-06 10:17:29</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -21034,7 +21034,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-10-06 09:47:27</t>
+          <t>2026-10-06 10:17:29</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -21267,7 +21267,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-10-06 09:47:27</t>
+          <t>2026-10-06 10:17:29</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -21500,7 +21500,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-10-06 09:47:27</t>
+          <t>2026-10-06 10:17:29</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -21733,17 +21733,17 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-10-06 09:47:30</t>
+          <t>2026-10-06 10:17:33</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="K97" t="n">
@@ -21966,7 +21966,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-10-06 09:47:32</t>
+          <t>2026-10-06 10:17:35</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -22199,7 +22199,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-10-06 09:47:32</t>
+          <t>2026-10-06 10:17:35</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -22432,7 +22432,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-10-06 09:47:32</t>
+          <t>2026-10-06 10:17:35</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -22665,7 +22665,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-10-06 09:47:32</t>
+          <t>2026-10-06 10:17:35</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -22898,17 +22898,17 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-10-06 09:47:35</t>
+          <t>2026-10-06 10:17:38</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="K102" t="n">
@@ -23119,7 +23119,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-10-06 09:47:37</t>
+          <t>2026-10-06 10:17:41</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -23352,7 +23352,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-10-06 09:47:37</t>
+          <t>2026-10-06 10:17:41</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -23585,7 +23585,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-10-06 09:47:37</t>
+          <t>2026-10-06 10:17:41</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -23818,7 +23818,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-10-06 09:47:37</t>
+          <t>2026-10-06 10:17:41</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -24051,17 +24051,17 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-10-06 09:47:40</t>
+          <t>2026-10-06 10:17:44</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="K107" t="n">
@@ -24284,7 +24284,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-10-06 09:47:42</t>
+          <t>2026-10-06 10:17:45</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -24517,7 +24517,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-10-06 09:47:42</t>
+          <t>2026-10-06 10:17:45</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -24750,7 +24750,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-10-06 09:47:42</t>
+          <t>2026-10-06 10:17:45</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -24983,7 +24983,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-10-06 09:47:42</t>
+          <t>2026-10-06 10:17:45</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -25216,17 +25216,17 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-10-06 09:47:45</t>
+          <t>2026-10-06 10:17:48</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="K112" t="n">
@@ -25437,7 +25437,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-10-06 09:47:47</t>
+          <t>2026-10-06 10:17:50</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -25670,7 +25670,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-10-06 09:47:47</t>
+          <t>2026-10-06 10:17:50</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -25903,7 +25903,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-10-06 09:47:47</t>
+          <t>2026-10-06 10:17:50</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -26136,7 +26136,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-10-06 09:47:47</t>
+          <t>2026-10-06 10:17:50</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -26369,17 +26369,17 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-10-06 09:47:50</t>
+          <t>2026-10-06 10:17:53</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="K117" t="n">
@@ -26610,7 +26610,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-10-06 09:47:52</t>
+          <t>2026-10-06 10:17:54</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -26851,7 +26851,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-10-06 09:47:52</t>
+          <t>2026-10-06 10:17:54</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -27092,7 +27092,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-10-06 09:47:52</t>
+          <t>2026-10-06 10:17:54</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -27333,7 +27333,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-10-06 09:47:52</t>
+          <t>2026-10-06 10:17:54</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -27574,17 +27574,17 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-10-06 09:47:55</t>
+          <t>2026-10-06 10:17:57</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="K122" t="n">
@@ -27807,7 +27807,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-10-06 09:47:57</t>
+          <t>2026-10-06 10:17:59</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -28040,7 +28040,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-10-06 09:47:57</t>
+          <t>2026-10-06 10:17:59</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -28273,7 +28273,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-10-06 09:47:57</t>
+          <t>2026-10-06 10:17:59</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -28506,7 +28506,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-10-06 09:47:57</t>
+          <t>2026-10-06 10:17:59</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -28739,17 +28739,17 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-10-06 09:48:00</t>
+          <t>2026-10-06 10:18:01</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="K127" t="n">
@@ -28972,7 +28972,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-10-06 09:48:02</t>
+          <t>2026-10-06 10:18:03</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -29205,7 +29205,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-10-06 09:48:02</t>
+          <t>2026-10-06 10:18:03</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -29438,7 +29438,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-10-06 09:48:02</t>
+          <t>2026-10-06 10:18:03</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -29671,7 +29671,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-10-06 09:48:02</t>
+          <t>2026-10-06 10:18:03</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -29904,17 +29904,17 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-10-06 09:48:05</t>
+          <t>2026-10-06 10:18:06</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="K132" t="n">
@@ -30029,7 +30029,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-10-06 09:48:07</t>
+          <t>2026-10-06 10:18:07</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -30250,7 +30250,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-10-06 09:48:07</t>
+          <t>2026-10-06 10:18:07</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -30471,7 +30471,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-10-06 09:48:07</t>
+          <t>2026-10-06 10:18:07</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -30692,7 +30692,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-10-06 09:48:07</t>
+          <t>2026-10-06 10:18:07</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -30913,17 +30913,17 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-10-06 09:48:11</t>
+          <t>2026-10-06 10:18:09</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="K137" t="n">
@@ -31146,7 +31146,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-10-06 09:48:13</t>
+          <t>2026-10-06 10:18:10</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -31379,7 +31379,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-10-06 09:48:13</t>
+          <t>2026-10-06 10:18:10</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -31612,7 +31612,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-10-06 09:48:13</t>
+          <t>2026-10-06 10:18:10</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -31845,7 +31845,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-10-06 09:48:13</t>
+          <t>2026-10-06 10:18:10</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -32078,17 +32078,17 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-10-06 09:48:16</t>
+          <t>2026-10-06 10:18:12</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="K142" t="n">
@@ -32311,7 +32311,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-10-06 09:48:17</t>
+          <t>2026-10-06 10:18:15</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -32544,7 +32544,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-10-06 09:48:17</t>
+          <t>2026-10-06 10:18:15</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -32777,7 +32777,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-10-06 09:48:17</t>
+          <t>2026-10-06 10:18:15</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -33010,7 +33010,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-10-06 09:48:17</t>
+          <t>2026-10-06 10:18:15</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -33243,17 +33243,17 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-10-06 09:48:20</t>
+          <t>2026-10-06 10:18:18</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="K147" t="n">
@@ -33476,7 +33476,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-10-06 09:48:22</t>
+          <t>2026-10-06 10:18:19</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -33709,7 +33709,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-10-06 09:48:22</t>
+          <t>2026-10-06 10:18:19</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -33942,7 +33942,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-10-06 09:48:22</t>
+          <t>2026-10-06 10:18:19</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -34175,7 +34175,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-10-06 09:48:22</t>
+          <t>2026-10-06 10:18:19</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -34408,17 +34408,17 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-10-06 09:48:25</t>
+          <t>2026-10-06 10:18:21</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="K152" t="n">
@@ -34641,7 +34641,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-10-06 09:48:27</t>
+          <t>2026-10-06 10:18:24</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -34874,7 +34874,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-10-06 09:48:27</t>
+          <t>2026-10-06 10:18:24</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -35107,7 +35107,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-10-06 09:48:27</t>
+          <t>2026-10-06 10:18:24</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -35340,7 +35340,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-10-06 09:48:27</t>
+          <t>2026-10-06 10:18:24</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -35573,17 +35573,17 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-10-06 09:48:30</t>
+          <t>2026-10-06 10:18:26</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="K157" t="n">
@@ -35814,7 +35814,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-10-06 09:48:32</t>
+          <t>2026-10-06 10:18:28</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -36055,7 +36055,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-10-06 09:48:32</t>
+          <t>2026-10-06 10:18:28</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -36296,7 +36296,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-10-06 09:48:32</t>
+          <t>2026-10-06 10:18:28</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -36537,7 +36537,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-10-06 09:48:32</t>
+          <t>2026-10-06 10:18:28</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -36778,17 +36778,17 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-10-06 09:48:35</t>
+          <t>2026-10-06 10:18:30</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="K162" t="n">
@@ -37007,7 +37007,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-10-06 09:48:37</t>
+          <t>2026-10-06 10:18:33</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -37248,7 +37248,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-10-06 09:48:37</t>
+          <t>2026-10-06 10:18:33</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -37489,7 +37489,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-10-06 09:48:37</t>
+          <t>2026-10-06 10:18:33</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -37730,7 +37730,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-10-06 09:48:37</t>
+          <t>2026-10-06 10:18:33</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -37971,17 +37971,17 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-10-06 09:48:40</t>
+          <t>2026-10-06 10:18:35</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="K167" t="n">
@@ -38204,7 +38204,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-10-06 09:48:42</t>
+          <t>2026-10-06 10:18:37</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -38437,7 +38437,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-10-06 09:48:42</t>
+          <t>2026-10-06 10:18:37</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -38670,7 +38670,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-10-06 09:48:42</t>
+          <t>2026-10-06 10:18:37</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -38903,7 +38903,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026-10-06 09:48:42</t>
+          <t>2026-10-06 10:18:37</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -39136,17 +39136,17 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-10-06 09:48:45</t>
+          <t>2026-10-06 10:18:40</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="K172" t="n">
@@ -39357,7 +39357,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-10-06 09:48:47</t>
+          <t>2026-10-06 10:18:41</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -39578,7 +39578,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026-10-06 09:48:47</t>
+          <t>2026-10-06 10:18:41</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -39799,7 +39799,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026-10-06 09:48:47</t>
+          <t>2026-10-06 10:18:41</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -40020,7 +40020,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026-10-06 09:48:47</t>
+          <t>2026-10-06 10:18:41</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -40241,17 +40241,17 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026-10-06 09:48:50</t>
+          <t>2026-10-06 10:18:43</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="K177" t="n">
@@ -40462,7 +40462,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026-10-06 09:48:52</t>
+          <t>2026-10-06 10:18:44</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -40683,7 +40683,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-10-06 09:48:52</t>
+          <t>2026-10-06 10:18:44</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -40904,7 +40904,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-10-06 09:48:52</t>
+          <t>2026-10-06 10:18:44</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -41125,7 +41125,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026-10-06 09:48:52</t>
+          <t>2026-10-06 10:18:44</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -41346,17 +41346,17 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026-10-06 09:48:54</t>
+          <t>2026-10-06 10:18:46</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="K182" t="n">
@@ -41567,7 +41567,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026-10-06 09:48:57</t>
+          <t>2026-10-06 10:18:48</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -41800,7 +41800,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026-10-06 09:48:57</t>
+          <t>2026-10-06 10:18:48</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -42033,7 +42033,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-10-06 09:48:57</t>
+          <t>2026-10-06 10:18:48</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -42266,7 +42266,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-10-06 09:48:57</t>
+          <t>2026-10-06 10:18:48</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -42499,17 +42499,17 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2026-10-06 09:49:00</t>
+          <t>2026-10-06 10:18:52</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="K187" t="n">
@@ -42696,7 +42696,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2026-10-06 09:49:02</t>
+          <t>2026-10-06 10:18:53</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -42893,7 +42893,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2026-10-06 09:49:02</t>
+          <t>2026-10-06 10:18:53</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -43090,7 +43090,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-10-06 09:49:02</t>
+          <t>2026-10-06 10:18:53</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -43287,7 +43287,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-10-06 09:49:02</t>
+          <t>2026-10-06 10:18:53</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -43484,17 +43484,17 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2026-10-06 09:49:05</t>
+          <t>2026-10-06 10:18:56</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="K192" t="n">
@@ -43717,7 +43717,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2026-10-06 09:49:07</t>
+          <t>2026-10-06 10:18:57</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -43950,7 +43950,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2026-10-06 09:49:07</t>
+          <t>2026-10-06 10:18:57</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -44183,7 +44183,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026-10-06 09:49:07</t>
+          <t>2026-10-06 10:18:57</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -44416,7 +44416,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2026-10-06 09:49:07</t>
+          <t>2026-10-06 10:18:57</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -44649,17 +44649,17 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2026-10-06 09:49:10</t>
+          <t>2026-10-06 10:19:00</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="K197" t="n">
@@ -44822,7 +44822,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2026-10-06 09:49:12</t>
+          <t>2026-10-06 10:19:02</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -44995,7 +44995,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2026-10-06 09:49:12</t>
+          <t>2026-10-06 10:19:02</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -45168,7 +45168,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2026-10-06 09:49:12</t>
+          <t>2026-10-06 10:19:02</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -45341,7 +45341,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-10-06 09:49:12</t>
+          <t>2026-10-06 10:19:02</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -45514,17 +45514,17 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>2026-10-06 09:49:15</t>
+          <t>2026-10-06 10:19:06</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="K202" t="n">
@@ -45735,7 +45735,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>2026-10-06 09:49:17</t>
+          <t>2026-10-06 10:19:07</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -45956,7 +45956,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>2026-10-06 09:49:17</t>
+          <t>2026-10-06 10:19:07</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -46177,7 +46177,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>2026-10-06 09:49:17</t>
+          <t>2026-10-06 10:19:07</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -46398,7 +46398,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>2026-10-06 09:49:17</t>
+          <t>2026-10-06 10:19:07</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -46583,17 +46583,17 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>2026-10-06 09:49:20</t>
+          <t>2026-10-06 10:19:10</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="K207" t="n">
@@ -46824,7 +46824,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>2026-10-06 09:49:22</t>
+          <t>2026-10-06 10:19:13</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -47065,7 +47065,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>2026-10-06 09:49:22</t>
+          <t>2026-10-06 10:19:13</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -47306,7 +47306,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>2026-10-06 09:49:22</t>
+          <t>2026-10-06 10:19:13</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -47547,7 +47547,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>2026-10-06 09:49:22</t>
+          <t>2026-10-06 10:19:13</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -47788,17 +47788,17 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>2026-10-06 09:49:25</t>
+          <t>2026-10-06 10:19:15</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="K212" t="n">
@@ -48029,7 +48029,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>2026-10-06 09:49:27</t>
+          <t>2026-10-06 10:19:16</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -48270,7 +48270,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>2026-10-06 09:49:27</t>
+          <t>2026-10-06 10:19:16</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -48511,7 +48511,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>2026-10-06 09:49:27</t>
+          <t>2026-10-06 10:19:16</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -48752,7 +48752,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>2026-10-06 09:49:27</t>
+          <t>2026-10-06 10:19:16</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -48993,17 +48993,17 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>2026-10-06 09:49:31</t>
+          <t>2026-10-06 10:19:18</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="K217" t="n">
@@ -49226,7 +49226,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>2026-10-06 09:49:33</t>
+          <t>2026-10-06 10:19:21</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -49459,7 +49459,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>2026-10-06 09:49:33</t>
+          <t>2026-10-06 10:19:21</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -49692,7 +49692,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>2026-10-06 09:49:33</t>
+          <t>2026-10-06 10:19:21</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -49925,7 +49925,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>2026-10-06 09:49:33</t>
+          <t>2026-10-06 10:19:21</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -50216,7 +50216,7 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -50247,7 +50247,7 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -50278,7 +50278,7 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -50309,7 +50309,7 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -50340,7 +50340,7 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -50371,7 +50371,7 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -50402,7 +50402,7 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -50433,7 +50433,7 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -50464,7 +50464,7 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -50495,7 +50495,7 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -50526,7 +50526,7 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -50557,7 +50557,7 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -50588,7 +50588,7 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -50619,7 +50619,7 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -50650,7 +50650,7 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -50681,7 +50681,7 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -50712,7 +50712,7 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -50743,7 +50743,7 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -50774,7 +50774,7 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -50805,7 +50805,7 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -50836,7 +50836,7 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -50867,7 +50867,7 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -50898,7 +50898,7 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -50929,7 +50929,7 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -50960,7 +50960,7 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -50991,7 +50991,7 @@
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -51022,7 +51022,7 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -51053,7 +51053,7 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -51084,7 +51084,7 @@
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -51115,7 +51115,7 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -51146,7 +51146,7 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -51177,7 +51177,7 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -51208,7 +51208,7 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -51239,7 +51239,7 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -51270,7 +51270,7 @@
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -51301,7 +51301,7 @@
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -51332,7 +51332,7 @@
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -51363,7 +51363,7 @@
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -51394,7 +51394,7 @@
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -51425,7 +51425,7 @@
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -51456,7 +51456,7 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -51487,7 +51487,7 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -51518,7 +51518,7 @@
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -51549,7 +51549,7 @@
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-10-06T09:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-10-06T09:30Z</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">

--- a/src/data/resum_periode_meteocat.xlsx
+++ b/src/data/resum_periode_meteocat.xlsx
@@ -722,17 +722,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-06 10:15:53</t>
+          <t>2026-10-06 10:45:57</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -955,7 +955,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-10-06 10:15:55</t>
+          <t>2026-10-06 10:45:59</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-10-06 10:15:55</t>
+          <t>2026-10-06 10:45:59</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-10-06 10:15:55</t>
+          <t>2026-10-06 10:45:59</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-10-06 10:15:55</t>
+          <t>2026-10-06 10:45:59</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1887,17 +1887,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-06 10:15:58</t>
+          <t>2026-10-06 10:46:02</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-06 10:16:00</t>
+          <t>2026-10-06 10:46:04</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-06 10:16:00</t>
+          <t>2026-10-06 10:46:04</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-06 10:16:00</t>
+          <t>2026-10-06 10:46:04</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-10-06 10:16:00</t>
+          <t>2026-10-06 10:46:04</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -3052,17 +3052,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-10-06 10:16:04</t>
+          <t>2026-10-06 10:46:07</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-10-06 10:16:06</t>
+          <t>2026-10-06 10:46:10</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-10-06 10:16:06</t>
+          <t>2026-10-06 10:46:10</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-10-06 10:16:06</t>
+          <t>2026-10-06 10:46:10</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-10-06 10:16:06</t>
+          <t>2026-10-06 10:46:10</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -4217,17 +4217,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-10-06 10:16:09</t>
+          <t>2026-10-06 10:46:13</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-10-06 10:16:12</t>
+          <t>2026-10-06 10:46:15</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-10-06 10:16:12</t>
+          <t>2026-10-06 10:46:15</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-10-06 10:16:12</t>
+          <t>2026-10-06 10:46:15</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -5149,7 +5149,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-10-06 10:16:12</t>
+          <t>2026-10-06 10:46:15</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -5382,17 +5382,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-10-06 10:16:15</t>
+          <t>2026-10-06 10:46:18</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-10-06 10:16:17</t>
+          <t>2026-10-06 10:46:20</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -5848,7 +5848,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-10-06 10:16:17</t>
+          <t>2026-10-06 10:46:20</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-10-06 10:16:17</t>
+          <t>2026-10-06 10:46:20</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-10-06 10:16:17</t>
+          <t>2026-10-06 10:46:20</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -6532,7 +6532,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:00 - 10:30</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -6547,17 +6547,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-10-06 10:16:21</t>
+          <t>2026-10-06 10:46:23</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -6578,12 +6578,12 @@
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>92</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1018.9</t>
+          <t>1018.7</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -6593,7 +6593,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:00 - 10:30</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -6603,17 +6603,17 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -6632,107 +6632,107 @@
       <c r="AD27" t="inlineStr"/>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:00 - 10:30</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
+          <t>19.6</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>19.4</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="AN27" t="inlineStr">
+        <is>
+          <t>1018.7</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>361</t>
+        </is>
+      </c>
+      <c r="AP27" t="inlineStr">
+        <is>
+          <t>10:00 - 10:30</t>
+        </is>
+      </c>
+      <c r="AQ27" t="inlineStr">
+        <is>
           <t>19.5</t>
         </is>
       </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>19.1</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>19.6</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>19.4</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AV27" t="inlineStr">
         <is>
           <t>6.1</t>
         </is>
       </c>
-      <c r="AL27" t="inlineStr">
+      <c r="AW27" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
+      <c r="AX27" t="inlineStr">
         <is>
           <t>6.1</t>
         </is>
       </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>1018.9</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>361</t>
-        </is>
-      </c>
-      <c r="AP27" t="inlineStr">
-        <is>
-          <t>09:00 - 09:30</t>
-        </is>
-      </c>
-      <c r="AQ27" t="inlineStr">
-        <is>
-          <t>19.3</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>19.5</t>
-        </is>
-      </c>
-      <c r="AS27" t="inlineStr">
-        <is>
-          <t>19.1</t>
-        </is>
-      </c>
-      <c r="AT27" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AV27" t="inlineStr">
-        <is>
-          <t>6.1</t>
-        </is>
-      </c>
-      <c r="AW27" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>6.1</t>
-        </is>
-      </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>1018.9</t>
+          <t>1018.7</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-10-06 10:16:23</t>
+          <t>2026-10-06 10:46:25</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -7013,7 +7013,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-10-06 10:16:23</t>
+          <t>2026-10-06 10:46:25</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-10-06 10:16:23</t>
+          <t>2026-10-06 10:46:25</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -7479,7 +7479,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-10-06 10:16:23</t>
+          <t>2026-10-06 10:46:25</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -7712,17 +7712,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-10-06 10:16:26</t>
+          <t>2026-10-06 10:46:29</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -7933,7 +7933,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-10-06 10:16:29</t>
+          <t>2026-10-06 10:46:31</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-10-06 10:16:29</t>
+          <t>2026-10-06 10:46:31</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -8375,7 +8375,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-10-06 10:16:29</t>
+          <t>2026-10-06 10:46:31</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-10-06 10:16:29</t>
+          <t>2026-10-06 10:46:31</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -8817,17 +8817,17 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-10-06 10:16:32</t>
+          <t>2026-10-06 10:46:34</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -9038,7 +9038,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-10-06 10:16:34</t>
+          <t>2026-10-06 10:46:36</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -9259,7 +9259,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-10-06 10:16:34</t>
+          <t>2026-10-06 10:46:36</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -9480,7 +9480,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-10-06 10:16:34</t>
+          <t>2026-10-06 10:46:36</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-10-06 10:16:34</t>
+          <t>2026-10-06 10:46:36</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -9922,17 +9922,17 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-10-06 10:16:38</t>
+          <t>2026-10-06 10:46:39</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -10095,7 +10095,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-10-06 10:16:40</t>
+          <t>2026-10-06 10:46:41</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-10-06 10:16:40</t>
+          <t>2026-10-06 10:46:41</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -10441,7 +10441,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-10-06 10:16:40</t>
+          <t>2026-10-06 10:46:41</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-10-06 10:16:40</t>
+          <t>2026-10-06 10:46:41</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -10787,17 +10787,17 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-10-06 10:16:43</t>
+          <t>2026-10-06 10:46:44</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -10960,7 +10960,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-10-06 10:16:44</t>
+          <t>2026-10-06 10:46:46</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -11133,7 +11133,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-10-06 10:16:44</t>
+          <t>2026-10-06 10:46:46</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -11306,7 +11306,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-10-06 10:16:44</t>
+          <t>2026-10-06 10:46:46</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -11479,7 +11479,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-10-06 10:16:44</t>
+          <t>2026-10-06 10:46:46</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -11652,17 +11652,17 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-10-06 10:16:47</t>
+          <t>2026-10-06 10:46:50</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="K52" t="n">
@@ -11893,7 +11893,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-10-06 10:16:50</t>
+          <t>2026-10-06 10:46:52</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -12134,7 +12134,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-10-06 10:16:50</t>
+          <t>2026-10-06 10:46:52</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -12375,7 +12375,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-10-06 10:16:50</t>
+          <t>2026-10-06 10:46:52</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -12616,7 +12616,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-10-06 10:16:50</t>
+          <t>2026-10-06 10:46:52</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -12857,17 +12857,17 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-10-06 10:16:53</t>
+          <t>2026-10-06 10:46:55</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="K57" t="n">
@@ -13078,7 +13078,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-10-06 10:16:55</t>
+          <t>2026-10-06 10:46:57</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -13299,7 +13299,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-10-06 10:16:55</t>
+          <t>2026-10-06 10:46:57</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -13520,7 +13520,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-10-06 10:16:55</t>
+          <t>2026-10-06 10:46:57</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -13741,7 +13741,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-10-06 10:16:55</t>
+          <t>2026-10-06 10:46:57</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -13962,17 +13962,17 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-10-06 10:16:58</t>
+          <t>2026-10-06 10:47:00</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="K62" t="n">
@@ -14135,7 +14135,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:00</t>
+          <t>2026-10-06 10:47:02</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:00</t>
+          <t>2026-10-06 10:47:02</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -14481,7 +14481,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:00</t>
+          <t>2026-10-06 10:47:02</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -14654,7 +14654,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:00</t>
+          <t>2026-10-06 10:47:02</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -14827,17 +14827,17 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:04</t>
+          <t>2026-10-06 10:47:05</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="K67" t="n">
@@ -15048,7 +15048,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:06</t>
+          <t>2026-10-06 10:47:07</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -15281,7 +15281,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:06</t>
+          <t>2026-10-06 10:47:07</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -15514,7 +15514,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:06</t>
+          <t>2026-10-06 10:47:07</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -15747,7 +15747,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:06</t>
+          <t>2026-10-06 10:47:07</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -15965,7 +15965,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>08:00 - 08:30</t>
+          <t>09:00 - 09:30</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -15980,17 +15980,17 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:09</t>
+          <t>2026-10-06 10:47:10</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="K72" t="n">
@@ -16026,32 +16026,32 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>08:00 - 08:30</t>
+          <t>09:00 - 09:30</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>362</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="W72" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr"/>
@@ -16065,22 +16065,22 @@
       <c r="AD72" t="inlineStr"/>
       <c r="AE72" t="inlineStr">
         <is>
-          <t>08:00 - 08:30</t>
+          <t>09:00 - 09:30</t>
         </is>
       </c>
       <c r="AF72" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AG72" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="AI72" t="inlineStr">
@@ -16100,7 +16100,7 @@
       </c>
       <c r="AL72" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="AM72" t="inlineStr">
@@ -16115,27 +16115,27 @@
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>362</t>
         </is>
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>08:00 - 08:30</t>
+          <t>09:00 - 09:30</t>
         </is>
       </c>
       <c r="AQ72" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AR72" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr">
@@ -16155,7 +16155,7 @@
       </c>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
@@ -16170,7 +16170,7 @@
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>362</t>
         </is>
       </c>
       <c r="BA72" t="inlineStr"/>
@@ -16213,7 +16213,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:11</t>
+          <t>2026-10-06 10:47:13</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -16446,7 +16446,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:11</t>
+          <t>2026-10-06 10:47:13</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -16679,7 +16679,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:11</t>
+          <t>2026-10-06 10:47:13</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -16912,7 +16912,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:11</t>
+          <t>2026-10-06 10:47:13</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -17145,17 +17145,17 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:13</t>
+          <t>2026-10-06 10:47:16</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="K77" t="n">
@@ -17378,7 +17378,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:16</t>
+          <t>2026-10-06 10:47:18</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -17611,7 +17611,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:16</t>
+          <t>2026-10-06 10:47:18</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -17844,7 +17844,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:16</t>
+          <t>2026-10-06 10:47:18</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -18077,7 +18077,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:16</t>
+          <t>2026-10-06 10:47:18</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -18310,17 +18310,17 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:18</t>
+          <t>2026-10-06 10:47:21</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="K82" t="n">
@@ -18531,7 +18531,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:20</t>
+          <t>2026-10-06 10:47:23</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -18752,7 +18752,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:20</t>
+          <t>2026-10-06 10:47:23</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -18973,7 +18973,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:20</t>
+          <t>2026-10-06 10:47:23</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -19194,7 +19194,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:20</t>
+          <t>2026-10-06 10:47:23</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -19415,17 +19415,17 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:22</t>
+          <t>2026-10-06 10:47:26</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="K87" t="n">
@@ -19636,7 +19636,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:25</t>
+          <t>2026-10-06 10:47:28</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -19869,7 +19869,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:25</t>
+          <t>2026-10-06 10:47:28</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -20102,7 +20102,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:25</t>
+          <t>2026-10-06 10:47:28</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -20335,7 +20335,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:25</t>
+          <t>2026-10-06 10:47:28</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -20568,17 +20568,17 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:28</t>
+          <t>2026-10-06 10:47:31</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="K92" t="n">
@@ -20801,7 +20801,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:29</t>
+          <t>2026-10-06 10:47:33</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -21034,7 +21034,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:29</t>
+          <t>2026-10-06 10:47:33</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -21267,7 +21267,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:29</t>
+          <t>2026-10-06 10:47:33</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -21500,7 +21500,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:29</t>
+          <t>2026-10-06 10:47:33</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -21733,17 +21733,17 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:33</t>
+          <t>2026-10-06 10:47:36</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="K97" t="n">
@@ -21966,7 +21966,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:35</t>
+          <t>2026-10-06 10:47:38</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -22199,7 +22199,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:35</t>
+          <t>2026-10-06 10:47:38</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -22432,7 +22432,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:35</t>
+          <t>2026-10-06 10:47:38</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -22665,7 +22665,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:35</t>
+          <t>2026-10-06 10:47:38</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -22898,17 +22898,17 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:38</t>
+          <t>2026-10-06 10:47:42</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="K102" t="n">
@@ -23119,7 +23119,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:41</t>
+          <t>2026-10-06 10:47:44</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -23352,7 +23352,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:41</t>
+          <t>2026-10-06 10:47:44</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -23585,7 +23585,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:41</t>
+          <t>2026-10-06 10:47:44</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -23818,7 +23818,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:41</t>
+          <t>2026-10-06 10:47:44</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -24051,17 +24051,17 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:44</t>
+          <t>2026-10-06 10:47:47</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="K107" t="n">
@@ -24284,7 +24284,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:45</t>
+          <t>2026-10-06 10:47:48</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -24517,7 +24517,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:45</t>
+          <t>2026-10-06 10:47:48</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -24750,7 +24750,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:45</t>
+          <t>2026-10-06 10:47:48</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -24983,7 +24983,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:45</t>
+          <t>2026-10-06 10:47:48</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -25216,17 +25216,17 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:48</t>
+          <t>2026-10-06 10:47:51</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="K112" t="n">
@@ -25437,7 +25437,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:50</t>
+          <t>2026-10-06 10:47:54</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -25670,7 +25670,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:50</t>
+          <t>2026-10-06 10:47:54</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -25903,7 +25903,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:50</t>
+          <t>2026-10-06 10:47:54</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -26136,7 +26136,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:50</t>
+          <t>2026-10-06 10:47:54</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -26369,17 +26369,17 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:53</t>
+          <t>2026-10-06 10:47:57</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="K117" t="n">
@@ -26610,7 +26610,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:54</t>
+          <t>2026-10-06 10:47:59</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -26851,7 +26851,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:54</t>
+          <t>2026-10-06 10:47:59</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -27092,7 +27092,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:54</t>
+          <t>2026-10-06 10:47:59</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -27333,7 +27333,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:54</t>
+          <t>2026-10-06 10:47:59</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -27574,17 +27574,17 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:57</t>
+          <t>2026-10-06 10:48:02</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="K122" t="n">
@@ -27807,7 +27807,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:59</t>
+          <t>2026-10-06 10:48:04</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -28040,7 +28040,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:59</t>
+          <t>2026-10-06 10:48:04</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -28273,7 +28273,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:59</t>
+          <t>2026-10-06 10:48:04</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -28506,7 +28506,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-10-06 10:17:59</t>
+          <t>2026-10-06 10:48:04</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -28739,17 +28739,17 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:01</t>
+          <t>2026-10-06 10:48:07</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="K127" t="n">
@@ -28972,7 +28972,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:03</t>
+          <t>2026-10-06 10:48:10</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -29205,7 +29205,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:03</t>
+          <t>2026-10-06 10:48:10</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -29438,7 +29438,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:03</t>
+          <t>2026-10-06 10:48:10</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -29671,7 +29671,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:03</t>
+          <t>2026-10-06 10:48:10</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -29904,17 +29904,17 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:06</t>
+          <t>2026-10-06 10:48:12</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="K132" t="n">
@@ -30029,7 +30029,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:07</t>
+          <t>2026-10-06 10:48:14</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -30250,7 +30250,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:07</t>
+          <t>2026-10-06 10:48:14</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -30471,7 +30471,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:07</t>
+          <t>2026-10-06 10:48:14</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -30692,7 +30692,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:07</t>
+          <t>2026-10-06 10:48:14</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -30913,17 +30913,17 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:09</t>
+          <t>2026-10-06 10:48:16</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="K137" t="n">
@@ -31146,7 +31146,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:10</t>
+          <t>2026-10-06 10:48:18</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -31379,7 +31379,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:10</t>
+          <t>2026-10-06 10:48:18</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -31612,7 +31612,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:10</t>
+          <t>2026-10-06 10:48:18</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -31845,7 +31845,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:10</t>
+          <t>2026-10-06 10:48:18</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -32078,17 +32078,17 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:12</t>
+          <t>2026-10-06 10:48:21</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="K142" t="n">
@@ -32311,7 +32311,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:15</t>
+          <t>2026-10-06 10:48:23</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -32544,7 +32544,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:15</t>
+          <t>2026-10-06 10:48:23</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -32777,7 +32777,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:15</t>
+          <t>2026-10-06 10:48:23</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -33010,7 +33010,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:15</t>
+          <t>2026-10-06 10:48:23</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -33243,17 +33243,17 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:18</t>
+          <t>2026-10-06 10:48:27</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="K147" t="n">
@@ -33476,7 +33476,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:19</t>
+          <t>2026-10-06 10:48:29</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -33709,7 +33709,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:19</t>
+          <t>2026-10-06 10:48:29</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -33942,7 +33942,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:19</t>
+          <t>2026-10-06 10:48:29</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -34175,7 +34175,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:19</t>
+          <t>2026-10-06 10:48:29</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -34408,17 +34408,17 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:21</t>
+          <t>2026-10-06 10:48:32</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="K152" t="n">
@@ -34641,7 +34641,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:24</t>
+          <t>2026-10-06 10:48:34</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -34874,7 +34874,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:24</t>
+          <t>2026-10-06 10:48:34</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -35107,7 +35107,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:24</t>
+          <t>2026-10-06 10:48:34</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -35340,7 +35340,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:24</t>
+          <t>2026-10-06 10:48:34</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -35573,17 +35573,17 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:26</t>
+          <t>2026-10-06 10:48:37</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="K157" t="n">
@@ -35814,7 +35814,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:28</t>
+          <t>2026-10-06 10:48:39</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -36055,7 +36055,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:28</t>
+          <t>2026-10-06 10:48:39</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -36296,7 +36296,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:28</t>
+          <t>2026-10-06 10:48:39</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -36537,7 +36537,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:28</t>
+          <t>2026-10-06 10:48:39</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -36778,17 +36778,17 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:30</t>
+          <t>2026-10-06 10:48:42</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="K162" t="n">
@@ -37007,7 +37007,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:33</t>
+          <t>2026-10-06 10:48:45</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -37248,7 +37248,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:33</t>
+          <t>2026-10-06 10:48:45</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -37489,7 +37489,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:33</t>
+          <t>2026-10-06 10:48:45</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -37730,7 +37730,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:33</t>
+          <t>2026-10-06 10:48:45</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -37971,17 +37971,17 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:35</t>
+          <t>2026-10-06 10:48:48</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="K167" t="n">
@@ -38204,7 +38204,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:37</t>
+          <t>2026-10-06 10:48:50</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -38437,7 +38437,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:37</t>
+          <t>2026-10-06 10:48:50</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -38670,7 +38670,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:37</t>
+          <t>2026-10-06 10:48:50</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -38903,7 +38903,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:37</t>
+          <t>2026-10-06 10:48:50</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -39136,17 +39136,17 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:40</t>
+          <t>2026-10-06 10:48:53</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="K172" t="n">
@@ -39357,7 +39357,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:41</t>
+          <t>2026-10-06 10:48:55</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -39578,7 +39578,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:41</t>
+          <t>2026-10-06 10:48:55</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -39799,7 +39799,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:41</t>
+          <t>2026-10-06 10:48:55</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -40020,7 +40020,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:41</t>
+          <t>2026-10-06 10:48:55</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -40241,17 +40241,17 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:43</t>
+          <t>2026-10-06 10:48:58</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="K177" t="n">
@@ -40462,7 +40462,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:44</t>
+          <t>2026-10-06 10:49:00</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -40683,7 +40683,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:44</t>
+          <t>2026-10-06 10:49:00</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -40904,7 +40904,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:44</t>
+          <t>2026-10-06 10:49:00</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -41125,7 +41125,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:44</t>
+          <t>2026-10-06 10:49:00</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -41346,17 +41346,17 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:46</t>
+          <t>2026-10-06 10:49:03</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="K182" t="n">
@@ -41567,7 +41567,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:48</t>
+          <t>2026-10-06 10:49:05</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -41800,7 +41800,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:48</t>
+          <t>2026-10-06 10:49:05</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -42033,7 +42033,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:48</t>
+          <t>2026-10-06 10:49:05</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -42266,7 +42266,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:48</t>
+          <t>2026-10-06 10:49:05</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -42499,17 +42499,17 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:52</t>
+          <t>2026-10-06 10:49:08</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="K187" t="n">
@@ -42696,7 +42696,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:53</t>
+          <t>2026-10-06 10:49:10</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -42893,7 +42893,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:53</t>
+          <t>2026-10-06 10:49:10</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -43090,7 +43090,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:53</t>
+          <t>2026-10-06 10:49:10</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -43287,7 +43287,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:53</t>
+          <t>2026-10-06 10:49:10</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -43484,17 +43484,17 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:56</t>
+          <t>2026-10-06 10:49:13</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="K192" t="n">
@@ -43717,7 +43717,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:57</t>
+          <t>2026-10-06 10:49:15</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -43950,7 +43950,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:57</t>
+          <t>2026-10-06 10:49:15</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -44183,7 +44183,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:57</t>
+          <t>2026-10-06 10:49:15</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -44416,7 +44416,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2026-10-06 10:18:57</t>
+          <t>2026-10-06 10:49:15</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -44649,17 +44649,17 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2026-10-06 10:19:00</t>
+          <t>2026-10-06 10:49:18</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="K197" t="n">
@@ -44822,7 +44822,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2026-10-06 10:19:02</t>
+          <t>2026-10-06 10:49:20</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -44995,7 +44995,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2026-10-06 10:19:02</t>
+          <t>2026-10-06 10:49:20</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -45168,7 +45168,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2026-10-06 10:19:02</t>
+          <t>2026-10-06 10:49:20</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -45341,7 +45341,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-10-06 10:19:02</t>
+          <t>2026-10-06 10:49:20</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -45514,17 +45514,17 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>2026-10-06 10:19:06</t>
+          <t>2026-10-06 10:49:23</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="K202" t="n">
@@ -45735,7 +45735,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>2026-10-06 10:19:07</t>
+          <t>2026-10-06 10:49:25</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -45956,7 +45956,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>2026-10-06 10:19:07</t>
+          <t>2026-10-06 10:49:25</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -46177,7 +46177,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>2026-10-06 10:19:07</t>
+          <t>2026-10-06 10:49:25</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -46398,7 +46398,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>2026-10-06 10:19:07</t>
+          <t>2026-10-06 10:49:25</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -46583,17 +46583,17 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>2026-10-06 10:19:10</t>
+          <t>2026-10-06 10:49:28</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="K207" t="n">
@@ -46824,7 +46824,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>2026-10-06 10:19:13</t>
+          <t>2026-10-06 10:49:31</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -47065,7 +47065,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>2026-10-06 10:19:13</t>
+          <t>2026-10-06 10:49:31</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -47306,7 +47306,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>2026-10-06 10:19:13</t>
+          <t>2026-10-06 10:49:31</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -47547,7 +47547,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>2026-10-06 10:19:13</t>
+          <t>2026-10-06 10:49:31</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -47788,17 +47788,17 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>2026-10-06 10:19:15</t>
+          <t>2026-10-06 10:49:34</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="K212" t="n">
@@ -48029,7 +48029,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>2026-10-06 10:19:16</t>
+          <t>2026-10-06 10:49:36</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -48270,7 +48270,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>2026-10-06 10:19:16</t>
+          <t>2026-10-06 10:49:36</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -48511,7 +48511,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>2026-10-06 10:19:16</t>
+          <t>2026-10-06 10:49:36</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -48752,7 +48752,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>2026-10-06 10:19:16</t>
+          <t>2026-10-06 10:49:36</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -48993,17 +48993,17 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>2026-10-06 10:19:18</t>
+          <t>2026-10-06 10:49:39</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="K217" t="n">
@@ -49226,7 +49226,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>2026-10-06 10:19:21</t>
+          <t>2026-10-06 10:49:41</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -49459,7 +49459,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>2026-10-06 10:19:21</t>
+          <t>2026-10-06 10:49:41</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -49692,7 +49692,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>2026-10-06 10:19:21</t>
+          <t>2026-10-06 10:49:41</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -49925,7 +49925,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>2026-10-06 10:19:21</t>
+          <t>2026-10-06 10:49:41</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -50216,7 +50216,7 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -50247,7 +50247,7 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -50278,7 +50278,7 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -50309,7 +50309,7 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -50340,7 +50340,7 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -50371,7 +50371,7 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -50402,7 +50402,7 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -50433,7 +50433,7 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -50464,7 +50464,7 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -50495,7 +50495,7 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -50526,7 +50526,7 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -50557,7 +50557,7 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -50588,7 +50588,7 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -50619,7 +50619,7 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -50650,7 +50650,7 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -50681,7 +50681,7 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -50712,7 +50712,7 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -50743,7 +50743,7 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -50774,7 +50774,7 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -50805,7 +50805,7 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -50836,7 +50836,7 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -50867,7 +50867,7 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -50898,7 +50898,7 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -50929,7 +50929,7 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -50960,7 +50960,7 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -50991,7 +50991,7 @@
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -51022,7 +51022,7 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -51053,7 +51053,7 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -51084,7 +51084,7 @@
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -51115,7 +51115,7 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -51146,7 +51146,7 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -51177,7 +51177,7 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -51208,7 +51208,7 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -51239,7 +51239,7 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -51270,7 +51270,7 @@
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -51301,7 +51301,7 @@
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -51332,7 +51332,7 @@
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -51363,7 +51363,7 @@
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -51394,7 +51394,7 @@
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -51425,7 +51425,7 @@
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -51456,7 +51456,7 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -51487,7 +51487,7 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -51518,7 +51518,7 @@
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -51549,7 +51549,7 @@
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-10-06T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-10-06T10:00Z</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">

--- a/src/data/resum_periode_meteocat.xlsx
+++ b/src/data/resum_periode_meteocat.xlsx
@@ -722,17 +722,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-06 10:45:57</t>
+          <t>2026-10-06 11:15:51</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -955,7 +955,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-10-06 10:45:59</t>
+          <t>2026-10-06 11:15:53</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-10-06 10:45:59</t>
+          <t>2026-10-06 11:15:53</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-10-06 10:45:59</t>
+          <t>2026-10-06 11:15:53</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-10-06 10:45:59</t>
+          <t>2026-10-06 11:15:53</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1887,17 +1887,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-06 10:46:02</t>
+          <t>2026-10-06 11:15:57</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-06 10:46:04</t>
+          <t>2026-10-06 11:15:59</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-06 10:46:04</t>
+          <t>2026-10-06 11:15:59</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-06 10:46:04</t>
+          <t>2026-10-06 11:15:59</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-10-06 10:46:04</t>
+          <t>2026-10-06 11:15:59</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -3052,17 +3052,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-10-06 10:46:07</t>
+          <t>2026-10-06 11:16:02</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-10-06 10:46:10</t>
+          <t>2026-10-06 11:16:04</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-10-06 10:46:10</t>
+          <t>2026-10-06 11:16:04</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-10-06 10:46:10</t>
+          <t>2026-10-06 11:16:04</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-10-06 10:46:10</t>
+          <t>2026-10-06 11:16:04</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -4217,17 +4217,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-10-06 10:46:13</t>
+          <t>2026-10-06 11:16:07</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-10-06 10:46:15</t>
+          <t>2026-10-06 11:16:10</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-10-06 10:46:15</t>
+          <t>2026-10-06 11:16:10</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-10-06 10:46:15</t>
+          <t>2026-10-06 11:16:10</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -5149,7 +5149,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-10-06 10:46:15</t>
+          <t>2026-10-06 11:16:10</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -5382,17 +5382,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-10-06 10:46:18</t>
+          <t>2026-10-06 11:16:13</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-10-06 10:46:20</t>
+          <t>2026-10-06 11:16:14</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -5848,7 +5848,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-10-06 10:46:20</t>
+          <t>2026-10-06 11:16:14</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-10-06 10:46:20</t>
+          <t>2026-10-06 11:16:14</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-10-06 10:46:20</t>
+          <t>2026-10-06 11:16:14</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -6532,7 +6532,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>10:00 - 10:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -6547,17 +6547,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-10-06 10:46:23</t>
+          <t>2026-10-06 11:16:17</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1018.7</t>
+          <t>1018.3</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -6593,7 +6593,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>10:00 - 10:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -6632,12 +6632,12 @@
       <c r="AD27" t="inlineStr"/>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>10:00 - 10:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
@@ -6647,92 +6647,92 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
+          <t>19.3</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="AN27" t="inlineStr">
+        <is>
+          <t>1018.3</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>361</t>
+        </is>
+      </c>
+      <c r="AP27" t="inlineStr">
+        <is>
+          <t>10:30 - 11:00</t>
+        </is>
+      </c>
+      <c r="AQ27" t="inlineStr">
+        <is>
           <t>19.4</t>
         </is>
       </c>
-      <c r="AI27" t="inlineStr">
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>19.6</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>19.3</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr">
         <is>
           <t>92</t>
         </is>
       </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AV27" t="inlineStr">
         <is>
           <t>6.1</t>
         </is>
       </c>
-      <c r="AL27" t="inlineStr">
+      <c r="AW27" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
+      <c r="AX27" t="inlineStr">
         <is>
           <t>6.1</t>
         </is>
       </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>1018.7</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>361</t>
-        </is>
-      </c>
-      <c r="AP27" t="inlineStr">
-        <is>
-          <t>10:00 - 10:30</t>
-        </is>
-      </c>
-      <c r="AQ27" t="inlineStr">
-        <is>
-          <t>19.5</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>19.6</t>
-        </is>
-      </c>
-      <c r="AS27" t="inlineStr">
-        <is>
-          <t>19.4</t>
-        </is>
-      </c>
-      <c r="AT27" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AV27" t="inlineStr">
-        <is>
-          <t>6.1</t>
-        </is>
-      </c>
-      <c r="AW27" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>6.1</t>
-        </is>
-      </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>1018.7</t>
+          <t>1018.3</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-10-06 10:46:25</t>
+          <t>2026-10-06 11:16:20</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -7013,7 +7013,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-10-06 10:46:25</t>
+          <t>2026-10-06 11:16:20</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-10-06 10:46:25</t>
+          <t>2026-10-06 11:16:20</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -7479,7 +7479,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-10-06 10:46:25</t>
+          <t>2026-10-06 11:16:20</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -7712,17 +7712,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-10-06 10:46:29</t>
+          <t>2026-10-06 11:16:22</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -7933,7 +7933,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-10-06 10:46:31</t>
+          <t>2026-10-06 11:16:24</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-10-06 10:46:31</t>
+          <t>2026-10-06 11:16:24</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -8375,7 +8375,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-10-06 10:46:31</t>
+          <t>2026-10-06 11:16:24</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-10-06 10:46:31</t>
+          <t>2026-10-06 11:16:24</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -8817,17 +8817,17 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-10-06 10:46:34</t>
+          <t>2026-10-06 11:16:27</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -9038,7 +9038,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-10-06 10:46:36</t>
+          <t>2026-10-06 11:16:28</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -9259,7 +9259,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-10-06 10:46:36</t>
+          <t>2026-10-06 11:16:28</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -9480,7 +9480,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-10-06 10:46:36</t>
+          <t>2026-10-06 11:16:28</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-10-06 10:46:36</t>
+          <t>2026-10-06 11:16:28</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -9922,17 +9922,17 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-10-06 10:46:39</t>
+          <t>2026-10-06 11:16:30</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -10095,7 +10095,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-10-06 10:46:41</t>
+          <t>2026-10-06 11:16:31</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-10-06 10:46:41</t>
+          <t>2026-10-06 11:16:31</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -10441,7 +10441,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-10-06 10:46:41</t>
+          <t>2026-10-06 11:16:31</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-10-06 10:46:41</t>
+          <t>2026-10-06 11:16:31</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -10787,17 +10787,17 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-10-06 10:46:44</t>
+          <t>2026-10-06 11:16:34</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -10960,7 +10960,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-10-06 10:46:46</t>
+          <t>2026-10-06 11:16:37</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -11133,7 +11133,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-10-06 10:46:46</t>
+          <t>2026-10-06 11:16:37</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -11306,7 +11306,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-10-06 10:46:46</t>
+          <t>2026-10-06 11:16:37</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -11479,7 +11479,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-10-06 10:46:46</t>
+          <t>2026-10-06 11:16:37</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -11652,17 +11652,17 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-10-06 10:46:50</t>
+          <t>2026-10-06 11:16:40</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="K52" t="n">
@@ -11893,7 +11893,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-10-06 10:46:52</t>
+          <t>2026-10-06 11:16:42</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -12134,7 +12134,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-10-06 10:46:52</t>
+          <t>2026-10-06 11:16:42</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -12375,7 +12375,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-10-06 10:46:52</t>
+          <t>2026-10-06 11:16:42</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -12616,7 +12616,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-10-06 10:46:52</t>
+          <t>2026-10-06 11:16:42</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -12857,17 +12857,17 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-10-06 10:46:55</t>
+          <t>2026-10-06 11:16:45</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="K57" t="n">
@@ -13078,7 +13078,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-10-06 10:46:57</t>
+          <t>2026-10-06 11:16:48</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -13299,7 +13299,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-10-06 10:46:57</t>
+          <t>2026-10-06 11:16:48</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -13520,7 +13520,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-10-06 10:46:57</t>
+          <t>2026-10-06 11:16:48</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -13741,7 +13741,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-10-06 10:46:57</t>
+          <t>2026-10-06 11:16:48</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -13962,17 +13962,17 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-10-06 10:47:00</t>
+          <t>2026-10-06 11:16:51</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="K62" t="n">
@@ -14135,7 +14135,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-10-06 10:47:02</t>
+          <t>2026-10-06 11:16:53</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-10-06 10:47:02</t>
+          <t>2026-10-06 11:16:53</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -14481,7 +14481,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-10-06 10:47:02</t>
+          <t>2026-10-06 11:16:53</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -14654,7 +14654,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-10-06 10:47:02</t>
+          <t>2026-10-06 11:16:53</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -14827,17 +14827,17 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-10-06 10:47:05</t>
+          <t>2026-10-06 11:16:56</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="K67" t="n">
@@ -15048,7 +15048,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-10-06 10:47:07</t>
+          <t>2026-10-06 11:16:59</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -15281,7 +15281,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-10-06 10:47:07</t>
+          <t>2026-10-06 11:16:59</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -15514,7 +15514,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-10-06 10:47:07</t>
+          <t>2026-10-06 11:16:59</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -15747,7 +15747,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-10-06 10:47:07</t>
+          <t>2026-10-06 11:16:59</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -15980,17 +15980,17 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-10-06 10:47:10</t>
+          <t>2026-10-06 11:17:02</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="K72" t="n">
@@ -16213,7 +16213,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-10-06 10:47:13</t>
+          <t>2026-10-06 11:17:04</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -16446,7 +16446,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-10-06 10:47:13</t>
+          <t>2026-10-06 11:17:04</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -16679,7 +16679,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-10-06 10:47:13</t>
+          <t>2026-10-06 11:17:04</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -16912,7 +16912,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-10-06 10:47:13</t>
+          <t>2026-10-06 11:17:04</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -17145,17 +17145,17 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-10-06 10:47:16</t>
+          <t>2026-10-06 11:17:07</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="K77" t="n">
@@ -17378,7 +17378,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-10-06 10:47:18</t>
+          <t>2026-10-06 11:17:09</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -17611,7 +17611,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-10-06 10:47:18</t>
+          <t>2026-10-06 11:17:09</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -17844,7 +17844,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-10-06 10:47:18</t>
+          <t>2026-10-06 11:17:09</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -18077,7 +18077,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-10-06 10:47:18</t>
+          <t>2026-10-06 11:17:09</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -18310,17 +18310,17 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-10-06 10:47:21</t>
+          <t>2026-10-06 11:17:13</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="K82" t="n">
@@ -18531,7 +18531,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-10-06 10:47:23</t>
+          <t>2026-10-06 11:17:15</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -18752,7 +18752,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-10-06 10:47:23</t>
+          <t>2026-10-06 11:17:15</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -18973,7 +18973,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-10-06 10:47:23</t>
+          <t>2026-10-06 11:17:15</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -19194,7 +19194,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-10-06 10:47:23</t>
+          <t>2026-10-06 11:17:15</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -19415,17 +19415,17 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-10-06 10:47:26</t>
+          <t>2026-10-06 11:17:18</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="K87" t="n">
@@ -19636,7 +19636,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-10-06 10:47:28</t>
+          <t>2026-10-06 11:17:20</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -19869,7 +19869,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-10-06 10:47:28</t>
+          <t>2026-10-06 11:17:20</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -20102,7 +20102,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-10-06 10:47:28</t>
+          <t>2026-10-06 11:17:20</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -20335,7 +20335,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-10-06 10:47:28</t>
+          <t>2026-10-06 11:17:20</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -20568,17 +20568,17 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-10-06 10:47:31</t>
+          <t>2026-10-06 11:17:24</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="K92" t="n">
@@ -20801,7 +20801,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-10-06 10:47:33</t>
+          <t>2026-10-06 11:17:26</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -21034,7 +21034,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-10-06 10:47:33</t>
+          <t>2026-10-06 11:17:26</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -21267,7 +21267,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-10-06 10:47:33</t>
+          <t>2026-10-06 11:17:26</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -21500,7 +21500,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-10-06 10:47:33</t>
+          <t>2026-10-06 11:17:26</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -21733,17 +21733,17 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-10-06 10:47:36</t>
+          <t>2026-10-06 11:17:29</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="K97" t="n">
@@ -21966,7 +21966,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-10-06 10:47:38</t>
+          <t>2026-10-06 11:17:31</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -22199,7 +22199,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-10-06 10:47:38</t>
+          <t>2026-10-06 11:17:31</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -22432,7 +22432,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-10-06 10:47:38</t>
+          <t>2026-10-06 11:17:31</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -22665,7 +22665,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-10-06 10:47:38</t>
+          <t>2026-10-06 11:17:31</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -22898,17 +22898,17 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-10-06 10:47:42</t>
+          <t>2026-10-06 11:17:34</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="K102" t="n">
@@ -23119,7 +23119,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-10-06 10:47:44</t>
+          <t>2026-10-06 11:17:37</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -23352,7 +23352,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-10-06 10:47:44</t>
+          <t>2026-10-06 11:17:37</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -23585,7 +23585,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-10-06 10:47:44</t>
+          <t>2026-10-06 11:17:37</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -23818,7 +23818,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-10-06 10:47:44</t>
+          <t>2026-10-06 11:17:37</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -24051,17 +24051,17 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-10-06 10:47:47</t>
+          <t>2026-10-06 11:17:40</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="K107" t="n">
@@ -24284,7 +24284,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-10-06 10:47:48</t>
+          <t>2026-10-06 11:17:42</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -24517,7 +24517,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-10-06 10:47:48</t>
+          <t>2026-10-06 11:17:42</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -24750,7 +24750,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-10-06 10:47:48</t>
+          <t>2026-10-06 11:17:42</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -24983,7 +24983,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-10-06 10:47:48</t>
+          <t>2026-10-06 11:17:42</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -25216,17 +25216,17 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-10-06 10:47:51</t>
+          <t>2026-10-06 11:17:45</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="K112" t="n">
@@ -25437,7 +25437,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-10-06 10:47:54</t>
+          <t>2026-10-06 11:17:47</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -25670,7 +25670,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-10-06 10:47:54</t>
+          <t>2026-10-06 11:17:47</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -25903,7 +25903,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-10-06 10:47:54</t>
+          <t>2026-10-06 11:17:47</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -26136,7 +26136,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-10-06 10:47:54</t>
+          <t>2026-10-06 11:17:47</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -26369,17 +26369,17 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-10-06 10:47:57</t>
+          <t>2026-10-06 11:17:51</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="K117" t="n">
@@ -26610,7 +26610,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-10-06 10:47:59</t>
+          <t>2026-10-06 11:17:53</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -26851,7 +26851,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-10-06 10:47:59</t>
+          <t>2026-10-06 11:17:53</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -27092,7 +27092,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-10-06 10:47:59</t>
+          <t>2026-10-06 11:17:53</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -27333,7 +27333,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-10-06 10:47:59</t>
+          <t>2026-10-06 11:17:53</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -27574,17 +27574,17 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-10-06 10:48:02</t>
+          <t>2026-10-06 11:17:56</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="K122" t="n">
@@ -27807,7 +27807,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-10-06 10:48:04</t>
+          <t>2026-10-06 11:17:58</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -28040,7 +28040,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-10-06 10:48:04</t>
+          <t>2026-10-06 11:17:58</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -28273,7 +28273,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-10-06 10:48:04</t>
+          <t>2026-10-06 11:17:58</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -28506,7 +28506,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-10-06 10:48:04</t>
+          <t>2026-10-06 11:17:58</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -28739,17 +28739,17 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-10-06 10:48:07</t>
+          <t>2026-10-06 11:18:02</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="K127" t="n">
@@ -28972,7 +28972,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-10-06 10:48:10</t>
+          <t>2026-10-06 11:18:04</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -29205,7 +29205,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-10-06 10:48:10</t>
+          <t>2026-10-06 11:18:04</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -29438,7 +29438,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-10-06 10:48:10</t>
+          <t>2026-10-06 11:18:04</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -29671,7 +29671,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-10-06 10:48:10</t>
+          <t>2026-10-06 11:18:04</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -29904,17 +29904,17 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-10-06 10:48:12</t>
+          <t>2026-10-06 11:18:07</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="K132" t="n">
@@ -30029,7 +30029,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-10-06 10:48:14</t>
+          <t>2026-10-06 11:18:09</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -30250,7 +30250,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-10-06 10:48:14</t>
+          <t>2026-10-06 11:18:09</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -30471,7 +30471,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-10-06 10:48:14</t>
+          <t>2026-10-06 11:18:09</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -30692,7 +30692,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-10-06 10:48:14</t>
+          <t>2026-10-06 11:18:09</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -30913,17 +30913,17 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-10-06 10:48:16</t>
+          <t>2026-10-06 11:18:12</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="K137" t="n">
@@ -31146,7 +31146,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-10-06 10:48:18</t>
+          <t>2026-10-06 11:18:15</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -31379,7 +31379,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-10-06 10:48:18</t>
+          <t>2026-10-06 11:18:15</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -31612,7 +31612,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-10-06 10:48:18</t>
+          <t>2026-10-06 11:18:15</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -31845,7 +31845,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-10-06 10:48:18</t>
+          <t>2026-10-06 11:18:15</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -32078,17 +32078,17 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-10-06 10:48:21</t>
+          <t>2026-10-06 11:18:17</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="K142" t="n">
@@ -32311,7 +32311,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-10-06 10:48:23</t>
+          <t>2026-10-06 11:18:19</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -32544,7 +32544,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-10-06 10:48:23</t>
+          <t>2026-10-06 11:18:19</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -32777,7 +32777,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-10-06 10:48:23</t>
+          <t>2026-10-06 11:18:19</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -33010,7 +33010,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-10-06 10:48:23</t>
+          <t>2026-10-06 11:18:19</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -33243,17 +33243,17 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-10-06 10:48:27</t>
+          <t>2026-10-06 11:18:21</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="K147" t="n">
@@ -33476,7 +33476,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-10-06 10:48:29</t>
+          <t>2026-10-06 11:18:23</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -33709,7 +33709,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-10-06 10:48:29</t>
+          <t>2026-10-06 11:18:23</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -33942,7 +33942,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-10-06 10:48:29</t>
+          <t>2026-10-06 11:18:23</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -34175,7 +34175,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-10-06 10:48:29</t>
+          <t>2026-10-06 11:18:23</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -34408,17 +34408,17 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-10-06 10:48:32</t>
+          <t>2026-10-06 11:18:26</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="K152" t="n">
@@ -34641,7 +34641,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-10-06 10:48:34</t>
+          <t>2026-10-06 11:18:28</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -34874,7 +34874,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-10-06 10:48:34</t>
+          <t>2026-10-06 11:18:28</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -35107,7 +35107,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-10-06 10:48:34</t>
+          <t>2026-10-06 11:18:28</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -35340,7 +35340,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-10-06 10:48:34</t>
+          <t>2026-10-06 11:18:28</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -35573,17 +35573,17 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-10-06 10:48:37</t>
+          <t>2026-10-06 11:18:31</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="K157" t="n">
@@ -35814,7 +35814,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-10-06 10:48:39</t>
+          <t>2026-10-06 11:18:33</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -36055,7 +36055,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-10-06 10:48:39</t>
+          <t>2026-10-06 11:18:33</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -36296,7 +36296,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-10-06 10:48:39</t>
+          <t>2026-10-06 11:18:33</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -36537,7 +36537,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-10-06 10:48:39</t>
+          <t>2026-10-06 11:18:33</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -36778,17 +36778,17 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-10-06 10:48:42</t>
+          <t>2026-10-06 11:18:36</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="K162" t="n">
@@ -37007,7 +37007,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-10-06 10:48:45</t>
+          <t>2026-10-06 11:18:39</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -37248,7 +37248,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-10-06 10:48:45</t>
+          <t>2026-10-06 11:18:39</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -37489,7 +37489,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-10-06 10:48:45</t>
+          <t>2026-10-06 11:18:39</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -37730,7 +37730,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-10-06 10:48:45</t>
+          <t>2026-10-06 11:18:39</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -37971,17 +37971,17 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-10-06 10:48:48</t>
+          <t>2026-10-06 11:18:42</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="K167" t="n">
@@ -38204,7 +38204,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-10-06 10:48:50</t>
+          <t>2026-10-06 11:18:44</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -38437,7 +38437,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-10-06 10:48:50</t>
+          <t>2026-10-06 11:18:44</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -38670,7 +38670,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-10-06 10:48:50</t>
+          <t>2026-10-06 11:18:44</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -38903,7 +38903,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026-10-06 10:48:50</t>
+          <t>2026-10-06 11:18:44</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -39136,17 +39136,17 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-10-06 10:48:53</t>
+          <t>2026-10-06 11:18:48</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="K172" t="n">
@@ -39357,7 +39357,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-10-06 10:48:55</t>
+          <t>2026-10-06 11:18:50</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -39578,7 +39578,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026-10-06 10:48:55</t>
+          <t>2026-10-06 11:18:50</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -39799,7 +39799,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026-10-06 10:48:55</t>
+          <t>2026-10-06 11:18:50</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -40020,7 +40020,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026-10-06 10:48:55</t>
+          <t>2026-10-06 11:18:50</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -40241,17 +40241,17 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026-10-06 10:48:58</t>
+          <t>2026-10-06 11:18:53</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="K177" t="n">
@@ -40462,7 +40462,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026-10-06 10:49:00</t>
+          <t>2026-10-06 11:18:55</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -40683,7 +40683,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-10-06 10:49:00</t>
+          <t>2026-10-06 11:18:55</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -40904,7 +40904,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-10-06 10:49:00</t>
+          <t>2026-10-06 11:18:55</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -41125,7 +41125,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026-10-06 10:49:00</t>
+          <t>2026-10-06 11:18:55</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -41346,17 +41346,17 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026-10-06 10:49:03</t>
+          <t>2026-10-06 11:18:58</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="K182" t="n">
@@ -41567,7 +41567,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026-10-06 10:49:05</t>
+          <t>2026-10-06 11:19:01</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -41800,7 +41800,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026-10-06 10:49:05</t>
+          <t>2026-10-06 11:19:01</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -42033,7 +42033,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-10-06 10:49:05</t>
+          <t>2026-10-06 11:19:01</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -42266,7 +42266,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-10-06 10:49:05</t>
+          <t>2026-10-06 11:19:01</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -42499,17 +42499,17 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2026-10-06 10:49:08</t>
+          <t>2026-10-06 11:19:04</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="K187" t="n">
@@ -42696,7 +42696,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2026-10-06 10:49:10</t>
+          <t>2026-10-06 11:19:06</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -42893,7 +42893,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2026-10-06 10:49:10</t>
+          <t>2026-10-06 11:19:06</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -43090,7 +43090,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-10-06 10:49:10</t>
+          <t>2026-10-06 11:19:06</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -43287,7 +43287,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-10-06 10:49:10</t>
+          <t>2026-10-06 11:19:06</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -43484,17 +43484,17 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2026-10-06 10:49:13</t>
+          <t>2026-10-06 11:19:09</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="K192" t="n">
@@ -43717,7 +43717,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2026-10-06 10:49:15</t>
+          <t>2026-10-06 11:19:12</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -43950,7 +43950,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2026-10-06 10:49:15</t>
+          <t>2026-10-06 11:19:12</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -44183,7 +44183,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026-10-06 10:49:15</t>
+          <t>2026-10-06 11:19:12</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -44416,7 +44416,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2026-10-06 10:49:15</t>
+          <t>2026-10-06 11:19:12</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -44649,17 +44649,17 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2026-10-06 10:49:18</t>
+          <t>2026-10-06 11:19:15</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="K197" t="n">
@@ -44822,7 +44822,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2026-10-06 10:49:20</t>
+          <t>2026-10-06 11:19:17</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -44995,7 +44995,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2026-10-06 10:49:20</t>
+          <t>2026-10-06 11:19:17</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -45168,7 +45168,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2026-10-06 10:49:20</t>
+          <t>2026-10-06 11:19:17</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -45341,7 +45341,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-10-06 10:49:20</t>
+          <t>2026-10-06 11:19:17</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -45514,17 +45514,17 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>2026-10-06 10:49:23</t>
+          <t>2026-10-06 11:19:20</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="K202" t="n">
@@ -45735,7 +45735,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>2026-10-06 10:49:25</t>
+          <t>2026-10-06 11:19:22</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -45956,7 +45956,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>2026-10-06 10:49:25</t>
+          <t>2026-10-06 11:19:22</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -46177,7 +46177,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>2026-10-06 10:49:25</t>
+          <t>2026-10-06 11:19:22</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -46398,7 +46398,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>2026-10-06 10:49:25</t>
+          <t>2026-10-06 11:19:22</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -46583,17 +46583,17 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>2026-10-06 10:49:28</t>
+          <t>2026-10-06 11:19:26</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="K207" t="n">
@@ -46824,7 +46824,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>2026-10-06 10:49:31</t>
+          <t>2026-10-06 11:19:28</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -47065,7 +47065,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>2026-10-06 10:49:31</t>
+          <t>2026-10-06 11:19:28</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -47306,7 +47306,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>2026-10-06 10:49:31</t>
+          <t>2026-10-06 11:19:28</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -47547,7 +47547,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>2026-10-06 10:49:31</t>
+          <t>2026-10-06 11:19:28</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -47788,17 +47788,17 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>2026-10-06 10:49:34</t>
+          <t>2026-10-06 11:19:32</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="K212" t="n">
@@ -48029,7 +48029,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>2026-10-06 10:49:36</t>
+          <t>2026-10-06 11:19:34</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -48270,7 +48270,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>2026-10-06 10:49:36</t>
+          <t>2026-10-06 11:19:34</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -48511,7 +48511,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>2026-10-06 10:49:36</t>
+          <t>2026-10-06 11:19:34</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -48752,7 +48752,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>2026-10-06 10:49:36</t>
+          <t>2026-10-06 11:19:34</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -48993,17 +48993,17 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>2026-10-06 10:49:39</t>
+          <t>2026-10-06 11:19:37</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="K217" t="n">
@@ -49226,7 +49226,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>2026-10-06 10:49:41</t>
+          <t>2026-10-06 11:19:40</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -49459,7 +49459,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>2026-10-06 10:49:41</t>
+          <t>2026-10-06 11:19:40</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -49692,7 +49692,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>2026-10-06 10:49:41</t>
+          <t>2026-10-06 11:19:40</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -49925,7 +49925,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>2026-10-06 10:49:41</t>
+          <t>2026-10-06 11:19:40</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -50216,7 +50216,7 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -50247,7 +50247,7 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -50278,7 +50278,7 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -50309,7 +50309,7 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -50340,7 +50340,7 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -50371,7 +50371,7 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -50402,7 +50402,7 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -50433,7 +50433,7 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -50464,7 +50464,7 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -50495,7 +50495,7 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -50526,7 +50526,7 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -50557,7 +50557,7 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -50588,7 +50588,7 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -50619,7 +50619,7 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -50650,7 +50650,7 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -50681,7 +50681,7 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -50712,7 +50712,7 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -50743,7 +50743,7 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -50774,7 +50774,7 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -50805,7 +50805,7 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -50836,7 +50836,7 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -50867,7 +50867,7 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -50898,7 +50898,7 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -50929,7 +50929,7 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -50960,7 +50960,7 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -50991,7 +50991,7 @@
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -51022,7 +51022,7 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -51053,7 +51053,7 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -51084,7 +51084,7 @@
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -51115,7 +51115,7 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -51146,7 +51146,7 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -51177,7 +51177,7 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -51208,7 +51208,7 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -51239,7 +51239,7 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -51270,7 +51270,7 @@
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -51301,7 +51301,7 @@
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -51332,7 +51332,7 @@
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -51363,7 +51363,7 @@
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -51394,7 +51394,7 @@
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -51425,7 +51425,7 @@
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -51456,7 +51456,7 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -51487,7 +51487,7 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -51518,7 +51518,7 @@
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -51549,7 +51549,7 @@
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-10-06T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-10-06T10:30Z</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">

--- a/src/data/resum_periode_meteocat.xlsx
+++ b/src/data/resum_periode_meteocat.xlsx
@@ -722,17 +722,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-06 11:15:51</t>
+          <t>2026-10-06 11:45:52</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -955,7 +955,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-10-06 11:15:53</t>
+          <t>2026-10-06 11:45:54</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-10-06 11:15:53</t>
+          <t>2026-10-06 11:45:54</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-10-06 11:15:53</t>
+          <t>2026-10-06 11:45:54</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-10-06 11:15:53</t>
+          <t>2026-10-06 11:45:54</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1887,17 +1887,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-06 11:15:57</t>
+          <t>2026-10-06 11:45:58</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-06 11:15:59</t>
+          <t>2026-10-06 11:46:00</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-06 11:15:59</t>
+          <t>2026-10-06 11:46:00</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-06 11:15:59</t>
+          <t>2026-10-06 11:46:00</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-10-06 11:15:59</t>
+          <t>2026-10-06 11:46:00</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -3052,17 +3052,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:02</t>
+          <t>2026-10-06 11:46:03</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:04</t>
+          <t>2026-10-06 11:46:05</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:04</t>
+          <t>2026-10-06 11:46:05</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:04</t>
+          <t>2026-10-06 11:46:05</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:04</t>
+          <t>2026-10-06 11:46:05</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -4217,17 +4217,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:07</t>
+          <t>2026-10-06 11:46:08</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:10</t>
+          <t>2026-10-06 11:46:10</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:10</t>
+          <t>2026-10-06 11:46:10</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:10</t>
+          <t>2026-10-06 11:46:10</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -5149,7 +5149,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:10</t>
+          <t>2026-10-06 11:46:10</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -5382,17 +5382,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:13</t>
+          <t>2026-10-06 11:46:14</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:14</t>
+          <t>2026-10-06 11:46:16</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -5848,7 +5848,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:14</t>
+          <t>2026-10-06 11:46:16</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:14</t>
+          <t>2026-10-06 11:46:16</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:14</t>
+          <t>2026-10-06 11:46:16</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -6532,7 +6532,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>10:30 - 11:00</t>
+          <t>11:00 - 11:30</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -6547,17 +6547,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:17</t>
+          <t>2026-10-06 11:46:19</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1018.3</t>
+          <t>1017.8</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -6593,7 +6593,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>10:30 - 11:00</t>
+          <t>11:00 - 11:30</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -6603,17 +6603,17 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -6632,24 +6632,24 @@
       <c r="AD27" t="inlineStr"/>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>10:30 - 11:00</t>
+          <t>11:00 - 11:30</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
           <t>19.6</t>
         </is>
       </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>19.3</t>
-        </is>
-      </c>
       <c r="AI27" t="inlineStr">
         <is>
           <t>92</t>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>1018.3</t>
+          <t>1017.8</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -6687,24 +6687,24 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>10:30 - 11:00</t>
+          <t>11:00 - 11:30</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
           <t>19.6</t>
         </is>
       </c>
-      <c r="AS27" t="inlineStr">
-        <is>
-          <t>19.3</t>
-        </is>
-      </c>
       <c r="AT27" t="inlineStr">
         <is>
           <t>92</t>
@@ -6732,7 +6732,7 @@
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>1018.3</t>
+          <t>1017.8</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:20</t>
+          <t>2026-10-06 11:46:21</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -7013,7 +7013,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:20</t>
+          <t>2026-10-06 11:46:21</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:20</t>
+          <t>2026-10-06 11:46:21</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -7479,7 +7479,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:20</t>
+          <t>2026-10-06 11:46:21</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -7712,17 +7712,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:22</t>
+          <t>2026-10-06 11:46:24</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -7933,7 +7933,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:24</t>
+          <t>2026-10-06 11:46:27</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:24</t>
+          <t>2026-10-06 11:46:27</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -8375,7 +8375,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:24</t>
+          <t>2026-10-06 11:46:27</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:24</t>
+          <t>2026-10-06 11:46:27</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -8817,17 +8817,17 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:27</t>
+          <t>2026-10-06 11:46:30</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -9038,7 +9038,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:28</t>
+          <t>2026-10-06 11:46:32</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -9259,7 +9259,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:28</t>
+          <t>2026-10-06 11:46:32</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -9480,7 +9480,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:28</t>
+          <t>2026-10-06 11:46:32</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:28</t>
+          <t>2026-10-06 11:46:32</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -9922,17 +9922,17 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:30</t>
+          <t>2026-10-06 11:46:34</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -10095,7 +10095,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:31</t>
+          <t>2026-10-06 11:46:36</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:31</t>
+          <t>2026-10-06 11:46:36</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -10441,7 +10441,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:31</t>
+          <t>2026-10-06 11:46:36</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:31</t>
+          <t>2026-10-06 11:46:36</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -10787,17 +10787,17 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:34</t>
+          <t>2026-10-06 11:46:39</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -10960,7 +10960,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:37</t>
+          <t>2026-10-06 11:46:42</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -11133,7 +11133,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:37</t>
+          <t>2026-10-06 11:46:42</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -11306,7 +11306,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:37</t>
+          <t>2026-10-06 11:46:42</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -11479,7 +11479,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:37</t>
+          <t>2026-10-06 11:46:42</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -11652,17 +11652,17 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:40</t>
+          <t>2026-10-06 11:46:45</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="K52" t="n">
@@ -11893,7 +11893,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:42</t>
+          <t>2026-10-06 11:46:47</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -12134,7 +12134,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:42</t>
+          <t>2026-10-06 11:46:47</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -12375,7 +12375,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:42</t>
+          <t>2026-10-06 11:46:47</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -12616,7 +12616,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:42</t>
+          <t>2026-10-06 11:46:47</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -12857,17 +12857,17 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:45</t>
+          <t>2026-10-06 11:46:50</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="K57" t="n">
@@ -13078,7 +13078,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:48</t>
+          <t>2026-10-06 11:46:52</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -13299,7 +13299,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:48</t>
+          <t>2026-10-06 11:46:52</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -13520,7 +13520,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:48</t>
+          <t>2026-10-06 11:46:52</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -13741,7 +13741,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:48</t>
+          <t>2026-10-06 11:46:52</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -13962,17 +13962,17 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:51</t>
+          <t>2026-10-06 11:46:55</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="K62" t="n">
@@ -14135,7 +14135,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:53</t>
+          <t>2026-10-06 11:46:57</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:53</t>
+          <t>2026-10-06 11:46:57</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -14481,7 +14481,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:53</t>
+          <t>2026-10-06 11:46:57</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -14654,7 +14654,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:53</t>
+          <t>2026-10-06 11:46:57</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -14827,17 +14827,17 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:56</t>
+          <t>2026-10-06 11:47:01</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="K67" t="n">
@@ -15048,7 +15048,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:59</t>
+          <t>2026-10-06 11:47:03</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -15281,7 +15281,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:59</t>
+          <t>2026-10-06 11:47:03</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -15514,7 +15514,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:59</t>
+          <t>2026-10-06 11:47:03</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -15747,7 +15747,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:59</t>
+          <t>2026-10-06 11:47:03</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -15980,17 +15980,17 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-10-06 11:17:02</t>
+          <t>2026-10-06 11:47:06</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="K72" t="n">
@@ -16213,7 +16213,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-10-06 11:17:04</t>
+          <t>2026-10-06 11:47:08</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -16446,7 +16446,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-10-06 11:17:04</t>
+          <t>2026-10-06 11:47:08</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -16679,7 +16679,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-10-06 11:17:04</t>
+          <t>2026-10-06 11:47:08</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -16912,7 +16912,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-10-06 11:17:04</t>
+          <t>2026-10-06 11:47:08</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -17145,17 +17145,17 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-10-06 11:17:07</t>
+          <t>2026-10-06 11:47:12</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="K77" t="n">
@@ -17378,7 +17378,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-10-06 11:17:09</t>
+          <t>2026-10-06 11:47:14</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -17611,7 +17611,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-10-06 11:17:09</t>
+          <t>2026-10-06 11:47:14</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -17844,7 +17844,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-10-06 11:17:09</t>
+          <t>2026-10-06 11:47:14</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -18077,7 +18077,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-10-06 11:17:09</t>
+          <t>2026-10-06 11:47:14</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -18310,17 +18310,17 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-10-06 11:17:13</t>
+          <t>2026-10-06 11:47:17</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="K82" t="n">
@@ -18531,7 +18531,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-10-06 11:17:15</t>
+          <t>2026-10-06 11:47:19</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -18752,7 +18752,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-10-06 11:17:15</t>
+          <t>2026-10-06 11:47:19</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -18973,7 +18973,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-10-06 11:17:15</t>
+          <t>2026-10-06 11:47:19</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -19194,7 +19194,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-10-06 11:17:15</t>
+          <t>2026-10-06 11:47:19</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -19415,17 +19415,17 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-10-06 11:17:18</t>
+          <t>2026-10-06 11:47:22</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="K87" t="n">
@@ -19636,7 +19636,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-10-06 11:17:20</t>
+          <t>2026-10-06 11:47:25</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -19869,7 +19869,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-10-06 11:17:20</t>
+          <t>2026-10-06 11:47:25</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -20102,7 +20102,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-10-06 11:17:20</t>
+          <t>2026-10-06 11:47:25</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -20335,7 +20335,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-10-06 11:17:20</t>
+          <t>2026-10-06 11:47:25</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -20568,17 +20568,17 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-10-06 11:17:24</t>
+          <t>2026-10-06 11:47:28</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="K92" t="n">
@@ -20801,7 +20801,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-10-06 11:17:26</t>
+          <t>2026-10-06 11:47:30</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -21034,7 +21034,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-10-06 11:17:26</t>
+          <t>2026-10-06 11:47:30</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -21267,7 +21267,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-10-06 11:17:26</t>
+          <t>2026-10-06 11:47:30</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -21500,7 +21500,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-10-06 11:17:26</t>
+          <t>2026-10-06 11:47:30</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -21733,17 +21733,17 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-10-06 11:17:29</t>
+          <t>2026-10-06 11:47:33</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="K97" t="n">
@@ -21966,7 +21966,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-10-06 11:17:31</t>
+          <t>2026-10-06 11:47:36</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -22199,7 +22199,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-10-06 11:17:31</t>
+          <t>2026-10-06 11:47:36</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -22432,7 +22432,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-10-06 11:17:31</t>
+          <t>2026-10-06 11:47:36</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -22665,7 +22665,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-10-06 11:17:31</t>
+          <t>2026-10-06 11:47:36</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -22898,17 +22898,17 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-10-06 11:17:34</t>
+          <t>2026-10-06 11:47:39</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="K102" t="n">
@@ -23119,7 +23119,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-10-06 11:17:37</t>
+          <t>2026-10-06 11:47:41</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -23352,7 +23352,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-10-06 11:17:37</t>
+          <t>2026-10-06 11:47:41</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -23585,7 +23585,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-10-06 11:17:37</t>
+          <t>2026-10-06 11:47:41</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -23818,7 +23818,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-10-06 11:17:37</t>
+          <t>2026-10-06 11:47:41</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -24051,17 +24051,17 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-10-06 11:17:40</t>
+          <t>2026-10-06 11:47:44</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="K107" t="n">
@@ -24284,7 +24284,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-10-06 11:17:42</t>
+          <t>2026-10-06 11:47:46</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -24517,7 +24517,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-10-06 11:17:42</t>
+          <t>2026-10-06 11:47:46</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -24750,7 +24750,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-10-06 11:17:42</t>
+          <t>2026-10-06 11:47:46</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -24983,7 +24983,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-10-06 11:17:42</t>
+          <t>2026-10-06 11:47:46</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -25216,17 +25216,17 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-10-06 11:17:45</t>
+          <t>2026-10-06 11:47:49</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="K112" t="n">
@@ -25437,7 +25437,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-10-06 11:17:47</t>
+          <t>2026-10-06 11:47:52</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -25670,7 +25670,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-10-06 11:17:47</t>
+          <t>2026-10-06 11:47:52</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -25903,7 +25903,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-10-06 11:17:47</t>
+          <t>2026-10-06 11:47:52</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -26136,7 +26136,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-10-06 11:17:47</t>
+          <t>2026-10-06 11:47:52</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -26369,17 +26369,17 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-10-06 11:17:51</t>
+          <t>2026-10-06 11:47:55</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="K117" t="n">
@@ -26610,7 +26610,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-10-06 11:17:53</t>
+          <t>2026-10-06 11:47:57</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -26851,7 +26851,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-10-06 11:17:53</t>
+          <t>2026-10-06 11:47:57</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -27092,7 +27092,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-10-06 11:17:53</t>
+          <t>2026-10-06 11:47:57</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -27333,7 +27333,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-10-06 11:17:53</t>
+          <t>2026-10-06 11:47:57</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -27574,17 +27574,17 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-10-06 11:17:56</t>
+          <t>2026-10-06 11:48:00</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="K122" t="n">
@@ -27807,7 +27807,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-10-06 11:17:58</t>
+          <t>2026-10-06 11:48:03</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -28040,7 +28040,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-10-06 11:17:58</t>
+          <t>2026-10-06 11:48:03</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -28273,7 +28273,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-10-06 11:17:58</t>
+          <t>2026-10-06 11:48:03</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -28506,7 +28506,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-10-06 11:17:58</t>
+          <t>2026-10-06 11:48:03</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -28739,17 +28739,17 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:02</t>
+          <t>2026-10-06 11:48:06</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="K127" t="n">
@@ -28972,7 +28972,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:04</t>
+          <t>2026-10-06 11:48:07</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -29205,7 +29205,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:04</t>
+          <t>2026-10-06 11:48:07</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -29438,7 +29438,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:04</t>
+          <t>2026-10-06 11:48:07</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -29671,7 +29671,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:04</t>
+          <t>2026-10-06 11:48:07</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -29904,17 +29904,17 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:07</t>
+          <t>2026-10-06 11:48:10</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="K132" t="n">
@@ -30029,7 +30029,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:09</t>
+          <t>2026-10-06 11:48:12</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -30250,7 +30250,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:09</t>
+          <t>2026-10-06 11:48:12</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -30471,7 +30471,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:09</t>
+          <t>2026-10-06 11:48:12</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -30692,7 +30692,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:09</t>
+          <t>2026-10-06 11:48:12</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -30913,17 +30913,17 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:12</t>
+          <t>2026-10-06 11:48:16</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="K137" t="n">
@@ -31146,7 +31146,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:15</t>
+          <t>2026-10-06 11:48:18</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -31379,7 +31379,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:15</t>
+          <t>2026-10-06 11:48:18</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -31612,7 +31612,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:15</t>
+          <t>2026-10-06 11:48:18</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -31845,7 +31845,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:15</t>
+          <t>2026-10-06 11:48:18</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -32078,17 +32078,17 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:17</t>
+          <t>2026-10-06 11:48:21</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="K142" t="n">
@@ -32311,7 +32311,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:19</t>
+          <t>2026-10-06 11:48:23</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -32544,7 +32544,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:19</t>
+          <t>2026-10-06 11:48:23</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -32777,7 +32777,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:19</t>
+          <t>2026-10-06 11:48:23</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -33010,7 +33010,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:19</t>
+          <t>2026-10-06 11:48:23</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -33243,17 +33243,17 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:21</t>
+          <t>2026-10-06 11:48:26</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="K147" t="n">
@@ -33476,7 +33476,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:23</t>
+          <t>2026-10-06 11:48:28</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -33709,7 +33709,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:23</t>
+          <t>2026-10-06 11:48:28</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -33942,7 +33942,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:23</t>
+          <t>2026-10-06 11:48:28</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -34175,7 +34175,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:23</t>
+          <t>2026-10-06 11:48:28</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -34408,17 +34408,17 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:26</t>
+          <t>2026-10-06 11:48:31</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="K152" t="n">
@@ -34641,7 +34641,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:28</t>
+          <t>2026-10-06 11:48:34</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -34874,7 +34874,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:28</t>
+          <t>2026-10-06 11:48:34</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -35107,7 +35107,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:28</t>
+          <t>2026-10-06 11:48:34</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -35340,7 +35340,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:28</t>
+          <t>2026-10-06 11:48:34</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -35573,17 +35573,17 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:31</t>
+          <t>2026-10-06 11:48:36</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="K157" t="n">
@@ -35814,7 +35814,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:33</t>
+          <t>2026-10-06 11:48:38</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -36055,7 +36055,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:33</t>
+          <t>2026-10-06 11:48:38</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -36296,7 +36296,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:33</t>
+          <t>2026-10-06 11:48:38</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -36537,7 +36537,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:33</t>
+          <t>2026-10-06 11:48:38</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -36778,17 +36778,17 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:36</t>
+          <t>2026-10-06 11:48:41</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="K162" t="n">
@@ -37007,7 +37007,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:39</t>
+          <t>2026-10-06 11:48:44</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -37248,7 +37248,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:39</t>
+          <t>2026-10-06 11:48:44</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -37489,7 +37489,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:39</t>
+          <t>2026-10-06 11:48:44</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -37730,7 +37730,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:39</t>
+          <t>2026-10-06 11:48:44</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -37971,17 +37971,17 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:42</t>
+          <t>2026-10-06 11:48:47</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="K167" t="n">
@@ -38204,7 +38204,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:44</t>
+          <t>2026-10-06 11:48:49</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -38437,7 +38437,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:44</t>
+          <t>2026-10-06 11:48:49</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -38670,7 +38670,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:44</t>
+          <t>2026-10-06 11:48:49</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -38903,7 +38903,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:44</t>
+          <t>2026-10-06 11:48:49</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -39136,17 +39136,17 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:48</t>
+          <t>2026-10-06 11:48:51</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="K172" t="n">
@@ -39357,7 +39357,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:50</t>
+          <t>2026-10-06 11:48:54</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -39578,7 +39578,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:50</t>
+          <t>2026-10-06 11:48:54</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -39799,7 +39799,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:50</t>
+          <t>2026-10-06 11:48:54</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -40020,7 +40020,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:50</t>
+          <t>2026-10-06 11:48:54</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -40241,17 +40241,17 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:53</t>
+          <t>2026-10-06 11:48:57</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="K177" t="n">
@@ -40462,7 +40462,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:55</t>
+          <t>2026-10-06 11:48:59</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -40683,7 +40683,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:55</t>
+          <t>2026-10-06 11:48:59</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -40904,7 +40904,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:55</t>
+          <t>2026-10-06 11:48:59</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -41125,7 +41125,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:55</t>
+          <t>2026-10-06 11:48:59</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -41346,17 +41346,17 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:58</t>
+          <t>2026-10-06 11:49:02</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="K182" t="n">
@@ -41567,7 +41567,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026-10-06 11:19:01</t>
+          <t>2026-10-06 11:49:04</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -41800,7 +41800,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026-10-06 11:19:01</t>
+          <t>2026-10-06 11:49:04</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -42033,7 +42033,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-10-06 11:19:01</t>
+          <t>2026-10-06 11:49:04</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -42266,7 +42266,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-10-06 11:19:01</t>
+          <t>2026-10-06 11:49:04</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -42499,17 +42499,17 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2026-10-06 11:19:04</t>
+          <t>2026-10-06 11:49:07</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="K187" t="n">
@@ -42696,7 +42696,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2026-10-06 11:19:06</t>
+          <t>2026-10-06 11:49:09</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -42893,7 +42893,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2026-10-06 11:19:06</t>
+          <t>2026-10-06 11:49:09</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -43090,7 +43090,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-10-06 11:19:06</t>
+          <t>2026-10-06 11:49:09</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -43287,7 +43287,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-10-06 11:19:06</t>
+          <t>2026-10-06 11:49:09</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -43484,17 +43484,17 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2026-10-06 11:19:09</t>
+          <t>2026-10-06 11:49:13</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="K192" t="n">
@@ -43717,7 +43717,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2026-10-06 11:19:12</t>
+          <t>2026-10-06 11:49:15</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -43950,7 +43950,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2026-10-06 11:19:12</t>
+          <t>2026-10-06 11:49:15</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -44183,7 +44183,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026-10-06 11:19:12</t>
+          <t>2026-10-06 11:49:15</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -44416,7 +44416,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2026-10-06 11:19:12</t>
+          <t>2026-10-06 11:49:15</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -44649,17 +44649,17 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2026-10-06 11:19:15</t>
+          <t>2026-10-06 11:49:18</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="K197" t="n">
@@ -44822,7 +44822,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2026-10-06 11:19:17</t>
+          <t>2026-10-06 11:49:20</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -44995,7 +44995,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2026-10-06 11:19:17</t>
+          <t>2026-10-06 11:49:20</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -45168,7 +45168,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2026-10-06 11:19:17</t>
+          <t>2026-10-06 11:49:20</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -45341,7 +45341,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-10-06 11:19:17</t>
+          <t>2026-10-06 11:49:20</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -45514,17 +45514,17 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>2026-10-06 11:19:20</t>
+          <t>2026-10-06 11:49:23</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="K202" t="n">
@@ -45735,7 +45735,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>2026-10-06 11:19:22</t>
+          <t>2026-10-06 11:49:25</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -45956,7 +45956,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>2026-10-06 11:19:22</t>
+          <t>2026-10-06 11:49:25</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -46177,7 +46177,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>2026-10-06 11:19:22</t>
+          <t>2026-10-06 11:49:25</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -46398,7 +46398,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>2026-10-06 11:19:22</t>
+          <t>2026-10-06 11:49:25</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -46583,17 +46583,17 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>2026-10-06 11:19:26</t>
+          <t>2026-10-06 11:49:29</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="K207" t="n">
@@ -46824,7 +46824,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>2026-10-06 11:19:28</t>
+          <t>2026-10-06 11:49:31</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -47065,7 +47065,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>2026-10-06 11:19:28</t>
+          <t>2026-10-06 11:49:31</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -47306,7 +47306,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>2026-10-06 11:19:28</t>
+          <t>2026-10-06 11:49:31</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -47547,7 +47547,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>2026-10-06 11:19:28</t>
+          <t>2026-10-06 11:49:31</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -47788,17 +47788,17 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>2026-10-06 11:19:32</t>
+          <t>2026-10-06 11:49:34</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="K212" t="n">
@@ -48029,7 +48029,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>2026-10-06 11:19:34</t>
+          <t>2026-10-06 11:49:36</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -48270,7 +48270,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>2026-10-06 11:19:34</t>
+          <t>2026-10-06 11:49:36</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -48511,7 +48511,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>2026-10-06 11:19:34</t>
+          <t>2026-10-06 11:49:36</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -48752,7 +48752,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>2026-10-06 11:19:34</t>
+          <t>2026-10-06 11:49:36</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -48993,17 +48993,17 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>2026-10-06 11:19:37</t>
+          <t>2026-10-06 11:49:39</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="K217" t="n">
@@ -49226,7 +49226,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>2026-10-06 11:19:40</t>
+          <t>2026-10-06 11:49:42</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -49459,7 +49459,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>2026-10-06 11:19:40</t>
+          <t>2026-10-06 11:49:42</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -49692,7 +49692,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>2026-10-06 11:19:40</t>
+          <t>2026-10-06 11:49:42</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -49925,7 +49925,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>2026-10-06 11:19:40</t>
+          <t>2026-10-06 11:49:42</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -50216,7 +50216,7 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -50247,7 +50247,7 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -50278,7 +50278,7 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -50309,7 +50309,7 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -50340,7 +50340,7 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -50371,7 +50371,7 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -50402,7 +50402,7 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -50433,7 +50433,7 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -50464,7 +50464,7 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -50495,7 +50495,7 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -50526,7 +50526,7 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -50557,7 +50557,7 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -50588,7 +50588,7 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -50619,7 +50619,7 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -50650,7 +50650,7 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -50681,7 +50681,7 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -50712,7 +50712,7 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -50743,7 +50743,7 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -50774,7 +50774,7 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -50805,7 +50805,7 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -50836,7 +50836,7 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -50867,7 +50867,7 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -50898,7 +50898,7 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -50929,7 +50929,7 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -50960,7 +50960,7 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -50991,7 +50991,7 @@
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -51022,7 +51022,7 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -51053,7 +51053,7 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -51084,7 +51084,7 @@
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -51115,7 +51115,7 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -51146,7 +51146,7 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -51177,7 +51177,7 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -51208,7 +51208,7 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -51239,7 +51239,7 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -51270,7 +51270,7 @@
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -51301,7 +51301,7 @@
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -51332,7 +51332,7 @@
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -51363,7 +51363,7 @@
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -51394,7 +51394,7 @@
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -51425,7 +51425,7 @@
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -51456,7 +51456,7 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -51487,7 +51487,7 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -51518,7 +51518,7 @@
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -51549,7 +51549,7 @@
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-10-06T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-10-06T11:00Z</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">

--- a/src/data/resum_periode_meteocat.xlsx
+++ b/src/data/resum_periode_meteocat.xlsx
@@ -722,17 +722,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-21 08:15:39</t>
+          <t>2026-10-21 08:45:37</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -919,7 +919,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-10-21 08:15:41</t>
+          <t>2026-10-21 08:45:39</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -945,7 +945,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-10-21 08:15:41</t>
+          <t>2026-10-21 08:45:39</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1142,7 +1142,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-10-21 08:15:41</t>
+          <t>2026-10-21 08:45:39</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1339,7 +1339,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-10-21 08:15:41</t>
+          <t>2026-10-21 08:45:39</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1536,7 +1536,7 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-21 08:15:44</t>
+          <t>2026-10-21 08:45:42</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-21 08:15:46</t>
+          <t>2026-10-21 08:45:44</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-21 08:15:46</t>
+          <t>2026-10-21 08:45:44</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-21 08:15:46</t>
+          <t>2026-10-21 08:45:44</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-10-21 08:15:46</t>
+          <t>2026-10-21 08:45:44</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2872,17 +2872,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-10-21 08:15:49</t>
+          <t>2026-10-21 08:45:47</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-10-21 08:15:51</t>
+          <t>2026-10-21 08:45:49</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-10-21 08:15:51</t>
+          <t>2026-10-21 08:45:49</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-10-21 08:15:51</t>
+          <t>2026-10-21 08:45:49</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-10-21 08:15:51</t>
+          <t>2026-10-21 08:45:49</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -4037,17 +4037,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-10-21 08:15:54</t>
+          <t>2026-10-21 08:45:52</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-10-21 08:15:56</t>
+          <t>2026-10-21 08:45:54</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -4300,7 +4300,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-10-21 08:15:56</t>
+          <t>2026-10-21 08:45:54</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -4533,7 +4533,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -4618,7 +4618,7 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-10-21 08:15:56</t>
+          <t>2026-10-21 08:45:54</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-10-21 08:15:56</t>
+          <t>2026-10-21 08:45:54</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -4999,7 +4999,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
@@ -5202,17 +5202,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:00</t>
+          <t>2026-10-21 08:45:57</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:02</t>
+          <t>2026-10-21 08:45:59</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:02</t>
+          <t>2026-10-21 08:45:59</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:02</t>
+          <t>2026-10-21 08:45:59</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:02</t>
+          <t>2026-10-21 08:45:59</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -6367,17 +6367,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:05</t>
+          <t>2026-10-21 08:46:02</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -6600,7 +6600,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:07</t>
+          <t>2026-10-21 08:46:04</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -6833,7 +6833,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:07</t>
+          <t>2026-10-21 08:46:04</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:07</t>
+          <t>2026-10-21 08:46:04</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:07</t>
+          <t>2026-10-21 08:46:04</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -7532,17 +7532,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:10</t>
+          <t>2026-10-21 08:46:07</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -7765,7 +7765,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:11</t>
+          <t>2026-10-21 08:46:09</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:11</t>
+          <t>2026-10-21 08:46:09</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:11</t>
+          <t>2026-10-21 08:46:09</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -8464,7 +8464,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:11</t>
+          <t>2026-10-21 08:46:09</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -8697,17 +8697,17 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:13</t>
+          <t>2026-10-21 08:46:12</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -8918,7 +8918,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:15</t>
+          <t>2026-10-21 08:46:14</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:15</t>
+          <t>2026-10-21 08:46:14</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -9360,7 +9360,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:15</t>
+          <t>2026-10-21 08:46:14</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:15</t>
+          <t>2026-10-21 08:46:14</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -9802,17 +9802,17 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:18</t>
+          <t>2026-10-21 08:46:17</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -10023,7 +10023,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:21</t>
+          <t>2026-10-21 08:46:19</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -10244,7 +10244,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:21</t>
+          <t>2026-10-21 08:46:19</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:21</t>
+          <t>2026-10-21 08:46:19</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -10686,7 +10686,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:21</t>
+          <t>2026-10-21 08:46:19</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -10907,17 +10907,17 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:23</t>
+          <t>2026-10-21 08:46:21</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -11080,7 +11080,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:24</t>
+          <t>2026-10-21 08:46:23</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -11253,7 +11253,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:24</t>
+          <t>2026-10-21 08:46:23</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -11426,7 +11426,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:24</t>
+          <t>2026-10-21 08:46:23</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -11599,7 +11599,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:24</t>
+          <t>2026-10-21 08:46:23</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -11772,17 +11772,17 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:27</t>
+          <t>2026-10-21 08:46:26</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
       <c r="K52" t="n">
@@ -11945,7 +11945,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:29</t>
+          <t>2026-10-21 08:46:28</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:29</t>
+          <t>2026-10-21 08:46:28</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -12291,7 +12291,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:29</t>
+          <t>2026-10-21 08:46:28</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -12464,7 +12464,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:29</t>
+          <t>2026-10-21 08:46:28</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -12637,17 +12637,17 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:32</t>
+          <t>2026-10-21 08:46:31</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
       <c r="K57" t="n">
@@ -12878,7 +12878,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:34</t>
+          <t>2026-10-21 08:46:33</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -12908,7 +12908,7 @@
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
@@ -12997,7 +12997,7 @@
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AL58" t="inlineStr">
@@ -13037,7 +13037,7 @@
       </c>
       <c r="AS58" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr">
@@ -13119,7 +13119,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:34</t>
+          <t>2026-10-21 08:46:33</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -13149,7 +13149,7 @@
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
@@ -13238,7 +13238,7 @@
       </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AL59" t="inlineStr">
@@ -13278,7 +13278,7 @@
       </c>
       <c r="AS59" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:34</t>
+          <t>2026-10-21 08:46:33</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -13390,7 +13390,7 @@
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
@@ -13479,7 +13479,7 @@
       </c>
       <c r="AK60" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AL60" t="inlineStr">
@@ -13519,7 +13519,7 @@
       </c>
       <c r="AS60" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr">
@@ -13601,7 +13601,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:34</t>
+          <t>2026-10-21 08:46:33</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -13631,7 +13631,7 @@
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
@@ -13720,7 +13720,7 @@
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AL61" t="inlineStr">
@@ -13760,7 +13760,7 @@
       </c>
       <c r="AS61" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr">
@@ -13842,17 +13842,17 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:36</t>
+          <t>2026-10-21 08:46:36</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
       <c r="K62" t="n">
@@ -14063,7 +14063,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:39</t>
+          <t>2026-10-21 08:46:38</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -14284,7 +14284,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:39</t>
+          <t>2026-10-21 08:46:38</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -14505,7 +14505,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:39</t>
+          <t>2026-10-21 08:46:38</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -14726,7 +14726,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:39</t>
+          <t>2026-10-21 08:46:38</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -14947,17 +14947,17 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:42</t>
+          <t>2026-10-21 08:46:41</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
       <c r="K67" t="n">
@@ -15120,7 +15120,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:44</t>
+          <t>2026-10-21 08:46:43</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -15293,7 +15293,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:44</t>
+          <t>2026-10-21 08:46:43</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -15466,7 +15466,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:44</t>
+          <t>2026-10-21 08:46:43</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -15639,7 +15639,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:44</t>
+          <t>2026-10-21 08:46:43</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -15812,17 +15812,17 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:47</t>
+          <t>2026-10-21 08:46:45</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
       <c r="K72" t="n">
@@ -16045,7 +16045,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:49</t>
+          <t>2026-10-21 08:46:47</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -16073,7 +16073,11 @@
       </c>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="Q73" t="inlineStr">
         <is>
           <t>41</t>
@@ -16154,7 +16158,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="AK73" t="inlineStr"/>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="AL73" t="inlineStr">
         <is>
           <t>26.3</t>
@@ -16190,7 +16198,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="AS73" t="inlineStr"/>
+      <c r="AS73" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="AT73" t="inlineStr">
         <is>
           <t>26.3</t>
@@ -16266,7 +16278,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:49</t>
+          <t>2026-10-21 08:46:47</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -16296,7 +16308,7 @@
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
@@ -16381,7 +16393,7 @@
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AL74" t="inlineStr">
@@ -16421,7 +16433,7 @@
       </c>
       <c r="AS74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr">
@@ -16499,7 +16511,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:49</t>
+          <t>2026-10-21 08:46:47</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -16529,7 +16541,7 @@
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
@@ -16614,7 +16626,7 @@
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AL75" t="inlineStr">
@@ -16654,7 +16666,7 @@
       </c>
       <c r="AS75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr">
@@ -16732,7 +16744,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:49</t>
+          <t>2026-10-21 08:46:47</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -16762,7 +16774,7 @@
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
@@ -16847,7 +16859,7 @@
       </c>
       <c r="AK76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AL76" t="inlineStr">
@@ -16887,7 +16899,7 @@
       </c>
       <c r="AS76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr">
@@ -16965,17 +16977,17 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:52</t>
+          <t>2026-10-21 08:46:50</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
       <c r="K77" t="n">
@@ -17198,7 +17210,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:54</t>
+          <t>2026-10-21 08:46:52</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -17431,7 +17443,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:54</t>
+          <t>2026-10-21 08:46:52</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -17461,7 +17473,7 @@
       <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
@@ -17546,7 +17558,7 @@
       </c>
       <c r="AK79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AL79" t="inlineStr">
@@ -17586,7 +17598,7 @@
       </c>
       <c r="AS79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr">
@@ -17664,7 +17676,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:54</t>
+          <t>2026-10-21 08:46:52</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -17897,7 +17909,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:54</t>
+          <t>2026-10-21 08:46:52</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -18130,17 +18142,17 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:57</t>
+          <t>2026-10-21 08:46:55</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
       <c r="K82" t="n">
@@ -18363,7 +18375,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:59</t>
+          <t>2026-10-21 08:46:58</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -18596,7 +18608,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:59</t>
+          <t>2026-10-21 08:46:58</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -18829,7 +18841,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:59</t>
+          <t>2026-10-21 08:46:58</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -19062,7 +19074,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-10-21 08:16:59</t>
+          <t>2026-10-21 08:46:58</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -19295,17 +19307,17 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-10-21 08:17:03</t>
+          <t>2026-10-21 08:47:01</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
       <c r="K87" t="n">
@@ -19516,7 +19528,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-10-21 08:17:05</t>
+          <t>2026-10-21 08:47:02</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -19737,7 +19749,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-10-21 08:17:05</t>
+          <t>2026-10-21 08:47:02</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -19958,7 +19970,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-10-21 08:17:05</t>
+          <t>2026-10-21 08:47:02</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -20179,7 +20191,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-10-21 08:17:05</t>
+          <t>2026-10-21 08:47:02</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -20400,17 +20412,17 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-10-21 08:17:08</t>
+          <t>2026-10-21 08:47:05</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
       <c r="K92" t="n">
@@ -20621,7 +20633,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-10-21 08:17:10</t>
+          <t>2026-10-21 08:47:07</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -20649,7 +20661,11 @@
       </c>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr"/>
-      <c r="P93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="Q93" t="inlineStr">
         <is>
           <t>54</t>
@@ -20730,7 +20746,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="AK93" t="inlineStr"/>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AL93" t="inlineStr">
         <is>
           <t>17.3</t>
@@ -20766,7 +20786,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="AS93" t="inlineStr"/>
+      <c r="AS93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AT93" t="inlineStr">
         <is>
           <t>17.3</t>
@@ -20842,7 +20866,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-10-21 08:17:10</t>
+          <t>2026-10-21 08:47:07</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -20870,7 +20894,11 @@
       </c>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr"/>
-      <c r="P94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="Q94" t="inlineStr">
         <is>
           <t>77</t>
@@ -20951,7 +20979,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="AK94" t="inlineStr"/>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AL94" t="inlineStr">
         <is>
           <t>17.3</t>
@@ -20987,7 +21019,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="AS94" t="inlineStr"/>
+      <c r="AS94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AT94" t="inlineStr">
         <is>
           <t>17.3</t>
@@ -21063,7 +21099,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-10-21 08:17:10</t>
+          <t>2026-10-21 08:47:07</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -21091,7 +21127,11 @@
       </c>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr"/>
-      <c r="P95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="Q95" t="inlineStr">
         <is>
           <t>85</t>
@@ -21172,7 +21212,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="AK95" t="inlineStr"/>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AL95" t="inlineStr">
         <is>
           <t>13.3</t>
@@ -21208,7 +21252,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="AS95" t="inlineStr"/>
+      <c r="AS95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AT95" t="inlineStr">
         <is>
           <t>13.3</t>
@@ -21284,7 +21332,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-10-21 08:17:10</t>
+          <t>2026-10-21 08:47:07</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -21312,7 +21360,11 @@
       </c>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr"/>
-      <c r="P96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="Q96" t="inlineStr">
         <is>
           <t>99</t>
@@ -21393,7 +21445,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="AK96" t="inlineStr"/>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AL96" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -21429,7 +21485,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="AS96" t="inlineStr"/>
+      <c r="AS96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AT96" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -21505,17 +21565,17 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-10-21 08:17:13</t>
+          <t>2026-10-21 08:47:10</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
       <c r="K97" t="n">
@@ -21738,7 +21798,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-10-21 08:17:16</t>
+          <t>2026-10-21 08:47:12</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -21971,7 +22031,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-10-21 08:17:16</t>
+          <t>2026-10-21 08:47:12</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -22204,7 +22264,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-10-21 08:17:16</t>
+          <t>2026-10-21 08:47:12</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -22437,7 +22497,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-10-21 08:17:16</t>
+          <t>2026-10-21 08:47:12</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -22670,17 +22730,17 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-10-21 08:17:19</t>
+          <t>2026-10-21 08:47:15</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
       <c r="K102" t="n">
@@ -22903,7 +22963,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-10-21 08:17:21</t>
+          <t>2026-10-21 08:47:17</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -22933,7 +22993,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
@@ -23018,7 +23078,7 @@
       </c>
       <c r="AK103" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AL103" t="inlineStr">
@@ -23058,7 +23118,7 @@
       </c>
       <c r="AS103" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr">
@@ -23136,7 +23196,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-10-21 08:17:21</t>
+          <t>2026-10-21 08:47:17</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -23166,7 +23226,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
@@ -23251,7 +23311,7 @@
       </c>
       <c r="AK104" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AL104" t="inlineStr">
@@ -23291,7 +23351,7 @@
       </c>
       <c r="AS104" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr">
@@ -23369,7 +23429,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-10-21 08:17:21</t>
+          <t>2026-10-21 08:47:17</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -23399,7 +23459,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
@@ -23484,7 +23544,7 @@
       </c>
       <c r="AK105" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AL105" t="inlineStr">
@@ -23524,7 +23584,7 @@
       </c>
       <c r="AS105" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr">
@@ -23602,7 +23662,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-10-21 08:17:21</t>
+          <t>2026-10-21 08:47:17</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -23632,7 +23692,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
@@ -23717,7 +23777,7 @@
       </c>
       <c r="AK106" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AL106" t="inlineStr">
@@ -23757,7 +23817,7 @@
       </c>
       <c r="AS106" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr">
@@ -23835,17 +23895,17 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-10-21 08:17:24</t>
+          <t>2026-10-21 08:47:19</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
       <c r="K107" t="n">
@@ -24068,7 +24128,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-10-21 08:17:25</t>
+          <t>2026-10-21 08:47:21</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -24301,7 +24361,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-10-21 08:17:25</t>
+          <t>2026-10-21 08:47:21</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -24534,7 +24594,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-10-21 08:17:25</t>
+          <t>2026-10-21 08:47:21</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -24564,7 +24624,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
@@ -24649,7 +24709,7 @@
       </c>
       <c r="AK110" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AL110" t="inlineStr">
@@ -24689,7 +24749,7 @@
       </c>
       <c r="AS110" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr">
@@ -24767,7 +24827,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-10-21 08:17:25</t>
+          <t>2026-10-21 08:47:21</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -24797,7 +24857,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
@@ -24882,7 +24942,7 @@
       </c>
       <c r="AK111" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AL111" t="inlineStr">
@@ -24922,7 +24982,7 @@
       </c>
       <c r="AS111" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AT111" t="inlineStr">
@@ -25000,17 +25060,17 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-10-21 08:17:28</t>
+          <t>2026-10-21 08:47:24</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
       <c r="K112" t="n">
@@ -25233,7 +25293,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-10-21 08:17:30</t>
+          <t>2026-10-21 08:47:26</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -25466,7 +25526,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-10-21 08:17:30</t>
+          <t>2026-10-21 08:47:26</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -25699,7 +25759,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-10-21 08:17:30</t>
+          <t>2026-10-21 08:47:26</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -25932,7 +25992,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-10-21 08:17:30</t>
+          <t>2026-10-21 08:47:26</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -26165,17 +26225,17 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-10-21 08:17:32</t>
+          <t>2026-10-21 08:47:29</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
       <c r="K117" t="n">
@@ -26386,7 +26446,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-10-21 08:17:35</t>
+          <t>2026-10-21 08:47:31</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -26414,7 +26474,11 @@
           <t>290</t>
         </is>
       </c>
-      <c r="P118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="Q118" t="inlineStr">
         <is>
           <t>78</t>
@@ -26495,7 +26559,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="AK118" t="inlineStr"/>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AL118" t="inlineStr">
         <is>
           <t>3.2</t>
@@ -26531,7 +26599,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="AS118" t="inlineStr"/>
+      <c r="AS118" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AT118" t="inlineStr">
         <is>
           <t>3.2</t>
@@ -26607,7 +26679,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-10-21 08:17:35</t>
+          <t>2026-10-21 08:47:31</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -26635,7 +26707,11 @@
           <t>324</t>
         </is>
       </c>
-      <c r="P119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="Q119" t="inlineStr">
         <is>
           <t>62</t>
@@ -26716,7 +26792,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="AK119" t="inlineStr"/>
+      <c r="AK119" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AL119" t="inlineStr">
         <is>
           <t>3.6</t>
@@ -26752,7 +26832,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="AS119" t="inlineStr"/>
+      <c r="AS119" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AT119" t="inlineStr">
         <is>
           <t>3.6</t>
@@ -26828,7 +26912,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-10-21 08:17:35</t>
+          <t>2026-10-21 08:47:31</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -26856,7 +26940,11 @@
           <t>16</t>
         </is>
       </c>
-      <c r="P120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="Q120" t="inlineStr">
         <is>
           <t>86</t>
@@ -26937,7 +27025,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="AK120" t="inlineStr"/>
+      <c r="AK120" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AL120" t="inlineStr">
         <is>
           <t>1.1</t>
@@ -26973,7 +27065,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="AS120" t="inlineStr"/>
+      <c r="AS120" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AT120" t="inlineStr">
         <is>
           <t>1.1</t>
@@ -27049,7 +27145,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-10-21 08:17:35</t>
+          <t>2026-10-21 08:47:31</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -27077,7 +27173,11 @@
           <t>31</t>
         </is>
       </c>
-      <c r="P121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="Q121" t="inlineStr">
         <is>
           <t>92</t>
@@ -27158,7 +27258,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="AK121" t="inlineStr"/>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AL121" t="inlineStr">
         <is>
           <t>0.7</t>
@@ -27194,7 +27298,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="AS121" t="inlineStr"/>
+      <c r="AS121" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AT121" t="inlineStr">
         <is>
           <t>0.7</t>
@@ -27270,17 +27378,17 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-10-21 08:17:37</t>
+          <t>2026-10-21 08:47:34</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
       <c r="K122" t="n">
@@ -27511,7 +27619,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-10-21 08:17:40</t>
+          <t>2026-10-21 08:47:36</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -27541,7 +27649,7 @@
       <c r="O123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q123" t="inlineStr">
@@ -27630,7 +27738,7 @@
       </c>
       <c r="AK123" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AL123" t="inlineStr">
@@ -27670,7 +27778,7 @@
       </c>
       <c r="AS123" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AT123" t="inlineStr">
@@ -27752,7 +27860,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-10-21 08:17:40</t>
+          <t>2026-10-21 08:47:36</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -27782,7 +27890,7 @@
       <c r="O124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q124" t="inlineStr">
@@ -27871,7 +27979,7 @@
       </c>
       <c r="AK124" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AL124" t="inlineStr">
@@ -27911,7 +28019,7 @@
       </c>
       <c r="AS124" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr">
@@ -27993,7 +28101,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-10-21 08:17:40</t>
+          <t>2026-10-21 08:47:36</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -28023,7 +28131,7 @@
       <c r="O125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q125" t="inlineStr">
@@ -28112,7 +28220,7 @@
       </c>
       <c r="AK125" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AL125" t="inlineStr">
@@ -28152,7 +28260,7 @@
       </c>
       <c r="AS125" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AT125" t="inlineStr">
@@ -28234,7 +28342,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-10-21 08:17:40</t>
+          <t>2026-10-21 08:47:36</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -28264,7 +28372,7 @@
       <c r="O126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
@@ -28353,7 +28461,7 @@
       </c>
       <c r="AK126" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AL126" t="inlineStr">
@@ -28393,7 +28501,7 @@
       </c>
       <c r="AS126" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AT126" t="inlineStr">
@@ -28475,17 +28583,17 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-10-21 08:17:43</t>
+          <t>2026-10-21 08:47:39</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
       <c r="K127" t="n">
@@ -28708,7 +28816,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-10-21 08:17:45</t>
+          <t>2026-10-21 08:47:41</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -28738,7 +28846,7 @@
       <c r="O128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
@@ -28823,7 +28931,7 @@
       </c>
       <c r="AK128" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AL128" t="inlineStr">
@@ -28863,7 +28971,7 @@
       </c>
       <c r="AS128" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AT128" t="inlineStr">
@@ -28941,7 +29049,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-10-21 08:17:45</t>
+          <t>2026-10-21 08:47:41</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -28971,7 +29079,7 @@
       <c r="O129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q129" t="inlineStr">
@@ -29056,7 +29164,7 @@
       </c>
       <c r="AK129" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AL129" t="inlineStr">
@@ -29096,7 +29204,7 @@
       </c>
       <c r="AS129" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AT129" t="inlineStr">
@@ -29174,7 +29282,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-10-21 08:17:45</t>
+          <t>2026-10-21 08:47:41</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -29407,7 +29515,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-10-21 08:17:45</t>
+          <t>2026-10-21 08:47:41</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -29640,17 +29748,17 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-10-21 08:17:48</t>
+          <t>2026-10-21 08:47:44</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
       <c r="K132" t="n">
@@ -29873,7 +29981,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-10-21 08:17:50</t>
+          <t>2026-10-21 08:47:46</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -30106,7 +30214,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-10-21 08:17:50</t>
+          <t>2026-10-21 08:47:46</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -30339,7 +30447,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-10-21 08:17:50</t>
+          <t>2026-10-21 08:47:46</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -30572,7 +30680,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-10-21 08:17:50</t>
+          <t>2026-10-21 08:47:46</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -30805,17 +30913,17 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-10-21 08:17:52</t>
+          <t>2026-10-21 08:47:49</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
       <c r="K137" t="n">
@@ -31026,7 +31134,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-10-21 08:17:54</t>
+          <t>2026-10-21 08:47:51</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -31247,7 +31355,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-10-21 08:17:54</t>
+          <t>2026-10-21 08:47:51</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -31468,7 +31576,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-10-21 08:17:54</t>
+          <t>2026-10-21 08:47:51</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -31689,7 +31797,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-10-21 08:17:54</t>
+          <t>2026-10-21 08:47:51</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -31910,17 +32018,17 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-10-21 08:17:58</t>
+          <t>2026-10-21 08:47:54</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
       <c r="K142" t="n">
@@ -32143,7 +32251,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:00</t>
+          <t>2026-10-21 08:47:56</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -32376,7 +32484,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:00</t>
+          <t>2026-10-21 08:47:56</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -32609,7 +32717,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:00</t>
+          <t>2026-10-21 08:47:56</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -32842,7 +32950,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:00</t>
+          <t>2026-10-21 08:47:56</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -33075,17 +33183,17 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:03</t>
+          <t>2026-10-21 08:47:59</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
       <c r="K147" t="n">
@@ -33308,7 +33416,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:05</t>
+          <t>2026-10-21 08:48:02</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -33541,7 +33649,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:05</t>
+          <t>2026-10-21 08:48:02</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -33774,7 +33882,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:05</t>
+          <t>2026-10-21 08:48:02</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -34007,7 +34115,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:05</t>
+          <t>2026-10-21 08:48:02</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -34240,17 +34348,17 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:08</t>
+          <t>2026-10-21 08:48:04</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
       <c r="K152" t="n">
@@ -34473,7 +34581,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:10</t>
+          <t>2026-10-21 08:48:06</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -34503,7 +34611,7 @@
       <c r="O153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q153" t="inlineStr">
@@ -34588,7 +34696,7 @@
       </c>
       <c r="AK153" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AL153" t="inlineStr">
@@ -34628,7 +34736,7 @@
       </c>
       <c r="AS153" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AT153" t="inlineStr">
@@ -34706,7 +34814,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:10</t>
+          <t>2026-10-21 08:48:06</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -34736,7 +34844,7 @@
       <c r="O154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q154" t="inlineStr">
@@ -34821,7 +34929,7 @@
       </c>
       <c r="AK154" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AL154" t="inlineStr">
@@ -34861,7 +34969,7 @@
       </c>
       <c r="AS154" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AT154" t="inlineStr">
@@ -34939,7 +35047,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:10</t>
+          <t>2026-10-21 08:48:06</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -34969,7 +35077,7 @@
       <c r="O155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q155" t="inlineStr">
@@ -35054,7 +35162,7 @@
       </c>
       <c r="AK155" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AL155" t="inlineStr">
@@ -35094,7 +35202,7 @@
       </c>
       <c r="AS155" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AT155" t="inlineStr">
@@ -35172,7 +35280,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:10</t>
+          <t>2026-10-21 08:48:06</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -35202,7 +35310,7 @@
       <c r="O156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q156" t="inlineStr">
@@ -35287,7 +35395,7 @@
       </c>
       <c r="AK156" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AL156" t="inlineStr">
@@ -35327,7 +35435,7 @@
       </c>
       <c r="AS156" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AT156" t="inlineStr">
@@ -35405,17 +35513,17 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:13</t>
+          <t>2026-10-21 08:48:09</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
       <c r="K157" t="n">
@@ -35638,7 +35746,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:15</t>
+          <t>2026-10-21 08:48:11</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -35871,7 +35979,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:15</t>
+          <t>2026-10-21 08:48:11</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -36104,7 +36212,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:15</t>
+          <t>2026-10-21 08:48:11</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -36337,7 +36445,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:15</t>
+          <t>2026-10-21 08:48:11</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -36570,17 +36678,17 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:18</t>
+          <t>2026-10-21 08:48:14</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
       <c r="K162" t="n">
@@ -36811,7 +36919,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:20</t>
+          <t>2026-10-21 08:48:16</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -36841,7 +36949,7 @@
       <c r="O163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q163" t="inlineStr">
@@ -36930,7 +37038,7 @@
       </c>
       <c r="AK163" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AL163" t="inlineStr">
@@ -36970,7 +37078,7 @@
       </c>
       <c r="AS163" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AT163" t="inlineStr">
@@ -37052,7 +37160,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:20</t>
+          <t>2026-10-21 08:48:16</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -37082,7 +37190,7 @@
       <c r="O164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q164" t="inlineStr">
@@ -37171,7 +37279,7 @@
       </c>
       <c r="AK164" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AL164" t="inlineStr">
@@ -37211,7 +37319,7 @@
       </c>
       <c r="AS164" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AT164" t="inlineStr">
@@ -37293,7 +37401,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:20</t>
+          <t>2026-10-21 08:48:16</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -37323,7 +37431,7 @@
       <c r="O165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q165" t="inlineStr">
@@ -37412,7 +37520,7 @@
       </c>
       <c r="AK165" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AL165" t="inlineStr">
@@ -37452,7 +37560,7 @@
       </c>
       <c r="AS165" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AT165" t="inlineStr">
@@ -37534,7 +37642,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:20</t>
+          <t>2026-10-21 08:48:16</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -37564,7 +37672,7 @@
       <c r="O166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q166" t="inlineStr">
@@ -37653,7 +37761,7 @@
       </c>
       <c r="AK166" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AL166" t="inlineStr">
@@ -37693,7 +37801,7 @@
       </c>
       <c r="AS166" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AT166" t="inlineStr">
@@ -37775,17 +37883,17 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:23</t>
+          <t>2026-10-21 08:48:19</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
       <c r="K167" t="n">
@@ -38004,7 +38112,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:26</t>
+          <t>2026-10-21 08:48:21</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -38032,7 +38140,11 @@
       </c>
       <c r="N168" t="inlineStr"/>
       <c r="O168" t="inlineStr"/>
-      <c r="P168" t="inlineStr"/>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="Q168" t="inlineStr">
         <is>
           <t>72</t>
@@ -38117,7 +38229,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="AK168" t="inlineStr"/>
+      <c r="AK168" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AL168" t="inlineStr">
         <is>
           <t>23.4</t>
@@ -38153,7 +38269,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="AS168" t="inlineStr"/>
+      <c r="AS168" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AT168" t="inlineStr">
         <is>
           <t>23.4</t>
@@ -38233,7 +38353,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:26</t>
+          <t>2026-10-21 08:48:21</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -38261,7 +38381,11 @@
       </c>
       <c r="N169" t="inlineStr"/>
       <c r="O169" t="inlineStr"/>
-      <c r="P169" t="inlineStr"/>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="Q169" t="inlineStr">
         <is>
           <t>71</t>
@@ -38346,7 +38470,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="AK169" t="inlineStr"/>
+      <c r="AK169" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AL169" t="inlineStr">
         <is>
           <t>22.0</t>
@@ -38382,7 +38510,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="AS169" t="inlineStr"/>
+      <c r="AS169" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AT169" t="inlineStr">
         <is>
           <t>22.0</t>
@@ -38462,7 +38594,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:26</t>
+          <t>2026-10-21 08:48:21</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -38490,7 +38622,11 @@
       </c>
       <c r="N170" t="inlineStr"/>
       <c r="O170" t="inlineStr"/>
-      <c r="P170" t="inlineStr"/>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="Q170" t="inlineStr">
         <is>
           <t>68</t>
@@ -38575,7 +38711,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="AK170" t="inlineStr"/>
+      <c r="AK170" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AL170" t="inlineStr">
         <is>
           <t>22.3</t>
@@ -38611,7 +38751,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="AS170" t="inlineStr"/>
+      <c r="AS170" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AT170" t="inlineStr">
         <is>
           <t>22.3</t>
@@ -38691,7 +38835,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:26</t>
+          <t>2026-10-21 08:48:21</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -38719,7 +38863,11 @@
       </c>
       <c r="N171" t="inlineStr"/>
       <c r="O171" t="inlineStr"/>
-      <c r="P171" t="inlineStr"/>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="Q171" t="inlineStr">
         <is>
           <t>69</t>
@@ -38804,7 +38952,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="AK171" t="inlineStr"/>
+      <c r="AK171" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AL171" t="inlineStr">
         <is>
           <t>21.6</t>
@@ -38840,7 +38992,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="AS171" t="inlineStr"/>
+      <c r="AS171" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AT171" t="inlineStr">
         <is>
           <t>21.6</t>
@@ -38920,17 +39076,17 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:28</t>
+          <t>2026-10-21 08:48:24</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
       <c r="K172" t="n">
@@ -39153,7 +39309,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:31</t>
+          <t>2026-10-21 08:48:26</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -39182,10 +39338,14 @@
       <c r="N173" t="inlineStr"/>
       <c r="O173" t="inlineStr"/>
       <c r="P173" t="inlineStr"/>
-      <c r="Q173" t="inlineStr"/>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="R173" t="inlineStr">
         <is>
-          <t>1012.2</t>
+          <t>1012.3</t>
         </is>
       </c>
       <c r="S173" t="inlineStr">
@@ -39203,9 +39363,21 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V173" t="inlineStr"/>
-      <c r="W173" t="inlineStr"/>
-      <c r="X173" t="inlineStr"/>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>13.8</t>
+        </is>
+      </c>
+      <c r="W173" t="inlineStr">
+        <is>
+          <t>13.4</t>
+        </is>
+      </c>
+      <c r="X173" t="inlineStr">
+        <is>
+          <t>14.1</t>
+        </is>
+      </c>
       <c r="Y173" t="inlineStr">
         <is>
           <t>3.6</t>
@@ -39225,10 +39397,26 @@
           <t>23:30 - 00:00</t>
         </is>
       </c>
-      <c r="AF173" t="inlineStr"/>
-      <c r="AG173" t="inlineStr"/>
-      <c r="AH173" t="inlineStr"/>
-      <c r="AI173" t="inlineStr"/>
+      <c r="AF173" t="inlineStr">
+        <is>
+          <t>13.8</t>
+        </is>
+      </c>
+      <c r="AG173" t="inlineStr">
+        <is>
+          <t>14.1</t>
+        </is>
+      </c>
+      <c r="AH173" t="inlineStr">
+        <is>
+          <t>13.4</t>
+        </is>
+      </c>
+      <c r="AI173" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="AJ173" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -39249,10 +39437,26 @@
           <t>23:30 - 00:00</t>
         </is>
       </c>
-      <c r="AN173" t="inlineStr"/>
-      <c r="AO173" t="inlineStr"/>
-      <c r="AP173" t="inlineStr"/>
-      <c r="AQ173" t="inlineStr"/>
+      <c r="AN173" t="inlineStr">
+        <is>
+          <t>13.8</t>
+        </is>
+      </c>
+      <c r="AO173" t="inlineStr">
+        <is>
+          <t>14.1</t>
+        </is>
+      </c>
+      <c r="AP173" t="inlineStr">
+        <is>
+          <t>13.4</t>
+        </is>
+      </c>
+      <c r="AQ173" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="AR173" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -39275,7 +39479,7 @@
       </c>
       <c r="AV173" t="inlineStr">
         <is>
-          <t>1012.2</t>
+          <t>1012.3</t>
         </is>
       </c>
       <c r="AW173" t="inlineStr">
@@ -39290,7 +39494,7 @@
       </c>
       <c r="AY173" t="inlineStr">
         <is>
-          <t>1012.2</t>
+          <t>1012.3</t>
         </is>
       </c>
       <c r="AZ173" t="inlineStr">
@@ -39338,7 +39542,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:31</t>
+          <t>2026-10-21 08:48:26</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -39571,7 +39775,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:31</t>
+          <t>2026-10-21 08:48:26</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -39804,7 +40008,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:31</t>
+          <t>2026-10-21 08:48:26</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -40037,17 +40241,17 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:33</t>
+          <t>2026-10-21 08:48:28</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
       <c r="K177" t="n">
@@ -40258,7 +40462,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:35</t>
+          <t>2026-10-21 08:48:30</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -40479,7 +40683,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:35</t>
+          <t>2026-10-21 08:48:30</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -40700,7 +40904,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:35</t>
+          <t>2026-10-21 08:48:30</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -40921,7 +41125,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:35</t>
+          <t>2026-10-21 08:48:30</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -41142,17 +41346,17 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:37</t>
+          <t>2026-10-21 08:48:33</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
       <c r="K182" t="n">
@@ -41363,7 +41567,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:39</t>
+          <t>2026-10-21 08:48:35</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -41584,7 +41788,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:39</t>
+          <t>2026-10-21 08:48:35</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -41805,7 +42009,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:39</t>
+          <t>2026-10-21 08:48:35</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -42026,7 +42230,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:39</t>
+          <t>2026-10-21 08:48:35</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -42247,17 +42451,17 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:43</t>
+          <t>2026-10-21 08:48:38</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
       <c r="K187" t="n">
@@ -42480,7 +42684,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:44</t>
+          <t>2026-10-21 08:48:40</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -42508,7 +42712,11 @@
       </c>
       <c r="N188" t="inlineStr"/>
       <c r="O188" t="inlineStr"/>
-      <c r="P188" t="inlineStr"/>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="Q188" t="inlineStr">
         <is>
           <t>49</t>
@@ -42589,7 +42797,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="AK188" t="inlineStr"/>
+      <c r="AK188" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AL188" t="inlineStr">
         <is>
           <t>15.5</t>
@@ -42625,7 +42837,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="AS188" t="inlineStr"/>
+      <c r="AS188" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AT188" t="inlineStr">
         <is>
           <t>15.5</t>
@@ -42701,7 +42917,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:44</t>
+          <t>2026-10-21 08:48:40</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -42729,7 +42945,11 @@
       </c>
       <c r="N189" t="inlineStr"/>
       <c r="O189" t="inlineStr"/>
-      <c r="P189" t="inlineStr"/>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="Q189" t="inlineStr">
         <is>
           <t>61</t>
@@ -42810,7 +43030,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="AK189" t="inlineStr"/>
+      <c r="AK189" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AL189" t="inlineStr">
         <is>
           <t>15.1</t>
@@ -42846,7 +43070,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="AS189" t="inlineStr"/>
+      <c r="AS189" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AT189" t="inlineStr">
         <is>
           <t>15.1</t>
@@ -42922,7 +43150,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:44</t>
+          <t>2026-10-21 08:48:40</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -42950,7 +43178,11 @@
       </c>
       <c r="N190" t="inlineStr"/>
       <c r="O190" t="inlineStr"/>
-      <c r="P190" t="inlineStr"/>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="Q190" t="inlineStr">
         <is>
           <t>71</t>
@@ -43031,7 +43263,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="AK190" t="inlineStr"/>
+      <c r="AK190" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AL190" t="inlineStr">
         <is>
           <t>12.6</t>
@@ -43067,7 +43303,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="AS190" t="inlineStr"/>
+      <c r="AS190" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AT190" t="inlineStr">
         <is>
           <t>12.6</t>
@@ -43143,7 +43383,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:44</t>
+          <t>2026-10-21 08:48:40</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -43171,7 +43411,11 @@
       </c>
       <c r="N191" t="inlineStr"/>
       <c r="O191" t="inlineStr"/>
-      <c r="P191" t="inlineStr"/>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="Q191" t="inlineStr">
         <is>
           <t>77</t>
@@ -43252,7 +43496,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="AK191" t="inlineStr"/>
+      <c r="AK191" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AL191" t="inlineStr">
         <is>
           <t>18.4</t>
@@ -43288,7 +43536,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="AS191" t="inlineStr"/>
+      <c r="AS191" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AT191" t="inlineStr">
         <is>
           <t>18.4</t>
@@ -43364,17 +43616,17 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:47</t>
+          <t>2026-10-21 08:48:43</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
       <c r="K192" t="n">
@@ -43561,7 +43813,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:48</t>
+          <t>2026-10-21 08:48:44</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -43587,7 +43839,7 @@
       <c r="O193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q193" t="inlineStr">
@@ -43664,7 +43916,7 @@
       </c>
       <c r="AK193" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AL193" t="inlineStr">
@@ -43704,7 +43956,7 @@
       </c>
       <c r="AS193" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AT193" t="inlineStr">
@@ -43758,7 +44010,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:48</t>
+          <t>2026-10-21 08:48:44</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -43784,7 +44036,7 @@
       <c r="O194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q194" t="inlineStr">
@@ -43861,7 +44113,7 @@
       </c>
       <c r="AK194" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AL194" t="inlineStr">
@@ -43901,7 +44153,7 @@
       </c>
       <c r="AS194" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AT194" t="inlineStr">
@@ -43955,7 +44207,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:48</t>
+          <t>2026-10-21 08:48:44</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -43981,7 +44233,7 @@
       <c r="O195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q195" t="inlineStr">
@@ -44058,7 +44310,7 @@
       </c>
       <c r="AK195" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AL195" t="inlineStr">
@@ -44098,7 +44350,7 @@
       </c>
       <c r="AS195" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AT195" t="inlineStr">
@@ -44152,7 +44404,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:48</t>
+          <t>2026-10-21 08:48:44</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -44178,7 +44430,7 @@
       <c r="O196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q196" t="inlineStr">
@@ -44255,7 +44507,7 @@
       </c>
       <c r="AK196" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AL196" t="inlineStr">
@@ -44295,7 +44547,7 @@
       </c>
       <c r="AS196" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AT196" t="inlineStr">
@@ -44349,17 +44601,17 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:51</t>
+          <t>2026-10-21 08:48:47</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
       <c r="K197" t="n">
@@ -44582,7 +44834,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:53</t>
+          <t>2026-10-21 08:48:49</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -44815,7 +45067,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:53</t>
+          <t>2026-10-21 08:48:49</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -45048,7 +45300,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:53</t>
+          <t>2026-10-21 08:48:49</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -45281,7 +45533,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:53</t>
+          <t>2026-10-21 08:48:49</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -45514,17 +45766,17 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:56</t>
+          <t>2026-10-21 08:48:52</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
       <c r="K202" t="n">
@@ -45687,7 +45939,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:58</t>
+          <t>2026-10-21 08:48:54</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -45860,7 +46112,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:58</t>
+          <t>2026-10-21 08:48:54</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -46033,7 +46285,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:58</t>
+          <t>2026-10-21 08:48:54</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -46206,7 +46458,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>2026-10-21 08:18:58</t>
+          <t>2026-10-21 08:48:54</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -46379,17 +46631,17 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>2026-10-21 08:19:02</t>
+          <t>2026-10-21 08:48:56</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
       <c r="K207" t="n">
@@ -46600,7 +46852,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>2026-10-21 08:19:05</t>
+          <t>2026-10-21 08:48:58</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -46821,7 +47073,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>2026-10-21 08:19:05</t>
+          <t>2026-10-21 08:48:58</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -47042,7 +47294,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>2026-10-21 08:19:05</t>
+          <t>2026-10-21 08:48:58</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -47263,7 +47515,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>2026-10-21 08:19:05</t>
+          <t>2026-10-21 08:48:58</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -47484,17 +47736,17 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>2026-10-21 08:19:08</t>
+          <t>2026-10-21 08:49:01</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
       <c r="K212" t="n">
@@ -47725,7 +47977,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>2026-10-21 08:19:10</t>
+          <t>2026-10-21 08:49:02</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -47966,7 +48218,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>2026-10-21 08:19:10</t>
+          <t>2026-10-21 08:49:02</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -48207,7 +48459,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>2026-10-21 08:19:10</t>
+          <t>2026-10-21 08:49:02</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -48448,7 +48700,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>2026-10-21 08:19:10</t>
+          <t>2026-10-21 08:49:02</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -48689,17 +48941,17 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>2026-10-21 08:19:12</t>
+          <t>2026-10-21 08:49:05</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
       <c r="K217" t="n">
@@ -48930,7 +49182,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>2026-10-21 08:19:14</t>
+          <t>2026-10-21 08:49:07</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -48960,7 +49212,7 @@
       </c>
       <c r="P218" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q218" t="inlineStr">
@@ -49049,7 +49301,7 @@
       </c>
       <c r="AK218" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AL218" t="inlineStr">
@@ -49089,7 +49341,7 @@
       </c>
       <c r="AS218" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AT218" t="inlineStr">
@@ -49171,7 +49423,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>2026-10-21 08:19:14</t>
+          <t>2026-10-21 08:49:07</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -49201,7 +49453,7 @@
       </c>
       <c r="P219" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q219" t="inlineStr">
@@ -49290,7 +49542,7 @@
       </c>
       <c r="AK219" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AL219" t="inlineStr">
@@ -49330,7 +49582,7 @@
       </c>
       <c r="AS219" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AT219" t="inlineStr">
@@ -49412,7 +49664,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>2026-10-21 08:19:14</t>
+          <t>2026-10-21 08:49:07</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -49442,7 +49694,7 @@
       </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q220" t="inlineStr">
@@ -49531,7 +49783,7 @@
       </c>
       <c r="AK220" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AL220" t="inlineStr">
@@ -49571,7 +49823,7 @@
       </c>
       <c r="AS220" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AT220" t="inlineStr">
@@ -49653,7 +49905,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>2026-10-21 08:19:14</t>
+          <t>2026-10-21 08:49:07</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -49683,7 +49935,7 @@
       </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q221" t="inlineStr">
@@ -49772,7 +50024,7 @@
       </c>
       <c r="AK221" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AL221" t="inlineStr">
@@ -49812,7 +50064,7 @@
       </c>
       <c r="AS221" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AT221" t="inlineStr">
@@ -49894,17 +50146,17 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>2026-10-21 08:19:17</t>
+          <t>2026-10-21 08:49:10</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
       <c r="K222" t="n">
@@ -50127,7 +50379,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>2026-10-21 08:19:20</t>
+          <t>2026-10-21 08:49:12</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -50360,7 +50612,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>2026-10-21 08:19:20</t>
+          <t>2026-10-21 08:49:12</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -50593,7 +50845,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>2026-10-21 08:19:20</t>
+          <t>2026-10-21 08:49:12</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -50826,7 +51078,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>2026-10-21 08:19:20</t>
+          <t>2026-10-21 08:49:12</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -51093,7 +51345,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51123,7 +51375,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51153,7 +51405,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51183,7 +51435,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51213,7 +51465,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51243,7 +51495,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51273,7 +51525,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51303,7 +51555,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51333,7 +51585,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51363,7 +51615,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51393,7 +51645,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51423,7 +51675,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51453,7 +51705,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51483,7 +51735,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51513,7 +51765,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51543,7 +51795,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51573,7 +51825,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51603,7 +51855,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51633,7 +51885,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51663,7 +51915,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51693,7 +51945,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51723,7 +51975,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51753,7 +52005,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51783,7 +52035,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51813,7 +52065,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51843,7 +52095,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51873,7 +52125,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51903,7 +52155,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51933,7 +52185,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51963,7 +52215,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51993,7 +52245,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
     </row>
@@ -52023,7 +52275,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
     </row>
@@ -52053,7 +52305,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
     </row>
@@ -52083,7 +52335,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
     </row>
@@ -52113,7 +52365,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
     </row>
@@ -52143,7 +52395,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
     </row>
@@ -52173,7 +52425,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
     </row>
@@ -52203,7 +52455,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
     </row>
@@ -52233,7 +52485,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
     </row>
@@ -52263,7 +52515,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
     </row>
@@ -52293,7 +52545,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
     </row>
@@ -52323,7 +52575,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
     </row>
@@ -52353,7 +52605,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
     </row>
@@ -52383,7 +52635,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
     </row>
@@ -52413,7 +52665,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-10-21T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-10-21T08:00Z</t>
         </is>
       </c>
     </row>

--- a/src/data/resum_periode_meteocat.xlsx
+++ b/src/data/resum_periode_meteocat.xlsx
@@ -722,17 +722,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-21 08:45:37</t>
+          <t>2026-10-21 09:15:36</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -919,7 +919,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-10-21 08:45:39</t>
+          <t>2026-10-21 09:15:37</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-10-21 08:45:39</t>
+          <t>2026-10-21 09:15:37</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-10-21 08:45:39</t>
+          <t>2026-10-21 09:15:37</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-10-21 08:45:39</t>
+          <t>2026-10-21 09:15:37</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-21 08:45:42</t>
+          <t>2026-10-21 09:15:40</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-21 08:45:44</t>
+          <t>2026-10-21 09:15:42</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-21 08:45:44</t>
+          <t>2026-10-21 09:15:42</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-21 08:45:44</t>
+          <t>2026-10-21 09:15:42</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-10-21 08:45:44</t>
+          <t>2026-10-21 09:15:42</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2872,17 +2872,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-10-21 08:45:47</t>
+          <t>2026-10-21 09:15:45</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-10-21 08:45:49</t>
+          <t>2026-10-21 09:15:47</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-10-21 08:45:49</t>
+          <t>2026-10-21 09:15:47</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-10-21 08:45:49</t>
+          <t>2026-10-21 09:15:47</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-10-21 08:45:49</t>
+          <t>2026-10-21 09:15:47</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -4037,17 +4037,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-10-21 08:45:52</t>
+          <t>2026-10-21 09:15:49</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-10-21 08:45:54</t>
+          <t>2026-10-21 09:15:51</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-10-21 08:45:54</t>
+          <t>2026-10-21 09:15:51</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-10-21 08:45:54</t>
+          <t>2026-10-21 09:15:51</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-10-21 08:45:54</t>
+          <t>2026-10-21 09:15:51</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -5202,17 +5202,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-10-21 08:45:57</t>
+          <t>2026-10-21 09:15:53</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-10-21 08:45:59</t>
+          <t>2026-10-21 09:15:55</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-10-21 08:45:59</t>
+          <t>2026-10-21 09:15:55</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-10-21 08:45:59</t>
+          <t>2026-10-21 09:15:55</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-10-21 08:45:59</t>
+          <t>2026-10-21 09:15:55</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -6367,17 +6367,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:02</t>
+          <t>2026-10-21 09:15:58</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -6600,7 +6600,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:04</t>
+          <t>2026-10-21 09:16:00</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -6833,7 +6833,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:04</t>
+          <t>2026-10-21 09:16:00</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:04</t>
+          <t>2026-10-21 09:16:00</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:04</t>
+          <t>2026-10-21 09:16:00</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -7532,17 +7532,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:07</t>
+          <t>2026-10-21 09:16:02</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -7765,7 +7765,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:09</t>
+          <t>2026-10-21 09:16:04</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:09</t>
+          <t>2026-10-21 09:16:04</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:09</t>
+          <t>2026-10-21 09:16:04</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -8464,7 +8464,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:09</t>
+          <t>2026-10-21 09:16:04</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -8697,17 +8697,17 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:12</t>
+          <t>2026-10-21 09:16:06</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -8918,7 +8918,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:14</t>
+          <t>2026-10-21 09:16:08</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:14</t>
+          <t>2026-10-21 09:16:08</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -9360,7 +9360,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:14</t>
+          <t>2026-10-21 09:16:08</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:14</t>
+          <t>2026-10-21 09:16:08</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -9802,17 +9802,17 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:17</t>
+          <t>2026-10-21 09:16:11</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -10023,7 +10023,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:19</t>
+          <t>2026-10-21 09:16:13</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -10244,7 +10244,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:19</t>
+          <t>2026-10-21 09:16:13</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:19</t>
+          <t>2026-10-21 09:16:13</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -10686,7 +10686,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:19</t>
+          <t>2026-10-21 09:16:13</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -10907,17 +10907,17 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:21</t>
+          <t>2026-10-21 09:16:15</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -11080,7 +11080,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:23</t>
+          <t>2026-10-21 09:16:17</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -11253,7 +11253,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:23</t>
+          <t>2026-10-21 09:16:17</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -11426,7 +11426,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:23</t>
+          <t>2026-10-21 09:16:17</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -11599,7 +11599,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:23</t>
+          <t>2026-10-21 09:16:17</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -11772,17 +11772,17 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:26</t>
+          <t>2026-10-21 09:16:19</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
       <c r="K52" t="n">
@@ -11945,7 +11945,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:28</t>
+          <t>2026-10-21 09:16:20</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:28</t>
+          <t>2026-10-21 09:16:20</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -12291,7 +12291,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:28</t>
+          <t>2026-10-21 09:16:20</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -12464,7 +12464,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:28</t>
+          <t>2026-10-21 09:16:20</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -12637,17 +12637,17 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:31</t>
+          <t>2026-10-21 09:16:23</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
       <c r="K57" t="n">
@@ -12878,7 +12878,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:33</t>
+          <t>2026-10-21 09:16:24</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -13119,7 +13119,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:33</t>
+          <t>2026-10-21 09:16:24</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:33</t>
+          <t>2026-10-21 09:16:24</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -13601,7 +13601,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:33</t>
+          <t>2026-10-21 09:16:24</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -13842,17 +13842,17 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:36</t>
+          <t>2026-10-21 09:16:27</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
       <c r="K62" t="n">
@@ -14063,7 +14063,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:38</t>
+          <t>2026-10-21 09:16:28</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -14284,7 +14284,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:38</t>
+          <t>2026-10-21 09:16:28</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -14505,7 +14505,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:38</t>
+          <t>2026-10-21 09:16:28</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -14726,7 +14726,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:38</t>
+          <t>2026-10-21 09:16:28</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -14947,17 +14947,17 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:41</t>
+          <t>2026-10-21 09:16:31</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
       <c r="K67" t="n">
@@ -15120,7 +15120,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:43</t>
+          <t>2026-10-21 09:16:32</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -15293,7 +15293,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:43</t>
+          <t>2026-10-21 09:16:32</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -15466,7 +15466,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:43</t>
+          <t>2026-10-21 09:16:32</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -15639,7 +15639,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:43</t>
+          <t>2026-10-21 09:16:32</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -15812,17 +15812,17 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:45</t>
+          <t>2026-10-21 09:16:35</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
       <c r="K72" t="n">
@@ -16045,7 +16045,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:47</t>
+          <t>2026-10-21 09:16:37</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -16278,7 +16278,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:47</t>
+          <t>2026-10-21 09:16:37</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -16511,7 +16511,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:47</t>
+          <t>2026-10-21 09:16:37</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:47</t>
+          <t>2026-10-21 09:16:37</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -16977,17 +16977,17 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:50</t>
+          <t>2026-10-21 09:16:39</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
       <c r="K77" t="n">
@@ -17210,7 +17210,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:52</t>
+          <t>2026-10-21 09:16:41</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -17443,7 +17443,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:52</t>
+          <t>2026-10-21 09:16:41</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -17676,7 +17676,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:52</t>
+          <t>2026-10-21 09:16:41</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -17909,7 +17909,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:52</t>
+          <t>2026-10-21 09:16:41</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -18142,17 +18142,17 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:55</t>
+          <t>2026-10-21 09:16:44</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
       <c r="K82" t="n">
@@ -18375,7 +18375,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:58</t>
+          <t>2026-10-21 09:16:45</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -18608,7 +18608,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:58</t>
+          <t>2026-10-21 09:16:45</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -18841,7 +18841,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:58</t>
+          <t>2026-10-21 09:16:45</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:58</t>
+          <t>2026-10-21 09:16:45</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -19307,17 +19307,17 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:01</t>
+          <t>2026-10-21 09:16:48</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
       <c r="K87" t="n">
@@ -19528,7 +19528,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:02</t>
+          <t>2026-10-21 09:16:50</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -19749,7 +19749,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:02</t>
+          <t>2026-10-21 09:16:50</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -19970,7 +19970,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:02</t>
+          <t>2026-10-21 09:16:50</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -20191,7 +20191,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:02</t>
+          <t>2026-10-21 09:16:50</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -20412,17 +20412,17 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:05</t>
+          <t>2026-10-21 09:16:52</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
       <c r="K92" t="n">
@@ -20633,7 +20633,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:07</t>
+          <t>2026-10-21 09:16:54</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -20866,7 +20866,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:07</t>
+          <t>2026-10-21 09:16:54</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -21099,7 +21099,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:07</t>
+          <t>2026-10-21 09:16:54</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -21332,7 +21332,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:07</t>
+          <t>2026-10-21 09:16:54</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -21565,17 +21565,17 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:10</t>
+          <t>2026-10-21 09:16:57</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
       <c r="K97" t="n">
@@ -21798,7 +21798,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:12</t>
+          <t>2026-10-21 09:16:58</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -22031,7 +22031,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:12</t>
+          <t>2026-10-21 09:16:58</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -22264,7 +22264,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:12</t>
+          <t>2026-10-21 09:16:58</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -22497,7 +22497,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:12</t>
+          <t>2026-10-21 09:16:58</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -22730,17 +22730,17 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:15</t>
+          <t>2026-10-21 09:17:01</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
       <c r="K102" t="n">
@@ -22963,7 +22963,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:17</t>
+          <t>2026-10-21 09:17:03</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -23196,7 +23196,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:17</t>
+          <t>2026-10-21 09:17:03</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -23429,7 +23429,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:17</t>
+          <t>2026-10-21 09:17:03</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -23662,7 +23662,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:17</t>
+          <t>2026-10-21 09:17:03</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -23895,17 +23895,17 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:19</t>
+          <t>2026-10-21 09:17:05</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
       <c r="K107" t="n">
@@ -24128,7 +24128,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:21</t>
+          <t>2026-10-21 09:17:07</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -24361,7 +24361,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:21</t>
+          <t>2026-10-21 09:17:07</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -24594,7 +24594,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:21</t>
+          <t>2026-10-21 09:17:07</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -24827,7 +24827,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:21</t>
+          <t>2026-10-21 09:17:07</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -25060,17 +25060,17 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:24</t>
+          <t>2026-10-21 09:17:10</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
       <c r="K112" t="n">
@@ -25293,7 +25293,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:26</t>
+          <t>2026-10-21 09:17:12</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -25526,7 +25526,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:26</t>
+          <t>2026-10-21 09:17:12</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -25759,7 +25759,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:26</t>
+          <t>2026-10-21 09:17:12</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -25992,7 +25992,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:26</t>
+          <t>2026-10-21 09:17:12</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -26225,17 +26225,17 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:29</t>
+          <t>2026-10-21 09:17:15</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
       <c r="K117" t="n">
@@ -26446,7 +26446,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:31</t>
+          <t>2026-10-21 09:17:16</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -26679,7 +26679,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:31</t>
+          <t>2026-10-21 09:17:16</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -26912,7 +26912,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:31</t>
+          <t>2026-10-21 09:17:16</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -27145,7 +27145,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:31</t>
+          <t>2026-10-21 09:17:16</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -27378,17 +27378,17 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:34</t>
+          <t>2026-10-21 09:17:19</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
       <c r="K122" t="n">
@@ -27619,7 +27619,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:36</t>
+          <t>2026-10-21 09:17:21</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -27860,7 +27860,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:36</t>
+          <t>2026-10-21 09:17:21</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -28101,7 +28101,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:36</t>
+          <t>2026-10-21 09:17:21</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -28342,7 +28342,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:36</t>
+          <t>2026-10-21 09:17:21</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -28583,17 +28583,17 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:39</t>
+          <t>2026-10-21 09:17:23</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
       <c r="K127" t="n">
@@ -28816,7 +28816,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:41</t>
+          <t>2026-10-21 09:17:25</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -29049,7 +29049,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:41</t>
+          <t>2026-10-21 09:17:25</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -29282,7 +29282,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:41</t>
+          <t>2026-10-21 09:17:25</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -29515,7 +29515,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:41</t>
+          <t>2026-10-21 09:17:25</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -29748,17 +29748,17 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:44</t>
+          <t>2026-10-21 09:17:28</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
       <c r="K132" t="n">
@@ -29981,7 +29981,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:46</t>
+          <t>2026-10-21 09:17:29</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -30214,7 +30214,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:46</t>
+          <t>2026-10-21 09:17:29</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -30447,7 +30447,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:46</t>
+          <t>2026-10-21 09:17:29</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -30680,7 +30680,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:46</t>
+          <t>2026-10-21 09:17:29</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -30913,17 +30913,17 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:49</t>
+          <t>2026-10-21 09:17:32</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
       <c r="K137" t="n">
@@ -31134,7 +31134,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:51</t>
+          <t>2026-10-21 09:17:34</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -31355,7 +31355,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:51</t>
+          <t>2026-10-21 09:17:34</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -31576,7 +31576,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:51</t>
+          <t>2026-10-21 09:17:34</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -31797,7 +31797,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:51</t>
+          <t>2026-10-21 09:17:34</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -32018,17 +32018,17 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:54</t>
+          <t>2026-10-21 09:17:36</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
       <c r="K142" t="n">
@@ -32251,7 +32251,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:56</t>
+          <t>2026-10-21 09:17:38</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -32484,7 +32484,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:56</t>
+          <t>2026-10-21 09:17:38</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -32717,7 +32717,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:56</t>
+          <t>2026-10-21 09:17:38</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -32950,7 +32950,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:56</t>
+          <t>2026-10-21 09:17:38</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -33183,17 +33183,17 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-10-21 08:47:59</t>
+          <t>2026-10-21 09:17:41</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
       <c r="K147" t="n">
@@ -33416,7 +33416,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:02</t>
+          <t>2026-10-21 09:17:42</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -33649,7 +33649,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:02</t>
+          <t>2026-10-21 09:17:42</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -33882,7 +33882,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:02</t>
+          <t>2026-10-21 09:17:42</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -34115,7 +34115,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:02</t>
+          <t>2026-10-21 09:17:42</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -34348,17 +34348,17 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:04</t>
+          <t>2026-10-21 09:17:45</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
       <c r="K152" t="n">
@@ -34581,7 +34581,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:06</t>
+          <t>2026-10-21 09:17:46</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -34814,7 +34814,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:06</t>
+          <t>2026-10-21 09:17:46</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -35047,7 +35047,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:06</t>
+          <t>2026-10-21 09:17:46</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -35280,7 +35280,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:06</t>
+          <t>2026-10-21 09:17:46</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -35513,17 +35513,17 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:09</t>
+          <t>2026-10-21 09:17:49</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
       <c r="K157" t="n">
@@ -35746,7 +35746,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:11</t>
+          <t>2026-10-21 09:17:51</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -35979,7 +35979,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:11</t>
+          <t>2026-10-21 09:17:51</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -36212,7 +36212,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:11</t>
+          <t>2026-10-21 09:17:51</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -36445,7 +36445,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:11</t>
+          <t>2026-10-21 09:17:51</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -36678,17 +36678,17 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:14</t>
+          <t>2026-10-21 09:17:53</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
       <c r="K162" t="n">
@@ -36919,7 +36919,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:16</t>
+          <t>2026-10-21 09:17:55</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -37160,7 +37160,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:16</t>
+          <t>2026-10-21 09:17:55</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -37401,7 +37401,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:16</t>
+          <t>2026-10-21 09:17:55</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -37642,7 +37642,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:16</t>
+          <t>2026-10-21 09:17:55</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -37883,17 +37883,17 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:19</t>
+          <t>2026-10-21 09:17:58</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
       <c r="K167" t="n">
@@ -38112,7 +38112,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:21</t>
+          <t>2026-10-21 09:17:59</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -38353,7 +38353,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:21</t>
+          <t>2026-10-21 09:17:59</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -38594,7 +38594,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:21</t>
+          <t>2026-10-21 09:17:59</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -38835,7 +38835,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:21</t>
+          <t>2026-10-21 09:17:59</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -39076,17 +39076,17 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:24</t>
+          <t>2026-10-21 09:18:02</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
       <c r="K172" t="n">
@@ -39309,7 +39309,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:26</t>
+          <t>2026-10-21 09:18:04</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -39542,7 +39542,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:26</t>
+          <t>2026-10-21 09:18:04</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -39775,7 +39775,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:26</t>
+          <t>2026-10-21 09:18:04</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -40008,7 +40008,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:26</t>
+          <t>2026-10-21 09:18:04</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -40241,17 +40241,17 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:28</t>
+          <t>2026-10-21 09:18:07</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
       <c r="K177" t="n">
@@ -40462,7 +40462,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:30</t>
+          <t>2026-10-21 09:18:08</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -40683,7 +40683,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:30</t>
+          <t>2026-10-21 09:18:08</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -40904,7 +40904,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:30</t>
+          <t>2026-10-21 09:18:08</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -41125,7 +41125,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:30</t>
+          <t>2026-10-21 09:18:08</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -41346,17 +41346,17 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:33</t>
+          <t>2026-10-21 09:18:11</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
       <c r="K182" t="n">
@@ -41567,7 +41567,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:35</t>
+          <t>2026-10-21 09:18:13</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -41788,7 +41788,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:35</t>
+          <t>2026-10-21 09:18:13</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -42009,7 +42009,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:35</t>
+          <t>2026-10-21 09:18:13</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -42230,7 +42230,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:35</t>
+          <t>2026-10-21 09:18:13</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -42451,17 +42451,17 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:38</t>
+          <t>2026-10-21 09:18:15</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
       <c r="K187" t="n">
@@ -42684,7 +42684,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:40</t>
+          <t>2026-10-21 09:18:17</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -42917,7 +42917,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:40</t>
+          <t>2026-10-21 09:18:17</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -43150,7 +43150,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:40</t>
+          <t>2026-10-21 09:18:17</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -43383,7 +43383,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:40</t>
+          <t>2026-10-21 09:18:17</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -43616,17 +43616,17 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:43</t>
+          <t>2026-10-21 09:18:19</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
       <c r="K192" t="n">
@@ -43813,7 +43813,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:44</t>
+          <t>2026-10-21 09:18:21</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -44010,7 +44010,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:44</t>
+          <t>2026-10-21 09:18:21</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -44207,7 +44207,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:44</t>
+          <t>2026-10-21 09:18:21</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -44404,7 +44404,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:44</t>
+          <t>2026-10-21 09:18:21</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -44601,17 +44601,17 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:47</t>
+          <t>2026-10-21 09:18:24</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
       <c r="K197" t="n">
@@ -44834,7 +44834,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:49</t>
+          <t>2026-10-21 09:18:25</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -45067,7 +45067,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:49</t>
+          <t>2026-10-21 09:18:25</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -45300,7 +45300,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:49</t>
+          <t>2026-10-21 09:18:25</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -45533,7 +45533,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:49</t>
+          <t>2026-10-21 09:18:25</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -45766,17 +45766,17 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:52</t>
+          <t>2026-10-21 09:18:28</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
       <c r="K202" t="n">
@@ -45939,7 +45939,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:54</t>
+          <t>2026-10-21 09:18:29</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -46112,7 +46112,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:54</t>
+          <t>2026-10-21 09:18:29</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -46285,7 +46285,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:54</t>
+          <t>2026-10-21 09:18:29</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -46458,7 +46458,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:54</t>
+          <t>2026-10-21 09:18:29</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -46631,17 +46631,17 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:56</t>
+          <t>2026-10-21 09:18:32</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
       <c r="K207" t="n">
@@ -46852,7 +46852,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:58</t>
+          <t>2026-10-21 09:18:34</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -47073,7 +47073,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:58</t>
+          <t>2026-10-21 09:18:34</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -47294,7 +47294,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:58</t>
+          <t>2026-10-21 09:18:34</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -47515,7 +47515,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>2026-10-21 08:48:58</t>
+          <t>2026-10-21 09:18:34</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -47736,17 +47736,17 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>2026-10-21 08:49:01</t>
+          <t>2026-10-21 09:18:36</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
       <c r="K212" t="n">
@@ -47977,7 +47977,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>2026-10-21 08:49:02</t>
+          <t>2026-10-21 09:18:38</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -48218,7 +48218,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>2026-10-21 08:49:02</t>
+          <t>2026-10-21 09:18:38</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -48459,7 +48459,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>2026-10-21 08:49:02</t>
+          <t>2026-10-21 09:18:38</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -48700,7 +48700,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>2026-10-21 08:49:02</t>
+          <t>2026-10-21 09:18:38</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -48941,17 +48941,17 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>2026-10-21 08:49:05</t>
+          <t>2026-10-21 09:18:41</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
       <c r="K217" t="n">
@@ -49182,7 +49182,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>2026-10-21 08:49:07</t>
+          <t>2026-10-21 09:18:43</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -49423,7 +49423,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>2026-10-21 08:49:07</t>
+          <t>2026-10-21 09:18:43</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -49664,7 +49664,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>2026-10-21 08:49:07</t>
+          <t>2026-10-21 09:18:43</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -49905,7 +49905,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>2026-10-21 08:49:07</t>
+          <t>2026-10-21 09:18:43</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -50146,17 +50146,17 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>2026-10-21 08:49:10</t>
+          <t>2026-10-21 09:18:45</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
       <c r="K222" t="n">
@@ -50379,7 +50379,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>2026-10-21 08:49:12</t>
+          <t>2026-10-21 09:18:47</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -50612,7 +50612,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>2026-10-21 08:49:12</t>
+          <t>2026-10-21 09:18:47</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -50845,7 +50845,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>2026-10-21 08:49:12</t>
+          <t>2026-10-21 09:18:47</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -51078,7 +51078,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>2026-10-21 08:49:12</t>
+          <t>2026-10-21 09:18:47</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -51345,7 +51345,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
     </row>
@@ -51375,7 +51375,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
     </row>
@@ -51405,7 +51405,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
     </row>
@@ -51435,7 +51435,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
     </row>
@@ -51465,7 +51465,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
     </row>
@@ -51495,7 +51495,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
     </row>
@@ -51525,7 +51525,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
     </row>
@@ -51555,7 +51555,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
     </row>
@@ -51585,7 +51585,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
     </row>
@@ -51615,7 +51615,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
     </row>
@@ -51645,7 +51645,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
     </row>
@@ -51675,7 +51675,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
     </row>
@@ -51705,7 +51705,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
     </row>
@@ -51735,7 +51735,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
     </row>
@@ -51765,7 +51765,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
     </row>
@@ -51795,7 +51795,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
     </row>
@@ -51825,7 +51825,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
     </row>
@@ -51855,7 +51855,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
     </row>
@@ -51885,7 +51885,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
     </row>
@@ -51915,7 +51915,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
     </row>
@@ -51945,7 +51945,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
     </row>
@@ -51975,7 +51975,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
     </row>
@@ -52005,7 +52005,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
     </row>
@@ -52035,7 +52035,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
     </row>
@@ -52065,7 +52065,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
     </row>
@@ -52095,7 +52095,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
     </row>
@@ -52125,7 +52125,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
     </row>
@@ -52155,7 +52155,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
     </row>
@@ -52185,7 +52185,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
     </row>
@@ -52215,7 +52215,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
     </row>
@@ -52245,7 +52245,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
     </row>
@@ -52275,7 +52275,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
     </row>
@@ -52305,7 +52305,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
     </row>
@@ -52335,7 +52335,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
     </row>
@@ -52365,7 +52365,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
     </row>
@@ -52395,7 +52395,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
     </row>
@@ -52425,7 +52425,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
     </row>
@@ -52455,7 +52455,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
     </row>
@@ -52485,7 +52485,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
     </row>
@@ -52515,7 +52515,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
     </row>
@@ -52545,7 +52545,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
     </row>
@@ -52575,7 +52575,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
     </row>
@@ -52605,7 +52605,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
     </row>
@@ -52635,7 +52635,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
     </row>
@@ -52665,7 +52665,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-10-21T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-10-21T08:30Z</t>
         </is>
       </c>
     </row>

--- a/src/data/resum_periode_meteocat.xlsx
+++ b/src/data/resum_periode_meteocat.xlsx
@@ -722,17 +722,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-21 09:15:36</t>
+          <t>2026-10-21 09:45:38</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -919,7 +919,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-10-21 09:15:37</t>
+          <t>2026-10-21 09:45:40</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-10-21 09:15:37</t>
+          <t>2026-10-21 09:45:40</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-10-21 09:15:37</t>
+          <t>2026-10-21 09:45:40</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-10-21 09:15:37</t>
+          <t>2026-10-21 09:45:40</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-21 09:15:40</t>
+          <t>2026-10-21 09:45:43</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-21 09:15:42</t>
+          <t>2026-10-21 09:45:46</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-21 09:15:42</t>
+          <t>2026-10-21 09:45:46</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-21 09:15:42</t>
+          <t>2026-10-21 09:45:46</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-10-21 09:15:42</t>
+          <t>2026-10-21 09:45:46</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2872,17 +2872,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-10-21 09:15:45</t>
+          <t>2026-10-21 09:45:49</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-10-21 09:15:47</t>
+          <t>2026-10-21 09:45:51</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-10-21 09:15:47</t>
+          <t>2026-10-21 09:45:51</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-10-21 09:15:47</t>
+          <t>2026-10-21 09:45:51</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-10-21 09:15:47</t>
+          <t>2026-10-21 09:45:51</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -4037,17 +4037,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-10-21 09:15:49</t>
+          <t>2026-10-21 09:45:54</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-10-21 09:15:51</t>
+          <t>2026-10-21 09:45:57</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-10-21 09:15:51</t>
+          <t>2026-10-21 09:45:57</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-10-21 09:15:51</t>
+          <t>2026-10-21 09:45:57</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-10-21 09:15:51</t>
+          <t>2026-10-21 09:45:57</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -5202,17 +5202,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-10-21 09:15:53</t>
+          <t>2026-10-21 09:45:59</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-10-21 09:15:55</t>
+          <t>2026-10-21 09:46:02</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-10-21 09:15:55</t>
+          <t>2026-10-21 09:46:02</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-10-21 09:15:55</t>
+          <t>2026-10-21 09:46:02</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-10-21 09:15:55</t>
+          <t>2026-10-21 09:46:02</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -6367,17 +6367,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-10-21 09:15:58</t>
+          <t>2026-10-21 09:46:05</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -6600,7 +6600,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:00</t>
+          <t>2026-10-21 09:46:07</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -6833,7 +6833,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:00</t>
+          <t>2026-10-21 09:46:07</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:00</t>
+          <t>2026-10-21 09:46:07</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:00</t>
+          <t>2026-10-21 09:46:07</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -7532,17 +7532,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:02</t>
+          <t>2026-10-21 09:46:10</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -7765,7 +7765,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:04</t>
+          <t>2026-10-21 09:46:12</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:04</t>
+          <t>2026-10-21 09:46:12</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:04</t>
+          <t>2026-10-21 09:46:12</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -8464,7 +8464,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:04</t>
+          <t>2026-10-21 09:46:12</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -8697,17 +8697,17 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:06</t>
+          <t>2026-10-21 09:46:15</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -8918,7 +8918,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:08</t>
+          <t>2026-10-21 09:46:18</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:08</t>
+          <t>2026-10-21 09:46:18</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -9360,7 +9360,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:08</t>
+          <t>2026-10-21 09:46:18</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:08</t>
+          <t>2026-10-21 09:46:18</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -9802,17 +9802,17 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:11</t>
+          <t>2026-10-21 09:46:21</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -10023,7 +10023,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:13</t>
+          <t>2026-10-21 09:46:23</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -10244,7 +10244,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:13</t>
+          <t>2026-10-21 09:46:23</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:13</t>
+          <t>2026-10-21 09:46:23</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -10686,7 +10686,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:13</t>
+          <t>2026-10-21 09:46:23</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -10907,17 +10907,17 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:15</t>
+          <t>2026-10-21 09:46:26</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -11080,7 +11080,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:17</t>
+          <t>2026-10-21 09:46:28</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -11253,7 +11253,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:17</t>
+          <t>2026-10-21 09:46:28</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -11426,7 +11426,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:17</t>
+          <t>2026-10-21 09:46:28</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -11599,7 +11599,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:17</t>
+          <t>2026-10-21 09:46:28</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -11772,17 +11772,17 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:19</t>
+          <t>2026-10-21 09:46:31</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
       <c r="K52" t="n">
@@ -11945,7 +11945,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:20</t>
+          <t>2026-10-21 09:46:33</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:20</t>
+          <t>2026-10-21 09:46:33</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -12291,7 +12291,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:20</t>
+          <t>2026-10-21 09:46:33</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -12464,7 +12464,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:20</t>
+          <t>2026-10-21 09:46:33</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -12637,17 +12637,17 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:23</t>
+          <t>2026-10-21 09:46:36</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
       <c r="K57" t="n">
@@ -12878,7 +12878,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:24</t>
+          <t>2026-10-21 09:46:39</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -13119,7 +13119,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:24</t>
+          <t>2026-10-21 09:46:39</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:24</t>
+          <t>2026-10-21 09:46:39</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -13601,7 +13601,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:24</t>
+          <t>2026-10-21 09:46:39</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -13842,17 +13842,17 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:27</t>
+          <t>2026-10-21 09:46:42</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
       <c r="K62" t="n">
@@ -14063,7 +14063,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:28</t>
+          <t>2026-10-21 09:46:44</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -14284,7 +14284,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:28</t>
+          <t>2026-10-21 09:46:44</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -14505,7 +14505,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:28</t>
+          <t>2026-10-21 09:46:44</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -14726,7 +14726,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:28</t>
+          <t>2026-10-21 09:46:44</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -14947,17 +14947,17 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:31</t>
+          <t>2026-10-21 09:46:47</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
       <c r="K67" t="n">
@@ -15120,7 +15120,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:32</t>
+          <t>2026-10-21 09:46:49</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -15293,7 +15293,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:32</t>
+          <t>2026-10-21 09:46:49</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -15466,7 +15466,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:32</t>
+          <t>2026-10-21 09:46:49</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -15639,7 +15639,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:32</t>
+          <t>2026-10-21 09:46:49</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -15812,17 +15812,17 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:35</t>
+          <t>2026-10-21 09:46:52</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
       <c r="K72" t="n">
@@ -16045,7 +16045,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:37</t>
+          <t>2026-10-21 09:46:54</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -16278,7 +16278,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:37</t>
+          <t>2026-10-21 09:46:54</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -16511,7 +16511,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:37</t>
+          <t>2026-10-21 09:46:54</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:37</t>
+          <t>2026-10-21 09:46:54</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -16977,17 +16977,17 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:39</t>
+          <t>2026-10-21 09:46:57</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
       <c r="K77" t="n">
@@ -17210,7 +17210,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:41</t>
+          <t>2026-10-21 09:47:00</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -17443,7 +17443,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:41</t>
+          <t>2026-10-21 09:47:00</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -17676,7 +17676,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:41</t>
+          <t>2026-10-21 09:47:00</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -17909,7 +17909,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:41</t>
+          <t>2026-10-21 09:47:00</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -18142,17 +18142,17 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:44</t>
+          <t>2026-10-21 09:47:03</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
       <c r="K82" t="n">
@@ -18375,7 +18375,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:45</t>
+          <t>2026-10-21 09:47:05</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -18608,7 +18608,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:45</t>
+          <t>2026-10-21 09:47:05</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -18841,7 +18841,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:45</t>
+          <t>2026-10-21 09:47:05</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:45</t>
+          <t>2026-10-21 09:47:05</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -19307,17 +19307,17 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:48</t>
+          <t>2026-10-21 09:47:08</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
       <c r="K87" t="n">
@@ -19528,7 +19528,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:50</t>
+          <t>2026-10-21 09:47:10</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -19749,7 +19749,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:50</t>
+          <t>2026-10-21 09:47:10</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -19970,7 +19970,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:50</t>
+          <t>2026-10-21 09:47:10</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -20191,7 +20191,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:50</t>
+          <t>2026-10-21 09:47:10</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -20412,17 +20412,17 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:52</t>
+          <t>2026-10-21 09:47:13</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
       <c r="K92" t="n">
@@ -20633,7 +20633,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:54</t>
+          <t>2026-10-21 09:47:15</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -20866,7 +20866,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:54</t>
+          <t>2026-10-21 09:47:15</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -21099,7 +21099,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:54</t>
+          <t>2026-10-21 09:47:15</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -21332,7 +21332,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:54</t>
+          <t>2026-10-21 09:47:15</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -21565,17 +21565,17 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:57</t>
+          <t>2026-10-21 09:47:17</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
       <c r="K97" t="n">
@@ -21798,7 +21798,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:58</t>
+          <t>2026-10-21 09:47:19</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -22031,7 +22031,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:58</t>
+          <t>2026-10-21 09:47:19</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -22264,7 +22264,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:58</t>
+          <t>2026-10-21 09:47:19</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -22497,7 +22497,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-10-21 09:16:58</t>
+          <t>2026-10-21 09:47:19</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -22730,17 +22730,17 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:01</t>
+          <t>2026-10-21 09:47:22</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
       <c r="K102" t="n">
@@ -22963,7 +22963,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:03</t>
+          <t>2026-10-21 09:47:25</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -23196,7 +23196,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:03</t>
+          <t>2026-10-21 09:47:25</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -23429,7 +23429,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:03</t>
+          <t>2026-10-21 09:47:25</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -23662,7 +23662,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:03</t>
+          <t>2026-10-21 09:47:25</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -23895,17 +23895,17 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:05</t>
+          <t>2026-10-21 09:47:28</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
       <c r="K107" t="n">
@@ -24128,7 +24128,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:07</t>
+          <t>2026-10-21 09:47:30</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -24361,7 +24361,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:07</t>
+          <t>2026-10-21 09:47:30</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -24594,7 +24594,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:07</t>
+          <t>2026-10-21 09:47:30</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -24827,7 +24827,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:07</t>
+          <t>2026-10-21 09:47:30</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -25060,17 +25060,17 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:10</t>
+          <t>2026-10-21 09:47:33</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
       <c r="K112" t="n">
@@ -25293,7 +25293,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:12</t>
+          <t>2026-10-21 09:47:35</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -25526,7 +25526,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:12</t>
+          <t>2026-10-21 09:47:35</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -25759,7 +25759,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:12</t>
+          <t>2026-10-21 09:47:35</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -25992,7 +25992,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:12</t>
+          <t>2026-10-21 09:47:35</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -26225,17 +26225,17 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:15</t>
+          <t>2026-10-21 09:47:37</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
       <c r="K117" t="n">
@@ -26446,7 +26446,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:16</t>
+          <t>2026-10-21 09:47:39</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -26679,7 +26679,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:16</t>
+          <t>2026-10-21 09:47:39</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -26912,7 +26912,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:16</t>
+          <t>2026-10-21 09:47:39</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -27145,7 +27145,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:16</t>
+          <t>2026-10-21 09:47:39</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -27378,17 +27378,17 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:19</t>
+          <t>2026-10-21 09:47:43</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
       <c r="K122" t="n">
@@ -27619,7 +27619,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:21</t>
+          <t>2026-10-21 09:47:45</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -27860,7 +27860,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:21</t>
+          <t>2026-10-21 09:47:45</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -28101,7 +28101,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:21</t>
+          <t>2026-10-21 09:47:45</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -28342,7 +28342,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:21</t>
+          <t>2026-10-21 09:47:45</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -28583,17 +28583,17 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:23</t>
+          <t>2026-10-21 09:47:48</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
       <c r="K127" t="n">
@@ -28816,7 +28816,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:25</t>
+          <t>2026-10-21 09:47:50</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -29049,7 +29049,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:25</t>
+          <t>2026-10-21 09:47:50</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -29282,7 +29282,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:25</t>
+          <t>2026-10-21 09:47:50</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -29515,7 +29515,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:25</t>
+          <t>2026-10-21 09:47:50</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -29748,17 +29748,17 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:28</t>
+          <t>2026-10-21 09:47:53</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
       <c r="K132" t="n">
@@ -29981,7 +29981,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:29</t>
+          <t>2026-10-21 09:47:56</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -30214,7 +30214,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:29</t>
+          <t>2026-10-21 09:47:56</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -30447,7 +30447,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:29</t>
+          <t>2026-10-21 09:47:56</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -30680,7 +30680,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:29</t>
+          <t>2026-10-21 09:47:56</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -30913,17 +30913,17 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:32</t>
+          <t>2026-10-21 09:47:59</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
       <c r="K137" t="n">
@@ -31134,7 +31134,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:34</t>
+          <t>2026-10-21 09:48:01</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -31355,7 +31355,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:34</t>
+          <t>2026-10-21 09:48:01</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -31576,7 +31576,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:34</t>
+          <t>2026-10-21 09:48:01</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -31797,7 +31797,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:34</t>
+          <t>2026-10-21 09:48:01</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -32018,17 +32018,17 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:36</t>
+          <t>2026-10-21 09:48:04</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
       <c r="K142" t="n">
@@ -32251,7 +32251,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:38</t>
+          <t>2026-10-21 09:48:06</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -32484,7 +32484,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:38</t>
+          <t>2026-10-21 09:48:06</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -32717,7 +32717,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:38</t>
+          <t>2026-10-21 09:48:06</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -32950,7 +32950,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:38</t>
+          <t>2026-10-21 09:48:06</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -33183,17 +33183,17 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:41</t>
+          <t>2026-10-21 09:48:09</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
       <c r="K147" t="n">
@@ -33416,7 +33416,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:42</t>
+          <t>2026-10-21 09:48:12</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -33649,7 +33649,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:42</t>
+          <t>2026-10-21 09:48:12</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -33882,7 +33882,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:42</t>
+          <t>2026-10-21 09:48:12</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -34115,7 +34115,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:42</t>
+          <t>2026-10-21 09:48:12</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -34348,17 +34348,17 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:45</t>
+          <t>2026-10-21 09:48:14</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
       <c r="K152" t="n">
@@ -34581,7 +34581,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:46</t>
+          <t>2026-10-21 09:48:17</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -34814,7 +34814,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:46</t>
+          <t>2026-10-21 09:48:17</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -35047,7 +35047,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:46</t>
+          <t>2026-10-21 09:48:17</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -35280,7 +35280,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:46</t>
+          <t>2026-10-21 09:48:17</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -35513,17 +35513,17 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:49</t>
+          <t>2026-10-21 09:48:20</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
       <c r="K157" t="n">
@@ -35746,7 +35746,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:51</t>
+          <t>2026-10-21 09:48:22</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -35979,7 +35979,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:51</t>
+          <t>2026-10-21 09:48:22</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -36212,7 +36212,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:51</t>
+          <t>2026-10-21 09:48:22</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -36445,7 +36445,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:51</t>
+          <t>2026-10-21 09:48:22</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -36678,17 +36678,17 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:53</t>
+          <t>2026-10-21 09:48:24</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
       <c r="K162" t="n">
@@ -36919,7 +36919,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:55</t>
+          <t>2026-10-21 09:48:27</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -37160,7 +37160,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:55</t>
+          <t>2026-10-21 09:48:27</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -37401,7 +37401,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:55</t>
+          <t>2026-10-21 09:48:27</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -37642,7 +37642,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:55</t>
+          <t>2026-10-21 09:48:27</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -37883,17 +37883,17 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:58</t>
+          <t>2026-10-21 09:48:30</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
       <c r="K167" t="n">
@@ -38112,7 +38112,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:59</t>
+          <t>2026-10-21 09:48:32</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -38353,7 +38353,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:59</t>
+          <t>2026-10-21 09:48:32</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -38594,7 +38594,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:59</t>
+          <t>2026-10-21 09:48:32</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -38835,7 +38835,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026-10-21 09:17:59</t>
+          <t>2026-10-21 09:48:32</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -39076,17 +39076,17 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-10-21 09:18:02</t>
+          <t>2026-10-21 09:48:35</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
       <c r="K172" t="n">
@@ -39309,7 +39309,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-10-21 09:18:04</t>
+          <t>2026-10-21 09:48:36</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -39542,7 +39542,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026-10-21 09:18:04</t>
+          <t>2026-10-21 09:48:36</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -39775,7 +39775,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026-10-21 09:18:04</t>
+          <t>2026-10-21 09:48:36</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -40008,7 +40008,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026-10-21 09:18:04</t>
+          <t>2026-10-21 09:48:36</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -40241,17 +40241,17 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026-10-21 09:18:07</t>
+          <t>2026-10-21 09:48:39</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
       <c r="K177" t="n">
@@ -40462,7 +40462,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026-10-21 09:18:08</t>
+          <t>2026-10-21 09:48:40</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -40683,7 +40683,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-10-21 09:18:08</t>
+          <t>2026-10-21 09:48:40</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -40904,7 +40904,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-10-21 09:18:08</t>
+          <t>2026-10-21 09:48:40</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -41125,7 +41125,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026-10-21 09:18:08</t>
+          <t>2026-10-21 09:48:40</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -41346,17 +41346,17 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026-10-21 09:18:11</t>
+          <t>2026-10-21 09:48:44</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
       <c r="K182" t="n">
@@ -41567,7 +41567,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026-10-21 09:18:13</t>
+          <t>2026-10-21 09:48:46</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -41788,7 +41788,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026-10-21 09:18:13</t>
+          <t>2026-10-21 09:48:46</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -42009,7 +42009,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-10-21 09:18:13</t>
+          <t>2026-10-21 09:48:46</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -42230,7 +42230,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-10-21 09:18:13</t>
+          <t>2026-10-21 09:48:46</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -42451,17 +42451,17 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2026-10-21 09:18:15</t>
+          <t>2026-10-21 09:48:49</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
       <c r="K187" t="n">
@@ -42684,7 +42684,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2026-10-21 09:18:17</t>
+          <t>2026-10-21 09:48:51</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -42917,7 +42917,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2026-10-21 09:18:17</t>
+          <t>2026-10-21 09:48:51</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -43150,7 +43150,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-10-21 09:18:17</t>
+          <t>2026-10-21 09:48:51</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -43383,7 +43383,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-10-21 09:18:17</t>
+          <t>2026-10-21 09:48:51</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -43616,17 +43616,17 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2026-10-21 09:18:19</t>
+          <t>2026-10-21 09:48:54</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
       <c r="K192" t="n">
@@ -43813,7 +43813,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2026-10-21 09:18:21</t>
+          <t>2026-10-21 09:48:56</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -44010,7 +44010,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2026-10-21 09:18:21</t>
+          <t>2026-10-21 09:48:56</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -44207,7 +44207,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026-10-21 09:18:21</t>
+          <t>2026-10-21 09:48:56</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -44404,7 +44404,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2026-10-21 09:18:21</t>
+          <t>2026-10-21 09:48:56</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -44601,17 +44601,17 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2026-10-21 09:18:24</t>
+          <t>2026-10-21 09:48:59</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
       <c r="K197" t="n">
@@ -44834,7 +44834,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2026-10-21 09:18:25</t>
+          <t>2026-10-21 09:49:01</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -45067,7 +45067,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2026-10-21 09:18:25</t>
+          <t>2026-10-21 09:49:01</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -45300,7 +45300,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2026-10-21 09:18:25</t>
+          <t>2026-10-21 09:49:01</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -45533,7 +45533,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-10-21 09:18:25</t>
+          <t>2026-10-21 09:49:01</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -45766,17 +45766,17 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>2026-10-21 09:18:28</t>
+          <t>2026-10-21 09:49:04</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
       <c r="K202" t="n">
@@ -45939,7 +45939,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>2026-10-21 09:18:29</t>
+          <t>2026-10-21 09:49:06</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -46112,7 +46112,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>2026-10-21 09:18:29</t>
+          <t>2026-10-21 09:49:06</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -46285,7 +46285,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>2026-10-21 09:18:29</t>
+          <t>2026-10-21 09:49:06</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -46458,7 +46458,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>2026-10-21 09:18:29</t>
+          <t>2026-10-21 09:49:06</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -46631,17 +46631,17 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>2026-10-21 09:18:32</t>
+          <t>2026-10-21 09:49:09</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
       <c r="K207" t="n">
@@ -46852,7 +46852,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>2026-10-21 09:18:34</t>
+          <t>2026-10-21 09:49:10</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -47073,7 +47073,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>2026-10-21 09:18:34</t>
+          <t>2026-10-21 09:49:10</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -47294,7 +47294,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>2026-10-21 09:18:34</t>
+          <t>2026-10-21 09:49:10</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -47515,7 +47515,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>2026-10-21 09:18:34</t>
+          <t>2026-10-21 09:49:10</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -47736,17 +47736,17 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>2026-10-21 09:18:36</t>
+          <t>2026-10-21 09:49:12</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
       <c r="K212" t="n">
@@ -47977,7 +47977,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>2026-10-21 09:18:38</t>
+          <t>2026-10-21 09:49:15</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -48218,7 +48218,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>2026-10-21 09:18:38</t>
+          <t>2026-10-21 09:49:15</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -48459,7 +48459,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>2026-10-21 09:18:38</t>
+          <t>2026-10-21 09:49:15</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -48700,7 +48700,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>2026-10-21 09:18:38</t>
+          <t>2026-10-21 09:49:15</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -48941,17 +48941,17 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>2026-10-21 09:18:41</t>
+          <t>2026-10-21 09:49:17</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
       <c r="K217" t="n">
@@ -49182,7 +49182,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>2026-10-21 09:18:43</t>
+          <t>2026-10-21 09:49:19</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -49423,7 +49423,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>2026-10-21 09:18:43</t>
+          <t>2026-10-21 09:49:19</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -49664,7 +49664,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>2026-10-21 09:18:43</t>
+          <t>2026-10-21 09:49:19</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -49905,7 +49905,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>2026-10-21 09:18:43</t>
+          <t>2026-10-21 09:49:19</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -50146,17 +50146,17 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>2026-10-21 09:18:45</t>
+          <t>2026-10-21 09:49:22</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
       <c r="K222" t="n">
@@ -50379,7 +50379,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>2026-10-21 09:18:47</t>
+          <t>2026-10-21 09:49:25</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -50612,7 +50612,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>2026-10-21 09:18:47</t>
+          <t>2026-10-21 09:49:25</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -50845,7 +50845,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>2026-10-21 09:18:47</t>
+          <t>2026-10-21 09:49:25</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -51078,7 +51078,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>2026-10-21 09:18:47</t>
+          <t>2026-10-21 09:49:25</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -51345,7 +51345,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
     </row>
@@ -51375,7 +51375,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
     </row>
@@ -51405,7 +51405,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
     </row>
@@ -51435,7 +51435,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
     </row>
@@ -51465,7 +51465,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
     </row>
@@ -51495,7 +51495,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
     </row>
@@ -51525,7 +51525,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
     </row>
@@ -51555,7 +51555,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
     </row>
@@ -51585,7 +51585,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
     </row>
@@ -51615,7 +51615,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
     </row>
@@ -51645,7 +51645,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
     </row>
@@ -51675,7 +51675,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
     </row>
@@ -51705,7 +51705,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
     </row>
@@ -51735,7 +51735,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
     </row>
@@ -51765,7 +51765,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
     </row>
@@ -51795,7 +51795,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
     </row>
@@ -51825,7 +51825,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
     </row>
@@ -51855,7 +51855,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
     </row>
@@ -51885,7 +51885,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
     </row>
@@ -51915,7 +51915,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
     </row>
@@ -51945,7 +51945,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
     </row>
@@ -51975,7 +51975,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
     </row>
@@ -52005,7 +52005,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
     </row>
@@ -52035,7 +52035,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
     </row>
@@ -52065,7 +52065,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
     </row>
@@ -52095,7 +52095,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
     </row>
@@ -52125,7 +52125,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
     </row>
@@ -52155,7 +52155,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
     </row>
@@ -52185,7 +52185,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
     </row>
@@ -52215,7 +52215,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
     </row>
@@ -52245,7 +52245,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
     </row>
@@ -52275,7 +52275,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
     </row>
@@ -52305,7 +52305,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
     </row>
@@ -52335,7 +52335,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
     </row>
@@ -52365,7 +52365,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
     </row>
@@ -52395,7 +52395,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
     </row>
@@ -52425,7 +52425,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
     </row>
@@ -52455,7 +52455,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
     </row>
@@ -52485,7 +52485,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
     </row>
@@ -52515,7 +52515,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
     </row>
@@ -52545,7 +52545,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
     </row>
@@ -52575,7 +52575,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
     </row>
@@ -52605,7 +52605,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
     </row>
@@ -52635,7 +52635,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
     </row>
@@ -52665,7 +52665,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-10-21T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-10-21T09:00Z</t>
         </is>
       </c>
     </row>

--- a/src/data/resum_periode_meteocat.xlsx
+++ b/src/data/resum_periode_meteocat.xlsx
@@ -722,17 +722,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-21 10:15:36</t>
+          <t>2026-10-21 10:45:35</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -919,7 +919,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-10-21 10:15:38</t>
+          <t>2026-10-21 10:45:37</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-10-21 10:15:38</t>
+          <t>2026-10-21 10:45:37</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-10-21 10:15:38</t>
+          <t>2026-10-21 10:45:37</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-10-21 10:15:38</t>
+          <t>2026-10-21 10:45:37</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-21 10:15:40</t>
+          <t>2026-10-21 10:45:39</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-21 10:15:42</t>
+          <t>2026-10-21 10:45:41</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-21 10:15:42</t>
+          <t>2026-10-21 10:45:41</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-21 10:15:42</t>
+          <t>2026-10-21 10:45:41</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-10-21 10:15:42</t>
+          <t>2026-10-21 10:45:41</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2872,17 +2872,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-10-21 10:15:45</t>
+          <t>2026-10-21 10:45:44</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-10-21 10:15:46</t>
+          <t>2026-10-21 10:45:45</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-10-21 10:15:46</t>
+          <t>2026-10-21 10:45:45</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-10-21 10:15:46</t>
+          <t>2026-10-21 10:45:45</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-10-21 10:15:46</t>
+          <t>2026-10-21 10:45:45</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -4037,17 +4037,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-10-21 10:15:49</t>
+          <t>2026-10-21 10:45:48</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-10-21 10:15:51</t>
+          <t>2026-10-21 10:45:50</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-10-21 10:15:51</t>
+          <t>2026-10-21 10:45:50</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-10-21 10:15:51</t>
+          <t>2026-10-21 10:45:50</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-10-21 10:15:51</t>
+          <t>2026-10-21 10:45:50</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -5202,17 +5202,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-10-21 10:15:53</t>
+          <t>2026-10-21 10:45:52</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-10-21 10:15:55</t>
+          <t>2026-10-21 10:45:54</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-10-21 10:15:55</t>
+          <t>2026-10-21 10:45:54</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-10-21 10:15:55</t>
+          <t>2026-10-21 10:45:54</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-10-21 10:15:55</t>
+          <t>2026-10-21 10:45:54</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -6367,17 +6367,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-10-21 10:15:57</t>
+          <t>2026-10-21 10:45:57</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -6600,7 +6600,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-10-21 10:15:59</t>
+          <t>2026-10-21 10:45:58</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -6833,7 +6833,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-10-21 10:15:59</t>
+          <t>2026-10-21 10:45:58</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-10-21 10:15:59</t>
+          <t>2026-10-21 10:45:58</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-10-21 10:15:59</t>
+          <t>2026-10-21 10:45:58</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -7532,17 +7532,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:02</t>
+          <t>2026-10-21 10:46:01</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -7765,7 +7765,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:04</t>
+          <t>2026-10-21 10:46:02</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:04</t>
+          <t>2026-10-21 10:46:02</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:04</t>
+          <t>2026-10-21 10:46:02</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -8464,7 +8464,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:04</t>
+          <t>2026-10-21 10:46:02</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -8697,17 +8697,17 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:06</t>
+          <t>2026-10-21 10:46:05</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -8918,7 +8918,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:08</t>
+          <t>2026-10-21 10:46:07</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:08</t>
+          <t>2026-10-21 10:46:07</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -9360,7 +9360,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:08</t>
+          <t>2026-10-21 10:46:07</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:08</t>
+          <t>2026-10-21 10:46:07</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -9802,17 +9802,17 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:11</t>
+          <t>2026-10-21 10:46:10</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -10023,7 +10023,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:12</t>
+          <t>2026-10-21 10:46:11</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -10244,7 +10244,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:12</t>
+          <t>2026-10-21 10:46:11</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:12</t>
+          <t>2026-10-21 10:46:11</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -10686,7 +10686,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:12</t>
+          <t>2026-10-21 10:46:11</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -10907,17 +10907,17 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:15</t>
+          <t>2026-10-21 10:46:14</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -11080,7 +11080,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:16</t>
+          <t>2026-10-21 10:46:15</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -11253,7 +11253,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:16</t>
+          <t>2026-10-21 10:46:15</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -11426,7 +11426,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:16</t>
+          <t>2026-10-21 10:46:15</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -11599,7 +11599,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:16</t>
+          <t>2026-10-21 10:46:15</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -11772,17 +11772,17 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:19</t>
+          <t>2026-10-21 10:46:18</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
       <c r="K52" t="n">
@@ -11945,7 +11945,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:20</t>
+          <t>2026-10-21 10:46:19</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:20</t>
+          <t>2026-10-21 10:46:19</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -12291,7 +12291,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:20</t>
+          <t>2026-10-21 10:46:19</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -12464,7 +12464,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:20</t>
+          <t>2026-10-21 10:46:19</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -12637,17 +12637,17 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:22</t>
+          <t>2026-10-21 10:46:22</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
       <c r="K57" t="n">
@@ -12878,7 +12878,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:24</t>
+          <t>2026-10-21 10:46:24</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -13119,7 +13119,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:24</t>
+          <t>2026-10-21 10:46:24</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:24</t>
+          <t>2026-10-21 10:46:24</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -13601,7 +13601,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:24</t>
+          <t>2026-10-21 10:46:24</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -13842,17 +13842,17 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:26</t>
+          <t>2026-10-21 10:46:26</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
       <c r="K62" t="n">
@@ -14063,7 +14063,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:28</t>
+          <t>2026-10-21 10:46:28</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -14284,7 +14284,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:28</t>
+          <t>2026-10-21 10:46:28</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -14505,7 +14505,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:28</t>
+          <t>2026-10-21 10:46:28</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -14726,7 +14726,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:28</t>
+          <t>2026-10-21 10:46:28</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -14947,17 +14947,17 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:30</t>
+          <t>2026-10-21 10:46:30</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
       <c r="K67" t="n">
@@ -15120,7 +15120,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:32</t>
+          <t>2026-10-21 10:46:32</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -15293,7 +15293,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:32</t>
+          <t>2026-10-21 10:46:32</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -15466,7 +15466,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:32</t>
+          <t>2026-10-21 10:46:32</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -15639,7 +15639,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:32</t>
+          <t>2026-10-21 10:46:32</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -15812,17 +15812,17 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:34</t>
+          <t>2026-10-21 10:46:34</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
       <c r="K72" t="n">
@@ -16033,7 +16033,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:36</t>
+          <t>2026-10-21 10:46:36</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -16266,7 +16266,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:36</t>
+          <t>2026-10-21 10:46:36</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -16499,7 +16499,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:36</t>
+          <t>2026-10-21 10:46:36</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -16732,7 +16732,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:36</t>
+          <t>2026-10-21 10:46:36</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -16965,17 +16965,17 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:39</t>
+          <t>2026-10-21 10:46:39</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
       <c r="K77" t="n">
@@ -17198,7 +17198,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:40</t>
+          <t>2026-10-21 10:46:41</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -17431,7 +17431,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:40</t>
+          <t>2026-10-21 10:46:41</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -17664,7 +17664,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:40</t>
+          <t>2026-10-21 10:46:41</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -17897,7 +17897,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:40</t>
+          <t>2026-10-21 10:46:41</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -18130,17 +18130,17 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:42</t>
+          <t>2026-10-21 10:46:44</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
       <c r="K82" t="n">
@@ -18363,7 +18363,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:44</t>
+          <t>2026-10-21 10:46:45</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -18596,7 +18596,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:44</t>
+          <t>2026-10-21 10:46:45</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -18829,7 +18829,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:44</t>
+          <t>2026-10-21 10:46:45</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -19062,7 +19062,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:44</t>
+          <t>2026-10-21 10:46:45</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -19295,17 +19295,17 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:47</t>
+          <t>2026-10-21 10:46:48</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
       <c r="K87" t="n">
@@ -19516,7 +19516,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:48</t>
+          <t>2026-10-21 10:46:50</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -19737,7 +19737,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:48</t>
+          <t>2026-10-21 10:46:50</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -19958,7 +19958,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:48</t>
+          <t>2026-10-21 10:46:50</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -20179,7 +20179,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:48</t>
+          <t>2026-10-21 10:46:50</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -20400,17 +20400,17 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:51</t>
+          <t>2026-10-21 10:46:52</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
       <c r="K92" t="n">
@@ -20621,7 +20621,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:53</t>
+          <t>2026-10-21 10:46:54</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -20854,7 +20854,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:53</t>
+          <t>2026-10-21 10:46:54</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -21087,7 +21087,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:53</t>
+          <t>2026-10-21 10:46:54</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -21320,7 +21320,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:53</t>
+          <t>2026-10-21 10:46:54</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -21553,17 +21553,17 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:55</t>
+          <t>2026-10-21 10:46:57</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
       <c r="K97" t="n">
@@ -21786,7 +21786,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:57</t>
+          <t>2026-10-21 10:46:58</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -22019,7 +22019,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:57</t>
+          <t>2026-10-21 10:46:58</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -22252,7 +22252,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:57</t>
+          <t>2026-10-21 10:46:58</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -22485,7 +22485,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-10-21 10:16:57</t>
+          <t>2026-10-21 10:46:58</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -22718,17 +22718,17 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:00</t>
+          <t>2026-10-21 10:47:01</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
       <c r="K102" t="n">
@@ -22951,7 +22951,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:01</t>
+          <t>2026-10-21 10:47:03</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:01</t>
+          <t>2026-10-21 10:47:03</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -23417,7 +23417,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:01</t>
+          <t>2026-10-21 10:47:03</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -23650,7 +23650,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:01</t>
+          <t>2026-10-21 10:47:03</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -23883,17 +23883,17 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:04</t>
+          <t>2026-10-21 10:47:05</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
       <c r="K107" t="n">
@@ -24116,7 +24116,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:06</t>
+          <t>2026-10-21 10:47:07</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -24349,7 +24349,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:06</t>
+          <t>2026-10-21 10:47:07</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -24582,7 +24582,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:06</t>
+          <t>2026-10-21 10:47:07</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -24815,7 +24815,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:06</t>
+          <t>2026-10-21 10:47:07</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -25048,17 +25048,17 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:09</t>
+          <t>2026-10-21 10:47:10</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
       <c r="K112" t="n">
@@ -25281,7 +25281,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:10</t>
+          <t>2026-10-21 10:47:11</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -25514,7 +25514,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:10</t>
+          <t>2026-10-21 10:47:11</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -25747,7 +25747,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:10</t>
+          <t>2026-10-21 10:47:11</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -25980,7 +25980,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:10</t>
+          <t>2026-10-21 10:47:11</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -26213,17 +26213,17 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:12</t>
+          <t>2026-10-21 10:47:14</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
       <c r="K117" t="n">
@@ -26434,7 +26434,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:14</t>
+          <t>2026-10-21 10:47:16</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -26667,7 +26667,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:14</t>
+          <t>2026-10-21 10:47:16</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -26900,7 +26900,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:14</t>
+          <t>2026-10-21 10:47:16</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -27133,7 +27133,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:14</t>
+          <t>2026-10-21 10:47:16</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -27366,17 +27366,17 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:17</t>
+          <t>2026-10-21 10:47:18</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
       <c r="K122" t="n">
@@ -27607,7 +27607,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:18</t>
+          <t>2026-10-21 10:47:20</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -27848,7 +27848,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:18</t>
+          <t>2026-10-21 10:47:20</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -28089,7 +28089,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:18</t>
+          <t>2026-10-21 10:47:20</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -28330,7 +28330,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:18</t>
+          <t>2026-10-21 10:47:20</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -28571,17 +28571,17 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:21</t>
+          <t>2026-10-21 10:47:23</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
       <c r="K127" t="n">
@@ -28804,7 +28804,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:23</t>
+          <t>2026-10-21 10:47:24</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -29037,7 +29037,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:23</t>
+          <t>2026-10-21 10:47:24</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -29270,7 +29270,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:23</t>
+          <t>2026-10-21 10:47:24</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -29503,7 +29503,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:23</t>
+          <t>2026-10-21 10:47:24</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -29736,17 +29736,17 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:25</t>
+          <t>2026-10-21 10:47:27</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
       <c r="K132" t="n">
@@ -29969,7 +29969,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:27</t>
+          <t>2026-10-21 10:47:28</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -30202,7 +30202,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:27</t>
+          <t>2026-10-21 10:47:28</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -30435,7 +30435,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:27</t>
+          <t>2026-10-21 10:47:28</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -30668,7 +30668,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:27</t>
+          <t>2026-10-21 10:47:28</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -30901,17 +30901,17 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:30</t>
+          <t>2026-10-21 10:47:31</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
       <c r="K137" t="n">
@@ -31122,7 +31122,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:31</t>
+          <t>2026-10-21 10:47:33</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -31343,7 +31343,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:31</t>
+          <t>2026-10-21 10:47:33</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -31564,7 +31564,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:31</t>
+          <t>2026-10-21 10:47:33</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -31785,7 +31785,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:31</t>
+          <t>2026-10-21 10:47:33</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -32006,17 +32006,17 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:34</t>
+          <t>2026-10-21 10:47:35</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
       <c r="K142" t="n">
@@ -32239,7 +32239,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:36</t>
+          <t>2026-10-21 10:47:37</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -32472,7 +32472,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:36</t>
+          <t>2026-10-21 10:47:37</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -32705,7 +32705,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:36</t>
+          <t>2026-10-21 10:47:37</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -32938,7 +32938,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:36</t>
+          <t>2026-10-21 10:47:37</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -33171,17 +33171,17 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:38</t>
+          <t>2026-10-21 10:47:40</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
       <c r="K147" t="n">
@@ -33404,7 +33404,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:40</t>
+          <t>2026-10-21 10:47:41</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -33637,7 +33637,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:40</t>
+          <t>2026-10-21 10:47:41</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -33870,7 +33870,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:40</t>
+          <t>2026-10-21 10:47:41</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -34103,7 +34103,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:40</t>
+          <t>2026-10-21 10:47:41</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -34336,17 +34336,17 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:42</t>
+          <t>2026-10-21 10:47:44</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
       <c r="K152" t="n">
@@ -34569,7 +34569,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:44</t>
+          <t>2026-10-21 10:47:46</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -34802,7 +34802,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:44</t>
+          <t>2026-10-21 10:47:46</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -35035,7 +35035,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:44</t>
+          <t>2026-10-21 10:47:46</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -35268,7 +35268,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:44</t>
+          <t>2026-10-21 10:47:46</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -35501,17 +35501,17 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:47</t>
+          <t>2026-10-21 10:47:48</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
       <c r="K157" t="n">
@@ -35734,7 +35734,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:48</t>
+          <t>2026-10-21 10:47:50</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -35967,7 +35967,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:48</t>
+          <t>2026-10-21 10:47:50</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -36200,7 +36200,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:48</t>
+          <t>2026-10-21 10:47:50</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -36433,7 +36433,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:48</t>
+          <t>2026-10-21 10:47:50</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -36666,17 +36666,17 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:51</t>
+          <t>2026-10-21 10:47:52</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
       <c r="K162" t="n">
@@ -36907,7 +36907,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:53</t>
+          <t>2026-10-21 10:47:54</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -37148,7 +37148,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:53</t>
+          <t>2026-10-21 10:47:54</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -37389,7 +37389,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:53</t>
+          <t>2026-10-21 10:47:54</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -37630,7 +37630,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:53</t>
+          <t>2026-10-21 10:47:54</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -37871,17 +37871,17 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:56</t>
+          <t>2026-10-21 10:47:57</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
       <c r="K167" t="n">
@@ -38100,7 +38100,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:57</t>
+          <t>2026-10-21 10:47:59</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -38341,7 +38341,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:57</t>
+          <t>2026-10-21 10:47:59</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -38582,7 +38582,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:57</t>
+          <t>2026-10-21 10:47:59</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -38823,7 +38823,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026-10-21 10:17:57</t>
+          <t>2026-10-21 10:47:59</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -39064,17 +39064,17 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-10-21 10:18:00</t>
+          <t>2026-10-21 10:48:01</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
       <c r="K172" t="n">
@@ -39297,7 +39297,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-10-21 10:18:02</t>
+          <t>2026-10-21 10:48:03</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -39530,7 +39530,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026-10-21 10:18:02</t>
+          <t>2026-10-21 10:48:03</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -39763,7 +39763,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026-10-21 10:18:02</t>
+          <t>2026-10-21 10:48:03</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -39996,7 +39996,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026-10-21 10:18:02</t>
+          <t>2026-10-21 10:48:03</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -40229,17 +40229,17 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026-10-21 10:18:04</t>
+          <t>2026-10-21 10:48:06</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
       <c r="K177" t="n">
@@ -40450,7 +40450,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026-10-21 10:18:06</t>
+          <t>2026-10-21 10:48:07</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -40671,7 +40671,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-10-21 10:18:06</t>
+          <t>2026-10-21 10:48:07</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -40892,7 +40892,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-10-21 10:18:06</t>
+          <t>2026-10-21 10:48:07</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -41113,7 +41113,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026-10-21 10:18:06</t>
+          <t>2026-10-21 10:48:07</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -41334,17 +41334,17 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026-10-21 10:18:08</t>
+          <t>2026-10-21 10:48:10</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
       <c r="K182" t="n">
@@ -41555,7 +41555,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026-10-21 10:18:10</t>
+          <t>2026-10-21 10:48:11</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -41776,7 +41776,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026-10-21 10:18:10</t>
+          <t>2026-10-21 10:48:11</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -41997,7 +41997,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-10-21 10:18:10</t>
+          <t>2026-10-21 10:48:11</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -42218,7 +42218,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-10-21 10:18:10</t>
+          <t>2026-10-21 10:48:11</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -42439,17 +42439,17 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2026-10-21 10:18:13</t>
+          <t>2026-10-21 10:48:14</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
       <c r="K187" t="n">
@@ -42660,7 +42660,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2026-10-21 10:18:14</t>
+          <t>2026-10-21 10:48:16</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -42893,7 +42893,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2026-10-21 10:18:14</t>
+          <t>2026-10-21 10:48:16</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -43126,7 +43126,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-10-21 10:18:14</t>
+          <t>2026-10-21 10:48:16</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -43359,7 +43359,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-10-21 10:18:14</t>
+          <t>2026-10-21 10:48:16</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -43592,17 +43592,17 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2026-10-21 10:18:17</t>
+          <t>2026-10-21 10:48:18</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
       <c r="K192" t="n">
@@ -43789,7 +43789,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2026-10-21 10:18:18</t>
+          <t>2026-10-21 10:48:20</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -43986,7 +43986,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2026-10-21 10:18:18</t>
+          <t>2026-10-21 10:48:20</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -44183,7 +44183,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026-10-21 10:18:18</t>
+          <t>2026-10-21 10:48:20</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -44380,7 +44380,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2026-10-21 10:18:18</t>
+          <t>2026-10-21 10:48:20</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -44577,17 +44577,17 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2026-10-21 10:18:21</t>
+          <t>2026-10-21 10:48:23</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
       <c r="K197" t="n">
@@ -44810,7 +44810,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2026-10-21 10:18:23</t>
+          <t>2026-10-21 10:48:24</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -45043,7 +45043,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2026-10-21 10:18:23</t>
+          <t>2026-10-21 10:48:24</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -45276,7 +45276,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2026-10-21 10:18:23</t>
+          <t>2026-10-21 10:48:24</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -45509,7 +45509,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-10-21 10:18:23</t>
+          <t>2026-10-21 10:48:24</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -45742,17 +45742,17 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>2026-10-21 10:18:25</t>
+          <t>2026-10-21 10:48:27</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
       <c r="K202" t="n">
@@ -45915,7 +45915,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>2026-10-21 10:18:27</t>
+          <t>2026-10-21 10:48:28</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -46088,7 +46088,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>2026-10-21 10:18:27</t>
+          <t>2026-10-21 10:48:28</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -46261,7 +46261,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>2026-10-21 10:18:27</t>
+          <t>2026-10-21 10:48:28</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -46434,7 +46434,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>2026-10-21 10:18:27</t>
+          <t>2026-10-21 10:48:28</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -46607,17 +46607,17 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>2026-10-21 10:18:29</t>
+          <t>2026-10-21 10:48:31</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
       <c r="K207" t="n">
@@ -46828,7 +46828,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>2026-10-21 10:18:31</t>
+          <t>2026-10-21 10:48:33</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -47049,7 +47049,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>2026-10-21 10:18:31</t>
+          <t>2026-10-21 10:48:33</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -47270,7 +47270,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>2026-10-21 10:18:31</t>
+          <t>2026-10-21 10:48:33</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -47491,7 +47491,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>2026-10-21 10:18:31</t>
+          <t>2026-10-21 10:48:33</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -47712,17 +47712,17 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>2026-10-21 10:18:34</t>
+          <t>2026-10-21 10:48:35</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
       <c r="K212" t="n">
@@ -47953,7 +47953,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>2026-10-21 10:18:36</t>
+          <t>2026-10-21 10:48:37</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -48194,7 +48194,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>2026-10-21 10:18:36</t>
+          <t>2026-10-21 10:48:37</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -48435,7 +48435,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>2026-10-21 10:18:36</t>
+          <t>2026-10-21 10:48:37</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -48676,7 +48676,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>2026-10-21 10:18:36</t>
+          <t>2026-10-21 10:48:37</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -48917,17 +48917,17 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>2026-10-21 10:18:38</t>
+          <t>2026-10-21 10:48:40</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
       <c r="K217" t="n">
@@ -49158,7 +49158,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>2026-10-21 10:18:40</t>
+          <t>2026-10-21 10:48:41</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -49399,7 +49399,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>2026-10-21 10:18:40</t>
+          <t>2026-10-21 10:48:41</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -49640,7 +49640,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>2026-10-21 10:18:40</t>
+          <t>2026-10-21 10:48:41</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -49881,7 +49881,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>2026-10-21 10:18:40</t>
+          <t>2026-10-21 10:48:41</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -50122,17 +50122,17 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>2026-10-21 10:18:43</t>
+          <t>2026-10-21 10:48:44</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
       <c r="K222" t="n">
@@ -50355,7 +50355,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>2026-10-21 10:18:44</t>
+          <t>2026-10-21 10:48:46</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -50588,7 +50588,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>2026-10-21 10:18:44</t>
+          <t>2026-10-21 10:48:46</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -50821,7 +50821,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>2026-10-21 10:18:44</t>
+          <t>2026-10-21 10:48:46</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -51054,7 +51054,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>2026-10-21 10:18:44</t>
+          <t>2026-10-21 10:48:46</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -51321,7 +51321,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
     </row>
@@ -51351,7 +51351,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
     </row>
@@ -51381,7 +51381,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
     </row>
@@ -51411,7 +51411,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
     </row>
@@ -51441,7 +51441,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
     </row>
@@ -51471,7 +51471,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
     </row>
@@ -51501,7 +51501,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
     </row>
@@ -51531,7 +51531,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
     </row>
@@ -51561,7 +51561,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
     </row>
@@ -51591,7 +51591,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
     </row>
@@ -51621,7 +51621,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
     </row>
@@ -51651,7 +51651,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
     </row>
@@ -51681,7 +51681,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
     </row>
@@ -51711,7 +51711,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
     </row>
@@ -51741,7 +51741,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
     </row>
@@ -51771,7 +51771,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
     </row>
@@ -51801,7 +51801,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
     </row>
@@ -51831,7 +51831,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
     </row>
@@ -51861,7 +51861,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
     </row>
@@ -51891,7 +51891,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
     </row>
@@ -51921,7 +51921,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
     </row>
@@ -51951,7 +51951,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
     </row>
@@ -51981,7 +51981,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
     </row>
@@ -52011,7 +52011,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
     </row>
@@ -52041,7 +52041,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
     </row>
@@ -52071,7 +52071,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
     </row>
@@ -52101,7 +52101,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
     </row>
@@ -52131,7 +52131,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
     </row>
@@ -52161,7 +52161,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
     </row>
@@ -52191,7 +52191,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
     </row>
@@ -52221,7 +52221,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
     </row>
@@ -52251,7 +52251,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
     </row>
@@ -52281,7 +52281,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
     </row>
@@ -52311,7 +52311,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
     </row>
@@ -52341,7 +52341,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
     </row>
@@ -52371,7 +52371,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
     </row>
@@ -52401,7 +52401,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
     </row>
@@ -52431,7 +52431,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
     </row>
@@ -52461,7 +52461,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
     </row>
@@ -52491,7 +52491,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
     </row>
@@ -52521,7 +52521,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
     </row>
@@ -52551,7 +52551,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
     </row>
@@ -52581,7 +52581,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
     </row>
@@ -52611,7 +52611,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
     </row>
@@ -52641,7 +52641,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-10-21T09:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-10-21T10:00Z</t>
         </is>
       </c>
     </row>

--- a/src/data/resum_periode_meteocat.xlsx
+++ b/src/data/resum_periode_meteocat.xlsx
@@ -722,17 +722,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-21 10:45:35</t>
+          <t>2026-10-21 11:15:37</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -919,7 +919,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-10-21 10:45:37</t>
+          <t>2026-10-21 11:15:38</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-10-21 10:45:37</t>
+          <t>2026-10-21 11:15:38</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-10-21 10:45:37</t>
+          <t>2026-10-21 11:15:38</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-10-21 10:45:37</t>
+          <t>2026-10-21 11:15:38</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-21 10:45:39</t>
+          <t>2026-10-21 11:15:41</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-21 10:45:41</t>
+          <t>2026-10-21 11:15:43</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-21 10:45:41</t>
+          <t>2026-10-21 11:15:43</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-21 10:45:41</t>
+          <t>2026-10-21 11:15:43</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-10-21 10:45:41</t>
+          <t>2026-10-21 11:15:43</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>08:00 - 08:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2872,17 +2872,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-10-21 10:45:44</t>
+          <t>2026-10-21 11:15:45</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>296</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2903,12 +2903,12 @@
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>50</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1016.0</t>
+          <t>1017.1</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -2918,66 +2918,66 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>08:00 - 08:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>595</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>08:00 - 08:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2987,37 +2987,37 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>296</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>08:00 - 08:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -3027,42 +3027,42 @@
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>296</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1016.0</t>
+          <t>1017.1</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>595</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1016.0</t>
+          <t>1017.1</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>595</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr"/>
@@ -3105,7 +3105,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-10-21 10:45:45</t>
+          <t>2026-10-21 11:15:47</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-10-21 10:45:45</t>
+          <t>2026-10-21 11:15:47</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-10-21 10:45:45</t>
+          <t>2026-10-21 11:15:47</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-10-21 10:45:45</t>
+          <t>2026-10-21 11:15:47</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -4037,17 +4037,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-10-21 10:45:48</t>
+          <t>2026-10-21 11:15:50</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-10-21 10:45:50</t>
+          <t>2026-10-21 11:15:51</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-10-21 10:45:50</t>
+          <t>2026-10-21 11:15:51</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-10-21 10:45:50</t>
+          <t>2026-10-21 11:15:51</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-10-21 10:45:50</t>
+          <t>2026-10-21 11:15:51</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -5202,17 +5202,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-10-21 10:45:52</t>
+          <t>2026-10-21 11:15:54</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -5225,7 +5225,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>79</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -5233,166 +5233,166 @@
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>60</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1016.9</t>
+          <t>1017.6</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>467</t>
+          <t>600</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>15.4</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr"/>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr"/>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>15.4</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>15.4</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1016.9</t>
+          <t>1017.6</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>467</t>
+          <t>600</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>1016.9</t>
+          <t>1017.6</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>467</t>
+          <t>600</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr"/>
@@ -5435,7 +5435,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-10-21 10:45:54</t>
+          <t>2026-10-21 11:15:56</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-10-21 10:45:54</t>
+          <t>2026-10-21 11:15:56</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-10-21 10:45:54</t>
+          <t>2026-10-21 11:15:56</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-10-21 10:45:54</t>
+          <t>2026-10-21 11:15:56</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -6352,7 +6352,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -6367,17 +6367,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-10-21 10:45:57</t>
+          <t>2026-10-21 11:15:58</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>250</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -6398,12 +6398,12 @@
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>41</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1017.1</t>
+          <t>1017.4</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -6413,66 +6413,66 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>613</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>18.3</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr"/>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr"/>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>18.3</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -6482,37 +6482,37 @@
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>250</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>18.3</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
@@ -6522,42 +6522,42 @@
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>250</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>1017.1</t>
+          <t>1017.4</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>613</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>1017.1</t>
+          <t>1017.4</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>613</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr"/>
@@ -6600,7 +6600,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-10-21 10:45:58</t>
+          <t>2026-10-21 11:16:00</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -6833,7 +6833,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-10-21 10:45:58</t>
+          <t>2026-10-21 11:16:00</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-10-21 10:45:58</t>
+          <t>2026-10-21 11:16:00</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-10-21 10:45:58</t>
+          <t>2026-10-21 11:16:00</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -7532,17 +7532,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:01</t>
+          <t>2026-10-21 11:16:03</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -7765,7 +7765,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:02</t>
+          <t>2026-10-21 11:16:04</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:02</t>
+          <t>2026-10-21 11:16:04</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:02</t>
+          <t>2026-10-21 11:16:04</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -8464,7 +8464,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:02</t>
+          <t>2026-10-21 11:16:04</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -8697,17 +8697,17 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:05</t>
+          <t>2026-10-21 11:16:07</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -8918,7 +8918,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:07</t>
+          <t>2026-10-21 11:16:09</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:07</t>
+          <t>2026-10-21 11:16:09</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -9360,7 +9360,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:07</t>
+          <t>2026-10-21 11:16:09</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:07</t>
+          <t>2026-10-21 11:16:09</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -9787,7 +9787,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -9802,17 +9802,17 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:10</t>
+          <t>2026-10-21 11:16:11</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -9826,160 +9826,160 @@
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>185</t>
         </is>
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>65</t>
         </is>
       </c>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>514</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>15.6</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr"/>
       <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr"/>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>15.6</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AL42" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>185</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>15.6</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AQ42" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AR42" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>185</t>
         </is>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>514</t>
         </is>
       </c>
       <c r="AW42" t="inlineStr"/>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>514</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr"/>
@@ -10023,7 +10023,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:11</t>
+          <t>2026-10-21 11:16:13</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -10244,7 +10244,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:11</t>
+          <t>2026-10-21 11:16:13</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:11</t>
+          <t>2026-10-21 11:16:13</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -10686,7 +10686,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:11</t>
+          <t>2026-10-21 11:16:13</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -10907,17 +10907,17 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:14</t>
+          <t>2026-10-21 11:16:15</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -11080,7 +11080,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:15</t>
+          <t>2026-10-21 11:16:17</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -11253,7 +11253,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:15</t>
+          <t>2026-10-21 11:16:17</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -11426,7 +11426,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:15</t>
+          <t>2026-10-21 11:16:17</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -11599,7 +11599,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:15</t>
+          <t>2026-10-21 11:16:17</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -11772,17 +11772,17 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:18</t>
+          <t>2026-10-21 11:16:19</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
       <c r="K52" t="n">
@@ -11799,7 +11799,7 @@
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>56</t>
         </is>
       </c>
       <c r="R52" t="inlineStr"/>
@@ -11810,23 +11810,23 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr"/>
@@ -11837,27 +11837,27 @@
       <c r="AD52" t="inlineStr"/>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>56</t>
         </is>
       </c>
       <c r="AJ52" t="inlineStr">
@@ -11869,27 +11869,27 @@
       <c r="AL52" t="inlineStr"/>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AN52" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="AQ52" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>56</t>
         </is>
       </c>
       <c r="AR52" t="inlineStr">
@@ -11945,7 +11945,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:19</t>
+          <t>2026-10-21 11:16:21</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:19</t>
+          <t>2026-10-21 11:16:21</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -12291,7 +12291,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:19</t>
+          <t>2026-10-21 11:16:21</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -12464,7 +12464,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:19</t>
+          <t>2026-10-21 11:16:21</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -12622,7 +12622,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -12637,17 +12637,17 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:22</t>
+          <t>2026-10-21 11:16:23</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
       <c r="K57" t="n">
@@ -12660,24 +12660,24 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>158</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>52</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1018.6</t>
+          <t>1016.8</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -12687,66 +12687,66 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>622</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>13.9</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr"/>
       <c r="AA57" t="inlineStr"/>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr"/>
       <c r="AD57" t="inlineStr"/>
       <c r="AE57" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>13.9</t>
         </is>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AJ57" t="inlineStr">
@@ -12756,37 +12756,37 @@
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AL57" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AN57" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>13.9</t>
         </is>
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="AQ57" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AR57" t="inlineStr">
@@ -12796,47 +12796,47 @@
       </c>
       <c r="AS57" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>158</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>1018.6</t>
+          <t>1016.8</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>158</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>1018.6</t>
+          <t>1016.8</t>
         </is>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>622</t>
         </is>
       </c>
     </row>
@@ -12878,7 +12878,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:24</t>
+          <t>2026-10-21 11:16:25</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -13119,7 +13119,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:24</t>
+          <t>2026-10-21 11:16:25</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:24</t>
+          <t>2026-10-21 11:16:25</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -13601,7 +13601,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:24</t>
+          <t>2026-10-21 11:16:25</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -13827,7 +13827,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -13842,17 +13842,17 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:26</t>
+          <t>2026-10-21 11:16:28</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
       <c r="K62" t="n">
@@ -13865,7 +13865,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>224</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -13873,7 +13873,7 @@
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>51</t>
         </is>
       </c>
       <c r="R62" t="inlineStr"/>
@@ -13884,66 +13884,66 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>467</t>
+          <t>608</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="inlineStr"/>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr"/>
       <c r="AD62" t="inlineStr"/>
       <c r="AE62" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AF62" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="AG62" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>51</t>
         </is>
       </c>
       <c r="AJ62" t="inlineStr">
@@ -13953,37 +13953,37 @@
       </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="AL62" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>224</t>
         </is>
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AN62" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="AQ62" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>51</t>
         </is>
       </c>
       <c r="AR62" t="inlineStr">
@@ -13993,33 +13993,33 @@
       </c>
       <c r="AS62" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>224</t>
         </is>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
-          <t>467</t>
+          <t>608</t>
         </is>
       </c>
       <c r="AW62" t="inlineStr"/>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
-          <t>467</t>
+          <t>608</t>
         </is>
       </c>
       <c r="AZ62" t="inlineStr"/>
@@ -14063,7 +14063,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:28</t>
+          <t>2026-10-21 11:16:29</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -14284,7 +14284,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:28</t>
+          <t>2026-10-21 11:16:29</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -14505,7 +14505,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:28</t>
+          <t>2026-10-21 11:16:29</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -14726,7 +14726,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:28</t>
+          <t>2026-10-21 11:16:29</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -14932,7 +14932,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -14947,17 +14947,17 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:30</t>
+          <t>2026-10-21 11:16:31</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
       <c r="K67" t="n">
@@ -14974,7 +14974,7 @@
       <c r="P67" t="inlineStr"/>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>54</t>
         </is>
       </c>
       <c r="R67" t="inlineStr"/>
@@ -14985,23 +14985,23 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="U67" t="inlineStr"/>
       <c r="V67" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr"/>
@@ -15012,27 +15012,27 @@
       <c r="AD67" t="inlineStr"/>
       <c r="AE67" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AF67" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="AG67" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AJ67" t="inlineStr">
@@ -15044,27 +15044,27 @@
       <c r="AL67" t="inlineStr"/>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AN67" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AQ67" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AR67" t="inlineStr">
@@ -15120,7 +15120,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:32</t>
+          <t>2026-10-21 11:16:33</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -15293,7 +15293,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:32</t>
+          <t>2026-10-21 11:16:33</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -15466,7 +15466,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:32</t>
+          <t>2026-10-21 11:16:33</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -15639,7 +15639,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:32</t>
+          <t>2026-10-21 11:16:33</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -15812,17 +15812,17 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:34</t>
+          <t>2026-10-21 11:16:35</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
       <c r="K72" t="n">
@@ -16033,7 +16033,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:36</t>
+          <t>2026-10-21 11:16:37</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -16266,7 +16266,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:36</t>
+          <t>2026-10-21 11:16:37</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -16499,7 +16499,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:36</t>
+          <t>2026-10-21 11:16:37</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -16732,7 +16732,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:36</t>
+          <t>2026-10-21 11:16:37</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -16950,7 +16950,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -16965,17 +16965,17 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:39</t>
+          <t>2026-10-21 11:16:39</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
       <c r="K77" t="n">
@@ -16988,19 +16988,19 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>264</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>60</t>
         </is>
       </c>
       <c r="R77" t="inlineStr"/>
@@ -17011,66 +17011,66 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>671</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>8.9</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="W77" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr"/>
       <c r="AA77" t="inlineStr"/>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr"/>
       <c r="AD77" t="inlineStr"/>
       <c r="AE77" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AF77" t="inlineStr">
         <is>
-          <t>8.9</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="AG77" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AJ77" t="inlineStr">
@@ -17080,82 +17080,82 @@
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AL77" t="inlineStr">
         <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>10:30 - 11:00</t>
+        </is>
+      </c>
+      <c r="AN77" t="inlineStr">
+        <is>
+          <t>10.4</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>11.1</t>
+        </is>
+      </c>
+      <c r="AP77" t="inlineStr">
+        <is>
+          <t>9.8</t>
+        </is>
+      </c>
+      <c r="AQ77" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AT77" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="AV77" t="inlineStr">
+        <is>
           <t>16.6</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>09:00 - 09:30</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>8.9</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="AP77" t="inlineStr">
-        <is>
-          <t>8.2</t>
-        </is>
-      </c>
-      <c r="AQ77" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="AR77" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS77" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AT77" t="inlineStr">
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>671</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
         <is>
           <t>16.6</t>
         </is>
       </c>
-      <c r="AU77" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="AV77" t="inlineStr">
-        <is>
-          <t>25.6</t>
-        </is>
-      </c>
-      <c r="AW77" t="inlineStr">
-        <is>
-          <t>526</t>
-        </is>
-      </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr">
-        <is>
-          <t>25.6</t>
-        </is>
-      </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>671</t>
         </is>
       </c>
       <c r="BA77" t="inlineStr"/>
@@ -17198,7 +17198,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:41</t>
+          <t>2026-10-21 11:16:41</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -17431,7 +17431,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:41</t>
+          <t>2026-10-21 11:16:41</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -17664,7 +17664,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:41</t>
+          <t>2026-10-21 11:16:41</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -17897,7 +17897,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:41</t>
+          <t>2026-10-21 11:16:41</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -18130,17 +18130,17 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:44</t>
+          <t>2026-10-21 11:16:44</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
       <c r="K82" t="n">
@@ -18363,7 +18363,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:45</t>
+          <t>2026-10-21 11:16:45</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -18596,7 +18596,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:45</t>
+          <t>2026-10-21 11:16:45</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -18829,7 +18829,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:45</t>
+          <t>2026-10-21 11:16:45</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -19062,7 +19062,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:45</t>
+          <t>2026-10-21 11:16:45</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -19295,17 +19295,17 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:48</t>
+          <t>2026-10-21 11:16:48</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
       <c r="K87" t="n">
@@ -19516,7 +19516,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:50</t>
+          <t>2026-10-21 11:16:50</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -19737,7 +19737,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:50</t>
+          <t>2026-10-21 11:16:50</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -19958,7 +19958,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:50</t>
+          <t>2026-10-21 11:16:50</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -20179,7 +20179,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:50</t>
+          <t>2026-10-21 11:16:50</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -20400,17 +20400,17 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:52</t>
+          <t>2026-10-21 11:16:52</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
       <c r="K92" t="n">
@@ -20621,7 +20621,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:54</t>
+          <t>2026-10-21 11:16:54</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -20854,7 +20854,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:54</t>
+          <t>2026-10-21 11:16:54</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -21087,7 +21087,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:54</t>
+          <t>2026-10-21 11:16:54</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -21320,7 +21320,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:54</t>
+          <t>2026-10-21 11:16:54</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -21538,7 +21538,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -21553,17 +21553,17 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:57</t>
+          <t>2026-10-21 11:16:56</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
       <c r="K97" t="n">
@@ -21576,7 +21576,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>214</t>
         </is>
       </c>
       <c r="N97" t="inlineStr"/>
@@ -21584,12 +21584,12 @@
       <c r="P97" t="inlineStr"/>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>55</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>1018.4</t>
+          <t>1017.1</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
@@ -21599,66 +21599,66 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>629</t>
         </is>
       </c>
       <c r="V97" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="W97" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="Z97" t="inlineStr"/>
       <c r="AA97" t="inlineStr"/>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr"/>
       <c r="AD97" t="inlineStr"/>
       <c r="AE97" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AF97" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AG97" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AJ97" t="inlineStr">
@@ -21668,37 +21668,37 @@
       </c>
       <c r="AK97" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AL97" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>214</t>
         </is>
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AN97" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AQ97" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AR97" t="inlineStr">
@@ -21708,42 +21708,42 @@
       </c>
       <c r="AS97" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>214</t>
         </is>
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
-          <t>1018.4</t>
+          <t>1017.1</t>
         </is>
       </c>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>629</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
-          <t>1018.4</t>
+          <t>1017.1</t>
         </is>
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>629</t>
         </is>
       </c>
       <c r="BA97" t="inlineStr"/>
@@ -21786,7 +21786,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:58</t>
+          <t>2026-10-21 11:16:58</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -22019,7 +22019,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:58</t>
+          <t>2026-10-21 11:16:58</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -22252,7 +22252,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:58</t>
+          <t>2026-10-21 11:16:58</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -22485,7 +22485,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-10-21 10:46:58</t>
+          <t>2026-10-21 11:16:58</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -22718,17 +22718,17 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:01</t>
+          <t>2026-10-21 11:17:01</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
       <c r="K102" t="n">
@@ -22951,7 +22951,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:03</t>
+          <t>2026-10-21 11:17:02</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:03</t>
+          <t>2026-10-21 11:17:02</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -23417,7 +23417,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:03</t>
+          <t>2026-10-21 11:17:02</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -23650,7 +23650,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:03</t>
+          <t>2026-10-21 11:17:02</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -23883,17 +23883,17 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:05</t>
+          <t>2026-10-21 11:17:05</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
       <c r="K107" t="n">
@@ -24116,7 +24116,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:07</t>
+          <t>2026-10-21 11:17:07</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -24349,7 +24349,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:07</t>
+          <t>2026-10-21 11:17:07</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -24582,7 +24582,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:07</t>
+          <t>2026-10-21 11:17:07</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -24815,7 +24815,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:07</t>
+          <t>2026-10-21 11:17:07</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -25033,7 +25033,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -25048,17 +25048,17 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:10</t>
+          <t>2026-10-21 11:17:09</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
       <c r="K112" t="n">
@@ -25071,7 +25071,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>295</t>
         </is>
       </c>
       <c r="N112" t="inlineStr"/>
@@ -25079,12 +25079,12 @@
       <c r="P112" t="inlineStr"/>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>52</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>1018.9</t>
+          <t>1019.1</t>
         </is>
       </c>
       <c r="S112" t="inlineStr">
@@ -25094,66 +25094,66 @@
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>619</t>
         </is>
       </c>
       <c r="V112" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="W112" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>22.7</t>
         </is>
       </c>
       <c r="Z112" t="inlineStr"/>
       <c r="AA112" t="inlineStr"/>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="AC112" t="inlineStr"/>
       <c r="AD112" t="inlineStr"/>
       <c r="AE112" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AF112" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="AG112" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AJ112" t="inlineStr">
@@ -25163,37 +25163,37 @@
       </c>
       <c r="AK112" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>22.7</t>
         </is>
       </c>
       <c r="AL112" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>295</t>
         </is>
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AN112" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AQ112" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AR112" t="inlineStr">
@@ -25203,42 +25203,42 @@
       </c>
       <c r="AS112" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>22.7</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>295</t>
         </is>
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>1018.9</t>
+          <t>1019.1</t>
         </is>
       </c>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>619</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
-          <t>1018.9</t>
+          <t>1019.1</t>
         </is>
       </c>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>619</t>
         </is>
       </c>
       <c r="BA112" t="inlineStr"/>
@@ -25281,7 +25281,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:11</t>
+          <t>2026-10-21 11:17:11</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -25514,7 +25514,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:11</t>
+          <t>2026-10-21 11:17:11</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -25747,7 +25747,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:11</t>
+          <t>2026-10-21 11:17:11</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -25980,7 +25980,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:11</t>
+          <t>2026-10-21 11:17:11</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -26213,17 +26213,17 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:14</t>
+          <t>2026-10-21 11:17:14</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
       <c r="K117" t="n">
@@ -26434,7 +26434,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:16</t>
+          <t>2026-10-21 11:17:15</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -26667,7 +26667,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:16</t>
+          <t>2026-10-21 11:17:15</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -26900,7 +26900,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:16</t>
+          <t>2026-10-21 11:17:15</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -27133,7 +27133,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:16</t>
+          <t>2026-10-21 11:17:15</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -27366,17 +27366,17 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:18</t>
+          <t>2026-10-21 11:17:18</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
       <c r="K122" t="n">
@@ -27607,7 +27607,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:20</t>
+          <t>2026-10-21 11:17:19</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -27848,7 +27848,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:20</t>
+          <t>2026-10-21 11:17:19</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -28089,7 +28089,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:20</t>
+          <t>2026-10-21 11:17:19</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -28330,7 +28330,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:20</t>
+          <t>2026-10-21 11:17:19</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -28571,17 +28571,17 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:23</t>
+          <t>2026-10-21 11:17:22</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
       <c r="K127" t="n">
@@ -28804,7 +28804,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:24</t>
+          <t>2026-10-21 11:17:24</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -29037,7 +29037,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:24</t>
+          <t>2026-10-21 11:17:24</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -29270,7 +29270,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:24</t>
+          <t>2026-10-21 11:17:24</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -29503,7 +29503,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:24</t>
+          <t>2026-10-21 11:17:24</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -29736,17 +29736,17 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:27</t>
+          <t>2026-10-21 11:17:27</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
       <c r="K132" t="n">
@@ -29969,7 +29969,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:28</t>
+          <t>2026-10-21 11:17:28</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -30202,7 +30202,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:28</t>
+          <t>2026-10-21 11:17:28</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -30435,7 +30435,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:28</t>
+          <t>2026-10-21 11:17:28</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -30668,7 +30668,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:28</t>
+          <t>2026-10-21 11:17:28</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -30901,17 +30901,17 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:31</t>
+          <t>2026-10-21 11:17:31</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
       <c r="K137" t="n">
@@ -31122,7 +31122,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:33</t>
+          <t>2026-10-21 11:17:33</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -31343,7 +31343,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:33</t>
+          <t>2026-10-21 11:17:33</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -31564,7 +31564,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:33</t>
+          <t>2026-10-21 11:17:33</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -31785,7 +31785,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:33</t>
+          <t>2026-10-21 11:17:33</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -32006,17 +32006,17 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:35</t>
+          <t>2026-10-21 11:17:35</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
       <c r="K142" t="n">
@@ -32239,7 +32239,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:37</t>
+          <t>2026-10-21 11:17:37</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -32472,7 +32472,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:37</t>
+          <t>2026-10-21 11:17:37</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -32705,7 +32705,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:37</t>
+          <t>2026-10-21 11:17:37</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -32938,7 +32938,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:37</t>
+          <t>2026-10-21 11:17:37</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -33156,7 +33156,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -33171,17 +33171,17 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:40</t>
+          <t>2026-10-21 11:17:39</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
       <c r="K147" t="n">
@@ -33194,7 +33194,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>353</t>
         </is>
       </c>
       <c r="N147" t="inlineStr"/>
@@ -33202,12 +33202,12 @@
       <c r="P147" t="inlineStr"/>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>54</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>1016.3</t>
+          <t>1016.9</t>
         </is>
       </c>
       <c r="S147" t="inlineStr">
@@ -33217,66 +33217,66 @@
       </c>
       <c r="T147" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="U147" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>471</t>
         </is>
       </c>
       <c r="V147" t="inlineStr">
         <is>
-          <t>18.3</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="W147" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="X147" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="Z147" t="inlineStr"/>
       <c r="AA147" t="inlineStr"/>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="AC147" t="inlineStr"/>
       <c r="AD147" t="inlineStr"/>
       <c r="AE147" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AF147" t="inlineStr">
         <is>
-          <t>18.3</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="AG147" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="AI147" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AJ147" t="inlineStr">
@@ -33286,37 +33286,37 @@
       </c>
       <c r="AK147" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="AL147" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>353</t>
         </is>
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AN147" t="inlineStr">
         <is>
-          <t>18.3</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="AO147" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="AQ147" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AR147" t="inlineStr">
@@ -33326,42 +33326,42 @@
       </c>
       <c r="AS147" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="AT147" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>353</t>
         </is>
       </c>
       <c r="AU147" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="AV147" t="inlineStr">
         <is>
-          <t>1016.3</t>
+          <t>1016.9</t>
         </is>
       </c>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>471</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
         <is>
-          <t>1016.3</t>
+          <t>1016.9</t>
         </is>
       </c>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>471</t>
         </is>
       </c>
       <c r="BA147" t="inlineStr"/>
@@ -33404,7 +33404,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:41</t>
+          <t>2026-10-21 11:17:41</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -33637,7 +33637,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:41</t>
+          <t>2026-10-21 11:17:41</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -33870,7 +33870,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:41</t>
+          <t>2026-10-21 11:17:41</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -34103,7 +34103,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:41</t>
+          <t>2026-10-21 11:17:41</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -34321,7 +34321,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -34336,17 +34336,17 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:44</t>
+          <t>2026-10-21 11:17:44</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
       <c r="K152" t="n">
@@ -34360,13 +34360,13 @@
       <c r="M152" t="inlineStr"/>
       <c r="N152" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>298</t>
         </is>
       </c>
       <c r="O152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Q152" t="inlineStr">
@@ -34382,61 +34382,61 @@
       </c>
       <c r="T152" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="U152" t="inlineStr">
         <is>
-          <t>462</t>
+          <t>611</t>
         </is>
       </c>
       <c r="V152" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="W152" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>12.9</t>
         </is>
       </c>
       <c r="X152" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="Y152" t="inlineStr"/>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr"/>
       <c r="AB152" t="inlineStr"/>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="AD152" t="inlineStr"/>
       <c r="AE152" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AF152" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AG152" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="AH152" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>12.9</t>
         </is>
       </c>
       <c r="AI152" t="inlineStr">
@@ -34451,32 +34451,32 @@
       </c>
       <c r="AK152" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AL152" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AM152" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AN152" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AO152" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>12.9</t>
         </is>
       </c>
       <c r="AQ152" t="inlineStr">
@@ -34491,42 +34491,42 @@
       </c>
       <c r="AS152" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AT152" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>298</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>462</t>
+          <t>611</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>298</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>462</t>
+          <t>611</t>
         </is>
       </c>
       <c r="BA152" t="inlineStr"/>
@@ -34569,7 +34569,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:46</t>
+          <t>2026-10-21 11:17:45</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -34802,7 +34802,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:46</t>
+          <t>2026-10-21 11:17:45</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -35035,7 +35035,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:46</t>
+          <t>2026-10-21 11:17:45</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -35268,7 +35268,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:46</t>
+          <t>2026-10-21 11:17:45</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -35501,17 +35501,17 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:48</t>
+          <t>2026-10-21 11:17:48</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
       <c r="K157" t="n">
@@ -35734,7 +35734,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:50</t>
+          <t>2026-10-21 11:17:50</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -35967,7 +35967,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:50</t>
+          <t>2026-10-21 11:17:50</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -36200,7 +36200,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:50</t>
+          <t>2026-10-21 11:17:50</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -36433,7 +36433,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:50</t>
+          <t>2026-10-21 11:17:50</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -36651,7 +36651,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -36666,17 +36666,17 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:52</t>
+          <t>2026-10-21 11:17:52</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
       <c r="K162" t="n">
@@ -36689,24 +36689,24 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>207</t>
         </is>
       </c>
       <c r="N162" t="inlineStr"/>
       <c r="O162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q162" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>62</t>
         </is>
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>849.8</t>
+          <t>850.4</t>
         </is>
       </c>
       <c r="S162" t="inlineStr">
@@ -36716,66 +36716,66 @@
       </c>
       <c r="T162" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="U162" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>318</t>
         </is>
       </c>
       <c r="V162" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="W162" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="X162" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="Z162" t="inlineStr"/>
       <c r="AA162" t="inlineStr"/>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="AC162" t="inlineStr"/>
       <c r="AD162" t="inlineStr"/>
       <c r="AE162" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AF162" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="AG162" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AH162" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AI162" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AJ162" t="inlineStr">
@@ -36785,37 +36785,37 @@
       </c>
       <c r="AK162" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AL162" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AM162" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AN162" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="AO162" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AQ162" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AR162" t="inlineStr">
@@ -36825,47 +36825,47 @@
       </c>
       <c r="AS162" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AT162" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AU162" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>207</t>
         </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>849.8</t>
+          <t>850.4</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>207</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>849.8</t>
+          <t>850.4</t>
         </is>
       </c>
       <c r="BA162" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>318</t>
         </is>
       </c>
     </row>
@@ -36907,7 +36907,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:54</t>
+          <t>2026-10-21 11:17:54</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -37148,7 +37148,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:54</t>
+          <t>2026-10-21 11:17:54</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -37389,7 +37389,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:54</t>
+          <t>2026-10-21 11:17:54</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -37630,7 +37630,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:54</t>
+          <t>2026-10-21 11:17:54</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -37871,17 +37871,17 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:57</t>
+          <t>2026-10-21 11:17:57</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
       <c r="K167" t="n">
@@ -38100,7 +38100,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:59</t>
+          <t>2026-10-21 11:17:58</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -38341,7 +38341,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:59</t>
+          <t>2026-10-21 11:17:58</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -38582,7 +38582,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:59</t>
+          <t>2026-10-21 11:17:58</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -38823,7 +38823,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026-10-21 10:47:59</t>
+          <t>2026-10-21 11:17:58</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -39049,7 +39049,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -39064,17 +39064,17 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-10-21 10:48:01</t>
+          <t>2026-10-21 11:18:01</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
       <c r="K172" t="n">
@@ -39087,7 +39087,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>200</t>
         </is>
       </c>
       <c r="N172" t="inlineStr"/>
@@ -39095,12 +39095,12 @@
       <c r="P172" t="inlineStr"/>
       <c r="Q172" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>60</t>
         </is>
       </c>
       <c r="R172" t="inlineStr">
         <is>
-          <t>1016.8</t>
+          <t>1018.0</t>
         </is>
       </c>
       <c r="S172" t="inlineStr">
@@ -39110,32 +39110,32 @@
       </c>
       <c r="T172" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="U172" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>559</t>
         </is>
       </c>
       <c r="V172" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="W172" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="X172" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="Y172" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="Z172" t="inlineStr"/>
@@ -39149,27 +39149,27 @@
       <c r="AD172" t="inlineStr"/>
       <c r="AE172" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AF172" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="AG172" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="AH172" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="AI172" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AJ172" t="inlineStr">
@@ -39179,37 +39179,37 @@
       </c>
       <c r="AK172" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AL172" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>200</t>
         </is>
       </c>
       <c r="AM172" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AN172" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="AO172" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="AP172" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="AQ172" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AR172" t="inlineStr">
@@ -39219,12 +39219,12 @@
       </c>
       <c r="AS172" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AT172" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>200</t>
         </is>
       </c>
       <c r="AU172" t="inlineStr">
@@ -39234,12 +39234,12 @@
       </c>
       <c r="AV172" t="inlineStr">
         <is>
-          <t>1016.8</t>
+          <t>1018.0</t>
         </is>
       </c>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>559</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
@@ -39249,12 +39249,12 @@
       </c>
       <c r="AY172" t="inlineStr">
         <is>
-          <t>1016.8</t>
+          <t>1018.0</t>
         </is>
       </c>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>559</t>
         </is>
       </c>
       <c r="BA172" t="inlineStr"/>
@@ -39297,7 +39297,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-10-21 10:48:03</t>
+          <t>2026-10-21 11:18:02</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -39530,7 +39530,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026-10-21 10:48:03</t>
+          <t>2026-10-21 11:18:02</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -39763,7 +39763,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026-10-21 10:48:03</t>
+          <t>2026-10-21 11:18:02</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -39996,7 +39996,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026-10-21 10:48:03</t>
+          <t>2026-10-21 11:18:02</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -40214,7 +40214,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -40229,17 +40229,17 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026-10-21 10:48:06</t>
+          <t>2026-10-21 11:18:05</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
       <c r="K177" t="n">
@@ -40252,7 +40252,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>102</t>
         </is>
       </c>
       <c r="N177" t="inlineStr"/>
@@ -40260,12 +40260,12 @@
       <c r="P177" t="inlineStr"/>
       <c r="Q177" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>65</t>
         </is>
       </c>
       <c r="R177" t="inlineStr">
         <is>
-          <t>1017.3</t>
+          <t>1017.7</t>
         </is>
       </c>
       <c r="S177" t="inlineStr">
@@ -40275,62 +40275,62 @@
       </c>
       <c r="T177" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="U177" t="inlineStr"/>
       <c r="V177" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="W177" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="X177" t="inlineStr">
         <is>
-          <t>13.4</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="Z177" t="inlineStr"/>
       <c r="AA177" t="inlineStr"/>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AC177" t="inlineStr"/>
       <c r="AD177" t="inlineStr"/>
       <c r="AE177" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AF177" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="AG177" t="inlineStr">
         <is>
-          <t>13.4</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="AI177" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AJ177" t="inlineStr">
@@ -40340,37 +40340,37 @@
       </c>
       <c r="AK177" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AL177" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>102</t>
         </is>
       </c>
       <c r="AM177" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AN177" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="AO177" t="inlineStr">
         <is>
-          <t>13.4</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="AP177" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="AQ177" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AR177" t="inlineStr">
@@ -40380,33 +40380,33 @@
       </c>
       <c r="AS177" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AT177" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>102</t>
         </is>
       </c>
       <c r="AU177" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AV177" t="inlineStr">
         <is>
-          <t>1017.3</t>
+          <t>1017.7</t>
         </is>
       </c>
       <c r="AW177" t="inlineStr"/>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
         <is>
-          <t>1017.3</t>
+          <t>1017.7</t>
         </is>
       </c>
       <c r="AZ177" t="inlineStr"/>
@@ -40450,7 +40450,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026-10-21 10:48:07</t>
+          <t>2026-10-21 11:18:07</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -40671,7 +40671,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-10-21 10:48:07</t>
+          <t>2026-10-21 11:18:07</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -40892,7 +40892,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-10-21 10:48:07</t>
+          <t>2026-10-21 11:18:07</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -41113,7 +41113,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026-10-21 10:48:07</t>
+          <t>2026-10-21 11:18:07</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -41334,17 +41334,17 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026-10-21 10:48:10</t>
+          <t>2026-10-21 11:18:09</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
       <c r="K182" t="n">
@@ -41555,7 +41555,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026-10-21 10:48:11</t>
+          <t>2026-10-21 11:18:11</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -41776,7 +41776,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026-10-21 10:48:11</t>
+          <t>2026-10-21 11:18:11</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -41997,7 +41997,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-10-21 10:48:11</t>
+          <t>2026-10-21 11:18:11</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -42218,7 +42218,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-10-21 10:48:11</t>
+          <t>2026-10-21 11:18:11</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -42439,17 +42439,17 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2026-10-21 10:48:14</t>
+          <t>2026-10-21 11:18:13</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
       <c r="K187" t="n">
@@ -42660,7 +42660,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2026-10-21 10:48:16</t>
+          <t>2026-10-21 11:18:15</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -42893,7 +42893,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2026-10-21 10:48:16</t>
+          <t>2026-10-21 11:18:15</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -43126,7 +43126,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-10-21 10:48:16</t>
+          <t>2026-10-21 11:18:15</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -43359,7 +43359,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-10-21 10:48:16</t>
+          <t>2026-10-21 11:18:15</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -43592,17 +43592,17 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2026-10-21 10:48:18</t>
+          <t>2026-10-21 11:18:18</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
       <c r="K192" t="n">
@@ -43789,7 +43789,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2026-10-21 10:48:20</t>
+          <t>2026-10-21 11:18:19</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -43986,7 +43986,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2026-10-21 10:48:20</t>
+          <t>2026-10-21 11:18:19</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -44183,7 +44183,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026-10-21 10:48:20</t>
+          <t>2026-10-21 11:18:19</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -44380,7 +44380,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2026-10-21 10:48:20</t>
+          <t>2026-10-21 11:18:19</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -44562,7 +44562,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -44577,17 +44577,17 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2026-10-21 10:48:23</t>
+          <t>2026-10-21 11:18:22</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
       <c r="K197" t="n">
@@ -44600,7 +44600,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>274</t>
         </is>
       </c>
       <c r="N197" t="inlineStr"/>
@@ -44613,7 +44613,7 @@
       </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>1017.2</t>
+          <t>1017.6</t>
         </is>
       </c>
       <c r="S197" t="inlineStr">
@@ -44623,61 +44623,61 @@
       </c>
       <c r="T197" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="U197" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>618</t>
         </is>
       </c>
       <c r="V197" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="W197" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="X197" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="Z197" t="inlineStr"/>
       <c r="AA197" t="inlineStr"/>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>39.2</t>
         </is>
       </c>
       <c r="AC197" t="inlineStr"/>
       <c r="AD197" t="inlineStr"/>
       <c r="AE197" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AF197" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="AG197" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="AI197" t="inlineStr">
@@ -44692,32 +44692,32 @@
       </c>
       <c r="AK197" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AL197" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>274</t>
         </is>
       </c>
       <c r="AM197" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AN197" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="AO197" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="AP197" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="AQ197" t="inlineStr">
@@ -44732,42 +44732,42 @@
       </c>
       <c r="AS197" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AT197" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>274</t>
         </is>
       </c>
       <c r="AU197" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>39.2</t>
         </is>
       </c>
       <c r="AV197" t="inlineStr">
         <is>
-          <t>1017.2</t>
+          <t>1017.6</t>
         </is>
       </c>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>618</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>39.2</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr">
         <is>
-          <t>1017.2</t>
+          <t>1017.6</t>
         </is>
       </c>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>618</t>
         </is>
       </c>
       <c r="BA197" t="inlineStr"/>
@@ -44810,7 +44810,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2026-10-21 10:48:24</t>
+          <t>2026-10-21 11:18:23</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -45043,7 +45043,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2026-10-21 10:48:24</t>
+          <t>2026-10-21 11:18:23</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -45276,7 +45276,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2026-10-21 10:48:24</t>
+          <t>2026-10-21 11:18:23</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -45509,7 +45509,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-10-21 10:48:24</t>
+          <t>2026-10-21 11:18:23</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -45727,7 +45727,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -45742,17 +45742,17 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>2026-10-21 10:48:27</t>
+          <t>2026-10-21 11:18:26</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
       <c r="K202" t="n">
@@ -45769,7 +45769,7 @@
       <c r="P202" t="inlineStr"/>
       <c r="Q202" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>63</t>
         </is>
       </c>
       <c r="R202" t="inlineStr"/>
@@ -45780,23 +45780,23 @@
       </c>
       <c r="T202" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="U202" t="inlineStr"/>
       <c r="V202" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="W202" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="X202" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="Y202" t="inlineStr"/>
@@ -45807,27 +45807,27 @@
       <c r="AD202" t="inlineStr"/>
       <c r="AE202" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AF202" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="AG202" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="AH202" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="AI202" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AJ202" t="inlineStr">
@@ -45839,27 +45839,27 @@
       <c r="AL202" t="inlineStr"/>
       <c r="AM202" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AN202" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="AO202" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="AP202" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="AQ202" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AR202" t="inlineStr">
@@ -45915,7 +45915,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>2026-10-21 10:48:28</t>
+          <t>2026-10-21 11:18:27</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -46088,7 +46088,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>2026-10-21 10:48:28</t>
+          <t>2026-10-21 11:18:27</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -46261,7 +46261,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>2026-10-21 10:48:28</t>
+          <t>2026-10-21 11:18:27</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -46434,7 +46434,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>2026-10-21 10:48:28</t>
+          <t>2026-10-21 11:18:27</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -46607,17 +46607,17 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>2026-10-21 10:48:31</t>
+          <t>2026-10-21 11:18:29</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
       <c r="K207" t="n">
@@ -46828,7 +46828,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>2026-10-21 10:48:33</t>
+          <t>2026-10-21 11:18:31</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -47049,7 +47049,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>2026-10-21 10:48:33</t>
+          <t>2026-10-21 11:18:31</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -47270,7 +47270,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>2026-10-21 10:48:33</t>
+          <t>2026-10-21 11:18:31</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -47491,7 +47491,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>2026-10-21 10:48:33</t>
+          <t>2026-10-21 11:18:31</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -47712,17 +47712,17 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>2026-10-21 10:48:35</t>
+          <t>2026-10-21 11:18:33</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
       <c r="K212" t="n">
@@ -47953,7 +47953,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>2026-10-21 10:48:37</t>
+          <t>2026-10-21 11:18:35</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -48194,7 +48194,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>2026-10-21 10:48:37</t>
+          <t>2026-10-21 11:18:35</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -48435,7 +48435,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>2026-10-21 10:48:37</t>
+          <t>2026-10-21 11:18:35</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -48676,7 +48676,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>2026-10-21 10:48:37</t>
+          <t>2026-10-21 11:18:35</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -48917,17 +48917,17 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>2026-10-21 10:48:40</t>
+          <t>2026-10-21 11:18:38</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
       <c r="K217" t="n">
@@ -49158,7 +49158,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>2026-10-21 10:48:41</t>
+          <t>2026-10-21 11:18:39</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -49399,7 +49399,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>2026-10-21 10:48:41</t>
+          <t>2026-10-21 11:18:39</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -49640,7 +49640,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>2026-10-21 10:48:41</t>
+          <t>2026-10-21 11:18:39</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -49881,7 +49881,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>2026-10-21 10:48:41</t>
+          <t>2026-10-21 11:18:39</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -50107,7 +50107,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -50122,17 +50122,17 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>2026-10-21 10:48:44</t>
+          <t>2026-10-21 11:18:41</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
       <c r="K222" t="n">
@@ -50145,7 +50145,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>314</t>
         </is>
       </c>
       <c r="N222" t="inlineStr"/>
@@ -50153,12 +50153,12 @@
       <c r="P222" t="inlineStr"/>
       <c r="Q222" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>44</t>
         </is>
       </c>
       <c r="R222" t="inlineStr">
         <is>
-          <t>1019.8</t>
+          <t>1020.1</t>
         </is>
       </c>
       <c r="S222" t="inlineStr">
@@ -50168,66 +50168,66 @@
       </c>
       <c r="T222" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="U222" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>611</t>
         </is>
       </c>
       <c r="V222" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="W222" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="X222" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="Y222" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="Z222" t="inlineStr"/>
       <c r="AA222" t="inlineStr"/>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="AC222" t="inlineStr"/>
       <c r="AD222" t="inlineStr"/>
       <c r="AE222" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AF222" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="AG222" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AH222" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="AI222" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AJ222" t="inlineStr">
@@ -50237,37 +50237,37 @@
       </c>
       <c r="AK222" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AL222" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>314</t>
         </is>
       </c>
       <c r="AM222" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AN222" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="AO222" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AP222" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="AQ222" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AR222" t="inlineStr">
@@ -50277,42 +50277,42 @@
       </c>
       <c r="AS222" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AT222" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>314</t>
         </is>
       </c>
       <c r="AU222" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="AV222" t="inlineStr">
         <is>
-          <t>1019.8</t>
+          <t>1020.1</t>
         </is>
       </c>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>611</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr">
         <is>
-          <t>1019.8</t>
+          <t>1020.1</t>
         </is>
       </c>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>611</t>
         </is>
       </c>
       <c r="BA222" t="inlineStr"/>
@@ -50355,7 +50355,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>2026-10-21 10:48:46</t>
+          <t>2026-10-21 11:18:42</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -50588,7 +50588,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>2026-10-21 10:48:46</t>
+          <t>2026-10-21 11:18:42</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -50821,7 +50821,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>2026-10-21 10:48:46</t>
+          <t>2026-10-21 11:18:42</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -51054,7 +51054,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>2026-10-21 10:48:46</t>
+          <t>2026-10-21 11:18:42</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -51321,7 +51321,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
     </row>
@@ -51351,7 +51351,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
     </row>
@@ -51381,7 +51381,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
     </row>
@@ -51411,7 +51411,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
     </row>
@@ -51441,7 +51441,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
     </row>
@@ -51471,7 +51471,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
     </row>
@@ -51501,7 +51501,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
     </row>
@@ -51531,7 +51531,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
     </row>
@@ -51561,7 +51561,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
     </row>
@@ -51591,7 +51591,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
     </row>
@@ -51621,7 +51621,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
     </row>
@@ -51651,7 +51651,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
     </row>
@@ -51681,7 +51681,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
     </row>
@@ -51711,7 +51711,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
     </row>
@@ -51741,7 +51741,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
     </row>
@@ -51771,7 +51771,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
     </row>
@@ -51801,7 +51801,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
     </row>
@@ -51831,7 +51831,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
     </row>
@@ -51861,7 +51861,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
     </row>
@@ -51891,7 +51891,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
     </row>
@@ -51921,7 +51921,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
     </row>
@@ -51951,7 +51951,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
     </row>
@@ -51981,7 +51981,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
     </row>
@@ -52011,7 +52011,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
     </row>
@@ -52041,7 +52041,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
     </row>
@@ -52071,7 +52071,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
     </row>
@@ -52101,7 +52101,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
     </row>
@@ -52131,7 +52131,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
     </row>
@@ -52161,7 +52161,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
     </row>
@@ -52191,7 +52191,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
     </row>
@@ -52221,7 +52221,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
     </row>
@@ -52251,7 +52251,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
     </row>
@@ -52281,7 +52281,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
     </row>
@@ -52311,7 +52311,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
     </row>
@@ -52341,7 +52341,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
     </row>
@@ -52371,7 +52371,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
     </row>
@@ -52401,7 +52401,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
     </row>
@@ -52431,7 +52431,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
     </row>
@@ -52461,7 +52461,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
     </row>
@@ -52491,7 +52491,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
     </row>
@@ -52521,7 +52521,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
     </row>
@@ -52551,7 +52551,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
     </row>
@@ -52581,7 +52581,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
     </row>
@@ -52611,7 +52611,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
     </row>
@@ -52641,7 +52641,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-10-21T10:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-10-21T10:30Z</t>
         </is>
       </c>
     </row>

--- a/src/data/resum_periode_meteocat.xlsx
+++ b/src/data/resum_periode_meteocat.xlsx
@@ -722,17 +722,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-21 11:15:37</t>
+          <t>2026-10-21 11:45:33</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -919,7 +919,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-10-21 11:15:38</t>
+          <t>2026-10-21 11:45:35</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-10-21 11:15:38</t>
+          <t>2026-10-21 11:45:35</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-10-21 11:15:38</t>
+          <t>2026-10-21 11:45:35</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-10-21 11:15:38</t>
+          <t>2026-10-21 11:45:35</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-21 11:15:41</t>
+          <t>2026-10-21 11:45:38</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -1732,12 +1732,12 @@
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>250</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1748,156 +1748,156 @@
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>140</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>10:30 - 11:00</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>10.4</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>09:00 - 09:30</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>250</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>140</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>250</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>140</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr"/>
@@ -1940,7 +1940,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-21 11:15:43</t>
+          <t>2026-10-21 11:45:41</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-21 11:15:43</t>
+          <t>2026-10-21 11:45:41</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-21 11:15:43</t>
+          <t>2026-10-21 11:45:41</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-10-21 11:15:43</t>
+          <t>2026-10-21 11:45:41</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2872,17 +2872,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-10-21 11:15:45</t>
+          <t>2026-10-21 11:45:44</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-10-21 11:15:47</t>
+          <t>2026-10-21 11:45:46</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-10-21 11:15:47</t>
+          <t>2026-10-21 11:45:46</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-10-21 11:15:47</t>
+          <t>2026-10-21 11:45:46</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-10-21 11:15:47</t>
+          <t>2026-10-21 11:45:46</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -4037,17 +4037,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-10-21 11:15:50</t>
+          <t>2026-10-21 11:45:49</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -4062,12 +4062,12 @@
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>328</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -4078,156 +4078,156 @@
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>179</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="AG17" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>10:30 - 11:00</t>
+        </is>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
         <is>
           <t>98</t>
         </is>
       </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>0.4</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>09:00 - 09:30</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
+      <c r="AR17" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="AP17" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="AQ17" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>0.4</t>
-        </is>
-      </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>328</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>179</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>328</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>179</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr"/>
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-10-21 11:15:51</t>
+          <t>2026-10-21 11:45:51</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-10-21 11:15:51</t>
+          <t>2026-10-21 11:45:51</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-10-21 11:15:51</t>
+          <t>2026-10-21 11:45:51</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-10-21 11:15:51</t>
+          <t>2026-10-21 11:45:51</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -5202,17 +5202,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-10-21 11:15:54</t>
+          <t>2026-10-21 11:45:54</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-10-21 11:15:56</t>
+          <t>2026-10-21 11:45:56</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-10-21 11:15:56</t>
+          <t>2026-10-21 11:45:56</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-10-21 11:15:56</t>
+          <t>2026-10-21 11:45:56</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-10-21 11:15:56</t>
+          <t>2026-10-21 11:45:56</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -6367,17 +6367,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-10-21 11:15:58</t>
+          <t>2026-10-21 11:45:58</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -6600,7 +6600,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:00</t>
+          <t>2026-10-21 11:46:01</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -6833,7 +6833,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:00</t>
+          <t>2026-10-21 11:46:01</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:00</t>
+          <t>2026-10-21 11:46:01</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:00</t>
+          <t>2026-10-21 11:46:01</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -7532,17 +7532,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:03</t>
+          <t>2026-10-21 11:46:04</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -7555,7 +7555,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>270</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -7563,12 +7563,12 @@
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>54</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1017.0</t>
+          <t>1016.9</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -7578,66 +7578,66 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>630</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>13.8</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>16.1</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr"/>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr"/>
       <c r="AD32" t="inlineStr"/>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>13.8</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>16.1</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -7647,37 +7647,37 @@
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>270</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>13.8</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>16.1</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
@@ -7687,42 +7687,42 @@
       </c>
       <c r="AS32" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>270</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>1017.0</t>
+          <t>1016.9</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>630</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>1017.0</t>
+          <t>1016.9</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>630</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr"/>
@@ -7765,7 +7765,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:04</t>
+          <t>2026-10-21 11:46:06</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:04</t>
+          <t>2026-10-21 11:46:06</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:04</t>
+          <t>2026-10-21 11:46:06</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -8464,7 +8464,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:04</t>
+          <t>2026-10-21 11:46:06</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -8697,17 +8697,17 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:07</t>
+          <t>2026-10-21 11:46:08</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -8721,14 +8721,14 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>149</t>
         </is>
       </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>54</t>
         </is>
       </c>
       <c r="R37" t="inlineStr"/>
@@ -8739,66 +8739,66 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>604</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr"/>
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr"/>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -8808,37 +8808,37 @@
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>149</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="AQ37" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AR37" t="inlineStr">
@@ -8848,33 +8848,33 @@
       </c>
       <c r="AS37" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>149</t>
         </is>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>604</t>
         </is>
       </c>
       <c r="AW37" t="inlineStr"/>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>604</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr"/>
@@ -8918,7 +8918,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:09</t>
+          <t>2026-10-21 11:46:10</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:09</t>
+          <t>2026-10-21 11:46:10</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -9360,7 +9360,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:09</t>
+          <t>2026-10-21 11:46:10</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:09</t>
+          <t>2026-10-21 11:46:10</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -9802,17 +9802,17 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:11</t>
+          <t>2026-10-21 11:46:14</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -10023,7 +10023,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:13</t>
+          <t>2026-10-21 11:46:16</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -10244,7 +10244,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:13</t>
+          <t>2026-10-21 11:46:16</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:13</t>
+          <t>2026-10-21 11:46:16</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -10686,7 +10686,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:13</t>
+          <t>2026-10-21 11:46:16</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -10892,7 +10892,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -10907,17 +10907,17 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:15</t>
+          <t>2026-10-21 11:46:19</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -10934,7 +10934,7 @@
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>60</t>
         </is>
       </c>
       <c r="R47" t="inlineStr"/>
@@ -10945,23 +10945,23 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="U47" t="inlineStr"/>
       <c r="V47" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>15.3</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr"/>
@@ -10972,27 +10972,27 @@
       <c r="AD47" t="inlineStr"/>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>15.3</t>
         </is>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
@@ -11004,27 +11004,27 @@
       <c r="AL47" t="inlineStr"/>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>15.3</t>
         </is>
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AQ47" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AR47" t="inlineStr">
@@ -11080,7 +11080,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:17</t>
+          <t>2026-10-21 11:46:21</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -11253,7 +11253,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:17</t>
+          <t>2026-10-21 11:46:21</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -11426,7 +11426,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:17</t>
+          <t>2026-10-21 11:46:21</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -11599,7 +11599,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:17</t>
+          <t>2026-10-21 11:46:21</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -11772,17 +11772,17 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:19</t>
+          <t>2026-10-21 11:46:24</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
       <c r="K52" t="n">
@@ -11945,7 +11945,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:21</t>
+          <t>2026-10-21 11:46:26</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:21</t>
+          <t>2026-10-21 11:46:26</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -12291,7 +12291,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:21</t>
+          <t>2026-10-21 11:46:26</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -12464,7 +12464,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:21</t>
+          <t>2026-10-21 11:46:26</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -12637,17 +12637,17 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:23</t>
+          <t>2026-10-21 11:46:29</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
       <c r="K57" t="n">
@@ -12878,7 +12878,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:25</t>
+          <t>2026-10-21 11:46:31</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -13119,7 +13119,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:25</t>
+          <t>2026-10-21 11:46:31</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:25</t>
+          <t>2026-10-21 11:46:31</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -13601,7 +13601,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:25</t>
+          <t>2026-10-21 11:46:31</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -13842,17 +13842,17 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:28</t>
+          <t>2026-10-21 11:46:34</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
       <c r="K62" t="n">
@@ -14063,7 +14063,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:29</t>
+          <t>2026-10-21 11:46:37</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -14284,7 +14284,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:29</t>
+          <t>2026-10-21 11:46:37</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -14505,7 +14505,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:29</t>
+          <t>2026-10-21 11:46:37</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -14726,7 +14726,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:29</t>
+          <t>2026-10-21 11:46:37</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -14947,17 +14947,17 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:31</t>
+          <t>2026-10-21 11:46:40</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
       <c r="K67" t="n">
@@ -15120,7 +15120,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:33</t>
+          <t>2026-10-21 11:46:42</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -15293,7 +15293,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:33</t>
+          <t>2026-10-21 11:46:42</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -15466,7 +15466,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:33</t>
+          <t>2026-10-21 11:46:42</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -15639,7 +15639,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:33</t>
+          <t>2026-10-21 11:46:42</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -15797,7 +15797,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -15812,17 +15812,17 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:35</t>
+          <t>2026-10-21 11:46:45</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
       <c r="K72" t="n">
@@ -15835,15 +15835,19 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>72</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>100</t>
         </is>
       </c>
       <c r="R72" t="inlineStr"/>
@@ -15854,66 +15858,66 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>217</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="W72" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr"/>
       <c r="AA72" t="inlineStr"/>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr"/>
       <c r="AD72" t="inlineStr"/>
       <c r="AE72" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AF72" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AG72" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AJ72" t="inlineStr">
@@ -15921,35 +15925,39 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="AK72" t="inlineStr"/>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AL72" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AN72" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="AQ72" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AR72" t="inlineStr">
@@ -15957,40 +15965,44 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="AS72" t="inlineStr"/>
+      <c r="AS72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AT72" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>72</t>
         </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>217</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>72</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>217</t>
         </is>
       </c>
       <c r="BA72" t="inlineStr"/>
@@ -16033,7 +16045,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:37</t>
+          <t>2026-10-21 11:46:47</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -16266,7 +16278,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:37</t>
+          <t>2026-10-21 11:46:47</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -16499,7 +16511,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:37</t>
+          <t>2026-10-21 11:46:47</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -16732,7 +16744,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:37</t>
+          <t>2026-10-21 11:46:47</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -16965,17 +16977,17 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:39</t>
+          <t>2026-10-21 11:46:50</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
       <c r="K77" t="n">
@@ -17198,7 +17210,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:41</t>
+          <t>2026-10-21 11:46:52</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -17431,7 +17443,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:41</t>
+          <t>2026-10-21 11:46:52</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -17664,7 +17676,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:41</t>
+          <t>2026-10-21 11:46:52</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -17897,7 +17909,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:41</t>
+          <t>2026-10-21 11:46:52</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -18115,7 +18127,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -18130,17 +18142,17 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:44</t>
+          <t>2026-10-21 11:46:54</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
       <c r="K82" t="n">
@@ -18153,7 +18165,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>148</t>
         </is>
       </c>
       <c r="N82" t="inlineStr"/>
@@ -18161,12 +18173,12 @@
       <c r="P82" t="inlineStr"/>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>55</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>1016.9</t>
+          <t>1017.4</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
@@ -18176,66 +18188,66 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>614</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>16.1</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="W82" t="inlineStr">
         <is>
-          <t>15.4</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Z82" t="inlineStr"/>
       <c r="AA82" t="inlineStr"/>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr"/>
       <c r="AD82" t="inlineStr"/>
       <c r="AE82" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AF82" t="inlineStr">
         <is>
-          <t>16.1</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="AG82" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
-          <t>15.4</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AJ82" t="inlineStr">
@@ -18245,37 +18257,37 @@
       </c>
       <c r="AK82" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AL82" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AN82" t="inlineStr">
         <is>
-          <t>16.1</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>15.4</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AQ82" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AR82" t="inlineStr">
@@ -18285,42 +18297,42 @@
       </c>
       <c r="AS82" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
-          <t>1016.9</t>
+          <t>1017.4</t>
         </is>
       </c>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>614</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
-          <t>1016.9</t>
+          <t>1017.4</t>
         </is>
       </c>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>614</t>
         </is>
       </c>
       <c r="BA82" t="inlineStr"/>
@@ -18363,7 +18375,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:45</t>
+          <t>2026-10-21 11:46:56</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -18596,7 +18608,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:45</t>
+          <t>2026-10-21 11:46:56</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -18829,7 +18841,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:45</t>
+          <t>2026-10-21 11:46:56</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -19062,7 +19074,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:45</t>
+          <t>2026-10-21 11:46:56</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -19280,7 +19292,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -19295,17 +19307,17 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:48</t>
+          <t>2026-10-21 11:46:59</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
       <c r="K87" t="n">
@@ -19318,7 +19330,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>253</t>
         </is>
       </c>
       <c r="N87" t="inlineStr"/>
@@ -19326,7 +19338,7 @@
       <c r="P87" t="inlineStr"/>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>83</t>
         </is>
       </c>
       <c r="R87" t="inlineStr"/>
@@ -19337,66 +19349,66 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>615</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="W87" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="Z87" t="inlineStr"/>
       <c r="AA87" t="inlineStr"/>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr"/>
       <c r="AD87" t="inlineStr"/>
       <c r="AE87" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AF87" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="AG87" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AJ87" t="inlineStr">
@@ -19406,37 +19418,37 @@
       </c>
       <c r="AK87" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="AL87" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>253</t>
         </is>
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AN87" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="AQ87" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AR87" t="inlineStr">
@@ -19446,33 +19458,33 @@
       </c>
       <c r="AS87" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>253</t>
         </is>
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>615</t>
         </is>
       </c>
       <c r="AW87" t="inlineStr"/>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>615</t>
         </is>
       </c>
       <c r="AZ87" t="inlineStr"/>
@@ -19516,7 +19528,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:50</t>
+          <t>2026-10-21 11:47:01</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -19737,7 +19749,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:50</t>
+          <t>2026-10-21 11:47:01</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -19958,7 +19970,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:50</t>
+          <t>2026-10-21 11:47:01</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -20179,7 +20191,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:50</t>
+          <t>2026-10-21 11:47:01</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -20385,7 +20397,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -20400,17 +20412,17 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:52</t>
+          <t>2026-10-21 11:47:04</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
       <c r="K92" t="n">
@@ -20423,7 +20435,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>335</t>
         </is>
       </c>
       <c r="N92" t="inlineStr"/>
@@ -20431,7 +20443,7 @@
       <c r="P92" t="inlineStr"/>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>69</t>
         </is>
       </c>
       <c r="R92" t="inlineStr"/>
@@ -20442,66 +20454,66 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>656</t>
         </is>
       </c>
       <c r="V92" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="W92" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="Z92" t="inlineStr"/>
       <c r="AA92" t="inlineStr"/>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr"/>
       <c r="AD92" t="inlineStr"/>
       <c r="AE92" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AF92" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="AG92" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AJ92" t="inlineStr">
@@ -20512,32 +20524,32 @@
       <c r="AK92" t="inlineStr"/>
       <c r="AL92" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="AM92" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AN92" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="AQ92" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AR92" t="inlineStr">
@@ -20548,37 +20560,37 @@
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>335</t>
         </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>656</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>335</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>656</t>
         </is>
       </c>
       <c r="BA92" t="inlineStr"/>
@@ -20621,7 +20633,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:54</t>
+          <t>2026-10-21 11:47:06</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -20854,7 +20866,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:54</t>
+          <t>2026-10-21 11:47:06</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -21087,7 +21099,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:54</t>
+          <t>2026-10-21 11:47:06</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -21320,7 +21332,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:54</t>
+          <t>2026-10-21 11:47:06</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -21553,17 +21565,17 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:56</t>
+          <t>2026-10-21 11:47:09</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
       <c r="K97" t="n">
@@ -21786,7 +21798,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:58</t>
+          <t>2026-10-21 11:47:10</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -22019,7 +22031,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:58</t>
+          <t>2026-10-21 11:47:10</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -22252,7 +22264,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:58</t>
+          <t>2026-10-21 11:47:10</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -22485,7 +22497,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-10-21 11:16:58</t>
+          <t>2026-10-21 11:47:10</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -22703,7 +22715,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -22718,17 +22730,17 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:01</t>
+          <t>2026-10-21 11:47:12</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
       <c r="K102" t="n">
@@ -22743,12 +22755,12 @@
       <c r="N102" t="inlineStr"/>
       <c r="O102" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>301</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
@@ -22764,108 +22776,108 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>497</t>
+          <t>637</t>
         </is>
       </c>
       <c r="V102" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="W102" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="Y102" t="inlineStr"/>
       <c r="Z102" t="inlineStr"/>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr"/>
       <c r="AC102" t="inlineStr"/>
       <c r="AD102" t="inlineStr">
         <is>
+          <t>22.3</t>
+        </is>
+      </c>
+      <c r="AE102" t="inlineStr">
+        <is>
+          <t>10:30 - 11:00</t>
+        </is>
+      </c>
+      <c r="AF102" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="AG102" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AL102" t="inlineStr">
+        <is>
           <t>8.6</t>
         </is>
       </c>
-      <c r="AE102" t="inlineStr">
-        <is>
-          <t>09:00 - 09:30</t>
-        </is>
-      </c>
-      <c r="AF102" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="AG102" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="AH102" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AI102" t="inlineStr">
+      <c r="AM102" t="inlineStr">
+        <is>
+          <t>10:30 - 11:00</t>
+        </is>
+      </c>
+      <c r="AN102" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="AP102" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="AQ102" t="inlineStr">
         <is>
           <t>76</t>
         </is>
       </c>
-      <c r="AJ102" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK102" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AL102" t="inlineStr">
-        <is>
-          <t>4.7</t>
-        </is>
-      </c>
-      <c r="AM102" t="inlineStr">
-        <is>
-          <t>09:00 - 09:30</t>
-        </is>
-      </c>
-      <c r="AN102" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="AO102" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="AP102" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AQ102" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
       <c r="AR102" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -22873,42 +22885,42 @@
       </c>
       <c r="AS102" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>301</t>
         </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>497</t>
+          <t>637</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>301</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>497</t>
+          <t>637</t>
         </is>
       </c>
       <c r="BA102" t="inlineStr"/>
@@ -22951,7 +22963,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:02</t>
+          <t>2026-10-21 11:47:14</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -23184,7 +23196,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:02</t>
+          <t>2026-10-21 11:47:14</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -23417,7 +23429,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:02</t>
+          <t>2026-10-21 11:47:14</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -23650,7 +23662,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:02</t>
+          <t>2026-10-21 11:47:14</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -23868,7 +23880,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -23883,17 +23895,17 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:05</t>
+          <t>2026-10-21 11:47:17</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
       <c r="K107" t="n">
@@ -23913,137 +23925,137 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>83</t>
         </is>
       </c>
       <c r="R107" t="inlineStr"/>
       <c r="S107" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>348</t>
         </is>
       </c>
       <c r="V107" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="W107" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="Y107" t="inlineStr"/>
       <c r="Z107" t="inlineStr"/>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr"/>
       <c r="AC107" t="inlineStr"/>
       <c r="AD107" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="AE107" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AF107" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="AG107" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AL107" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AN107" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AQ107" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AR107" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS107" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="AU107" t="inlineStr">
@@ -24053,12 +24065,12 @@
       </c>
       <c r="AV107" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>348</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
@@ -24068,12 +24080,12 @@
       </c>
       <c r="AY107" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>348</t>
         </is>
       </c>
       <c r="BA107" t="inlineStr"/>
@@ -24116,7 +24128,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:07</t>
+          <t>2026-10-21 11:47:19</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -24349,7 +24361,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:07</t>
+          <t>2026-10-21 11:47:19</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -24582,7 +24594,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:07</t>
+          <t>2026-10-21 11:47:19</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -24815,7 +24827,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:07</t>
+          <t>2026-10-21 11:47:19</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -25048,17 +25060,17 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:09</t>
+          <t>2026-10-21 11:47:22</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
       <c r="K112" t="n">
@@ -25281,7 +25293,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:11</t>
+          <t>2026-10-21 11:47:24</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -25514,7 +25526,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:11</t>
+          <t>2026-10-21 11:47:24</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -25747,7 +25759,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:11</t>
+          <t>2026-10-21 11:47:24</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -25980,7 +25992,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:11</t>
+          <t>2026-10-21 11:47:24</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -26198,7 +26210,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -26213,17 +26225,17 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:14</t>
+          <t>2026-10-21 11:47:27</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
       <c r="K117" t="n">
@@ -26238,13 +26250,13 @@
       <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>198</t>
         </is>
       </c>
       <c r="P117" t="inlineStr"/>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>67</t>
         </is>
       </c>
       <c r="R117" t="inlineStr"/>
@@ -26255,27 +26267,27 @@
       </c>
       <c r="T117" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t>563</t>
+          <t>776</t>
         </is>
       </c>
       <c r="V117" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="W117" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="Y117" t="inlineStr"/>
@@ -26289,32 +26301,32 @@
       <c r="AC117" t="inlineStr"/>
       <c r="AD117" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>14.8</t>
         </is>
       </c>
       <c r="AE117" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AF117" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="AG117" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>67</t>
         </is>
       </c>
       <c r="AJ117" t="inlineStr">
@@ -26330,27 +26342,27 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AN117" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ117" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>67</t>
         </is>
       </c>
       <c r="AR117" t="inlineStr">
@@ -26366,32 +26378,32 @@
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>198</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>14.8</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>563</t>
+          <t>776</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>198</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>14.8</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>563</t>
+          <t>776</t>
         </is>
       </c>
       <c r="BA117" t="inlineStr"/>
@@ -26434,7 +26446,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:15</t>
+          <t>2026-10-21 11:47:28</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -26667,7 +26679,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:15</t>
+          <t>2026-10-21 11:47:28</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -26900,7 +26912,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:15</t>
+          <t>2026-10-21 11:47:28</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -27133,7 +27145,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:15</t>
+          <t>2026-10-21 11:47:28</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -27351,7 +27363,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -27366,17 +27378,17 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:18</t>
+          <t>2026-10-21 11:47:31</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
       <c r="K122" t="n">
@@ -27389,24 +27401,24 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>195</t>
         </is>
       </c>
       <c r="N122" t="inlineStr"/>
       <c r="O122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>72</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
         <is>
-          <t>1013.1</t>
+          <t>1015.5</t>
         </is>
       </c>
       <c r="S122" t="inlineStr">
@@ -27416,66 +27428,66 @@
       </c>
       <c r="T122" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="U122" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>533</t>
         </is>
       </c>
       <c r="V122" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="W122" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>14.1</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="Z122" t="inlineStr"/>
       <c r="AA122" t="inlineStr"/>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="AC122" t="inlineStr"/>
       <c r="AD122" t="inlineStr"/>
       <c r="AE122" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AF122" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="AG122" t="inlineStr">
         <is>
-          <t>14.1</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>72</t>
         </is>
       </c>
       <c r="AJ122" t="inlineStr">
@@ -27485,37 +27497,37 @@
       </c>
       <c r="AK122" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AL122" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="AM122" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AN122" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>14.1</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="AQ122" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>72</t>
         </is>
       </c>
       <c r="AR122" t="inlineStr">
@@ -27525,47 +27537,47 @@
       </c>
       <c r="AS122" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>195</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>1013.1</t>
+          <t>1015.5</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>195</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>1013.1</t>
+          <t>1015.5</t>
         </is>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>533</t>
         </is>
       </c>
     </row>
@@ -27607,7 +27619,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:19</t>
+          <t>2026-10-21 11:47:33</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -27848,7 +27860,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:19</t>
+          <t>2026-10-21 11:47:33</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -28089,7 +28101,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:19</t>
+          <t>2026-10-21 11:47:33</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -28330,7 +28342,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:19</t>
+          <t>2026-10-21 11:47:33</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -28556,7 +28568,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -28571,17 +28583,17 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:22</t>
+          <t>2026-10-21 11:47:36</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
       <c r="K127" t="n">
@@ -28594,7 +28606,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>222</t>
         </is>
       </c>
       <c r="N127" t="inlineStr"/>
@@ -28606,82 +28618,82 @@
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>59</t>
         </is>
       </c>
       <c r="R127" t="inlineStr"/>
       <c r="S127" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="T127" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="U127" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>644</t>
         </is>
       </c>
       <c r="V127" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="W127" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Z127" t="inlineStr"/>
       <c r="AA127" t="inlineStr"/>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="AC127" t="inlineStr"/>
       <c r="AD127" t="inlineStr"/>
       <c r="AE127" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AF127" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AG127" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AI127" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>59</t>
         </is>
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -28691,37 +28703,37 @@
       </c>
       <c r="AL127" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AN127" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AQ127" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>59</t>
         </is>
       </c>
       <c r="AR127" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS127" t="inlineStr">
@@ -28731,37 +28743,37 @@
       </c>
       <c r="AT127" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>222</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>644</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>222</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>644</t>
         </is>
       </c>
       <c r="BA127" t="inlineStr"/>
@@ -28804,7 +28816,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:24</t>
+          <t>2026-10-21 11:47:39</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -29037,7 +29049,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:24</t>
+          <t>2026-10-21 11:47:39</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -29270,7 +29282,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:24</t>
+          <t>2026-10-21 11:47:39</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -29503,7 +29515,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:24</t>
+          <t>2026-10-21 11:47:39</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -29721,7 +29733,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -29736,17 +29748,17 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:27</t>
+          <t>2026-10-21 11:47:42</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
       <c r="K132" t="n">
@@ -29759,7 +29771,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>173</t>
         </is>
       </c>
       <c r="N132" t="inlineStr"/>
@@ -29767,12 +29779,12 @@
       <c r="P132" t="inlineStr"/>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>61</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>1016.9</t>
+          <t>1017.1</t>
         </is>
       </c>
       <c r="S132" t="inlineStr">
@@ -29782,66 +29794,66 @@
       </c>
       <c r="T132" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="U132" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>597</t>
         </is>
       </c>
       <c r="V132" t="inlineStr">
         <is>
-          <t>13.9</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="W132" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="Z132" t="inlineStr"/>
       <c r="AA132" t="inlineStr"/>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AC132" t="inlineStr"/>
       <c r="AD132" t="inlineStr"/>
       <c r="AE132" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AF132" t="inlineStr">
         <is>
-          <t>13.9</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="AG132" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AJ132" t="inlineStr">
@@ -29851,37 +29863,37 @@
       </c>
       <c r="AK132" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="AL132" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>173</t>
         </is>
       </c>
       <c r="AM132" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AN132" t="inlineStr">
         <is>
-          <t>13.9</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="AO132" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="AQ132" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AR132" t="inlineStr">
@@ -29891,42 +29903,42 @@
       </c>
       <c r="AS132" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="AT132" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>173</t>
         </is>
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AV132" t="inlineStr">
         <is>
-          <t>1016.9</t>
+          <t>1017.1</t>
         </is>
       </c>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>597</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
-          <t>1016.9</t>
+          <t>1017.1</t>
         </is>
       </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>597</t>
         </is>
       </c>
       <c r="BA132" t="inlineStr"/>
@@ -29969,7 +29981,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:28</t>
+          <t>2026-10-21 11:47:44</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -30202,7 +30214,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:28</t>
+          <t>2026-10-21 11:47:44</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -30435,7 +30447,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:28</t>
+          <t>2026-10-21 11:47:44</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -30668,7 +30680,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:28</t>
+          <t>2026-10-21 11:47:44</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -30886,7 +30898,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -30901,17 +30913,17 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:31</t>
+          <t>2026-10-21 11:47:47</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
       <c r="K137" t="n">
@@ -30924,7 +30936,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>172</t>
         </is>
       </c>
       <c r="N137" t="inlineStr"/>
@@ -30932,7 +30944,7 @@
       <c r="P137" t="inlineStr"/>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>63</t>
         </is>
       </c>
       <c r="R137" t="inlineStr"/>
@@ -30943,66 +30955,66 @@
       </c>
       <c r="T137" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="U137" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>605</t>
         </is>
       </c>
       <c r="V137" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="W137" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="X137" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="Z137" t="inlineStr"/>
       <c r="AA137" t="inlineStr"/>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AC137" t="inlineStr"/>
       <c r="AD137" t="inlineStr"/>
       <c r="AE137" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AF137" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AG137" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AJ137" t="inlineStr">
@@ -31012,37 +31024,37 @@
       </c>
       <c r="AK137" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AL137" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>172</t>
         </is>
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AN137" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AO137" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="AQ137" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AR137" t="inlineStr">
@@ -31052,33 +31064,33 @@
       </c>
       <c r="AS137" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AT137" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>172</t>
         </is>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>605</t>
         </is>
       </c>
       <c r="AW137" t="inlineStr"/>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>605</t>
         </is>
       </c>
       <c r="AZ137" t="inlineStr"/>
@@ -31122,7 +31134,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:33</t>
+          <t>2026-10-21 11:47:50</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -31343,7 +31355,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:33</t>
+          <t>2026-10-21 11:47:50</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -31564,7 +31576,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:33</t>
+          <t>2026-10-21 11:47:50</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -31785,7 +31797,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:33</t>
+          <t>2026-10-21 11:47:50</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -31991,7 +32003,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -32006,17 +32018,17 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:35</t>
+          <t>2026-10-21 11:47:53</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
       <c r="K142" t="n">
@@ -32029,7 +32041,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>176</t>
         </is>
       </c>
       <c r="N142" t="inlineStr"/>
@@ -32037,12 +32049,12 @@
       <c r="P142" t="inlineStr"/>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>53</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>1016.6</t>
+          <t>1017.4</t>
         </is>
       </c>
       <c r="S142" t="inlineStr">
@@ -32052,66 +32064,66 @@
       </c>
       <c r="T142" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="U142" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>613</t>
         </is>
       </c>
       <c r="V142" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="W142" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="X142" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="Z142" t="inlineStr"/>
       <c r="AA142" t="inlineStr"/>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="AC142" t="inlineStr"/>
       <c r="AD142" t="inlineStr"/>
       <c r="AE142" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AF142" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="AG142" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="AH142" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AJ142" t="inlineStr">
@@ -32121,37 +32133,37 @@
       </c>
       <c r="AK142" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AL142" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>176</t>
         </is>
       </c>
       <c r="AM142" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AN142" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="AO142" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="AQ142" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AR142" t="inlineStr">
@@ -32161,42 +32173,42 @@
       </c>
       <c r="AS142" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AT142" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>176</t>
         </is>
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="AV142" t="inlineStr">
         <is>
-          <t>1016.6</t>
+          <t>1017.4</t>
         </is>
       </c>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>613</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
         <is>
-          <t>1016.6</t>
+          <t>1017.4</t>
         </is>
       </c>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>613</t>
         </is>
       </c>
       <c r="BA142" t="inlineStr"/>
@@ -32239,7 +32251,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:37</t>
+          <t>2026-10-21 11:47:55</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -32472,7 +32484,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:37</t>
+          <t>2026-10-21 11:47:55</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -32705,7 +32717,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:37</t>
+          <t>2026-10-21 11:47:55</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -32938,7 +32950,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:37</t>
+          <t>2026-10-21 11:47:55</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -33171,17 +33183,17 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:39</t>
+          <t>2026-10-21 11:47:58</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
       <c r="K147" t="n">
@@ -33404,7 +33416,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:41</t>
+          <t>2026-10-21 11:48:01</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -33637,7 +33649,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:41</t>
+          <t>2026-10-21 11:48:01</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -33870,7 +33882,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:41</t>
+          <t>2026-10-21 11:48:01</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -34103,7 +34115,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:41</t>
+          <t>2026-10-21 11:48:01</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -34336,17 +34348,17 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:44</t>
+          <t>2026-10-21 11:48:04</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
       <c r="K152" t="n">
@@ -34569,7 +34581,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:45</t>
+          <t>2026-10-21 11:48:06</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -34802,7 +34814,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:45</t>
+          <t>2026-10-21 11:48:06</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -35035,7 +35047,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:45</t>
+          <t>2026-10-21 11:48:06</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -35268,7 +35280,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:45</t>
+          <t>2026-10-21 11:48:06</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -35486,7 +35498,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -35501,17 +35513,17 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:48</t>
+          <t>2026-10-21 11:48:09</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
       <c r="K157" t="n">
@@ -35524,7 +35536,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>155</t>
         </is>
       </c>
       <c r="N157" t="inlineStr"/>
@@ -35532,12 +35544,12 @@
       <c r="P157" t="inlineStr"/>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>53</t>
         </is>
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>1017.8</t>
+          <t>1015.9</t>
         </is>
       </c>
       <c r="S157" t="inlineStr">
@@ -35547,66 +35559,66 @@
       </c>
       <c r="T157" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="U157" t="inlineStr">
         <is>
-          <t>486</t>
+          <t>676</t>
         </is>
       </c>
       <c r="V157" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>12.6</t>
         </is>
       </c>
       <c r="W157" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="X157" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="Z157" t="inlineStr"/>
       <c r="AA157" t="inlineStr"/>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AC157" t="inlineStr"/>
       <c r="AD157" t="inlineStr"/>
       <c r="AE157" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AF157" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>12.6</t>
         </is>
       </c>
       <c r="AG157" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="AI157" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AJ157" t="inlineStr">
@@ -35616,37 +35628,37 @@
       </c>
       <c r="AK157" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AL157" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>155</t>
         </is>
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AN157" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>12.6</t>
         </is>
       </c>
       <c r="AO157" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="AQ157" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AR157" t="inlineStr">
@@ -35656,42 +35668,42 @@
       </c>
       <c r="AS157" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AT157" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>155</t>
         </is>
       </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
-          <t>1017.8</t>
+          <t>1015.9</t>
         </is>
       </c>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>486</t>
+          <t>676</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
         <is>
-          <t>1017.8</t>
+          <t>1015.9</t>
         </is>
       </c>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>486</t>
+          <t>676</t>
         </is>
       </c>
       <c r="BA157" t="inlineStr"/>
@@ -35734,7 +35746,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:50</t>
+          <t>2026-10-21 11:48:12</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -35967,7 +35979,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:50</t>
+          <t>2026-10-21 11:48:12</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -36200,7 +36212,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:50</t>
+          <t>2026-10-21 11:48:12</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -36433,7 +36445,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:50</t>
+          <t>2026-10-21 11:48:12</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -36666,17 +36678,17 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:52</t>
+          <t>2026-10-21 11:48:14</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
       <c r="K162" t="n">
@@ -36907,7 +36919,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:54</t>
+          <t>2026-10-21 11:48:16</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -37148,7 +37160,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:54</t>
+          <t>2026-10-21 11:48:16</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -37389,7 +37401,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:54</t>
+          <t>2026-10-21 11:48:16</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -37630,7 +37642,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:54</t>
+          <t>2026-10-21 11:48:16</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -37856,7 +37868,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -37871,17 +37883,17 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:57</t>
+          <t>2026-10-21 11:48:19</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
       <c r="K167" t="n">
@@ -37894,7 +37906,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>251</t>
         </is>
       </c>
       <c r="N167" t="inlineStr"/>
@@ -37902,12 +37914,12 @@
       <c r="P167" t="inlineStr"/>
       <c r="Q167" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>62</t>
         </is>
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>1019.5</t>
+          <t>1019.4</t>
         </is>
       </c>
       <c r="S167" t="inlineStr">
@@ -37917,66 +37929,66 @@
       </c>
       <c r="T167" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="U167" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>657</t>
         </is>
       </c>
       <c r="V167" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="W167" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="X167" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="Z167" t="inlineStr"/>
       <c r="AA167" t="inlineStr"/>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="AC167" t="inlineStr"/>
       <c r="AD167" t="inlineStr"/>
       <c r="AE167" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AF167" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AG167" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AH167" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="AI167" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AJ167" t="inlineStr">
@@ -37987,32 +37999,32 @@
       <c r="AK167" t="inlineStr"/>
       <c r="AL167" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AN167" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AO167" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="AQ167" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AR167" t="inlineStr">
@@ -38023,42 +38035,42 @@
       <c r="AS167" t="inlineStr"/>
       <c r="AT167" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="AU167" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>251</t>
         </is>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>1019.5</t>
+          <t>1019.4</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>251</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>1019.5</t>
+          <t>1019.4</t>
         </is>
       </c>
       <c r="BA167" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>657</t>
         </is>
       </c>
     </row>
@@ -38100,7 +38112,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:58</t>
+          <t>2026-10-21 11:48:22</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -38341,7 +38353,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:58</t>
+          <t>2026-10-21 11:48:22</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -38582,7 +38594,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:58</t>
+          <t>2026-10-21 11:48:22</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -38823,7 +38835,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026-10-21 11:17:58</t>
+          <t>2026-10-21 11:48:22</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -39064,17 +39076,17 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-10-21 11:18:01</t>
+          <t>2026-10-21 11:48:25</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
       <c r="K172" t="n">
@@ -39297,7 +39309,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-10-21 11:18:02</t>
+          <t>2026-10-21 11:48:27</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -39530,7 +39542,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026-10-21 11:18:02</t>
+          <t>2026-10-21 11:48:27</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -39763,7 +39775,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026-10-21 11:18:02</t>
+          <t>2026-10-21 11:48:27</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -39996,7 +40008,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026-10-21 11:18:02</t>
+          <t>2026-10-21 11:48:27</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -40229,17 +40241,17 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026-10-21 11:18:05</t>
+          <t>2026-10-21 11:48:30</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
       <c r="K177" t="n">
@@ -40450,7 +40462,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026-10-21 11:18:07</t>
+          <t>2026-10-21 11:48:32</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -40671,7 +40683,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-10-21 11:18:07</t>
+          <t>2026-10-21 11:48:32</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -40892,7 +40904,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-10-21 11:18:07</t>
+          <t>2026-10-21 11:48:32</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -41113,7 +41125,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026-10-21 11:18:07</t>
+          <t>2026-10-21 11:48:32</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -41334,17 +41346,17 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026-10-21 11:18:09</t>
+          <t>2026-10-21 11:48:36</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
       <c r="K182" t="n">
@@ -41555,7 +41567,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026-10-21 11:18:11</t>
+          <t>2026-10-21 11:48:38</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -41776,7 +41788,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026-10-21 11:18:11</t>
+          <t>2026-10-21 11:48:38</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -41997,7 +42009,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-10-21 11:18:11</t>
+          <t>2026-10-21 11:48:38</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -42218,7 +42230,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-10-21 11:18:11</t>
+          <t>2026-10-21 11:48:38</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -42424,7 +42436,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>09:30 - 10:00</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -42439,17 +42451,17 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2026-10-21 11:18:13</t>
+          <t>2026-10-21 11:48:41</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
       <c r="K187" t="n">
@@ -42462,7 +42474,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>142</t>
         </is>
       </c>
       <c r="N187" t="inlineStr"/>
@@ -42481,61 +42493,61 @@
       </c>
       <c r="T187" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>09:30 - 10:00</t>
         </is>
       </c>
       <c r="U187" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>337</t>
         </is>
       </c>
       <c r="V187" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="W187" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="X187" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="Y187" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="Z187" t="inlineStr"/>
       <c r="AA187" t="inlineStr"/>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="AC187" t="inlineStr"/>
       <c r="AD187" t="inlineStr"/>
       <c r="AE187" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>09:30 - 10:00</t>
         </is>
       </c>
       <c r="AF187" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="AG187" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="AH187" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AI187" t="inlineStr">
@@ -42551,27 +42563,27 @@
       <c r="AK187" t="inlineStr"/>
       <c r="AL187" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>09:30 - 10:00</t>
         </is>
       </c>
       <c r="AN187" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="AO187" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="AP187" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ187" t="inlineStr">
@@ -42587,37 +42599,37 @@
       <c r="AS187" t="inlineStr"/>
       <c r="AT187" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="AU187" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>142</t>
         </is>
       </c>
       <c r="AV187" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>337</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>142</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>337</t>
         </is>
       </c>
       <c r="BA187" t="inlineStr"/>
@@ -42660,7 +42672,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2026-10-21 11:18:15</t>
+          <t>2026-10-21 11:48:43</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -42893,7 +42905,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2026-10-21 11:18:15</t>
+          <t>2026-10-21 11:48:43</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -43126,7 +43138,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-10-21 11:18:15</t>
+          <t>2026-10-21 11:48:43</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -43359,7 +43371,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-10-21 11:18:15</t>
+          <t>2026-10-21 11:48:43</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -43577,7 +43589,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -43592,17 +43604,17 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2026-10-21 11:18:18</t>
+          <t>2026-10-21 11:48:46</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
       <c r="K192" t="n">
@@ -43623,12 +43635,12 @@
       </c>
       <c r="Q192" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>53</t>
         </is>
       </c>
       <c r="R192" t="inlineStr">
         <is>
-          <t>1018.7</t>
+          <t>1017.7</t>
         </is>
       </c>
       <c r="S192" t="inlineStr">
@@ -43638,23 +43650,23 @@
       </c>
       <c r="T192" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="U192" t="inlineStr"/>
       <c r="V192" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="W192" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="X192" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>14.1</t>
         </is>
       </c>
       <c r="Y192" t="inlineStr"/>
@@ -43665,27 +43677,27 @@
       <c r="AD192" t="inlineStr"/>
       <c r="AE192" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AF192" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="AG192" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>14.1</t>
         </is>
       </c>
       <c r="AH192" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AI192" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AJ192" t="inlineStr">
@@ -43700,32 +43712,32 @@
       </c>
       <c r="AL192" t="inlineStr">
         <is>
-          <t>1018.7</t>
+          <t>1017.7</t>
         </is>
       </c>
       <c r="AM192" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AN192" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="AO192" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>14.1</t>
         </is>
       </c>
       <c r="AP192" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AQ192" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AR192" t="inlineStr">
@@ -43740,7 +43752,7 @@
       </c>
       <c r="AT192" t="inlineStr">
         <is>
-          <t>1018.7</t>
+          <t>1017.7</t>
         </is>
       </c>
       <c r="AU192" t="inlineStr"/>
@@ -43789,7 +43801,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2026-10-21 11:18:19</t>
+          <t>2026-10-21 11:48:48</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -43986,7 +43998,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2026-10-21 11:18:19</t>
+          <t>2026-10-21 11:48:48</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -44183,7 +44195,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026-10-21 11:18:19</t>
+          <t>2026-10-21 11:48:48</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -44380,7 +44392,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2026-10-21 11:18:19</t>
+          <t>2026-10-21 11:48:48</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -44577,17 +44589,17 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2026-10-21 11:18:22</t>
+          <t>2026-10-21 11:48:51</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
       <c r="K197" t="n">
@@ -44810,7 +44822,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2026-10-21 11:18:23</t>
+          <t>2026-10-21 11:48:53</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -45043,7 +45055,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2026-10-21 11:18:23</t>
+          <t>2026-10-21 11:48:53</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -45276,7 +45288,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2026-10-21 11:18:23</t>
+          <t>2026-10-21 11:48:53</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -45509,7 +45521,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-10-21 11:18:23</t>
+          <t>2026-10-21 11:48:53</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -45742,17 +45754,17 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>2026-10-21 11:18:26</t>
+          <t>2026-10-21 11:48:55</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
       <c r="K202" t="n">
@@ -45915,7 +45927,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>2026-10-21 11:18:27</t>
+          <t>2026-10-21 11:48:57</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -46088,7 +46100,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>2026-10-21 11:18:27</t>
+          <t>2026-10-21 11:48:57</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -46261,7 +46273,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>2026-10-21 11:18:27</t>
+          <t>2026-10-21 11:48:57</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -46434,7 +46446,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>2026-10-21 11:18:27</t>
+          <t>2026-10-21 11:48:57</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -46592,7 +46604,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -46607,17 +46619,17 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>2026-10-21 11:18:29</t>
+          <t>2026-10-21 11:49:00</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
       <c r="K207" t="n">
@@ -46630,7 +46642,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>38</t>
         </is>
       </c>
       <c r="N207" t="inlineStr"/>
@@ -46638,7 +46650,7 @@
       <c r="P207" t="inlineStr"/>
       <c r="Q207" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>70</t>
         </is>
       </c>
       <c r="R207" t="inlineStr"/>
@@ -46649,66 +46661,66 @@
       </c>
       <c r="T207" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="U207" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>610</t>
         </is>
       </c>
       <c r="V207" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>14.1</t>
         </is>
       </c>
       <c r="W207" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="X207" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="Z207" t="inlineStr"/>
       <c r="AA207" t="inlineStr"/>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AC207" t="inlineStr"/>
       <c r="AD207" t="inlineStr"/>
       <c r="AE207" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AF207" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>14.1</t>
         </is>
       </c>
       <c r="AG207" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="AH207" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="AI207" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AJ207" t="inlineStr">
@@ -46718,37 +46730,37 @@
       </c>
       <c r="AK207" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AL207" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AN207" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>14.1</t>
         </is>
       </c>
       <c r="AO207" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="AQ207" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AR207" t="inlineStr">
@@ -46758,33 +46770,33 @@
       </c>
       <c r="AS207" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AT207" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AV207" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>610</t>
         </is>
       </c>
       <c r="AW207" t="inlineStr"/>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>610</t>
         </is>
       </c>
       <c r="AZ207" t="inlineStr"/>
@@ -46828,7 +46840,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>2026-10-21 11:18:31</t>
+          <t>2026-10-21 11:49:02</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -47049,7 +47061,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>2026-10-21 11:18:31</t>
+          <t>2026-10-21 11:49:02</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -47270,7 +47282,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>2026-10-21 11:18:31</t>
+          <t>2026-10-21 11:49:02</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -47491,7 +47503,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>2026-10-21 11:18:31</t>
+          <t>2026-10-21 11:49:02</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -47697,7 +47709,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -47712,17 +47724,17 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>2026-10-21 11:18:33</t>
+          <t>2026-10-21 11:49:05</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
       <c r="K212" t="n">
@@ -47735,24 +47747,24 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>34</t>
         </is>
       </c>
       <c r="N212" t="inlineStr"/>
       <c r="O212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q212" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>99</t>
         </is>
       </c>
       <c r="R212" t="inlineStr">
         <is>
-          <t>851.5</t>
+          <t>852.5</t>
         </is>
       </c>
       <c r="S212" t="inlineStr">
@@ -47762,66 +47774,66 @@
       </c>
       <c r="T212" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="U212" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>181</t>
         </is>
       </c>
       <c r="V212" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="W212" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="X212" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="Y212" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="Z212" t="inlineStr"/>
       <c r="AA212" t="inlineStr"/>
       <c r="AB212" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="AC212" t="inlineStr"/>
       <c r="AD212" t="inlineStr"/>
       <c r="AE212" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AF212" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="AG212" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="AH212" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="AI212" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AJ212" t="inlineStr">
@@ -47831,37 +47843,37 @@
       </c>
       <c r="AK212" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AL212" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="AM212" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AN212" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="AO212" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="AP212" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="AQ212" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AR212" t="inlineStr">
@@ -47871,47 +47883,47 @@
       </c>
       <c r="AS212" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AT212" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="AU212" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AV212" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>851.5</t>
+          <t>852.5</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>851.5</t>
+          <t>852.5</t>
         </is>
       </c>
       <c r="BA212" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>181</t>
         </is>
       </c>
     </row>
@@ -47953,7 +47965,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>2026-10-21 11:18:35</t>
+          <t>2026-10-21 11:49:08</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -48194,7 +48206,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>2026-10-21 11:18:35</t>
+          <t>2026-10-21 11:49:08</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -48435,7 +48447,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>2026-10-21 11:18:35</t>
+          <t>2026-10-21 11:49:08</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -48676,7 +48688,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>2026-10-21 11:18:35</t>
+          <t>2026-10-21 11:49:08</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -48902,7 +48914,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -48917,17 +48929,17 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>2026-10-21 11:18:38</t>
+          <t>2026-10-21 11:49:11</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
       <c r="K217" t="n">
@@ -48942,7 +48954,7 @@
       <c r="N217" t="inlineStr"/>
       <c r="O217" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>273</t>
         </is>
       </c>
       <c r="P217" t="inlineStr">
@@ -48952,42 +48964,42 @@
       </c>
       <c r="Q217" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>95</t>
         </is>
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>1020.8</t>
+          <t>1021.6</t>
         </is>
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="T217" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="U217" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>181</t>
         </is>
       </c>
       <c r="V217" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="W217" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="X217" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="Y217" t="inlineStr"/>
@@ -49001,37 +49013,37 @@
       <c r="AC217" t="inlineStr"/>
       <c r="AD217" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="AE217" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AF217" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="AG217" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="AH217" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="AI217" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>95</t>
         </is>
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -49046,32 +49058,32 @@
       </c>
       <c r="AM217" t="inlineStr">
         <is>
-          <t>09:00 - 09:30</t>
+          <t>10:30 - 11:00</t>
         </is>
       </c>
       <c r="AN217" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="AO217" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="AP217" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="AQ217" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>95</t>
         </is>
       </c>
       <c r="AR217" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS217" t="inlineStr">
@@ -49086,37 +49098,37 @@
       </c>
       <c r="AU217" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>273</t>
         </is>
       </c>
       <c r="AV217" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="AW217" t="inlineStr">
         <is>
-          <t>1020.8</t>
+          <t>1021.6</t>
         </is>
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>273</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="AZ217" t="inlineStr">
         <is>
-          <t>1020.8</t>
+          <t>1021.6</t>
         </is>
       </c>
       <c r="BA217" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>181</t>
         </is>
       </c>
     </row>
@@ -49158,7 +49170,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>2026-10-21 11:18:39</t>
+          <t>2026-10-21 11:49:13</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -49399,7 +49411,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>2026-10-21 11:18:39</t>
+          <t>2026-10-21 11:49:13</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -49640,7 +49652,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>2026-10-21 11:18:39</t>
+          <t>2026-10-21 11:49:13</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -49881,7 +49893,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>2026-10-21 11:18:39</t>
+          <t>2026-10-21 11:49:13</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -50122,17 +50134,17 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>2026-10-21 11:18:41</t>
+          <t>2026-10-21 11:49:15</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
       <c r="K222" t="n">
@@ -50355,7 +50367,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>2026-10-21 11:18:42</t>
+          <t>2026-10-21 11:49:18</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -50588,7 +50600,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>2026-10-21 11:18:42</t>
+          <t>2026-10-21 11:49:18</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -50821,7 +50833,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>2026-10-21 11:18:42</t>
+          <t>2026-10-21 11:49:18</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -51054,7 +51066,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>2026-10-21 11:18:42</t>
+          <t>2026-10-21 11:49:18</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -51321,7 +51333,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
     </row>
@@ -51351,7 +51363,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
     </row>
@@ -51381,7 +51393,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
     </row>
@@ -51411,7 +51423,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
     </row>
@@ -51441,7 +51453,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
     </row>
@@ -51471,7 +51483,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
     </row>
@@ -51501,7 +51513,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
     </row>
@@ -51531,7 +51543,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
     </row>
@@ -51561,7 +51573,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
     </row>
@@ -51591,7 +51603,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
     </row>
@@ -51621,7 +51633,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
     </row>
@@ -51651,7 +51663,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
     </row>
@@ -51681,7 +51693,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
     </row>
@@ -51711,7 +51723,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
     </row>
@@ -51741,7 +51753,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
     </row>
@@ -51771,7 +51783,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
     </row>
@@ -51801,7 +51813,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
     </row>
@@ -51831,7 +51843,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
     </row>
@@ -51861,7 +51873,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
     </row>
@@ -51891,7 +51903,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
     </row>
@@ -51921,7 +51933,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
     </row>
@@ -51951,7 +51963,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
     </row>
@@ -51981,7 +51993,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
     </row>
@@ -52011,7 +52023,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
     </row>
@@ -52041,7 +52053,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
     </row>
@@ -52071,7 +52083,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
     </row>
@@ -52101,7 +52113,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
     </row>
@@ -52131,7 +52143,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
     </row>
@@ -52161,7 +52173,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
     </row>
@@ -52191,7 +52203,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
     </row>
@@ -52221,7 +52233,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
     </row>
@@ -52251,7 +52263,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
     </row>
@@ -52281,7 +52293,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
     </row>
@@ -52311,7 +52323,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
     </row>
@@ -52341,7 +52353,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
     </row>
@@ -52371,7 +52383,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
     </row>
@@ -52401,7 +52413,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
     </row>
@@ -52431,7 +52443,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
     </row>
@@ -52461,7 +52473,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
     </row>
@@ -52491,7 +52503,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
     </row>
@@ -52521,7 +52533,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
     </row>
@@ -52551,7 +52563,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
     </row>
@@ -52581,7 +52593,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
     </row>
@@ -52611,7 +52623,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
     </row>
@@ -52641,7 +52653,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-10-21T10:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-10-21T11:00Z</t>
         </is>
       </c>
     </row>

--- a/src/data/resum_periode_meteocat.xlsx
+++ b/src/data/resum_periode_meteocat.xlsx
@@ -722,17 +722,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-21 11:45:33</t>
+          <t>2026-10-21 12:15:39</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -919,7 +919,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-10-21 11:45:35</t>
+          <t>2026-10-21 12:15:41</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-10-21 11:45:35</t>
+          <t>2026-10-21 12:15:41</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-10-21 11:45:35</t>
+          <t>2026-10-21 12:15:41</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-10-21 11:45:35</t>
+          <t>2026-10-21 12:15:41</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-21 11:45:38</t>
+          <t>2026-10-21 12:15:44</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-21 11:45:41</t>
+          <t>2026-10-21 12:15:46</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-21 11:45:41</t>
+          <t>2026-10-21 12:15:46</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-21 11:45:41</t>
+          <t>2026-10-21 12:15:46</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-10-21 11:45:41</t>
+          <t>2026-10-21 12:15:46</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2872,17 +2872,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-10-21 11:45:44</t>
+          <t>2026-10-21 12:15:49</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-10-21 11:45:46</t>
+          <t>2026-10-21 12:15:51</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-10-21 11:45:46</t>
+          <t>2026-10-21 12:15:51</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-10-21 11:45:46</t>
+          <t>2026-10-21 12:15:51</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-10-21 11:45:46</t>
+          <t>2026-10-21 12:15:51</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -4037,17 +4037,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-10-21 11:45:49</t>
+          <t>2026-10-21 12:15:54</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-10-21 11:45:51</t>
+          <t>2026-10-21 12:15:56</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-10-21 11:45:51</t>
+          <t>2026-10-21 12:15:56</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-10-21 11:45:51</t>
+          <t>2026-10-21 12:15:56</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-10-21 11:45:51</t>
+          <t>2026-10-21 12:15:56</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -5202,17 +5202,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-10-21 11:45:54</t>
+          <t>2026-10-21 12:15:59</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-10-21 11:45:56</t>
+          <t>2026-10-21 12:16:01</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-10-21 11:45:56</t>
+          <t>2026-10-21 12:16:01</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-10-21 11:45:56</t>
+          <t>2026-10-21 12:16:01</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-10-21 11:45:56</t>
+          <t>2026-10-21 12:16:01</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -6367,17 +6367,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-10-21 11:45:58</t>
+          <t>2026-10-21 12:16:04</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -6600,7 +6600,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:01</t>
+          <t>2026-10-21 12:16:06</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -6833,7 +6833,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:01</t>
+          <t>2026-10-21 12:16:06</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:01</t>
+          <t>2026-10-21 12:16:06</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:01</t>
+          <t>2026-10-21 12:16:06</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -7532,17 +7532,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:04</t>
+          <t>2026-10-21 12:16:09</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -7765,7 +7765,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:06</t>
+          <t>2026-10-21 12:16:11</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:06</t>
+          <t>2026-10-21 12:16:11</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:06</t>
+          <t>2026-10-21 12:16:11</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -8464,7 +8464,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:06</t>
+          <t>2026-10-21 12:16:11</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -8697,17 +8697,17 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:08</t>
+          <t>2026-10-21 12:16:13</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -8918,7 +8918,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:10</t>
+          <t>2026-10-21 12:16:16</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:10</t>
+          <t>2026-10-21 12:16:16</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -9360,7 +9360,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:10</t>
+          <t>2026-10-21 12:16:16</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:10</t>
+          <t>2026-10-21 12:16:16</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -9802,17 +9802,17 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:14</t>
+          <t>2026-10-21 12:16:19</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -10023,7 +10023,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:16</t>
+          <t>2026-10-21 12:16:21</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -10244,7 +10244,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:16</t>
+          <t>2026-10-21 12:16:21</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:16</t>
+          <t>2026-10-21 12:16:21</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -10686,7 +10686,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:16</t>
+          <t>2026-10-21 12:16:21</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -10907,17 +10907,17 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:19</t>
+          <t>2026-10-21 12:16:24</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -11080,7 +11080,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:21</t>
+          <t>2026-10-21 12:16:25</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -11253,7 +11253,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:21</t>
+          <t>2026-10-21 12:16:25</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -11426,7 +11426,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:21</t>
+          <t>2026-10-21 12:16:25</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -11599,7 +11599,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:21</t>
+          <t>2026-10-21 12:16:25</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -11772,17 +11772,17 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:24</t>
+          <t>2026-10-21 12:16:28</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
       <c r="K52" t="n">
@@ -11945,7 +11945,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:26</t>
+          <t>2026-10-21 12:16:30</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:26</t>
+          <t>2026-10-21 12:16:30</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -12291,7 +12291,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:26</t>
+          <t>2026-10-21 12:16:30</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -12464,7 +12464,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:26</t>
+          <t>2026-10-21 12:16:30</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -12637,17 +12637,17 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:29</t>
+          <t>2026-10-21 12:16:33</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
       <c r="K57" t="n">
@@ -12878,7 +12878,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:31</t>
+          <t>2026-10-21 12:16:35</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -13119,7 +13119,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:31</t>
+          <t>2026-10-21 12:16:35</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:31</t>
+          <t>2026-10-21 12:16:35</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -13601,7 +13601,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:31</t>
+          <t>2026-10-21 12:16:35</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -13842,17 +13842,17 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:34</t>
+          <t>2026-10-21 12:16:38</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
       <c r="K62" t="n">
@@ -14063,7 +14063,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:37</t>
+          <t>2026-10-21 12:16:41</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -14284,7 +14284,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:37</t>
+          <t>2026-10-21 12:16:41</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -14505,7 +14505,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:37</t>
+          <t>2026-10-21 12:16:41</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -14726,7 +14726,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:37</t>
+          <t>2026-10-21 12:16:41</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -14947,17 +14947,17 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:40</t>
+          <t>2026-10-21 12:16:44</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
       <c r="K67" t="n">
@@ -15120,7 +15120,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:42</t>
+          <t>2026-10-21 12:16:46</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -15293,7 +15293,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:42</t>
+          <t>2026-10-21 12:16:46</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -15466,7 +15466,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:42</t>
+          <t>2026-10-21 12:16:46</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -15639,7 +15639,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:42</t>
+          <t>2026-10-21 12:16:46</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -15812,17 +15812,17 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:45</t>
+          <t>2026-10-21 12:16:49</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
       <c r="K72" t="n">
@@ -16045,7 +16045,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:47</t>
+          <t>2026-10-21 12:16:51</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -16278,7 +16278,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:47</t>
+          <t>2026-10-21 12:16:51</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -16511,7 +16511,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:47</t>
+          <t>2026-10-21 12:16:51</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:47</t>
+          <t>2026-10-21 12:16:51</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -16977,17 +16977,17 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:50</t>
+          <t>2026-10-21 12:16:54</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
       <c r="K77" t="n">
@@ -17210,7 +17210,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:52</t>
+          <t>2026-10-21 12:16:56</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -17443,7 +17443,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:52</t>
+          <t>2026-10-21 12:16:56</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -17676,7 +17676,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:52</t>
+          <t>2026-10-21 12:16:56</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -17909,7 +17909,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:52</t>
+          <t>2026-10-21 12:16:56</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -18142,17 +18142,17 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:54</t>
+          <t>2026-10-21 12:16:59</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
       <c r="K82" t="n">
@@ -18375,7 +18375,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:56</t>
+          <t>2026-10-21 12:17:02</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -18608,7 +18608,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:56</t>
+          <t>2026-10-21 12:17:02</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -18841,7 +18841,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:56</t>
+          <t>2026-10-21 12:17:02</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:56</t>
+          <t>2026-10-21 12:17:02</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -19307,17 +19307,17 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:59</t>
+          <t>2026-10-21 12:17:05</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
       <c r="K87" t="n">
@@ -19528,7 +19528,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47:01</t>
+          <t>2026-10-21 12:17:06</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -19749,7 +19749,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47:01</t>
+          <t>2026-10-21 12:17:06</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -19970,7 +19970,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47:01</t>
+          <t>2026-10-21 12:17:06</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -20191,7 +20191,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47:01</t>
+          <t>2026-10-21 12:17:06</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -20412,17 +20412,17 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47:04</t>
+          <t>2026-10-21 12:17:09</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
       <c r="K92" t="n">
@@ -20633,7 +20633,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47:06</t>
+          <t>2026-10-21 12:17:11</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -20866,7 +20866,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47:06</t>
+          <t>2026-10-21 12:17:11</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -21099,7 +21099,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47:06</t>
+          <t>2026-10-21 12:17:11</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -21332,7 +21332,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47:06</t>
+          <t>2026-10-21 12:17:11</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -21565,17 +21565,17 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47:09</t>
+          <t>2026-10-21 12:17:14</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
       <c r="K97" t="n">
@@ -21798,7 +21798,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47:10</t>
+          <t>2026-10-21 12:17:16</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -22031,7 +22031,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47:10</t>
+          <t>2026-10-21 12:17:16</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -22264,7 +22264,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47:10</t>
+          <t>2026-10-21 12:17:16</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -22497,7 +22497,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47:10</t>
+          <t>2026-10-21 12:17:16</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -22730,17 +22730,17 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47:12</t>
+          <t>2026-10-21 12:17:19</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
       <c r="K102" t="n">
@@ -22963,7 +22963,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47:14</t>
+          <t>2026-10-21 12:17:21</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -23196,7 +23196,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47:14</t>
+          <t>2026-10-21 12:17:21</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -23429,7 +23429,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47:14</t>
+          <t>2026-10-21 12:17:21</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -23662,7 +23662,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47:14</t>
+          <t>2026-10-21 12:17:21</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -23895,17 +23895,17 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47:17</t>
+          <t>2026-10-21 12:17:24</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
       <c r="K107" t="n">
@@ -24128,7 +24128,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47:19</t>
+          <t>2026-10-21 12:17:26</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -24361,7 +24361,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47:19</t>
+          <t>2026-10-21 12:17:26</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -24594,7 +24594,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47:19</t>
+          <t>2026-10-21 12:17:26</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -24827,7 +24827,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47:19</t>
+          <t>2026-10-21 12:17:26</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -25060,17 +25060,17 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47:22</t>
+          <t>2026-10-21 12:17:30</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
       <c r="K112" t="n">
@@ -25293,7 +25293,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47:24</t>
+          <t>2026-10-21 12:17:32</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -25526,7 +25526,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47:24</t>
+          <t>2026-10-21 12:17:32</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -25759,7 +25759,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47:24</t>
+          <t>2026-10-21 12:17:32</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -25992,7 +25992,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47:24</t>
+          <t>2026-10-21 12:17:32</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -26225,17 +26225,17 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47:27</t>
+          <t>2026-10-21 12:17:35</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
       <c r="K117" t="n">
@@ -26446,7 +26446,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47:28</t>
+          <t>2026-10-21 12:17:37</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -26679,7 +26679,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47:28</t>
+          <t>2026-10-21 12:17:37</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -26912,7 +26912,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47:28</t>
+          <t>2026-10-21 12:17:37</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -27145,7 +27145,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47:28</t>
+          <t>2026-10-21 12:17:37</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -27378,17 +27378,17 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47:31</t>
+          <t>2026-10-21 12:17:40</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
       <c r="K122" t="n">
@@ -27619,7 +27619,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47:33</t>
+          <t>2026-10-21 12:17:42</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -27860,7 +27860,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47:33</t>
+          <t>2026-10-21 12:17:42</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -28101,7 +28101,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47:33</t>
+          <t>2026-10-21 12:17:42</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -28342,7 +28342,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47:33</t>
+          <t>2026-10-21 12:17:42</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -28583,17 +28583,17 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47:36</t>
+          <t>2026-10-21 12:17:45</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
       <c r="K127" t="n">
@@ -28816,7 +28816,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47:39</t>
+          <t>2026-10-21 12:17:47</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -29049,7 +29049,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47:39</t>
+          <t>2026-10-21 12:17:47</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -29282,7 +29282,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47:39</t>
+          <t>2026-10-21 12:17:47</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -29515,7 +29515,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47:39</t>
+          <t>2026-10-21 12:17:47</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -29748,17 +29748,17 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47:42</t>
+          <t>2026-10-21 12:17:50</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
       <c r="K132" t="n">
@@ -29981,7 +29981,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47:44</t>
+          <t>2026-10-21 12:17:52</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -30214,7 +30214,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47:44</t>
+          <t>2026-10-21 12:17:52</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -30447,7 +30447,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47:44</t>
+          <t>2026-10-21 12:17:52</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -30680,7 +30680,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47:44</t>
+          <t>2026-10-21 12:17:52</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -30913,17 +30913,17 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47:47</t>
+          <t>2026-10-21 12:17:54</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
       <c r="K137" t="n">
@@ -31134,7 +31134,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47:50</t>
+          <t>2026-10-21 12:17:56</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -31355,7 +31355,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47:50</t>
+          <t>2026-10-21 12:17:56</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -31576,7 +31576,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47:50</t>
+          <t>2026-10-21 12:17:56</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -31797,7 +31797,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47:50</t>
+          <t>2026-10-21 12:17:56</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -32018,17 +32018,17 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47:53</t>
+          <t>2026-10-21 12:17:59</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
       <c r="K142" t="n">
@@ -32251,7 +32251,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47:55</t>
+          <t>2026-10-21 12:18:01</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -32484,7 +32484,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47:55</t>
+          <t>2026-10-21 12:18:01</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -32717,7 +32717,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47:55</t>
+          <t>2026-10-21 12:18:01</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -32950,7 +32950,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47:55</t>
+          <t>2026-10-21 12:18:01</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -33183,17 +33183,17 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-10-21 11:47:58</t>
+          <t>2026-10-21 12:18:04</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
       <c r="K147" t="n">
@@ -33416,7 +33416,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-10-21 11:48:01</t>
+          <t>2026-10-21 12:18:06</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -33649,7 +33649,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-10-21 11:48:01</t>
+          <t>2026-10-21 12:18:06</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -33882,7 +33882,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-10-21 11:48:01</t>
+          <t>2026-10-21 12:18:06</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -34115,7 +34115,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-10-21 11:48:01</t>
+          <t>2026-10-21 12:18:06</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -34348,17 +34348,17 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-10-21 11:48:04</t>
+          <t>2026-10-21 12:18:09</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
       <c r="K152" t="n">
@@ -34581,7 +34581,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-10-21 11:48:06</t>
+          <t>2026-10-21 12:18:11</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -34814,7 +34814,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-10-21 11:48:06</t>
+          <t>2026-10-21 12:18:11</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -35047,7 +35047,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-10-21 11:48:06</t>
+          <t>2026-10-21 12:18:11</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -35280,7 +35280,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-10-21 11:48:06</t>
+          <t>2026-10-21 12:18:11</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -35513,17 +35513,17 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-10-21 11:48:09</t>
+          <t>2026-10-21 12:18:14</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
       <c r="K157" t="n">
@@ -35746,7 +35746,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-10-21 11:48:12</t>
+          <t>2026-10-21 12:18:16</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -35979,7 +35979,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-10-21 11:48:12</t>
+          <t>2026-10-21 12:18:16</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -36212,7 +36212,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-10-21 11:48:12</t>
+          <t>2026-10-21 12:18:16</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -36445,7 +36445,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-10-21 11:48:12</t>
+          <t>2026-10-21 12:18:16</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -36678,17 +36678,17 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-10-21 11:48:14</t>
+          <t>2026-10-21 12:18:18</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
       <c r="K162" t="n">
@@ -36919,7 +36919,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-10-21 11:48:16</t>
+          <t>2026-10-21 12:18:20</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -37160,7 +37160,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-10-21 11:48:16</t>
+          <t>2026-10-21 12:18:20</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -37401,7 +37401,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-10-21 11:48:16</t>
+          <t>2026-10-21 12:18:20</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -37642,7 +37642,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-10-21 11:48:16</t>
+          <t>2026-10-21 12:18:20</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -37883,17 +37883,17 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-10-21 11:48:19</t>
+          <t>2026-10-21 12:18:23</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
       <c r="K167" t="n">
@@ -38112,7 +38112,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-10-21 11:48:22</t>
+          <t>2026-10-21 12:18:26</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -38353,7 +38353,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-10-21 11:48:22</t>
+          <t>2026-10-21 12:18:26</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -38594,7 +38594,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-10-21 11:48:22</t>
+          <t>2026-10-21 12:18:26</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -38835,7 +38835,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026-10-21 11:48:22</t>
+          <t>2026-10-21 12:18:26</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -39076,17 +39076,17 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-10-21 11:48:25</t>
+          <t>2026-10-21 12:18:29</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
       <c r="K172" t="n">
@@ -39309,7 +39309,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-10-21 11:48:27</t>
+          <t>2026-10-21 12:18:31</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -39542,7 +39542,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026-10-21 11:48:27</t>
+          <t>2026-10-21 12:18:31</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -39775,7 +39775,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026-10-21 11:48:27</t>
+          <t>2026-10-21 12:18:31</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -40008,7 +40008,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026-10-21 11:48:27</t>
+          <t>2026-10-21 12:18:31</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -40241,17 +40241,17 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026-10-21 11:48:30</t>
+          <t>2026-10-21 12:18:34</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
       <c r="K177" t="n">
@@ -40462,7 +40462,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026-10-21 11:48:32</t>
+          <t>2026-10-21 12:18:36</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -40683,7 +40683,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-10-21 11:48:32</t>
+          <t>2026-10-21 12:18:36</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -40904,7 +40904,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-10-21 11:48:32</t>
+          <t>2026-10-21 12:18:36</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -41125,7 +41125,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026-10-21 11:48:32</t>
+          <t>2026-10-21 12:18:36</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -41346,17 +41346,17 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026-10-21 11:48:36</t>
+          <t>2026-10-21 12:18:39</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
       <c r="K182" t="n">
@@ -41567,7 +41567,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026-10-21 11:48:38</t>
+          <t>2026-10-21 12:18:40</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -41788,7 +41788,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026-10-21 11:48:38</t>
+          <t>2026-10-21 12:18:40</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -42009,7 +42009,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-10-21 11:48:38</t>
+          <t>2026-10-21 12:18:40</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -42230,7 +42230,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-10-21 11:48:38</t>
+          <t>2026-10-21 12:18:40</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -42451,17 +42451,17 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2026-10-21 11:48:41</t>
+          <t>2026-10-21 12:18:43</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
       <c r="K187" t="n">
@@ -42672,7 +42672,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2026-10-21 11:48:43</t>
+          <t>2026-10-21 12:18:45</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -42905,7 +42905,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2026-10-21 11:48:43</t>
+          <t>2026-10-21 12:18:45</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -43138,7 +43138,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-10-21 11:48:43</t>
+          <t>2026-10-21 12:18:45</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -43371,7 +43371,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-10-21 11:48:43</t>
+          <t>2026-10-21 12:18:45</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -43604,17 +43604,17 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2026-10-21 11:48:46</t>
+          <t>2026-10-21 12:18:49</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
       <c r="K192" t="n">
@@ -43801,7 +43801,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2026-10-21 11:48:48</t>
+          <t>2026-10-21 12:18:51</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -43998,7 +43998,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2026-10-21 11:48:48</t>
+          <t>2026-10-21 12:18:51</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -44195,7 +44195,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026-10-21 11:48:48</t>
+          <t>2026-10-21 12:18:51</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -44392,7 +44392,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2026-10-21 11:48:48</t>
+          <t>2026-10-21 12:18:51</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -44589,17 +44589,17 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2026-10-21 11:48:51</t>
+          <t>2026-10-21 12:18:54</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
       <c r="K197" t="n">
@@ -44822,7 +44822,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2026-10-21 11:48:53</t>
+          <t>2026-10-21 12:18:56</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -45055,7 +45055,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2026-10-21 11:48:53</t>
+          <t>2026-10-21 12:18:56</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -45288,7 +45288,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2026-10-21 11:48:53</t>
+          <t>2026-10-21 12:18:56</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -45521,7 +45521,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-10-21 11:48:53</t>
+          <t>2026-10-21 12:18:56</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -45754,17 +45754,17 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>2026-10-21 11:48:55</t>
+          <t>2026-10-21 12:18:58</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
       <c r="K202" t="n">
@@ -45927,7 +45927,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>2026-10-21 11:48:57</t>
+          <t>2026-10-21 12:19:01</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -46100,7 +46100,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>2026-10-21 11:48:57</t>
+          <t>2026-10-21 12:19:01</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -46273,7 +46273,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>2026-10-21 11:48:57</t>
+          <t>2026-10-21 12:19:01</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -46446,7 +46446,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>2026-10-21 11:48:57</t>
+          <t>2026-10-21 12:19:01</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -46619,17 +46619,17 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>2026-10-21 11:49:00</t>
+          <t>2026-10-21 12:19:03</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
       <c r="K207" t="n">
@@ -46840,7 +46840,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>2026-10-21 11:49:02</t>
+          <t>2026-10-21 12:19:05</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -47061,7 +47061,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>2026-10-21 11:49:02</t>
+          <t>2026-10-21 12:19:05</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -47282,7 +47282,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>2026-10-21 11:49:02</t>
+          <t>2026-10-21 12:19:05</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -47503,7 +47503,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>2026-10-21 11:49:02</t>
+          <t>2026-10-21 12:19:05</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -47724,17 +47724,17 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>2026-10-21 11:49:05</t>
+          <t>2026-10-21 12:19:08</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
       <c r="K212" t="n">
@@ -47965,7 +47965,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>2026-10-21 11:49:08</t>
+          <t>2026-10-21 12:19:10</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -48206,7 +48206,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>2026-10-21 11:49:08</t>
+          <t>2026-10-21 12:19:10</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -48447,7 +48447,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>2026-10-21 11:49:08</t>
+          <t>2026-10-21 12:19:10</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -48688,7 +48688,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>2026-10-21 11:49:08</t>
+          <t>2026-10-21 12:19:10</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -48929,17 +48929,17 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>2026-10-21 11:49:11</t>
+          <t>2026-10-21 12:19:13</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
       <c r="K217" t="n">
@@ -49170,7 +49170,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>2026-10-21 11:49:13</t>
+          <t>2026-10-21 12:19:16</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -49411,7 +49411,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>2026-10-21 11:49:13</t>
+          <t>2026-10-21 12:19:16</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -49652,7 +49652,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>2026-10-21 11:49:13</t>
+          <t>2026-10-21 12:19:16</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -49893,7 +49893,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>2026-10-21 11:49:13</t>
+          <t>2026-10-21 12:19:16</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -50134,17 +50134,17 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>2026-10-21 11:49:15</t>
+          <t>2026-10-21 12:19:19</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
       <c r="K222" t="n">
@@ -50367,7 +50367,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>2026-10-21 11:49:18</t>
+          <t>2026-10-21 12:19:21</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -50600,7 +50600,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>2026-10-21 11:49:18</t>
+          <t>2026-10-21 12:19:21</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -50833,7 +50833,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>2026-10-21 11:49:18</t>
+          <t>2026-10-21 12:19:21</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -51066,7 +51066,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>2026-10-21 11:49:18</t>
+          <t>2026-10-21 12:19:21</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -51333,7 +51333,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
     </row>
@@ -51363,7 +51363,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
     </row>
@@ -51393,7 +51393,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
     </row>
@@ -51423,7 +51423,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
     </row>
@@ -51453,7 +51453,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
     </row>
@@ -51483,7 +51483,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
     </row>
@@ -51513,7 +51513,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
     </row>
@@ -51543,7 +51543,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
     </row>
@@ -51573,7 +51573,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
     </row>
@@ -51603,7 +51603,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
     </row>
@@ -51633,7 +51633,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
     </row>
@@ -51663,7 +51663,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
     </row>
@@ -51693,7 +51693,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
     </row>
@@ -51723,7 +51723,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
     </row>
@@ -51753,7 +51753,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
     </row>
@@ -51783,7 +51783,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
     </row>
@@ -51813,7 +51813,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
     </row>
@@ -51843,7 +51843,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
     </row>
@@ -51873,7 +51873,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
     </row>
@@ -51903,7 +51903,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
     </row>
@@ -51933,7 +51933,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
     </row>
@@ -51963,7 +51963,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
     </row>
@@ -51993,7 +51993,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
     </row>
@@ -52023,7 +52023,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
     </row>
@@ -52053,7 +52053,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
     </row>
@@ -52083,7 +52083,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
     </row>
@@ -52113,7 +52113,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
     </row>
@@ -52143,7 +52143,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
     </row>
@@ -52173,7 +52173,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
     </row>
@@ -52203,7 +52203,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
     </row>
@@ -52233,7 +52233,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
     </row>
@@ -52263,7 +52263,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
     </row>
@@ -52293,7 +52293,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
     </row>
@@ -52323,7 +52323,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
     </row>
@@ -52353,7 +52353,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
     </row>
@@ -52383,7 +52383,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
     </row>
@@ -52413,7 +52413,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
     </row>
@@ -52443,7 +52443,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
     </row>
@@ -52473,7 +52473,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
     </row>
@@ -52503,7 +52503,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
     </row>
@@ -52533,7 +52533,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
     </row>
@@ -52563,7 +52563,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
     </row>
@@ -52593,7 +52593,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
     </row>
@@ -52623,7 +52623,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
     </row>
@@ -52653,7 +52653,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-10-21T11:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-10-21T11:30Z</t>
         </is>
       </c>
     </row>

--- a/src/data/resum_periode_meteocat.xlsx
+++ b/src/data/resum_periode_meteocat.xlsx
@@ -722,17 +722,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-21 12:15:39</t>
+          <t>2026-10-21 12:45:36</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -919,7 +919,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-10-21 12:15:41</t>
+          <t>2026-10-21 12:45:38</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-10-21 12:15:41</t>
+          <t>2026-10-21 12:45:38</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-10-21 12:15:41</t>
+          <t>2026-10-21 12:45:38</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-10-21 12:15:41</t>
+          <t>2026-10-21 12:45:38</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-21 12:15:44</t>
+          <t>2026-10-21 12:45:41</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-21 12:15:46</t>
+          <t>2026-10-21 12:45:43</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-21 12:15:46</t>
+          <t>2026-10-21 12:45:43</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-21 12:15:46</t>
+          <t>2026-10-21 12:45:43</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-10-21 12:15:46</t>
+          <t>2026-10-21 12:45:43</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2872,17 +2872,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-10-21 12:15:49</t>
+          <t>2026-10-21 12:45:46</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-10-21 12:15:51</t>
+          <t>2026-10-21 12:45:48</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-10-21 12:15:51</t>
+          <t>2026-10-21 12:45:48</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-10-21 12:15:51</t>
+          <t>2026-10-21 12:45:48</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-10-21 12:15:51</t>
+          <t>2026-10-21 12:45:48</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -4037,17 +4037,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-10-21 12:15:54</t>
+          <t>2026-10-21 12:45:51</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-10-21 12:15:56</t>
+          <t>2026-10-21 12:45:53</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-10-21 12:15:56</t>
+          <t>2026-10-21 12:45:53</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-10-21 12:15:56</t>
+          <t>2026-10-21 12:45:53</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-10-21 12:15:56</t>
+          <t>2026-10-21 12:45:53</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -5202,17 +5202,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-10-21 12:15:59</t>
+          <t>2026-10-21 12:45:56</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-10-21 12:16:01</t>
+          <t>2026-10-21 12:45:59</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-10-21 12:16:01</t>
+          <t>2026-10-21 12:45:59</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-10-21 12:16:01</t>
+          <t>2026-10-21 12:45:59</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-10-21 12:16:01</t>
+          <t>2026-10-21 12:45:59</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -6367,17 +6367,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-10-21 12:16:04</t>
+          <t>2026-10-21 12:46:01</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -6600,7 +6600,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-10-21 12:16:06</t>
+          <t>2026-10-21 12:46:03</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -6833,7 +6833,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-10-21 12:16:06</t>
+          <t>2026-10-21 12:46:03</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-10-21 12:16:06</t>
+          <t>2026-10-21 12:46:03</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-10-21 12:16:06</t>
+          <t>2026-10-21 12:46:03</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -7532,17 +7532,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-10-21 12:16:09</t>
+          <t>2026-10-21 12:46:06</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -7765,7 +7765,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-10-21 12:16:11</t>
+          <t>2026-10-21 12:46:07</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-10-21 12:16:11</t>
+          <t>2026-10-21 12:46:07</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-10-21 12:16:11</t>
+          <t>2026-10-21 12:46:07</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -8464,7 +8464,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-10-21 12:16:11</t>
+          <t>2026-10-21 12:46:07</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -8697,17 +8697,17 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-10-21 12:16:13</t>
+          <t>2026-10-21 12:46:10</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -8918,7 +8918,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-10-21 12:16:16</t>
+          <t>2026-10-21 12:46:11</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-10-21 12:16:16</t>
+          <t>2026-10-21 12:46:11</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -9360,7 +9360,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-10-21 12:16:16</t>
+          <t>2026-10-21 12:46:11</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-10-21 12:16:16</t>
+          <t>2026-10-21 12:46:11</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -9802,17 +9802,17 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-10-21 12:16:19</t>
+          <t>2026-10-21 12:46:14</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -10023,7 +10023,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-10-21 12:16:21</t>
+          <t>2026-10-21 12:46:16</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -10244,7 +10244,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-10-21 12:16:21</t>
+          <t>2026-10-21 12:46:16</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-10-21 12:16:21</t>
+          <t>2026-10-21 12:46:16</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -10686,7 +10686,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-10-21 12:16:21</t>
+          <t>2026-10-21 12:46:16</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -10907,17 +10907,17 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-10-21 12:16:24</t>
+          <t>2026-10-21 12:46:19</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -11080,7 +11080,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-10-21 12:16:25</t>
+          <t>2026-10-21 12:46:21</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -11253,7 +11253,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-10-21 12:16:25</t>
+          <t>2026-10-21 12:46:21</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -11426,7 +11426,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-10-21 12:16:25</t>
+          <t>2026-10-21 12:46:21</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -11599,7 +11599,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-10-21 12:16:25</t>
+          <t>2026-10-21 12:46:21</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -11772,17 +11772,17 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-10-21 12:16:28</t>
+          <t>2026-10-21 12:46:24</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
       <c r="K52" t="n">
@@ -11945,7 +11945,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-10-21 12:16:30</t>
+          <t>2026-10-21 12:46:26</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-10-21 12:16:30</t>
+          <t>2026-10-21 12:46:26</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -12291,7 +12291,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-10-21 12:16:30</t>
+          <t>2026-10-21 12:46:26</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -12464,7 +12464,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-10-21 12:16:30</t>
+          <t>2026-10-21 12:46:26</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -12637,17 +12637,17 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-10-21 12:16:33</t>
+          <t>2026-10-21 12:46:29</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
       <c r="K57" t="n">
@@ -12878,7 +12878,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-10-21 12:16:35</t>
+          <t>2026-10-21 12:46:31</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -13119,7 +13119,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-10-21 12:16:35</t>
+          <t>2026-10-21 12:46:31</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-10-21 12:16:35</t>
+          <t>2026-10-21 12:46:31</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -13601,7 +13601,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-10-21 12:16:35</t>
+          <t>2026-10-21 12:46:31</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -13842,17 +13842,17 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-10-21 12:16:38</t>
+          <t>2026-10-21 12:46:34</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
       <c r="K62" t="n">
@@ -14063,7 +14063,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-10-21 12:16:41</t>
+          <t>2026-10-21 12:46:36</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -14284,7 +14284,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-10-21 12:16:41</t>
+          <t>2026-10-21 12:46:36</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -14505,7 +14505,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-10-21 12:16:41</t>
+          <t>2026-10-21 12:46:36</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -14726,7 +14726,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-10-21 12:16:41</t>
+          <t>2026-10-21 12:46:36</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -14947,17 +14947,17 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-10-21 12:16:44</t>
+          <t>2026-10-21 12:46:38</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
       <c r="K67" t="n">
@@ -15120,7 +15120,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-10-21 12:16:46</t>
+          <t>2026-10-21 12:46:40</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -15293,7 +15293,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-10-21 12:16:46</t>
+          <t>2026-10-21 12:46:40</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -15466,7 +15466,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-10-21 12:16:46</t>
+          <t>2026-10-21 12:46:40</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -15639,7 +15639,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-10-21 12:16:46</t>
+          <t>2026-10-21 12:46:40</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -15812,17 +15812,17 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-10-21 12:16:49</t>
+          <t>2026-10-21 12:46:43</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
       <c r="K72" t="n">
@@ -16045,7 +16045,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-10-21 12:16:51</t>
+          <t>2026-10-21 12:46:45</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -16278,7 +16278,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-10-21 12:16:51</t>
+          <t>2026-10-21 12:46:45</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -16511,7 +16511,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-10-21 12:16:51</t>
+          <t>2026-10-21 12:46:45</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-10-21 12:16:51</t>
+          <t>2026-10-21 12:46:45</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -16977,17 +16977,17 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-10-21 12:16:54</t>
+          <t>2026-10-21 12:46:48</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
       <c r="K77" t="n">
@@ -17210,7 +17210,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-10-21 12:16:56</t>
+          <t>2026-10-21 12:46:50</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -17443,7 +17443,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-10-21 12:16:56</t>
+          <t>2026-10-21 12:46:50</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -17676,7 +17676,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-10-21 12:16:56</t>
+          <t>2026-10-21 12:46:50</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -17909,7 +17909,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-10-21 12:16:56</t>
+          <t>2026-10-21 12:46:50</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -18142,17 +18142,17 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-10-21 12:16:59</t>
+          <t>2026-10-21 12:46:52</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
       <c r="K82" t="n">
@@ -18375,7 +18375,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-10-21 12:17:02</t>
+          <t>2026-10-21 12:46:55</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -18608,7 +18608,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-10-21 12:17:02</t>
+          <t>2026-10-21 12:46:55</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -18841,7 +18841,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-10-21 12:17:02</t>
+          <t>2026-10-21 12:46:55</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-10-21 12:17:02</t>
+          <t>2026-10-21 12:46:55</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -19307,17 +19307,17 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-10-21 12:17:05</t>
+          <t>2026-10-21 12:46:57</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
       <c r="K87" t="n">
@@ -19528,7 +19528,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-10-21 12:17:06</t>
+          <t>2026-10-21 12:46:59</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -19749,7 +19749,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-10-21 12:17:06</t>
+          <t>2026-10-21 12:46:59</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -19970,7 +19970,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-10-21 12:17:06</t>
+          <t>2026-10-21 12:46:59</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -20191,7 +20191,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-10-21 12:17:06</t>
+          <t>2026-10-21 12:46:59</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -20412,17 +20412,17 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-10-21 12:17:09</t>
+          <t>2026-10-21 12:47:02</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
       <c r="K92" t="n">
@@ -20633,7 +20633,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-10-21 12:17:11</t>
+          <t>2026-10-21 12:47:04</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -20866,7 +20866,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-10-21 12:17:11</t>
+          <t>2026-10-21 12:47:04</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -21099,7 +21099,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-10-21 12:17:11</t>
+          <t>2026-10-21 12:47:04</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -21332,7 +21332,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-10-21 12:17:11</t>
+          <t>2026-10-21 12:47:04</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -21565,17 +21565,17 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-10-21 12:17:14</t>
+          <t>2026-10-21 12:47:07</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
       <c r="K97" t="n">
@@ -21798,7 +21798,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-10-21 12:17:16</t>
+          <t>2026-10-21 12:47:08</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -22031,7 +22031,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-10-21 12:17:16</t>
+          <t>2026-10-21 12:47:08</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -22264,7 +22264,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-10-21 12:17:16</t>
+          <t>2026-10-21 12:47:08</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -22497,7 +22497,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-10-21 12:17:16</t>
+          <t>2026-10-21 12:47:08</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -22730,17 +22730,17 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-10-21 12:17:19</t>
+          <t>2026-10-21 12:47:11</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
       <c r="K102" t="n">
@@ -22963,7 +22963,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-10-21 12:17:21</t>
+          <t>2026-10-21 12:47:13</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -23196,7 +23196,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-10-21 12:17:21</t>
+          <t>2026-10-21 12:47:13</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -23429,7 +23429,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-10-21 12:17:21</t>
+          <t>2026-10-21 12:47:13</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -23662,7 +23662,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-10-21 12:17:21</t>
+          <t>2026-10-21 12:47:13</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -23895,17 +23895,17 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-10-21 12:17:24</t>
+          <t>2026-10-21 12:47:15</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
       <c r="K107" t="n">
@@ -24128,7 +24128,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-10-21 12:17:26</t>
+          <t>2026-10-21 12:47:17</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -24361,7 +24361,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-10-21 12:17:26</t>
+          <t>2026-10-21 12:47:17</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -24594,7 +24594,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-10-21 12:17:26</t>
+          <t>2026-10-21 12:47:17</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -24827,7 +24827,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-10-21 12:17:26</t>
+          <t>2026-10-21 12:47:17</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -25060,17 +25060,17 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-10-21 12:17:30</t>
+          <t>2026-10-21 12:47:20</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
       <c r="K112" t="n">
@@ -25293,7 +25293,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-10-21 12:17:32</t>
+          <t>2026-10-21 12:47:22</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -25526,7 +25526,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-10-21 12:17:32</t>
+          <t>2026-10-21 12:47:22</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -25759,7 +25759,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-10-21 12:17:32</t>
+          <t>2026-10-21 12:47:22</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -25992,7 +25992,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-10-21 12:17:32</t>
+          <t>2026-10-21 12:47:22</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -26225,17 +26225,17 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-10-21 12:17:35</t>
+          <t>2026-10-21 12:47:25</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
       <c r="K117" t="n">
@@ -26446,7 +26446,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-10-21 12:17:37</t>
+          <t>2026-10-21 12:47:27</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -26679,7 +26679,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-10-21 12:17:37</t>
+          <t>2026-10-21 12:47:27</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -26912,7 +26912,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-10-21 12:17:37</t>
+          <t>2026-10-21 12:47:27</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -27145,7 +27145,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-10-21 12:17:37</t>
+          <t>2026-10-21 12:47:27</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -27378,17 +27378,17 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-10-21 12:17:40</t>
+          <t>2026-10-21 12:47:30</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
       <c r="K122" t="n">
@@ -27619,7 +27619,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-10-21 12:17:42</t>
+          <t>2026-10-21 12:47:31</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -27860,7 +27860,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-10-21 12:17:42</t>
+          <t>2026-10-21 12:47:31</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -28101,7 +28101,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-10-21 12:17:42</t>
+          <t>2026-10-21 12:47:31</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -28342,7 +28342,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-10-21 12:17:42</t>
+          <t>2026-10-21 12:47:31</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -28583,17 +28583,17 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-10-21 12:17:45</t>
+          <t>2026-10-21 12:47:34</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
       <c r="K127" t="n">
@@ -28816,7 +28816,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-10-21 12:17:47</t>
+          <t>2026-10-21 12:47:36</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -29049,7 +29049,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-10-21 12:17:47</t>
+          <t>2026-10-21 12:47:36</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -29282,7 +29282,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-10-21 12:17:47</t>
+          <t>2026-10-21 12:47:36</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -29515,7 +29515,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-10-21 12:17:47</t>
+          <t>2026-10-21 12:47:36</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -29748,17 +29748,17 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-10-21 12:17:50</t>
+          <t>2026-10-21 12:47:39</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
       <c r="K132" t="n">
@@ -29981,7 +29981,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-10-21 12:17:52</t>
+          <t>2026-10-21 12:47:41</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -30214,7 +30214,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-10-21 12:17:52</t>
+          <t>2026-10-21 12:47:41</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -30447,7 +30447,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-10-21 12:17:52</t>
+          <t>2026-10-21 12:47:41</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -30680,7 +30680,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-10-21 12:17:52</t>
+          <t>2026-10-21 12:47:41</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -30913,17 +30913,17 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-10-21 12:17:54</t>
+          <t>2026-10-21 12:47:44</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
       <c r="K137" t="n">
@@ -31134,7 +31134,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-10-21 12:17:56</t>
+          <t>2026-10-21 12:47:45</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -31355,7 +31355,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-10-21 12:17:56</t>
+          <t>2026-10-21 12:47:45</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -31576,7 +31576,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-10-21 12:17:56</t>
+          <t>2026-10-21 12:47:45</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -31797,7 +31797,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-10-21 12:17:56</t>
+          <t>2026-10-21 12:47:45</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -32018,17 +32018,17 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-10-21 12:17:59</t>
+          <t>2026-10-21 12:47:48</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
       <c r="K142" t="n">
@@ -32251,7 +32251,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-10-21 12:18:01</t>
+          <t>2026-10-21 12:47:50</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -32484,7 +32484,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-10-21 12:18:01</t>
+          <t>2026-10-21 12:47:50</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -32717,7 +32717,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-10-21 12:18:01</t>
+          <t>2026-10-21 12:47:50</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -32950,7 +32950,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-10-21 12:18:01</t>
+          <t>2026-10-21 12:47:50</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -33183,17 +33183,17 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-10-21 12:18:04</t>
+          <t>2026-10-21 12:47:53</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
       <c r="K147" t="n">
@@ -33416,7 +33416,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-10-21 12:18:06</t>
+          <t>2026-10-21 12:47:55</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -33649,7 +33649,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-10-21 12:18:06</t>
+          <t>2026-10-21 12:47:55</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -33882,7 +33882,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-10-21 12:18:06</t>
+          <t>2026-10-21 12:47:55</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -34115,7 +34115,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-10-21 12:18:06</t>
+          <t>2026-10-21 12:47:55</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -34348,17 +34348,17 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-10-21 12:18:09</t>
+          <t>2026-10-21 12:47:58</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
       <c r="K152" t="n">
@@ -34581,7 +34581,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-10-21 12:18:11</t>
+          <t>2026-10-21 12:48:00</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -34814,7 +34814,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-10-21 12:18:11</t>
+          <t>2026-10-21 12:48:00</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -35047,7 +35047,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-10-21 12:18:11</t>
+          <t>2026-10-21 12:48:00</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -35280,7 +35280,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-10-21 12:18:11</t>
+          <t>2026-10-21 12:48:00</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -35513,17 +35513,17 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-10-21 12:18:14</t>
+          <t>2026-10-21 12:48:03</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
       <c r="K157" t="n">
@@ -35746,7 +35746,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-10-21 12:18:16</t>
+          <t>2026-10-21 12:48:05</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -35979,7 +35979,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-10-21 12:18:16</t>
+          <t>2026-10-21 12:48:05</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -36212,7 +36212,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-10-21 12:18:16</t>
+          <t>2026-10-21 12:48:05</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -36445,7 +36445,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-10-21 12:18:16</t>
+          <t>2026-10-21 12:48:05</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -36678,17 +36678,17 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-10-21 12:18:18</t>
+          <t>2026-10-21 12:48:07</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
       <c r="K162" t="n">
@@ -36919,7 +36919,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-10-21 12:18:20</t>
+          <t>2026-10-21 12:48:09</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -37160,7 +37160,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-10-21 12:18:20</t>
+          <t>2026-10-21 12:48:09</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -37401,7 +37401,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-10-21 12:18:20</t>
+          <t>2026-10-21 12:48:09</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -37642,7 +37642,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-10-21 12:18:20</t>
+          <t>2026-10-21 12:48:09</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -37883,17 +37883,17 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-10-21 12:18:23</t>
+          <t>2026-10-21 12:48:12</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
       <c r="K167" t="n">
@@ -38112,7 +38112,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-10-21 12:18:26</t>
+          <t>2026-10-21 12:48:14</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -38353,7 +38353,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-10-21 12:18:26</t>
+          <t>2026-10-21 12:48:14</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -38594,7 +38594,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-10-21 12:18:26</t>
+          <t>2026-10-21 12:48:14</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -38835,7 +38835,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026-10-21 12:18:26</t>
+          <t>2026-10-21 12:48:14</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -39076,17 +39076,17 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-10-21 12:18:29</t>
+          <t>2026-10-21 12:48:16</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
       <c r="K172" t="n">
@@ -39309,7 +39309,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-10-21 12:18:31</t>
+          <t>2026-10-21 12:48:18</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -39542,7 +39542,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026-10-21 12:18:31</t>
+          <t>2026-10-21 12:48:18</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -39775,7 +39775,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026-10-21 12:18:31</t>
+          <t>2026-10-21 12:48:18</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -40008,7 +40008,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026-10-21 12:18:31</t>
+          <t>2026-10-21 12:48:18</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -40241,17 +40241,17 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026-10-21 12:18:34</t>
+          <t>2026-10-21 12:48:21</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
       <c r="K177" t="n">
@@ -40462,7 +40462,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026-10-21 12:18:36</t>
+          <t>2026-10-21 12:48:23</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -40683,7 +40683,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-10-21 12:18:36</t>
+          <t>2026-10-21 12:48:23</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -40904,7 +40904,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-10-21 12:18:36</t>
+          <t>2026-10-21 12:48:23</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -41125,7 +41125,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026-10-21 12:18:36</t>
+          <t>2026-10-21 12:48:23</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -41346,17 +41346,17 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026-10-21 12:18:39</t>
+          <t>2026-10-21 12:48:26</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
       <c r="K182" t="n">
@@ -41567,7 +41567,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026-10-21 12:18:40</t>
+          <t>2026-10-21 12:48:27</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -41788,7 +41788,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026-10-21 12:18:40</t>
+          <t>2026-10-21 12:48:27</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -42009,7 +42009,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-10-21 12:18:40</t>
+          <t>2026-10-21 12:48:27</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -42230,7 +42230,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-10-21 12:18:40</t>
+          <t>2026-10-21 12:48:27</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -42451,17 +42451,17 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2026-10-21 12:18:43</t>
+          <t>2026-10-21 12:48:30</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
       <c r="K187" t="n">
@@ -42672,7 +42672,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2026-10-21 12:18:45</t>
+          <t>2026-10-21 12:48:32</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -42905,7 +42905,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2026-10-21 12:18:45</t>
+          <t>2026-10-21 12:48:32</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -43138,7 +43138,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-10-21 12:18:45</t>
+          <t>2026-10-21 12:48:32</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -43371,7 +43371,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-10-21 12:18:45</t>
+          <t>2026-10-21 12:48:32</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -43604,17 +43604,17 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2026-10-21 12:18:49</t>
+          <t>2026-10-21 12:48:35</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
       <c r="K192" t="n">
@@ -43801,7 +43801,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2026-10-21 12:18:51</t>
+          <t>2026-10-21 12:48:36</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -43998,7 +43998,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2026-10-21 12:18:51</t>
+          <t>2026-10-21 12:48:36</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -44195,7 +44195,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026-10-21 12:18:51</t>
+          <t>2026-10-21 12:48:36</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -44392,7 +44392,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2026-10-21 12:18:51</t>
+          <t>2026-10-21 12:48:36</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -44589,17 +44589,17 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2026-10-21 12:18:54</t>
+          <t>2026-10-21 12:48:40</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
       <c r="K197" t="n">
@@ -44822,7 +44822,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2026-10-21 12:18:56</t>
+          <t>2026-10-21 12:48:42</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -45055,7 +45055,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2026-10-21 12:18:56</t>
+          <t>2026-10-21 12:48:42</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -45288,7 +45288,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2026-10-21 12:18:56</t>
+          <t>2026-10-21 12:48:42</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -45521,7 +45521,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-10-21 12:18:56</t>
+          <t>2026-10-21 12:48:42</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -45754,17 +45754,17 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>2026-10-21 12:18:58</t>
+          <t>2026-10-21 12:48:44</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
       <c r="K202" t="n">
@@ -45927,7 +45927,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>2026-10-21 12:19:01</t>
+          <t>2026-10-21 12:48:46</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -46100,7 +46100,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>2026-10-21 12:19:01</t>
+          <t>2026-10-21 12:48:46</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -46273,7 +46273,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>2026-10-21 12:19:01</t>
+          <t>2026-10-21 12:48:46</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -46446,7 +46446,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>2026-10-21 12:19:01</t>
+          <t>2026-10-21 12:48:46</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -46619,17 +46619,17 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>2026-10-21 12:19:03</t>
+          <t>2026-10-21 12:48:49</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
       <c r="K207" t="n">
@@ -46840,7 +46840,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>2026-10-21 12:19:05</t>
+          <t>2026-10-21 12:48:51</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -47061,7 +47061,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>2026-10-21 12:19:05</t>
+          <t>2026-10-21 12:48:51</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -47282,7 +47282,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>2026-10-21 12:19:05</t>
+          <t>2026-10-21 12:48:51</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -47503,7 +47503,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>2026-10-21 12:19:05</t>
+          <t>2026-10-21 12:48:51</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -47724,17 +47724,17 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>2026-10-21 12:19:08</t>
+          <t>2026-10-21 12:48:54</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
       <c r="K212" t="n">
@@ -47965,7 +47965,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>2026-10-21 12:19:10</t>
+          <t>2026-10-21 12:48:56</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -48206,7 +48206,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>2026-10-21 12:19:10</t>
+          <t>2026-10-21 12:48:56</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -48447,7 +48447,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>2026-10-21 12:19:10</t>
+          <t>2026-10-21 12:48:56</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -48688,7 +48688,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>2026-10-21 12:19:10</t>
+          <t>2026-10-21 12:48:56</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -48929,17 +48929,17 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>2026-10-21 12:19:13</t>
+          <t>2026-10-21 12:48:59</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
       <c r="K217" t="n">
@@ -49170,7 +49170,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>2026-10-21 12:19:16</t>
+          <t>2026-10-21 12:49:01</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -49411,7 +49411,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>2026-10-21 12:19:16</t>
+          <t>2026-10-21 12:49:01</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -49652,7 +49652,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>2026-10-21 12:19:16</t>
+          <t>2026-10-21 12:49:01</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -49893,7 +49893,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>2026-10-21 12:19:16</t>
+          <t>2026-10-21 12:49:01</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -50134,17 +50134,17 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>2026-10-21 12:19:19</t>
+          <t>2026-10-21 12:49:05</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
       <c r="K222" t="n">
@@ -50367,7 +50367,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>2026-10-21 12:19:21</t>
+          <t>2026-10-21 12:49:06</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -50600,7 +50600,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>2026-10-21 12:19:21</t>
+          <t>2026-10-21 12:49:06</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -50833,7 +50833,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>2026-10-21 12:19:21</t>
+          <t>2026-10-21 12:49:06</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -51066,7 +51066,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>2026-10-21 12:19:21</t>
+          <t>2026-10-21 12:49:06</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -51333,7 +51333,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
     </row>
@@ -51363,7 +51363,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
     </row>
@@ -51393,7 +51393,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
     </row>
@@ -51423,7 +51423,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
     </row>
@@ -51453,7 +51453,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
     </row>
@@ -51483,7 +51483,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
     </row>
@@ -51513,7 +51513,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
     </row>
@@ -51543,7 +51543,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
     </row>
@@ -51573,7 +51573,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
     </row>
@@ -51603,7 +51603,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
     </row>
@@ -51633,7 +51633,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
     </row>
@@ -51663,7 +51663,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
     </row>
@@ -51693,7 +51693,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
     </row>
@@ -51723,7 +51723,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
     </row>
@@ -51753,7 +51753,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
     </row>
@@ -51783,7 +51783,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
     </row>
@@ -51813,7 +51813,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
     </row>
@@ -51843,7 +51843,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
     </row>
@@ -51873,7 +51873,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
     </row>
@@ -51903,7 +51903,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
     </row>
@@ -51933,7 +51933,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
     </row>
@@ -51963,7 +51963,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
     </row>
@@ -51993,7 +51993,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
     </row>
@@ -52023,7 +52023,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
     </row>
@@ -52053,7 +52053,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
     </row>
@@ -52083,7 +52083,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
     </row>
@@ -52113,7 +52113,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
     </row>
@@ -52143,7 +52143,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
     </row>
@@ -52173,7 +52173,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
     </row>
@@ -52203,7 +52203,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
     </row>
@@ -52233,7 +52233,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
     </row>
@@ -52263,7 +52263,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
     </row>
@@ -52293,7 +52293,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
     </row>
@@ -52323,7 +52323,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
     </row>
@@ -52353,7 +52353,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
     </row>
@@ -52383,7 +52383,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
     </row>
@@ -52413,7 +52413,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
     </row>
@@ -52443,7 +52443,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
     </row>
@@ -52473,7 +52473,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
     </row>
@@ -52503,7 +52503,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
     </row>
@@ -52533,7 +52533,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
     </row>
@@ -52563,7 +52563,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
     </row>
@@ -52593,7 +52593,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
     </row>
@@ -52623,7 +52623,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
     </row>
@@ -52653,7 +52653,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-10-21T11:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-10-21T12:00Z</t>
         </is>
       </c>
     </row>

--- a/src/data/resum_periode_meteocat.xlsx
+++ b/src/data/resum_periode_meteocat.xlsx
@@ -722,7 +722,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:15:38</t>
+          <t>2026-10-25 00:45:38</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-10-25 00:15:40</t>
+          <t>2026-10-25 00:45:39</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-10-25 00:15:40</t>
+          <t>2026-10-25 00:45:39</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-10-25 00:15:40</t>
+          <t>2026-10-25 00:45:39</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-10-25 00:15:40</t>
+          <t>2026-10-25 00:45:39</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-25 00:15:43</t>
+          <t>2026-10-25 00:45:44</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-25 00:15:45</t>
+          <t>2026-10-25 00:45:46</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-25 00:15:45</t>
+          <t>2026-10-25 00:45:46</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-25 00:15:45</t>
+          <t>2026-10-25 00:45:46</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-10-25 00:15:45</t>
+          <t>2026-10-25 00:45:46</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-10-25 00:15:49</t>
+          <t>2026-10-25 00:45:50</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-10-25 00:15:51</t>
+          <t>2026-10-25 00:45:52</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-10-25 00:15:51</t>
+          <t>2026-10-25 00:45:52</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-10-25 00:15:51</t>
+          <t>2026-10-25 00:45:52</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-10-25 00:15:51</t>
+          <t>2026-10-25 00:45:52</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-10-25 00:15:54</t>
+          <t>2026-10-25 00:45:57</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -4258,7 +4258,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-10-25 00:15:57</t>
+          <t>2026-10-25 00:45:58</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-10-25 00:15:57</t>
+          <t>2026-10-25 00:45:58</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-10-25 00:15:57</t>
+          <t>2026-10-25 00:45:58</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-10-25 00:15:57</t>
+          <t>2026-10-25 00:45:58</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-10-25 00:15:59</t>
+          <t>2026-10-25 00:46:03</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -5375,7 +5375,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-10-25 00:16:01</t>
+          <t>2026-10-25 00:46:05</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-10-25 00:16:01</t>
+          <t>2026-10-25 00:46:05</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-10-25 00:16:01</t>
+          <t>2026-10-25 00:46:05</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-10-25 00:16:01</t>
+          <t>2026-10-25 00:46:05</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-10-25 00:16:04</t>
+          <t>2026-10-25 00:46:10</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -6540,7 +6540,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-10-25 00:16:06</t>
+          <t>2026-10-25 00:46:12</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -6773,7 +6773,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-10-25 00:16:06</t>
+          <t>2026-10-25 00:46:12</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-10-25 00:16:06</t>
+          <t>2026-10-25 00:46:12</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -7239,7 +7239,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-10-25 00:16:06</t>
+          <t>2026-10-25 00:46:12</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -7472,7 +7472,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-10-25 00:16:10</t>
+          <t>2026-10-25 00:46:16</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -7705,7 +7705,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-10-25 00:16:12</t>
+          <t>2026-10-25 00:46:18</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -7938,7 +7938,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-10-25 00:16:12</t>
+          <t>2026-10-25 00:46:18</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -8171,7 +8171,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-10-25 00:16:12</t>
+          <t>2026-10-25 00:46:18</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -8404,7 +8404,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-10-25 00:16:12</t>
+          <t>2026-10-25 00:46:18</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-10-25 00:16:15</t>
+          <t>2026-10-25 00:46:23</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -8858,7 +8858,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-10-25 00:16:17</t>
+          <t>2026-10-25 00:46:24</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -9079,7 +9079,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-10-25 00:16:17</t>
+          <t>2026-10-25 00:46:24</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -9300,7 +9300,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-10-25 00:16:17</t>
+          <t>2026-10-25 00:46:24</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -9521,7 +9521,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-10-25 00:16:17</t>
+          <t>2026-10-25 00:46:24</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -9742,7 +9742,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-10-25 00:16:20</t>
+          <t>2026-10-25 00:46:29</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -9963,7 +9963,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-10-25 00:16:22</t>
+          <t>2026-10-25 00:46:31</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -10184,7 +10184,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-10-25 00:16:22</t>
+          <t>2026-10-25 00:46:31</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -10405,7 +10405,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-10-25 00:16:22</t>
+          <t>2026-10-25 00:46:31</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -10626,7 +10626,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-10-25 00:16:22</t>
+          <t>2026-10-25 00:46:31</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -10847,7 +10847,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-10-25 00:16:25</t>
+          <t>2026-10-25 00:46:34</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -11020,7 +11020,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-10-25 00:16:27</t>
+          <t>2026-10-25 00:46:36</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -11193,7 +11193,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-10-25 00:16:27</t>
+          <t>2026-10-25 00:46:36</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -11366,7 +11366,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-10-25 00:16:27</t>
+          <t>2026-10-25 00:46:36</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -11539,7 +11539,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-10-25 00:16:27</t>
+          <t>2026-10-25 00:46:36</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -11712,7 +11712,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-10-25 00:16:30</t>
+          <t>2026-10-25 00:46:40</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -11885,7 +11885,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-10-25 00:16:32</t>
+          <t>2026-10-25 00:46:43</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -12058,7 +12058,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-10-25 00:16:32</t>
+          <t>2026-10-25 00:46:43</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -12231,7 +12231,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-10-25 00:16:32</t>
+          <t>2026-10-25 00:46:43</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-10-25 00:16:32</t>
+          <t>2026-10-25 00:46:43</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -12577,7 +12577,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-10-25 00:16:35</t>
+          <t>2026-10-25 00:46:47</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -12818,7 +12818,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-10-25 00:16:37</t>
+          <t>2026-10-25 00:46:48</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -13059,7 +13059,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-10-25 00:16:37</t>
+          <t>2026-10-25 00:46:48</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -13300,7 +13300,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-10-25 00:16:37</t>
+          <t>2026-10-25 00:46:48</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -13541,7 +13541,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-10-25 00:16:37</t>
+          <t>2026-10-25 00:46:48</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -13782,7 +13782,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-10-25 00:16:41</t>
+          <t>2026-10-25 00:46:53</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -14003,7 +14003,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-10-25 00:16:43</t>
+          <t>2026-10-25 00:46:55</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -14224,7 +14224,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-10-25 00:16:43</t>
+          <t>2026-10-25 00:46:55</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -14445,7 +14445,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-10-25 00:16:43</t>
+          <t>2026-10-25 00:46:55</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -14666,7 +14666,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-10-25 00:16:43</t>
+          <t>2026-10-25 00:46:55</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -14887,7 +14887,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-10-25 00:16:46</t>
+          <t>2026-10-25 00:46:59</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -15060,7 +15060,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-10-25 00:16:48</t>
+          <t>2026-10-25 00:47:01</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -15233,7 +15233,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-10-25 00:16:48</t>
+          <t>2026-10-25 00:47:01</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -15406,7 +15406,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-10-25 00:16:48</t>
+          <t>2026-10-25 00:47:01</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -15579,7 +15579,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-10-25 00:16:48</t>
+          <t>2026-10-25 00:47:01</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -15752,7 +15752,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-10-25 00:16:51</t>
+          <t>2026-10-25 00:47:05</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -15973,7 +15973,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-10-25 00:16:53</t>
+          <t>2026-10-25 00:47:07</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -16194,7 +16194,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-10-25 00:16:53</t>
+          <t>2026-10-25 00:47:07</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -16415,7 +16415,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-10-25 00:16:53</t>
+          <t>2026-10-25 00:47:07</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -16636,7 +16636,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-10-25 00:16:53</t>
+          <t>2026-10-25 00:47:07</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -16857,7 +16857,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-10-25 00:16:56</t>
+          <t>2026-10-25 00:47:12</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -17090,7 +17090,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-10-25 00:16:58</t>
+          <t>2026-10-25 00:47:14</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -17323,7 +17323,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-10-25 00:16:58</t>
+          <t>2026-10-25 00:47:14</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -17556,7 +17556,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-10-25 00:16:58</t>
+          <t>2026-10-25 00:47:14</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -17789,7 +17789,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-10-25 00:16:58</t>
+          <t>2026-10-25 00:47:14</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -18022,7 +18022,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:02</t>
+          <t>2026-10-25 00:47:19</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -18255,7 +18255,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:04</t>
+          <t>2026-10-25 00:47:20</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -18488,7 +18488,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:04</t>
+          <t>2026-10-25 00:47:20</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -18721,7 +18721,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:04</t>
+          <t>2026-10-25 00:47:20</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -18954,7 +18954,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:04</t>
+          <t>2026-10-25 00:47:20</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -19187,7 +19187,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:06</t>
+          <t>2026-10-25 00:47:24</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -19408,7 +19408,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:08</t>
+          <t>2026-10-25 00:47:25</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -19629,7 +19629,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:08</t>
+          <t>2026-10-25 00:47:25</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -19850,7 +19850,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:08</t>
+          <t>2026-10-25 00:47:25</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -20071,7 +20071,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:08</t>
+          <t>2026-10-25 00:47:25</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -20292,7 +20292,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:11</t>
+          <t>2026-10-25 00:47:29</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -20513,7 +20513,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:12</t>
+          <t>2026-10-25 00:47:31</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:12</t>
+          <t>2026-10-25 00:47:31</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -20955,7 +20955,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:12</t>
+          <t>2026-10-25 00:47:31</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -21176,7 +21176,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:12</t>
+          <t>2026-10-25 00:47:31</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -21397,7 +21397,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:16</t>
+          <t>2026-10-25 00:47:36</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -21630,7 +21630,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:17</t>
+          <t>2026-10-25 00:47:39</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -21863,7 +21863,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:17</t>
+          <t>2026-10-25 00:47:39</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -22096,7 +22096,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:17</t>
+          <t>2026-10-25 00:47:39</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -22329,7 +22329,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:17</t>
+          <t>2026-10-25 00:47:39</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -22562,7 +22562,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:19</t>
+          <t>2026-10-25 00:47:43</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -22795,7 +22795,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:21</t>
+          <t>2026-10-25 00:47:45</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -23028,7 +23028,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:21</t>
+          <t>2026-10-25 00:47:45</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -23261,7 +23261,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:21</t>
+          <t>2026-10-25 00:47:45</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -23494,7 +23494,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:21</t>
+          <t>2026-10-25 00:47:45</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -23727,7 +23727,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:24</t>
+          <t>2026-10-25 00:47:49</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -23948,7 +23948,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:26</t>
+          <t>2026-10-25 00:47:51</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -24169,7 +24169,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:26</t>
+          <t>2026-10-25 00:47:51</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -24390,7 +24390,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:26</t>
+          <t>2026-10-25 00:47:51</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -24623,7 +24623,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:26</t>
+          <t>2026-10-25 00:47:51</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -24856,7 +24856,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:30</t>
+          <t>2026-10-25 00:47:56</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -25089,7 +25089,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:31</t>
+          <t>2026-10-25 00:47:57</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -25322,7 +25322,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:31</t>
+          <t>2026-10-25 00:47:57</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -25555,7 +25555,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:31</t>
+          <t>2026-10-25 00:47:57</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -25788,7 +25788,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:31</t>
+          <t>2026-10-25 00:47:57</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -26021,7 +26021,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:34</t>
+          <t>2026-10-25 00:48:02</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -26242,7 +26242,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:36</t>
+          <t>2026-10-25 00:48:03</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -26463,7 +26463,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:36</t>
+          <t>2026-10-25 00:48:03</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:36</t>
+          <t>2026-10-25 00:48:03</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -26905,7 +26905,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:36</t>
+          <t>2026-10-25 00:48:03</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -27126,7 +27126,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:38</t>
+          <t>2026-10-25 00:48:08</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -27367,7 +27367,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:41</t>
+          <t>2026-10-25 00:48:09</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -27608,7 +27608,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:41</t>
+          <t>2026-10-25 00:48:09</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -27849,7 +27849,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:41</t>
+          <t>2026-10-25 00:48:09</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -28090,7 +28090,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:41</t>
+          <t>2026-10-25 00:48:09</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -28331,7 +28331,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:44</t>
+          <t>2026-10-25 00:48:14</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -28564,7 +28564,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:45</t>
+          <t>2026-10-25 00:48:15</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -28797,7 +28797,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:45</t>
+          <t>2026-10-25 00:48:15</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -29030,7 +29030,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:45</t>
+          <t>2026-10-25 00:48:15</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -29263,7 +29263,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:45</t>
+          <t>2026-10-25 00:48:15</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -29496,7 +29496,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:48</t>
+          <t>2026-10-25 00:48:20</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -29729,7 +29729,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:50</t>
+          <t>2026-10-25 00:48:22</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -29962,7 +29962,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:50</t>
+          <t>2026-10-25 00:48:22</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -30195,7 +30195,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:50</t>
+          <t>2026-10-25 00:48:22</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -30428,7 +30428,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:50</t>
+          <t>2026-10-25 00:48:22</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -30661,7 +30661,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:53</t>
+          <t>2026-10-25 00:48:26</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -30882,7 +30882,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:56</t>
+          <t>2026-10-25 00:48:28</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -31103,7 +31103,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:56</t>
+          <t>2026-10-25 00:48:28</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -31324,7 +31324,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:56</t>
+          <t>2026-10-25 00:48:28</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -31545,7 +31545,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:56</t>
+          <t>2026-10-25 00:48:28</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -31766,7 +31766,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-10-25 00:17:59</t>
+          <t>2026-10-25 00:48:32</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -31999,7 +31999,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-10-25 00:18:01</t>
+          <t>2026-10-25 00:48:34</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -32232,7 +32232,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-10-25 00:18:01</t>
+          <t>2026-10-25 00:48:34</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -32465,7 +32465,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-10-25 00:18:01</t>
+          <t>2026-10-25 00:48:34</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -32698,7 +32698,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-10-25 00:18:01</t>
+          <t>2026-10-25 00:48:34</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -32931,7 +32931,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-10-25 00:18:04</t>
+          <t>2026-10-25 00:48:38</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -33164,7 +33164,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-10-25 00:18:06</t>
+          <t>2026-10-25 00:48:40</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -33397,7 +33397,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-10-25 00:18:06</t>
+          <t>2026-10-25 00:48:40</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -33630,7 +33630,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-10-25 00:18:06</t>
+          <t>2026-10-25 00:48:40</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -33863,7 +33863,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-10-25 00:18:06</t>
+          <t>2026-10-25 00:48:40</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -34096,7 +34096,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-10-25 00:18:09</t>
+          <t>2026-10-25 00:48:45</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -34329,7 +34329,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-10-25 00:18:11</t>
+          <t>2026-10-25 00:48:46</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -34562,7 +34562,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-10-25 00:18:11</t>
+          <t>2026-10-25 00:48:46</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -34795,7 +34795,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-10-25 00:18:11</t>
+          <t>2026-10-25 00:48:46</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -35028,7 +35028,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-10-25 00:18:11</t>
+          <t>2026-10-25 00:48:46</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -35261,7 +35261,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-10-25 00:18:13</t>
+          <t>2026-10-25 00:48:51</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -35494,7 +35494,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-10-25 00:18:15</t>
+          <t>2026-10-25 00:48:53</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -35727,7 +35727,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-10-25 00:18:15</t>
+          <t>2026-10-25 00:48:53</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -35960,7 +35960,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-10-25 00:18:15</t>
+          <t>2026-10-25 00:48:53</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -36193,7 +36193,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-10-25 00:18:15</t>
+          <t>2026-10-25 00:48:53</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -36426,7 +36426,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-10-25 00:18:19</t>
+          <t>2026-10-25 00:48:57</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -36667,7 +36667,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-10-25 00:18:21</t>
+          <t>2026-10-25 00:48:59</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -36908,7 +36908,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-10-25 00:18:21</t>
+          <t>2026-10-25 00:48:59</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -37149,7 +37149,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-10-25 00:18:21</t>
+          <t>2026-10-25 00:48:59</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -37390,7 +37390,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-10-25 00:18:21</t>
+          <t>2026-10-25 00:48:59</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -37631,7 +37631,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-10-25 00:18:24</t>
+          <t>2026-10-25 00:49:04</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -37864,7 +37864,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-10-25 00:18:27</t>
+          <t>2026-10-25 00:49:05</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -38097,7 +38097,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-10-25 00:18:27</t>
+          <t>2026-10-25 00:49:05</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -38330,7 +38330,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-10-25 00:18:27</t>
+          <t>2026-10-25 00:49:05</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -38563,7 +38563,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026-10-25 00:18:27</t>
+          <t>2026-10-25 00:49:05</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -38796,7 +38796,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-10-25 00:18:30</t>
+          <t>2026-10-25 00:49:10</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -39029,7 +39029,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-10-25 00:18:32</t>
+          <t>2026-10-25 00:49:12</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -39262,7 +39262,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026-10-25 00:18:32</t>
+          <t>2026-10-25 00:49:12</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -39495,7 +39495,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026-10-25 00:18:32</t>
+          <t>2026-10-25 00:49:12</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -39728,7 +39728,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026-10-25 00:18:32</t>
+          <t>2026-10-25 00:49:12</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -39961,7 +39961,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026-10-25 00:18:35</t>
+          <t>2026-10-25 00:49:17</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -40182,7 +40182,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026-10-25 00:18:36</t>
+          <t>2026-10-25 00:49:18</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -40403,7 +40403,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-10-25 00:18:36</t>
+          <t>2026-10-25 00:49:18</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -40624,7 +40624,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-10-25 00:18:36</t>
+          <t>2026-10-25 00:49:18</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -40845,7 +40845,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026-10-25 00:18:36</t>
+          <t>2026-10-25 00:49:18</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -41066,7 +41066,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026-10-25 00:18:40</t>
+          <t>2026-10-25 00:49:23</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -41287,7 +41287,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026-10-25 00:18:42</t>
+          <t>2026-10-25 00:49:25</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -41508,7 +41508,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026-10-25 00:18:42</t>
+          <t>2026-10-25 00:49:25</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -41729,7 +41729,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-10-25 00:18:42</t>
+          <t>2026-10-25 00:49:25</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -41950,7 +41950,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-10-25 00:18:42</t>
+          <t>2026-10-25 00:49:25</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -42171,7 +42171,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2026-10-25 00:18:45</t>
+          <t>2026-10-25 00:49:29</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -42404,7 +42404,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2026-10-25 00:18:47</t>
+          <t>2026-10-25 00:49:31</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -42637,7 +42637,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2026-10-25 00:18:47</t>
+          <t>2026-10-25 00:49:31</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -42870,7 +42870,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-10-25 00:18:47</t>
+          <t>2026-10-25 00:49:31</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -43103,7 +43103,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-10-25 00:18:47</t>
+          <t>2026-10-25 00:49:31</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -43336,7 +43336,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2026-10-25 00:18:50</t>
+          <t>2026-10-25 00:49:35</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -43533,7 +43533,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2026-10-25 00:18:52</t>
+          <t>2026-10-25 00:49:36</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -43730,7 +43730,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2026-10-25 00:18:52</t>
+          <t>2026-10-25 00:49:36</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -43927,7 +43927,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026-10-25 00:18:52</t>
+          <t>2026-10-25 00:49:36</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -44124,7 +44124,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2026-10-25 00:18:52</t>
+          <t>2026-10-25 00:49:36</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -44321,7 +44321,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2026-10-25 00:18:55</t>
+          <t>2026-10-25 00:49:40</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -44554,7 +44554,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2026-10-25 00:18:58</t>
+          <t>2026-10-25 00:49:42</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -44787,7 +44787,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2026-10-25 00:18:58</t>
+          <t>2026-10-25 00:49:42</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -45020,7 +45020,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2026-10-25 00:18:58</t>
+          <t>2026-10-25 00:49:42</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -45253,7 +45253,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-10-25 00:18:58</t>
+          <t>2026-10-25 00:49:42</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -45486,7 +45486,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:01</t>
+          <t>2026-10-25 00:49:47</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -45659,7 +45659,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:02</t>
+          <t>2026-10-25 00:49:48</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -45832,7 +45832,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:02</t>
+          <t>2026-10-25 00:49:48</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -46005,7 +46005,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:02</t>
+          <t>2026-10-25 00:49:48</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -46178,7 +46178,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:02</t>
+          <t>2026-10-25 00:49:48</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -46351,7 +46351,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:06</t>
+          <t>2026-10-25 00:49:53</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -46572,7 +46572,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:08</t>
+          <t>2026-10-25 00:49:54</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -46793,7 +46793,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:08</t>
+          <t>2026-10-25 00:49:54</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -47014,7 +47014,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:08</t>
+          <t>2026-10-25 00:49:54</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -47235,7 +47235,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:08</t>
+          <t>2026-10-25 00:49:54</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -47456,7 +47456,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:11</t>
+          <t>2026-10-25 00:49:59</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -47697,7 +47697,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:13</t>
+          <t>2026-10-25 00:50:01</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -47938,7 +47938,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:13</t>
+          <t>2026-10-25 00:50:01</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -48179,7 +48179,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:13</t>
+          <t>2026-10-25 00:50:01</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -48420,7 +48420,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:13</t>
+          <t>2026-10-25 00:50:01</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -48661,7 +48661,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:16</t>
+          <t>2026-10-25 00:50:05</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -48902,7 +48902,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:19</t>
+          <t>2026-10-25 00:50:07</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -49143,7 +49143,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:19</t>
+          <t>2026-10-25 00:50:07</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -49384,7 +49384,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:19</t>
+          <t>2026-10-25 00:50:07</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -49625,7 +49625,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:19</t>
+          <t>2026-10-25 00:50:07</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -49866,7 +49866,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:22</t>
+          <t>2026-10-25 00:50:12</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -50099,7 +50099,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:24</t>
+          <t>2026-10-25 00:50:13</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -50332,7 +50332,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:24</t>
+          <t>2026-10-25 00:50:13</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -50565,7 +50565,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:24</t>
+          <t>2026-10-25 00:50:13</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -50798,7 +50798,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:24</t>
+          <t>2026-10-25 00:50:13</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
